--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -4648,7 +4648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE29"/>
+  <dimension ref="A1:AE32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="26"/>
@@ -8443,6 +8443,396 @@
       <c r="AE29" t="inlineStr">
         <is>
           <t>2026-10-10T14:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>5518421273</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n05/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_14_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_14_3.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>350</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Документы на пиломатериал, ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Занимаемся документами на пиломатериал: доска, брус, брусок, горбыль, тарная дощечка.&lt;br&gt;&lt;br&gt;После переработки учёт никуда не девается. На машину с доской нужен такой же сопроводительный документ, как на кругляк, и покупатели с бухгалтерией это спрашивают в первую очередь.&lt;br&gt;&lt;br&gt;Берём на себя: внесение объёмов в систему, оформление происхождения через договор, ЭСД с QR кодом на отгрузки, отчёт за период, закрытие расхождений по остаткам.&lt;br&gt;&lt;br&gt;Работаем с пилорамами, ИП и ООО, полностью удалённо, по всей стране.&lt;br&gt;&lt;br&gt;Напишите, что отгружаете и какой объём в месяц, посчитаем.</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Новгородская обл., Любытино, ул. Советов, 29</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2026-10-18T04:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>2026-09-18T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>2026-10-18T04:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>7039160996</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/08/08_01.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_10_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_09_1.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>350</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Лес есть, а документов нет. Оформим</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Древесина лежит, а по бумагам её не существует. Приводим такой объём в законный вид.&lt;br&gt;&lt;br&gt;Типичные случаи: лес спилили на своём поле или на расчистке, купили у населения без оформления, объём есть в наличии, но в государственной системе учёта его нет. Продать и вывезти в таком виде нельзя.&lt;br&gt;&lt;br&gt;Что делаем: оформляем происхождение объёма через договор купли-продажи со своей стороны, заносим партию в ФГИС ЛК, ставим её вам на баланс. Дальше по каждой машине идёт сопроводительный документ с QR кодом, а за период сдаётся отчётность.&lt;br&gt;&lt;br&gt;Разбираем ситуацию бесплатно. Напишите породу, объём и откуда лес, скажем сразу, что можно сделать.</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Республика Коми, Троицко-Печорск, ул. Ленина, 2</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2026-10-19T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>2026-09-19T09:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>2026-10-19T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4570672141</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/4382774059/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/02/02_02.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/02/02_03.jpg</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>350</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Документы на лес и пиломатериал</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Занимаемся документами на древесину: и на круглый лес, и на пиломатериал после распиловки.&lt;br&gt;&lt;br&gt;Что обычно нужно решить. Объёма нет в системе, а продать надо. Машину не выпускают без сопроводительного документа. Подходит срок отчётности, а она не собрана. Остатки в базе разошлись с фактом, и отгрузки встали.&lt;br&gt;&lt;br&gt;По каждому пункту работаем сами: оформляем происхождение через договор купли-продажи, вносим объёмы в ФГИС ЛК, выдаём ЭСД с QR кодом, сдаём отчёт за период, закрываем расхождения.&lt;br&gt;&lt;br&gt;Работаем по всей стране удалённо, с ИП, ООО и частниками. Разбор ситуации бесплатный.</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Смоленская обл., Рославль, ул. Советская, 66</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2026-10-19T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>2026-10-19T10:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -9095,7 +9485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK119"/>
+  <dimension ref="A1:AK139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -25420,6 +25810,2706 @@
       <c r="AK119" t="inlineStr">
         <is>
           <t>2026-10-04T03:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>6392718516</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Берёза дрова и баланс(QR код на рейс)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Оформляем документы на берёзу, которая уже заготовлена: дрова, баланс, кругляк с зарастающего поля.&lt;br&gt;&lt;br&gt;На каждую машину с древесиной нужен электронный сопроводительный документ с QR кодом. Без него рейс начинать рискованно, на посту это первый вопрос.&lt;br&gt;&lt;br&gt;Порядок простой. Вы пишете породу, объём, номер машины и маршрут. Мы проводим происхождение партии через договор купли-продажи, заносим объём в ФГИС ЛК и отдаём готовый документ на рейс. Обычно уходит пятнадцать минут.&lt;br&gt;&lt;br&gt;Работаем удалённо, свой кабинет в системе и электронную подпись заводить не придётся. Кто возит постоянно, берём на сопровождение помесячно.&lt;br&gt;&lt;br&gt;Берёза кругляк, дрова, баланс на комбинат, Кировская область.</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n01/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_03_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_03_3.jpg</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Кировская обл., Котельнич, ул. Ленина, 26</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>2026-10-16T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>2026-09-16T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>2026-10-16T02:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>3073730612</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Доска обрезная, документы и ЭСД</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Документы на пиломатериал. Доска обрезная, необрезная, брусок, горбыль.&lt;br&gt;&lt;br&gt;Многие думают, что учёт касается только круглого леса. На доску сопроводительный документ нужен ровно так же, и вопросы на дороге к машине с пиломатериалом возникают не реже.&lt;br&gt;&lt;br&gt;Что делаем: заводим объём в ФГИС ЛК, оформляем происхождение через договор, готовим ЭСД с QR кодом на каждую отгрузку. Если у покупателя бухгалтерия требует полный пакет, собираем и его.&lt;br&gt;&lt;br&gt;От вас нужны порода, объём в кубах, откуда и куда едет машина. Остальное на нас, приезжать никуда не надо.&lt;br&gt;&lt;br&gt;Доска обрезная сосна и ель, пиломатериал, кругляк, Кировская область.</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n03/1.png|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_04_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_04_3.jpg</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Кировская обл., Омутнинск, ул. Комсомольская, 9</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>2026-10-16T04:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>2026-09-16T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>2026-10-16T04:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>7628940116</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Осина баланс, QR код на вывоз</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Ставим на учёт осиновый баланс и делаем документы на вывозку.&lt;br&gt;&lt;br&gt;Осину берут плитные комбинаты, но без бумаг на происхождение партию на приёмке развернут. Отдельная история, когда лес пилили на своей земле или на расчистке, в системе такого объёма нет вообще.&lt;br&gt;&lt;br&gt;Мы это закрываем: заводим объём, оформляем договор купли-продажи как основание, дальше на каждый рейс выдаём ЭСД с QR кодом. Отчёт за период тоже готовим, если он с вас спросят.&lt;br&gt;&lt;br&gt;Объём любой, от одной машины до постоянного потока. Пишите, что и куда везёте, посчитаем сроки.&lt;br&gt;&lt;br&gt;Осина баланс, дрова, кругляк, ольха и берёза, Кировская область.</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n02/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_09_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_09_3.jpg</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Кировская обл., Яранск, ул. Кирова, 10</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Осина</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>2026-10-16T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>2026-09-16T09:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>2026-10-16T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>7023394603</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Берёза баланс, ЭСД на перевозку</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Оформляем документы на берёзовый баланс и кругляк, который уже лежит на площадке.&lt;br&gt;&lt;br&gt;Без электронного сопроводительного документа машину с лесом дальше поста не пустят, а если объёма нет в системе учёта, то и сам документ выписать не из чего. Мы закрываем обе части сразу.&lt;br&gt;&lt;br&gt;Сначала проводим происхождение партии через договор купли-продажи и ставим объём вам на баланс в ФГИС ЛК. Дальше на каждый рейс выдаём ЭСД с QR кодом, обычно в течение пятнадцати минут после ваших данных.&lt;br&gt;&lt;br&gt;Подойдёт и хозяйству, которое расчищает поля, и тем, кто скупает лес у населения.&lt;br&gt;&lt;br&gt;Берёза баланс, дрова, кругляк, осина, Псковская область.</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/6654494961/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_20_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_20_3.jpg</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Псковская обл., Великие Луки, пр-т Ленина, 14</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>280</v>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>2026-10-16T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>2026-09-16T13:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>2026-10-16T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>3195490619</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Лиственница кругляк, ЭСД на отгрузку</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Документы на лиственницу под отгрузку: машинами, вагонами, партиями на экспортёра.&lt;br&gt;&lt;br&gt;Когда объём идёт на станцию, покупатель смотрит не только на качество, но и на то, сходятся ли данные в системе. Если партия не проведена, отгрузка встаёт, и это дороже любых документов.&lt;br&gt;&lt;br&gt;Берём на себя всю цепочку: происхождение объёма через договор, внесение в ФГИС ЛК, ЭСД с QR на каждый рейс, сверка остатков перед отгрузкой. Работаем с ИП, ООО и с частниками.&lt;br&gt;&lt;br&gt;Напишите объём и куда идёт лес, разберём вашу ситуацию и скажем, что нужно.&lt;br&gt;&lt;br&gt;Лиственница кругляк, пиловочник, сосна, ель, Иркутская область.</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/9218798416/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_10_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_10_3.jpg</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Иркутская обл., Усть-Кут, ул. Кирова, 18</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Лиственница</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>2026-10-17T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>2026-09-17T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>2026-10-17T02:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>8122502691</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник, документы ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Ситуация обычная: пиловочник лежит на площадке, а в системе его нет. Мы делаем так, чтобы он там появился законно.&lt;br&gt;&lt;br&gt;Оформляем происхождение объёма договором купли-продажи, заводим партию в ФГИС ЛК, ставим её вам на баланс. После этого лес можно спокойно продавать и везти, а на каждую машину выписывать сопроводительный документ с QR кодом.&lt;br&gt;&lt;br&gt;Делаем и то, что обычно откладывают: лесную декларацию, отчёт 1-ИЛ, закрытие расхождений по остаткам.&lt;br&gt;&lt;br&gt;Всё удалённо, по всей стране. От вас порода, объём и что уже есть на руках.&lt;br&gt;&lt;br&gt;Сосна пиловочник, кругляк, баланс, ель и лиственница, Иркутская область.</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n08/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_08_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_08_3.jpg</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Иркутская обл., Усть-Илимск, ул. Героев Труда, 38</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>2026-10-17T04:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>2026-09-17T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>2026-10-17T04:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>3268226363</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Ель баланс, документы на перевозку</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Возите еловый баланс на комбинат, а документы каждый раз собираются в последний момент. Забираем эту часть себе.&lt;br&gt;&lt;br&gt;Оформляем электронный сопроводительный документ на рейс, тот самый с QR кодом. Заводим объём в систему учёта древесины, если его там ещё нет, и приводим в порядок остатки, чтобы приёмка не спорила с цифрами.&lt;br&gt;&lt;br&gt;Работаем и разово, и на потоке. Для постоянных отгрузок удобнее сопровождение: вы пишете машину и объём, документ приходит в ответ, без переписки на полдня.&lt;br&gt;&lt;br&gt;Ель баланс, сосна, берёза, кругляк и дрова, Вологодская область.</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n09/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_07_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_07_3.jpg</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Вологодская обл., Великий Устюг, Советский пр-т, 100</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>280</v>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>2026-10-17T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>2026-09-17T09:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>2026-10-17T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2790722386</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Пиломатериал хвоя, QR на машину</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Делаем QR код на машину с пиломатериалом. Доска, брус, брусок, тарная дощечка.&lt;br&gt;&lt;br&gt;Вопрос, который задают чаще всего: нужен ли документ на доску, если это уже не круглый лес. Нужен. Переработка не снимает учёт, и на посту это проверяют так же.&lt;br&gt;&lt;br&gt;Оформляем быстро. Вы даёте объём, породу и маршрут, мы вносим данные и отдаём готовый ЭСД. Если объём не заведён в системе, сначала проводим происхождение через договор, это тоже наша работа.&lt;br&gt;&lt;br&gt;Пилорамам, которые отгружают регулярно, считаем помесячно, так выходит дешевле.&lt;br&gt;&lt;br&gt;Пиломатериал хвоя, доска обрезная, брус, кругляк, Вологодская область.</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/8757513433/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_14_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_14_3.jpg</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Вологодская обл., Тотьма, ул. Ленина, 44</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>2026-10-17T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>2026-10-17T08:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>4857472831</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Сосна кругляк, QR код на вывоз</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Делаем QR код на вывоз соснового кругляка. Это тот самый электронный документ, который сейчас спрашивают на каждую машину с древесиной.&lt;br&gt;&lt;br&gt;Чаще всего к нам приходят, когда лес уже свален, покупатель найден, а бумаг на происхождение нет вообще. Оформляем их с нуля: договор купли-продажи как основание, внесение объёма в ФГИС ЛК, сопроводительный документ на рейс.&lt;br&gt;&lt;br&gt;Если остатки в системе не сходятся с фактом, приводим в порядок и это, иначе отгрузки начнут блокировать.&lt;br&gt;&lt;br&gt;Работаем удалённо, свой кабинет и электронную подпись заводить не нужно.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, ель, баланс, Псковская область.</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n16/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_13_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_13_2.jpg</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Псковская обл., Себеж, ул. 7 Ноября, 2</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>2026-10-17T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>2026-09-17T13:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>2026-10-17T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>1762058548</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Сосна кругляк с поля, оформим учёт</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Лес, выросший на пашне или в лесополосе, по документам такой же, как из делянки. Оформляем его с нуля.&lt;br&gt;&lt;br&gt;Собственники земли часто узнают об этом уже после того, как спилили: покупатель просит бумаги, а бумаг нет, и продать несколько сотен кубов не получается.&lt;br&gt;&lt;br&gt;Мы проводим объём через договор купли-продажи, заносим в ФГИС ЛК, ставим на баланс и дальше выдаём сопроводительные документы на вывоз. В сложных случаях помогаем разобраться с назначением участка и с тем, как это правильно показать.&lt;br&gt;&lt;br&gt;Работаем удалённо, приезжать не нужно. Напишите породу и примерный объём.&lt;br&gt;&lt;br&gt;Сосна кругляк, берёза, ель, лес с сельхозземель, Новгородская область.</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n11/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_10_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_09_1.jpg</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Новгородская обл., Чудово, ул. Некрасова, 24</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>2026-10-18T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>2026-09-18T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>2026-10-18T02:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>4787974535</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Берёза фанкряж, ЭСД и учёт объёма</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Фанкряж и берёзовый баланс отгружают быстро, а документы тормозят всю работу. Закрываем этот кусок.&lt;br&gt;&lt;br&gt;Ставим объём на учёт в ФГИС ЛК, оформляем основание через договор купли-продажи, готовим ЭСД с QR кодом на каждую машину. Если остатки в системе разошлись с фактом, приводим их в соответствие, чтобы отгрузки не блокировались.&lt;br&gt;&lt;br&gt;Подходит и тем, у кого своя делянка, и тем, кто берёт лес у населения и не понимает, как провести такую покупку.&lt;br&gt;&lt;br&gt;От вас порода, объём, маршрут. Ответим по срокам и цене сразу.&lt;br&gt;&lt;br&gt;Берёза фанкряж, баланс, кругляк, осина, Республика Коми.</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/2153018262/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_03_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_03_3.jpg</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Республика Коми, Усть-Кулом, ул. Советская, 37</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>320</v>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>2026-10-18T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>2026-09-18T09:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>2026-10-18T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2289536143</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Сосна кругляк, QR код за 15 минут</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Машина готова, водитель ждёт, а документа на рейс нет. Делаем его за пятнадцать минут.&lt;br&gt;&lt;br&gt;Электронный сопроводительный документ с QR кодом оформляем на любую породу и любой объём, хоть на одну машину дров, хоть на регулярные отгрузки пиловочника. Документ настоящий, виден в системе, на весовой и на посту вопросов не вызывает.&lt;br&gt;&lt;br&gt;Если объёма в системе нет, заводим его: договор купли-продажи как основание, партия на балансе, дальше рейсы.&lt;br&gt;&lt;br&gt;Нужны только данные машины, порода, объём и маршрут. Пишите в любое время, отвечаем быстро.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, ель, берёза, Республика Карелия.</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/7393214976/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_04_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_04_3.jpg</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Республика Карелия, Пудож, ул. Ленина, 90</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>2026-10-18T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>2026-10-18T08:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>9258836919</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Ель пиловочник, документы ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Ставим еловый пиловочник на учёт и готовим документы под продажу.&lt;br&gt;&lt;br&gt;Покупатели с производством почти всегда просят подтверждение происхождения. Если объём не проведён в государственной системе, сделка либо срывается, либо идёт в серую, а это уже риск для обеих сторон.&lt;br&gt;&lt;br&gt;Берём весь оформительский круг на себя: договор купли-продажи, внесение партии в ФГИС ЛК, сопроводительные документы с QR кодом на каждую машину, отчётность за период.&lt;br&gt;&lt;br&gt;Пишите породу, объём и откуда лес, скажем по срокам и цене сразу.&lt;br&gt;&lt;br&gt;Ель пиловочник, сосна, кругляк, баланс, Смоленская область.</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_12_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_11_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_13_3.jpg</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Смоленская обл., Вязьма, ул. Ленина, 14</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>2026-10-18T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>2026-10-18T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>8693589310</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Ель пиловочник, документы на вывоз</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Разбираемся с учётом ели и готовим документы на вывоз.&lt;br&gt;&lt;br&gt;Чаще всего приходят с двумя вещами. Первая: лес заготовлен, а в системе его нет, продать официально нельзя. Вторая: объёмы когда-то внесли неверно, остатки не сходятся, и отгрузка встала.&lt;br&gt;&lt;br&gt;Закрываем и то и другое. Оформляем происхождение через договор, вносим партию в ФГИС ЛК, правим расхождения по остаткам, дальше выписываем сопроводительные документы на каждую машину.&lt;br&gt;&lt;br&gt;Работаем по всей стране удалённо, нужен только ваш объём и понимание, откуда он взялся.&lt;br&gt;&lt;br&gt;Ель пиловочник, баланс, сосна, кругляк, Костромская область.</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/5312403632/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_09_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_09_3.jpg</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Костромская обл., Мантурово, ул. Советская, 25</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>280</v>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>2026-10-19T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>2026-09-19T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>2026-10-19T02:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2543470744</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Дрова колотые, документы на продажу</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Дрова тоже древесина, и учёт для них такой же, как для делового леса. Оформляем документы тем, кто продаёт дрова машинами.&lt;br&gt;&lt;br&gt;Частника с одной машиной для себя это не касается, а вот когда возишь на продажу регулярно, нужен сопроводительный документ на рейс. Особенно если покупатель юрлицо и ему нужно провести покупку по бухгалтерии.&lt;br&gt;&lt;br&gt;Делаем полный круг: происхождение объёма, внесение в ФГИС ЛК, ЭСД с QR на каждую отгрузку, отчётность за период.&lt;br&gt;&lt;br&gt;Напишите, сколько машин в месяц возите, подберём вариант по цене.&lt;br&gt;&lt;br&gt;Дрова колотые берёза и осина, баланс, горбыль, Нижегородская область.</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/05/05_01.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_10_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_10_3.jpg</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Нижегородская обл., Ветлуга, ул. Ленина, 6</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>2026-10-19T04:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>2026-09-19T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>2026-10-19T04:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>5542586163</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Брус и доска, документы ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Собираем документы на брус и доску для тех, кто продаёт пиломатериал юрлицам.&lt;br&gt;&lt;br&gt;Когда покупатель крупный, у него свои требования: происхождение древесины, сопроводительные документы, чтобы всё сходилось в системе. Без этого сделку часто просто не проводят, даже если товар устраивает.&lt;br&gt;&lt;br&gt;Что делаем: заводим объём в ФГИС ЛК, оформляем основание договором купли-продажи, готовим ЭСД с QR кодом на отгрузки и полный комплект, который спокойно уходит в бухгалтерию покупателя.&lt;br&gt;&lt;br&gt;Работаем с пилорамами и перекупщиками по всей стране, удалённо.&lt;br&gt;&lt;br&gt;Брус, доска обрезная, пиломатериал хвоя, кругляк, Архангельская область.</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n04/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_08_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_08_3.jpg</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Архангельская обл., Вельск, ул. Дзержинского, 48</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>2026-10-19T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>2026-09-19T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>2026-10-19T08:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>4323234383</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Осина дрова, документы на вывоз</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Документы на осину и дровяную древесину для тех, кто возит её на продажу.&lt;br&gt;&lt;br&gt;Многие считают, что дрова учитывать не надо. На деле это такая же древесина, и на рейс нужен электронный сопроводительный документ. Особенно если покупатель юрлицо и проводит покупку по бухгалтерии.&lt;br&gt;&lt;br&gt;Делаем полный круг: происхождение объёма через договор, внесение в ФГИС ЛК, ЭСД с QR кодом на каждую машину. Для постоянных перевозок считаем помесячно.&lt;br&gt;&lt;br&gt;От вас порода, объём, номер машины и маршрут. Остальное на нас.&lt;br&gt;&lt;br&gt;Осина дрова, баланс, берёза, горбыль, Брянская область.</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n14/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/04/04_02.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/04/04_03.jpg</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Брянская обл., Трубчевск, ул. Ленина, 60</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Осина</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>2026-10-20T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>2026-09-20T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>2026-10-20T02:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>4637367814</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Доска и брусок, ЭСД на машину</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Оформляем сопроводительные документы на машины с пиломатериалом. Доска, брусок, обапол, тарная дощечка.&lt;br&gt;&lt;br&gt;Вопрос от пилорам звучит одинаково: нужен ли документ, если лес уже распилен. Нужен. Учёт никуда не исчезает после переработки, и на дороге это проверяют.&lt;br&gt;&lt;br&gt;Мы вносим объёмы в ФГИС ЛК, оформляем происхождение договором, готовим ЭСД с QR кодом на каждую отгрузку и собираем пакет, который спокойно принимает бухгалтерия покупателя.&lt;br&gt;&lt;br&gt;Если отгружаете регулярно, берём на сопровождение, так дешевле и быстрее.&lt;br&gt;&lt;br&gt;Доска обрезная, брусок, брус, пиломатериал хвоя, Брянская область.</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n06/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_05_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_05_3.jpg</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Брянская обл., Жуковка, ул. Октябрьская, 3</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>2026-10-20T04:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>2026-09-20T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>2026-10-20T04:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>1410610101</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Пиломатериал хвоя, документы ФГИС</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Ведём документы на хвойный пиломатериал: доска, брус, оцилиндрованное бревно, погонаж.&lt;br&gt;&lt;br&gt;Покупатель из другого региона почти всегда просит показать происхождение древесины. Без этого товар смотрят, но сделку не проводят, и хороший объём зависает на площадке.&lt;br&gt;&lt;br&gt;Закрываем это полностью. Оформляем договор купли-продажи как основание, заводим объёмы в систему учёта, выдаём сопроводительный документ с QR кодом на каждую отгрузку, готовим отчётность.&lt;br&gt;&lt;br&gt;Работаем с пилорамами и перекупщиками, удалённо, по всей стране.&lt;br&gt;&lt;br&gt;Пиломатериал хвоя, доска обрезная, брус, кругляк, Калужская область.</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_15_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_13_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_13_3.jpg</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Калужская обл., Людиново, ул. Ленина, 20</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>2026-10-20T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>2026-09-20T09:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>2026-10-20T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>6900416887</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Берёза кругляк, QR код на рейс</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Берёза с расчистки полей и обочин, документы делаем мы.&lt;br&gt;&lt;br&gt;Такой лес по закону учитывается так же, как из делянки. Владельцы участков узнают об этом обычно уже после того, как спилили, и упираются в то, что вывезти объём нельзя.&lt;br&gt;&lt;br&gt;Порядок работы: проводим происхождение через договор купли-продажи, вносим партию в ФГИС ЛК, ставим её вам на баланс. Дальше на каждую машину выписываем ЭСД с QR кодом, делаем это быстро, обычно за пятнадцать минут.&lt;br&gt;&lt;br&gt;Объём любой, от одной машины до постоянных отгрузок на комбинат.&lt;br&gt;&lt;br&gt;Берёза кругляк, дрова, баланс, фанкряж, Рязанская область.</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/01/01_01.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_15_3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_18_2.jpg</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Рязанская обл., Касимов, ул. Советская, 14</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>280</v>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>2026-10-20T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>2026-09-20T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>2026-10-20T08:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -26816,7 +29906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="21"/>
@@ -29582,6 +32672,266 @@
       <c r="AD22" t="inlineStr">
         <is>
           <t>2026-10-10T12:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4740067166</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/8194168577/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_07_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_07_3.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>350</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ЭСД и QR код на перевозку леса</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Оформляем электронные сопроводительные документы на перевозку древесины.&lt;br&gt;&lt;br&gt;Это тот документ с QR кодом, который сейчас требуют на каждую машину с лесом. Делаем его на кругляк, на дрова, на пиломатериал, на любую породу.&lt;br&gt;&lt;br&gt;От вас данные: порода, объём, номер машины, откуда и куда. От нас готовый документ, обычно в течение пятнадцати минут. Если объёма в системе нет, сначала проводим происхождение через договор купли-продажи и ставим партию на баланс.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС ЛК и электронную подпись заводить не нужно, всё делаем со своей стороны.&lt;br&gt;&lt;br&gt;Есть сопровождение помесячно для тех, кто отгружает постоянно.</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Республика Карелия, Медвежьегорск, ул. Кирова, 7</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>У себя</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>2026-10-16T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2026-09-16T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>2026-10-16T08:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>8269348027</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/fgis_doc_mo/01_01.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_18_3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_11_3.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>350</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Закроем расхождения в ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Разбираем расхождения в ФГИС ЛК. Это когда по системе у вас один объём, а по факту другой, и отгрузки из-за этого встают.&lt;br&gt;&lt;br&gt;Причины обычно простые: внесли не ту породу или сортимент, задвоили партию, списали меньше, чем увезли, приняли объём без основания. Дальше ошибка тянется, а на стороне покупателя она видна сразу.&lt;br&gt;&lt;br&gt;Мы поднимаем историю по вашему кабинету, находим, где разошлось, и приводим данные в порядок. Там, где нужно основание на объём, оформляем договор купли-продажи со своей стороны.&lt;br&gt;&lt;br&gt;После этого отгрузки идут нормально, а отчётность за период сдаётся без вопросов.&lt;br&gt;&lt;br&gt;Пишите, что происходит, посмотрим и скажем, сколько это займёт.</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Рязанская обл., Спас-Клепики, ул. Просвещения, 64</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>У себя</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>2026-10-20T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>2026-10-20T10:00:00+03:00</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -8449,7 +8449,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5518421273</t>
+          <t>3052658678</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8478,7 +8478,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>350</v>
+        <v>990</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -8562,24 +8562,24 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-10-18T04:00:00+03:00</t>
+          <t>2026-10-16T04:00:00+03:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>2026-09-18T07:00:00+03:00</t>
+          <t>2026-09-16T07:00:00+03:00</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2026-10-18T04:00:00+03:00</t>
+          <t>2026-10-16T04:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7039160996</t>
+          <t>4947618913</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8608,7 +8608,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>350</v>
+        <v>1900</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -8692,24 +8692,24 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-10-19T06:00:00+03:00</t>
+          <t>2026-10-19T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>2026-09-19T09:00:00+03:00</t>
+          <t>2026-09-19T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2026-10-19T06:00:00+03:00</t>
+          <t>2026-10-19T08:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4570672141</t>
+          <t>6905101476</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8738,7 +8738,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>350</v>
+        <v>3900</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -8822,17 +8822,17 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>2026-10-19T10:00:00+03:00</t>
+          <t>2026-10-20T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>2026-09-19T13:00:00+03:00</t>
+          <t>2026-09-20T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2026-10-19T10:00:00+03:00</t>
+          <t>2026-10-20T02:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -25816,7 +25816,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>6392718516</t>
+          <t>2303325522</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -25865,7 +25865,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
       </c>
       <c r="AE120" t="inlineStr">
         <is>
-          <t>2026-10-16T02:00:00+03:00</t>
+          <t>2026-10-15T07:00:00+03:00</t>
         </is>
       </c>
       <c r="AF120" t="inlineStr">
@@ -25939,19 +25939,19 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>2026-09-16T05:00:00+03:00</t>
+          <t>2026-09-15T10:00:00+03:00</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>2026-10-16T02:00:00+03:00</t>
+          <t>2026-10-15T07:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3073730612</t>
+          <t>9672895232</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -25966,17 +25966,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Доска обрезная, документы и ЭСД</t>
+          <t>Берёза баланс, ЭСД на перевозку</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Документы на пиломатериал. Доска обрезная, необрезная, брусок, горбыль.&lt;br&gt;&lt;br&gt;Многие думают, что учёт касается только круглого леса. На доску сопроводительный документ нужен ровно так же, и вопросы на дороге к машине с пиломатериалом возникают не реже.&lt;br&gt;&lt;br&gt;Что делаем: заводим объём в ФГИС ЛК, оформляем происхождение через договор, готовим ЭСД с QR кодом на каждую отгрузку. Если у покупателя бухгалтерия требует полный пакет, собираем и его.&lt;br&gt;&lt;br&gt;От вас нужны порода, объём в кубах, откуда и куда едет машина. Остальное на нас, приезжать никуда не надо.&lt;br&gt;&lt;br&gt;Доска обрезная сосна и ель, пиломатериал, кругляк, Кировская область.</t>
+          <t>Оформляем документы на берёзовый баланс и кругляк, который уже лежит на площадке.&lt;br&gt;&lt;br&gt;Без электронного сопроводительного документа машину с лесом дальше поста не пустят, а если объёма нет в системе учёта, то и сам документ выписать не из чего. Мы закрываем обе части сразу.&lt;br&gt;&lt;br&gt;Сначала проводим происхождение партии через договор купли-продажи и ставим объём вам на баланс в ФГИС ЛК. Дальше на каждый рейс выдаём ЭСД с QR кодом, обычно в течение пятнадцати минут после ваших данных.&lt;br&gt;&lt;br&gt;Подойдёт и хозяйству, которое расчищает поля, и тем, кто скупает лес у населения.&lt;br&gt;&lt;br&gt;Берёза баланс, дрова, кругляк, осина, Псковская область.</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n03/1.png|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_04_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_04_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/6654494961/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_20_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_20_3.jpg</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -25991,7 +25991,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Кировская обл., Омутнинск, ул. Комсомольская, 9</t>
+          <t>Псковская обл., Великие Луки, пр-т Ленина, 14</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -26000,7 +26000,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Берёза</t>
         </is>
       </c>
       <c r="X121" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="AE121" t="inlineStr">
         <is>
-          <t>2026-10-16T04:00:00+03:00</t>
+          <t>2026-10-15T09:00:00+03:00</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
@@ -26074,19 +26074,19 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>2026-09-16T07:00:00+03:00</t>
+          <t>2026-09-15T12:00:00+03:00</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>2026-10-16T04:00:00+03:00</t>
+          <t>2026-10-15T09:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>7628940116</t>
+          <t>2571641051</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -26101,17 +26101,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Осина баланс, QR код на вывоз</t>
+          <t>Сосна кругляк, QR код за 15 минут</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ставим на учёт осиновый баланс и делаем документы на вывозку.&lt;br&gt;&lt;br&gt;Осину берут плитные комбинаты, но без бумаг на происхождение партию на приёмке развернут. Отдельная история, когда лес пилили на своей земле или на расчистке, в системе такого объёма нет вообще.&lt;br&gt;&lt;br&gt;Мы это закрываем: заводим объём, оформляем договор купли-продажи как основание, дальше на каждый рейс выдаём ЭСД с QR кодом. Отчёт за период тоже готовим, если он с вас спросят.&lt;br&gt;&lt;br&gt;Объём любой, от одной машины до постоянного потока. Пишите, что и куда везёте, посчитаем сроки.&lt;br&gt;&lt;br&gt;Осина баланс, дрова, кругляк, ольха и берёза, Кировская область.</t>
+          <t>Машина готова, водитель ждёт, а документа на рейс нет. Делаем его за пятнадцать минут.&lt;br&gt;&lt;br&gt;Электронный сопроводительный документ с QR кодом оформляем на любую породу и любой объём, хоть на одну машину дров, хоть на регулярные отгрузки пиловочника. Документ настоящий, виден в системе, на весовой и на посту вопросов не вызывает.&lt;br&gt;&lt;br&gt;Если объёма в системе нет, заводим его: договор купли-продажи как основание, партия на балансе, дальше рейсы.&lt;br&gt;&lt;br&gt;Нужны только данные машины, порода, объём и маршрут. Пишите в любое время, отвечаем быстро.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, ель, берёза, Республика Карелия.</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n02/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_09_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_09_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/7393214976/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_04_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_04_3.jpg</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -26126,7 +26126,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Кировская обл., Яранск, ул. Кирова, 10</t>
+          <t>Республика Карелия, Пудож, ул. Ленина, 90</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -26135,7 +26135,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>250</v>
+        <v>1500</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>Осина</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X122" t="inlineStr">
@@ -26189,7 +26189,7 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>2026-10-16T06:00:00+03:00</t>
+          <t>2026-10-15T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
@@ -26209,19 +26209,19 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>2026-09-16T09:00:00+03:00</t>
+          <t>2026-09-15T14:00:00+03:00</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>2026-10-16T06:00:00+03:00</t>
+          <t>2026-10-15T11:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>7023394603</t>
+          <t>9704114814</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -26236,17 +26236,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Берёза баланс, ЭСД на перевозку</t>
+          <t>Осина дрова, документы на вывоз</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Оформляем документы на берёзовый баланс и кругляк, который уже лежит на площадке.&lt;br&gt;&lt;br&gt;Без электронного сопроводительного документа машину с лесом дальше поста не пустят, а если объёма нет в системе учёта, то и сам документ выписать не из чего. Мы закрываем обе части сразу.&lt;br&gt;&lt;br&gt;Сначала проводим происхождение партии через договор купли-продажи и ставим объём вам на баланс в ФГИС ЛК. Дальше на каждый рейс выдаём ЭСД с QR кодом, обычно в течение пятнадцати минут после ваших данных.&lt;br&gt;&lt;br&gt;Подойдёт и хозяйству, которое расчищает поля, и тем, кто скупает лес у населения.&lt;br&gt;&lt;br&gt;Берёза баланс, дрова, кругляк, осина, Псковская область.</t>
+          <t>Документы на осину и дровяную древесину для тех, кто возит её на продажу.&lt;br&gt;&lt;br&gt;Многие считают, что дрова учитывать не надо. На деле это такая же древесина, и на рейс нужен электронный сопроводительный документ. Особенно если покупатель юрлицо и проводит покупку по бухгалтерии.&lt;br&gt;&lt;br&gt;Делаем полный круг: происхождение объёма через договор, внесение в ФГИС ЛК, ЭСД с QR кодом на каждую машину. Для постоянных перевозок считаем помесячно.&lt;br&gt;&lt;br&gt;От вас порода, объём, номер машины и маршрут. Остальное на нас.&lt;br&gt;&lt;br&gt;Осина дрова, баланс, берёза, горбыль, Брянская область.</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/6654494961/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_20_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_20_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n14/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/04/04_02.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/04/04_03.jpg</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -26261,7 +26261,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Псковская обл., Великие Луки, пр-т Ленина, 14</t>
+          <t>Брянская обл., Трубчевск, ул. Ленина, 60</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -26270,7 +26270,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>280</v>
+        <v>690</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>Берёза</t>
+          <t>Осина</t>
         </is>
       </c>
       <c r="X123" t="inlineStr">
@@ -26324,7 +26324,7 @@
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>2026-10-16T10:00:00+03:00</t>
+          <t>2026-10-15T13:00:00+03:00</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -26344,19 +26344,19 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>2026-09-16T13:00:00+03:00</t>
+          <t>2026-09-15T16:00:00+03:00</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
         <is>
-          <t>2026-10-16T10:00:00+03:00</t>
+          <t>2026-10-15T13:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>3195490619</t>
+          <t>3912477150</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -26371,17 +26371,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Лиственница кругляк, ЭСД на отгрузку</t>
+          <t>Сосна пиловочник, документы ФГИС ЛК</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Документы на лиственницу под отгрузку: машинами, вагонами, партиями на экспортёра.&lt;br&gt;&lt;br&gt;Когда объём идёт на станцию, покупатель смотрит не только на качество, но и на то, сходятся ли данные в системе. Если партия не проведена, отгрузка встаёт, и это дороже любых документов.&lt;br&gt;&lt;br&gt;Берём на себя всю цепочку: происхождение объёма через договор, внесение в ФГИС ЛК, ЭСД с QR на каждый рейс, сверка остатков перед отгрузкой. Работаем с ИП, ООО и с частниками.&lt;br&gt;&lt;br&gt;Напишите объём и куда идёт лес, разберём вашу ситуацию и скажем, что нужно.&lt;br&gt;&lt;br&gt;Лиственница кругляк, пиловочник, сосна, ель, Иркутская область.</t>
+          <t>Ситуация обычная: пиловочник лежит на площадке, а в системе его нет. Мы делаем так, чтобы он там появился законно.&lt;br&gt;&lt;br&gt;Оформляем происхождение объёма договором купли-продажи, заводим партию в ФГИС ЛК, ставим её вам на баланс. После этого лес можно спокойно продавать и везти, а на каждую машину выписывать сопроводительный документ с QR кодом.&lt;br&gt;&lt;br&gt;Делаем и то, что обычно откладывают: лесную декларацию, отчёт 1-ИЛ, закрытие расхождений по остаткам.&lt;br&gt;&lt;br&gt;Всё удалённо, по всей стране. От вас порода, объём и что уже есть на руках.&lt;br&gt;&lt;br&gt;Сосна пиловочник, кругляк, баланс, ель и лиственница, Иркутская область.</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/9218798416/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_10_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_10_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n08/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_08_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_08_3.jpg</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -26396,7 +26396,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Иркутская обл., Усть-Кут, ул. Кирова, 18</t>
+          <t>Иркутская обл., Усть-Илимск, ул. Героев Труда, 38</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -26405,7 +26405,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>350</v>
+        <v>2500</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>Лиственница</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X124" t="inlineStr">
@@ -26459,7 +26459,7 @@
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t>2026-10-17T02:00:00+03:00</t>
+          <t>2026-10-16T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr">
@@ -26479,19 +26479,19 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>2026-09-17T05:00:00+03:00</t>
+          <t>2026-09-16T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>2026-10-17T02:00:00+03:00</t>
+          <t>2026-10-16T02:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>8122502691</t>
+          <t>1900017240</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -26506,17 +26506,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Сосна пиловочник, документы ФГИС ЛК</t>
+          <t>Берёза кругляк, QR код на рейс</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ситуация обычная: пиловочник лежит на площадке, а в системе его нет. Мы делаем так, чтобы он там появился законно.&lt;br&gt;&lt;br&gt;Оформляем происхождение объёма договором купли-продажи, заводим партию в ФГИС ЛК, ставим её вам на баланс. После этого лес можно спокойно продавать и везти, а на каждую машину выписывать сопроводительный документ с QR кодом.&lt;br&gt;&lt;br&gt;Делаем и то, что обычно откладывают: лесную декларацию, отчёт 1-ИЛ, закрытие расхождений по остаткам.&lt;br&gt;&lt;br&gt;Всё удалённо, по всей стране. От вас порода, объём и что уже есть на руках.&lt;br&gt;&lt;br&gt;Сосна пиловочник, кругляк, баланс, ель и лиственница, Иркутская область.</t>
+          <t>Берёза с расчистки полей и обочин, документы делаем мы.&lt;br&gt;&lt;br&gt;Такой лес по закону учитывается так же, как из делянки. Владельцы участков узнают об этом обычно уже после того, как спилили, и упираются в то, что вывезти объём нельзя.&lt;br&gt;&lt;br&gt;Порядок работы: проводим происхождение через договор купли-продажи, вносим партию в ФГИС ЛК, ставим её вам на баланс. Дальше на каждую машину выписываем ЭСД с QR кодом, делаем это быстро, обычно за пятнадцать минут.&lt;br&gt;&lt;br&gt;Объём любой, от одной машины до постоянных отгрузок на комбинат.&lt;br&gt;&lt;br&gt;Берёза кругляк, дрова, баланс, фанкряж, Рязанская область.</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n08/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_08_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_08_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/01/01_01.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_15_3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_18_2.jpg</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -26531,7 +26531,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Иркутская обл., Усть-Илимск, ул. Героев Труда, 38</t>
+          <t>Рязанская обл., Касимов, ул. Советская, 14</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -26540,7 +26540,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Берёза</t>
         </is>
       </c>
       <c r="X125" t="inlineStr">
@@ -26594,7 +26594,7 @@
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>2026-10-17T04:00:00+03:00</t>
+          <t>2026-10-16T06:00:00+03:00</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
@@ -26614,19 +26614,19 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>2026-09-17T07:00:00+03:00</t>
+          <t>2026-09-16T09:00:00+03:00</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>2026-10-17T04:00:00+03:00</t>
+          <t>2026-10-16T06:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3268226363</t>
+          <t>2334437862</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -26675,7 +26675,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>280</v>
+        <v>890</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>2026-10-17T06:00:00+03:00</t>
+          <t>2026-10-16T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
@@ -26749,19 +26749,19 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>2026-09-17T09:00:00+03:00</t>
+          <t>2026-09-16T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>2026-10-17T06:00:00+03:00</t>
+          <t>2026-10-16T08:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2790722386</t>
+          <t>9919371422</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -26776,17 +26776,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Пиломатериал хвоя, QR на машину</t>
+          <t>Доска и брусок, ЭСД на машину</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Делаем QR код на машину с пиломатериалом. Доска, брус, брусок, тарная дощечка.&lt;br&gt;&lt;br&gt;Вопрос, который задают чаще всего: нужен ли документ на доску, если это уже не круглый лес. Нужен. Переработка не снимает учёт, и на посту это проверяют так же.&lt;br&gt;&lt;br&gt;Оформляем быстро. Вы даёте объём, породу и маршрут, мы вносим данные и отдаём готовый ЭСД. Если объём не заведён в системе, сначала проводим происхождение через договор, это тоже наша работа.&lt;br&gt;&lt;br&gt;Пилорамам, которые отгружают регулярно, считаем помесячно, так выходит дешевле.&lt;br&gt;&lt;br&gt;Пиломатериал хвоя, доска обрезная, брус, кругляк, Вологодская область.</t>
+          <t>Оформляем сопроводительные документы на машины с пиломатериалом. Доска, брусок, обапол, тарная дощечка.&lt;br&gt;&lt;br&gt;Вопрос от пилорам звучит одинаково: нужен ли документ, если лес уже распилен. Нужен. Учёт никуда не исчезает после переработки, и на дороге это проверяют.&lt;br&gt;&lt;br&gt;Мы вносим объёмы в ФГИС ЛК, оформляем происхождение договором, готовим ЭСД с QR кодом на каждую отгрузку и собираем пакет, который спокойно принимает бухгалтерия покупателя.&lt;br&gt;&lt;br&gt;Если отгружаете регулярно, берём на сопровождение, так дешевле и быстрее.&lt;br&gt;&lt;br&gt;Доска обрезная, брусок, брус, пиломатериал хвоя, Брянская область.</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/8757513433/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_14_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_14_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n06/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_05_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_05_3.jpg</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -26801,7 +26801,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Вологодская обл., Тотьма, ул. Ленина, 44</t>
+          <t>Брянская обл., Жуковка, ул. Октябрьская, 3</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -26810,7 +26810,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>2026-10-17T08:00:00+03:00</t>
+          <t>2026-10-16T10:00:00+03:00</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -26884,19 +26884,19 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>2026-09-17T11:00:00+03:00</t>
+          <t>2026-09-16T13:00:00+03:00</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>2026-10-17T08:00:00+03:00</t>
+          <t>2026-10-16T10:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>4857472831</t>
+          <t>2115446325</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -26911,17 +26911,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Сосна кругляк, QR код на вывоз</t>
+          <t>Берёза фанкряж, ЭСД и учёт объёма</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Делаем QR код на вывоз соснового кругляка. Это тот самый электронный документ, который сейчас спрашивают на каждую машину с древесиной.&lt;br&gt;&lt;br&gt;Чаще всего к нам приходят, когда лес уже свален, покупатель найден, а бумаг на происхождение нет вообще. Оформляем их с нуля: договор купли-продажи как основание, внесение объёма в ФГИС ЛК, сопроводительный документ на рейс.&lt;br&gt;&lt;br&gt;Если остатки в системе не сходятся с фактом, приводим в порядок и это, иначе отгрузки начнут блокировать.&lt;br&gt;&lt;br&gt;Работаем удалённо, свой кабинет и электронную подпись заводить не нужно.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, ель, баланс, Псковская область.</t>
+          <t>Фанкряж и берёзовый баланс отгружают быстро, а документы тормозят всю работу. Закрываем этот кусок.&lt;br&gt;&lt;br&gt;Ставим объём на учёт в ФГИС ЛК, оформляем основание через договор купли-продажи, готовим ЭСД с QR кодом на каждую машину. Если остатки в системе разошлись с фактом, приводим их в соответствие, чтобы отгрузки не блокировались.&lt;br&gt;&lt;br&gt;Подходит и тем, у кого своя делянка, и тем, кто берёт лес у населения и не понимает, как провести такую покупку.&lt;br&gt;&lt;br&gt;От вас порода, объём, маршрут. Ответим по срокам и цене сразу.&lt;br&gt;&lt;br&gt;Берёза фанкряж, баланс, кругляк, осина, Республика Коми.</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n16/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_13_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_13_2.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/2153018262/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_03_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_03_3.jpg</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -26936,7 +26936,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Псковская обл., Себеж, ул. 7 Ноября, 2</t>
+          <t>Республика Коми, Усть-Кулом, ул. Советская, 37</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -26945,7 +26945,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -26979,7 +26979,7 @@
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Берёза</t>
         </is>
       </c>
       <c r="X128" t="inlineStr">
@@ -26999,7 +26999,7 @@
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>2026-10-17T10:00:00+03:00</t>
+          <t>2026-10-17T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
@@ -27019,19 +27019,19 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>2026-09-17T13:00:00+03:00</t>
+          <t>2026-09-17T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
         <is>
-          <t>2026-10-17T10:00:00+03:00</t>
+          <t>2026-10-17T02:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1762058548</t>
+          <t>4789943875</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -27046,17 +27046,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Сосна кругляк с поля, оформим учёт</t>
+          <t>Доска обрезная, документы и ЭСД</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Лес, выросший на пашне или в лесополосе, по документам такой же, как из делянки. Оформляем его с нуля.&lt;br&gt;&lt;br&gt;Собственники земли часто узнают об этом уже после того, как спилили: покупатель просит бумаги, а бумаг нет, и продать несколько сотен кубов не получается.&lt;br&gt;&lt;br&gt;Мы проводим объём через договор купли-продажи, заносим в ФГИС ЛК, ставим на баланс и дальше выдаём сопроводительные документы на вывоз. В сложных случаях помогаем разобраться с назначением участка и с тем, как это правильно показать.&lt;br&gt;&lt;br&gt;Работаем удалённо, приезжать не нужно. Напишите породу и примерный объём.&lt;br&gt;&lt;br&gt;Сосна кругляк, берёза, ель, лес с сельхозземель, Новгородская область.</t>
+          <t>Документы на пиломатериал. Доска обрезная, необрезная, брусок, горбыль.&lt;br&gt;&lt;br&gt;Многие думают, что учёт касается только круглого леса. На доску сопроводительный документ нужен ровно так же, и вопросы на дороге к машине с пиломатериалом возникают не реже.&lt;br&gt;&lt;br&gt;Что делаем: заводим объём в ФГИС ЛК, оформляем происхождение через договор, готовим ЭСД с QR кодом на каждую отгрузку. Если у покупателя бухгалтерия требует полный пакет, собираем и его.&lt;br&gt;&lt;br&gt;От вас нужны порода, объём в кубах, откуда и куда едет машина. Остальное на нас, приезжать никуда не надо.&lt;br&gt;&lt;br&gt;Доска обрезная сосна и ель, пиломатериал, кругляк, Кировская область.</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n11/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_10_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_09_1.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n03/1.png|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_04_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_04_3.jpg</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -27071,7 +27071,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Новгородская обл., Чудово, ул. Некрасова, 24</t>
+          <t>Кировская обл., Омутнинск, ул. Комсомольская, 9</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -27080,7 +27080,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>2026-10-18T02:00:00+03:00</t>
+          <t>2026-10-17T04:00:00+03:00</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
@@ -27154,19 +27154,19 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>2026-09-18T05:00:00+03:00</t>
+          <t>2026-09-17T07:00:00+03:00</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>2026-10-18T02:00:00+03:00</t>
+          <t>2026-10-17T04:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>4787974535</t>
+          <t>4389846312</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -27181,17 +27181,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Берёза фанкряж, ЭСД и учёт объёма</t>
+          <t>Ель пиловочник, документы ФГИС ЛК</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Фанкряж и берёзовый баланс отгружают быстро, а документы тормозят всю работу. Закрываем этот кусок.&lt;br&gt;&lt;br&gt;Ставим объём на учёт в ФГИС ЛК, оформляем основание через договор купли-продажи, готовим ЭСД с QR кодом на каждую машину. Если остатки в системе разошлись с фактом, приводим их в соответствие, чтобы отгрузки не блокировались.&lt;br&gt;&lt;br&gt;Подходит и тем, у кого своя делянка, и тем, кто берёт лес у населения и не понимает, как провести такую покупку.&lt;br&gt;&lt;br&gt;От вас порода, объём, маршрут. Ответим по срокам и цене сразу.&lt;br&gt;&lt;br&gt;Берёза фанкряж, баланс, кругляк, осина, Республика Коми.</t>
+          <t>Ставим еловый пиловочник на учёт и готовим документы под продажу.&lt;br&gt;&lt;br&gt;Покупатели с производством почти всегда просят подтверждение происхождения. Если объём не проведён в государственной системе, сделка либо срывается, либо идёт в серую, а это уже риск для обеих сторон.&lt;br&gt;&lt;br&gt;Берём весь оформительский круг на себя: договор купли-продажи, внесение партии в ФГИС ЛК, сопроводительные документы с QR кодом на каждую машину, отчётность за период.&lt;br&gt;&lt;br&gt;Пишите породу, объём и откуда лес, скажем по срокам и цене сразу.&lt;br&gt;&lt;br&gt;Ель пиловочник, сосна, кругляк, баланс, Смоленская область.</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/2153018262/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_03_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_03_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_12_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_11_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_13_3.jpg</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Республика Коми, Усть-Кулом, ул. Советская, 37</t>
+          <t>Смоленская обл., Вязьма, ул. Ленина, 14</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -27215,7 +27215,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>320</v>
+        <v>5500</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>Берёза</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X130" t="inlineStr">
@@ -27269,7 +27269,7 @@
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>2026-10-18T06:00:00+03:00</t>
+          <t>2026-10-17T06:00:00+03:00</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
@@ -27289,19 +27289,19 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>2026-09-18T09:00:00+03:00</t>
+          <t>2026-09-17T09:00:00+03:00</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>2026-10-18T06:00:00+03:00</t>
+          <t>2026-10-17T06:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2289536143</t>
+          <t>5263922306</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -27316,17 +27316,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Сосна кругляк, QR код за 15 минут</t>
+          <t>Брус и доска, документы ФГИС ЛК</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Машина готова, водитель ждёт, а документа на рейс нет. Делаем его за пятнадцать минут.&lt;br&gt;&lt;br&gt;Электронный сопроводительный документ с QR кодом оформляем на любую породу и любой объём, хоть на одну машину дров, хоть на регулярные отгрузки пиловочника. Документ настоящий, виден в системе, на весовой и на посту вопросов не вызывает.&lt;br&gt;&lt;br&gt;Если объёма в системе нет, заводим его: договор купли-продажи как основание, партия на балансе, дальше рейсы.&lt;br&gt;&lt;br&gt;Нужны только данные машины, порода, объём и маршрут. Пишите в любое время, отвечаем быстро.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, ель, берёза, Республика Карелия.</t>
+          <t>Собираем документы на брус и доску для тех, кто продаёт пиломатериал юрлицам.&lt;br&gt;&lt;br&gt;Когда покупатель крупный, у него свои требования: происхождение древесины, сопроводительные документы, чтобы всё сходилось в системе. Без этого сделку часто просто не проводят, даже если товар устраивает.&lt;br&gt;&lt;br&gt;Что делаем: заводим объём в ФГИС ЛК, оформляем основание договором купли-продажи, готовим ЭСД с QR кодом на отгрузки и полный комплект, который спокойно уходит в бухгалтерию покупателя.&lt;br&gt;&lt;br&gt;Работаем с пилорамами и перекупщиками по всей стране, удалённо.&lt;br&gt;&lt;br&gt;Брус, доска обрезная, пиломатериал хвоя, кругляк, Архангельская область.</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/7393214976/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_04_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_04_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n04/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_08_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_08_3.jpg</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -27341,7 +27341,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Республика Карелия, Пудож, ул. Ленина, 90</t>
+          <t>Архангельская обл., Вельск, ул. Дзержинского, 48</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -27350,7 +27350,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>300</v>
+        <v>790</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -27404,7 +27404,7 @@
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>2026-10-18T08:00:00+03:00</t>
+          <t>2026-10-17T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
@@ -27424,19 +27424,19 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>2026-09-18T11:00:00+03:00</t>
+          <t>2026-09-17T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>2026-10-18T08:00:00+03:00</t>
+          <t>2026-10-17T08:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>9258836919</t>
+          <t>5104171983</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -27451,17 +27451,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Ель пиловочник, документы ФГИС ЛК</t>
+          <t>Ель пиловочник, документы на вывоз</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ставим еловый пиловочник на учёт и готовим документы под продажу.&lt;br&gt;&lt;br&gt;Покупатели с производством почти всегда просят подтверждение происхождения. Если объём не проведён в государственной системе, сделка либо срывается, либо идёт в серую, а это уже риск для обеих сторон.&lt;br&gt;&lt;br&gt;Берём весь оформительский круг на себя: договор купли-продажи, внесение партии в ФГИС ЛК, сопроводительные документы с QR кодом на каждую машину, отчётность за период.&lt;br&gt;&lt;br&gt;Пишите породу, объём и откуда лес, скажем по срокам и цене сразу.&lt;br&gt;&lt;br&gt;Ель пиловочник, сосна, кругляк, баланс, Смоленская область.</t>
+          <t>Разбираемся с учётом ели и готовим документы на вывоз.&lt;br&gt;&lt;br&gt;Чаще всего приходят с двумя вещами. Первая: лес заготовлен, а в системе его нет, продать официально нельзя. Вторая: объёмы когда-то внесли неверно, остатки не сходятся, и отгрузка встала.&lt;br&gt;&lt;br&gt;Закрываем и то и другое. Оформляем происхождение через договор, вносим партию в ФГИС ЛК, правим расхождения по остаткам, дальше выписываем сопроводительные документы на каждую машину.&lt;br&gt;&lt;br&gt;Работаем по всей стране удалённо, нужен только ваш объём и понимание, откуда он взялся.&lt;br&gt;&lt;br&gt;Ель пиловочник, баланс, сосна, кругляк, Костромская область.</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_12_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_11_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_13_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/5312403632/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_09_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_09_3.jpg</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -27476,7 +27476,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Смоленская обл., Вязьма, ул. Ленина, 14</t>
+          <t>Костромская обл., Мантурово, ул. Советская, 25</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -27539,7 +27539,7 @@
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>2026-10-18T10:00:00+03:00</t>
+          <t>2026-10-18T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
@@ -27559,19 +27559,19 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>2026-09-18T13:00:00+03:00</t>
+          <t>2026-09-18T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>2026-10-18T10:00:00+03:00</t>
+          <t>2026-10-18T02:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>8693589310</t>
+          <t>9718114042</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -27586,17 +27586,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ель пиловочник, документы на вывоз</t>
+          <t>Сосна кругляк, QR код на вывоз</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Разбираемся с учётом ели и готовим документы на вывоз.&lt;br&gt;&lt;br&gt;Чаще всего приходят с двумя вещами. Первая: лес заготовлен, а в системе его нет, продать официально нельзя. Вторая: объёмы когда-то внесли неверно, остатки не сходятся, и отгрузка встала.&lt;br&gt;&lt;br&gt;Закрываем и то и другое. Оформляем происхождение через договор, вносим партию в ФГИС ЛК, правим расхождения по остаткам, дальше выписываем сопроводительные документы на каждую машину.&lt;br&gt;&lt;br&gt;Работаем по всей стране удалённо, нужен только ваш объём и понимание, откуда он взялся.&lt;br&gt;&lt;br&gt;Ель пиловочник, баланс, сосна, кругляк, Костромская область.</t>
+          <t>Делаем QR код на вывоз соснового кругляка. Это тот самый электронный документ, который сейчас спрашивают на каждую машину с древесиной.&lt;br&gt;&lt;br&gt;Чаще всего к нам приходят, когда лес уже свален, покупатель найден, а бумаг на происхождение нет вообще. Оформляем их с нуля: договор купли-продажи как основание, внесение объёма в ФГИС ЛК, сопроводительный документ на рейс.&lt;br&gt;&lt;br&gt;Если остатки в системе не сходятся с фактом, приводим в порядок и это, иначе отгрузки начнут блокировать.&lt;br&gt;&lt;br&gt;Работаем удалённо, свой кабинет и электронную подпись заводить не нужно.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, ель, баланс, Псковская область.</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/5312403632/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_09_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_09_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n16/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_13_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_13_2.jpg</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -27611,7 +27611,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Костромская обл., Мантурово, ул. Советская, 25</t>
+          <t>Псковская обл., Себеж, ул. 7 Ноября, 2</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -27620,7 +27620,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>280</v>
+        <v>2900</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X133" t="inlineStr">
@@ -27674,7 +27674,7 @@
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>2026-10-19T02:00:00+03:00</t>
+          <t>2026-10-18T04:00:00+03:00</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -27694,19 +27694,19 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>2026-09-19T05:00:00+03:00</t>
+          <t>2026-09-18T07:00:00+03:00</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>2026-10-19T02:00:00+03:00</t>
+          <t>2026-10-18T04:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2543470744</t>
+          <t>2316630576</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -27721,17 +27721,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Дрова колотые, документы на продажу</t>
+          <t>Лиственница кругляк, ЭСД на отгрузку</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Дрова тоже древесина, и учёт для них такой же, как для делового леса. Оформляем документы тем, кто продаёт дрова машинами.&lt;br&gt;&lt;br&gt;Частника с одной машиной для себя это не касается, а вот когда возишь на продажу регулярно, нужен сопроводительный документ на рейс. Особенно если покупатель юрлицо и ему нужно провести покупку по бухгалтерии.&lt;br&gt;&lt;br&gt;Делаем полный круг: происхождение объёма, внесение в ФГИС ЛК, ЭСД с QR на каждую отгрузку, отчётность за период.&lt;br&gt;&lt;br&gt;Напишите, сколько машин в месяц возите, подберём вариант по цене.&lt;br&gt;&lt;br&gt;Дрова колотые берёза и осина, баланс, горбыль, Нижегородская область.</t>
+          <t>Документы на лиственницу под отгрузку: машинами, вагонами, партиями на экспортёра.&lt;br&gt;&lt;br&gt;Когда объём идёт на станцию, покупатель смотрит не только на качество, но и на то, сходятся ли данные в системе. Если партия не проведена, отгрузка встаёт, и это дороже любых документов.&lt;br&gt;&lt;br&gt;Берём на себя всю цепочку: происхождение объёма через договор, внесение в ФГИС ЛК, ЭСД с QR на каждый рейс, сверка остатков перед отгрузкой. Работаем с ИП, ООО и с частниками.&lt;br&gt;&lt;br&gt;Напишите объём и куда идёт лес, разберём вашу ситуацию и скажем, что нужно.&lt;br&gt;&lt;br&gt;Лиственница кругляк, пиловочник, сосна, ель, Иркутская область.</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/05/05_01.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_10_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_10_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/9218798416/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_10_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_10_3.jpg</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -27746,7 +27746,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Нижегородская обл., Ветлуга, ул. Ленина, 6</t>
+          <t>Иркутская обл., Усть-Кут, ул. Кирова, 18</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -27755,7 +27755,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>250</v>
+        <v>4500</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>Берёза</t>
+          <t>Лиственница</t>
         </is>
       </c>
       <c r="X134" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>2026-10-19T04:00:00+03:00</t>
+          <t>2026-10-18T06:00:00+03:00</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -27829,19 +27829,19 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>2026-09-19T07:00:00+03:00</t>
+          <t>2026-09-18T09:00:00+03:00</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
         <is>
-          <t>2026-10-19T04:00:00+03:00</t>
+          <t>2026-10-18T06:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>5542586163</t>
+          <t>1469021613</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -27856,17 +27856,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Брус и доска, документы ФГИС ЛК</t>
+          <t>Пиломатериал хвоя, документы ФГИС</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Собираем документы на брус и доску для тех, кто продаёт пиломатериал юрлицам.&lt;br&gt;&lt;br&gt;Когда покупатель крупный, у него свои требования: происхождение древесины, сопроводительные документы, чтобы всё сходилось в системе. Без этого сделку часто просто не проводят, даже если товар устраивает.&lt;br&gt;&lt;br&gt;Что делаем: заводим объём в ФГИС ЛК, оформляем основание договором купли-продажи, готовим ЭСД с QR кодом на отгрузки и полный комплект, который спокойно уходит в бухгалтерию покупателя.&lt;br&gt;&lt;br&gt;Работаем с пилорамами и перекупщиками по всей стране, удалённо.&lt;br&gt;&lt;br&gt;Брус, доска обрезная, пиломатериал хвоя, кругляк, Архангельская область.</t>
+          <t>Ведём документы на хвойный пиломатериал: доска, брус, оцилиндрованное бревно, погонаж.&lt;br&gt;&lt;br&gt;Покупатель из другого региона почти всегда просит показать происхождение древесины. Без этого товар смотрят, но сделку не проводят, и хороший объём зависает на площадке.&lt;br&gt;&lt;br&gt;Закрываем это полностью. Оформляем договор купли-продажи как основание, заводим объёмы в систему учёта, выдаём сопроводительный документ с QR кодом на каждую отгрузку, готовим отчётность.&lt;br&gt;&lt;br&gt;Работаем с пилорамами и перекупщиками, удалённо, по всей стране.&lt;br&gt;&lt;br&gt;Пиломатериал хвоя, доска обрезная, брус, кругляк, Калужская область.</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n04/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_08_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_08_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_15_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_13_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_13_3.jpg</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -27881,7 +27881,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Архангельская обл., Вельск, ул. Дзержинского, 48</t>
+          <t>Калужская обл., Людиново, ул. Ленина, 20</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -27890,7 +27890,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>350</v>
+        <v>590</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>2026-10-19T08:00:00+03:00</t>
+          <t>2026-10-18T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -27964,19 +27964,19 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>2026-09-19T11:00:00+03:00</t>
+          <t>2026-09-18T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>2026-10-19T08:00:00+03:00</t>
+          <t>2026-10-18T08:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>4323234383</t>
+          <t>6384601011</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -27991,17 +27991,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Осина дрова, документы на вывоз</t>
+          <t>Сосна кругляк с поля, оформим учёт</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Документы на осину и дровяную древесину для тех, кто возит её на продажу.&lt;br&gt;&lt;br&gt;Многие считают, что дрова учитывать не надо. На деле это такая же древесина, и на рейс нужен электронный сопроводительный документ. Особенно если покупатель юрлицо и проводит покупку по бухгалтерии.&lt;br&gt;&lt;br&gt;Делаем полный круг: происхождение объёма через договор, внесение в ФГИС ЛК, ЭСД с QR кодом на каждую машину. Для постоянных перевозок считаем помесячно.&lt;br&gt;&lt;br&gt;От вас порода, объём, номер машины и маршрут. Остальное на нас.&lt;br&gt;&lt;br&gt;Осина дрова, баланс, берёза, горбыль, Брянская область.</t>
+          <t>Лес, выросший на пашне или в лесополосе, по документам такой же, как из делянки. Оформляем его с нуля.&lt;br&gt;&lt;br&gt;Собственники земли часто узнают об этом уже после того, как спилили: покупатель просит бумаги, а бумаг нет, и продать несколько сотен кубов не получается.&lt;br&gt;&lt;br&gt;Мы проводим объём через договор купли-продажи, заносим в ФГИС ЛК, ставим на баланс и дальше выдаём сопроводительные документы на вывоз. В сложных случаях помогаем разобраться с назначением участка и с тем, как это правильно показать.&lt;br&gt;&lt;br&gt;Работаем удалённо, приезжать не нужно. Напишите породу и примерный объём.&lt;br&gt;&lt;br&gt;Сосна кругляк, берёза, ель, лес с сельхозземель, Новгородская область.</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n14/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/04/04_02.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/04/04_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n11/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_10_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_09_1.jpg</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -28016,7 +28016,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Брянская обл., Трубчевск, ул. Ленина, 60</t>
+          <t>Новгородская обл., Чудово, ул. Некрасова, 24</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -28025,7 +28025,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>Осина</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X136" t="inlineStr">
@@ -28079,7 +28079,7 @@
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>2026-10-20T02:00:00+03:00</t>
+          <t>2026-10-18T10:00:00+03:00</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
@@ -28099,19 +28099,19 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>2026-09-20T05:00:00+03:00</t>
+          <t>2026-09-18T13:00:00+03:00</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
         <is>
-          <t>2026-10-20T02:00:00+03:00</t>
+          <t>2026-10-18T10:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>4637367814</t>
+          <t>2048558862</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -28126,17 +28126,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Доска и брусок, ЭСД на машину</t>
+          <t>Осина баланс, QR код на вывоз</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Оформляем сопроводительные документы на машины с пиломатериалом. Доска, брусок, обапол, тарная дощечка.&lt;br&gt;&lt;br&gt;Вопрос от пилорам звучит одинаково: нужен ли документ, если лес уже распилен. Нужен. Учёт никуда не исчезает после переработки, и на дороге это проверяют.&lt;br&gt;&lt;br&gt;Мы вносим объёмы в ФГИС ЛК, оформляем происхождение договором, готовим ЭСД с QR кодом на каждую отгрузку и собираем пакет, который спокойно принимает бухгалтерия покупателя.&lt;br&gt;&lt;br&gt;Если отгружаете регулярно, берём на сопровождение, так дешевле и быстрее.&lt;br&gt;&lt;br&gt;Доска обрезная, брусок, брус, пиломатериал хвоя, Брянская область.</t>
+          <t>Ставим на учёт осиновый баланс и делаем документы на вывозку.&lt;br&gt;&lt;br&gt;Осину берут плитные комбинаты, но без бумаг на происхождение партию на приёмке развернут. Отдельная история, когда лес пилили на своей земле или на расчистке, в системе такого объёма нет вообще.&lt;br&gt;&lt;br&gt;Мы это закрываем: заводим объём, оформляем договор купли-продажи как основание, дальше на каждый рейс выдаём ЭСД с QR кодом. Отчёт за период тоже готовим, если он с вас спросят.&lt;br&gt;&lt;br&gt;Объём любой, от одной машины до постоянного потока. Пишите, что и куда везёте, посчитаем сроки.&lt;br&gt;&lt;br&gt;Осина баланс, дрова, кругляк, ольха и берёза, Кировская область.</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n06/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_05_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_05_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n02/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_09_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_09_3.jpg</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -28151,7 +28151,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Брянская обл., Жуковка, ул. Октябрьская, 3</t>
+          <t>Кировская обл., Яранск, ул. Кирова, 10</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -28160,7 +28160,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>350</v>
+        <v>1200</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Осина</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
@@ -28214,7 +28214,7 @@
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>2026-10-20T04:00:00+03:00</t>
+          <t>2026-10-19T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -28234,19 +28234,19 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>2026-09-20T07:00:00+03:00</t>
+          <t>2026-09-19T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>2026-10-20T04:00:00+03:00</t>
+          <t>2026-10-19T02:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1410610101</t>
+          <t>1041037816</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -28261,17 +28261,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Пиломатериал хвоя, документы ФГИС</t>
+          <t>Пиломатериал хвоя, QR на машину</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ведём документы на хвойный пиломатериал: доска, брус, оцилиндрованное бревно, погонаж.&lt;br&gt;&lt;br&gt;Покупатель из другого региона почти всегда просит показать происхождение древесины. Без этого товар смотрят, но сделку не проводят, и хороший объём зависает на площадке.&lt;br&gt;&lt;br&gt;Закрываем это полностью. Оформляем договор купли-продажи как основание, заводим объёмы в систему учёта, выдаём сопроводительный документ с QR кодом на каждую отгрузку, готовим отчётность.&lt;br&gt;&lt;br&gt;Работаем с пилорамами и перекупщиками, удалённо, по всей стране.&lt;br&gt;&lt;br&gt;Пиломатериал хвоя, доска обрезная, брус, кругляк, Калужская область.</t>
+          <t>Делаем QR код на машину с пиломатериалом. Доска, брус, брусок, тарная дощечка.&lt;br&gt;&lt;br&gt;Вопрос, который задают чаще всего: нужен ли документ на доску, если это уже не круглый лес. Нужен. Переработка не снимает учёт, и на посту это проверяют так же.&lt;br&gt;&lt;br&gt;Оформляем быстро. Вы даёте объём, породу и маршрут, мы вносим данные и отдаём готовый ЭСД. Если объём не заведён в системе, сначала проводим происхождение через договор, это тоже наша работа.&lt;br&gt;&lt;br&gt;Пилорамам, которые отгружают регулярно, считаем помесячно, так выходит дешевле.&lt;br&gt;&lt;br&gt;Пиломатериал хвоя, доска обрезная, брус, кругляк, Вологодская область.</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_15_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_13_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_13_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/8757513433/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_14_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_14_3.jpg</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -28286,7 +28286,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Калужская обл., Людиново, ул. Ленина, 20</t>
+          <t>Вологодская обл., Тотьма, ул. Ленина, 44</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -28295,7 +28295,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>350</v>
+        <v>3500</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>2026-10-20T06:00:00+03:00</t>
+          <t>2026-10-19T06:00:00+03:00</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -28369,19 +28369,19 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>2026-09-20T09:00:00+03:00</t>
+          <t>2026-09-19T09:00:00+03:00</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
         <is>
-          <t>2026-10-20T06:00:00+03:00</t>
+          <t>2026-10-19T06:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>6900416887</t>
+          <t>1172729374</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -28396,17 +28396,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Берёза кругляк, QR код на рейс</t>
+          <t>Дрова колотые, документы на продажу</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Берёза с расчистки полей и обочин, документы делаем мы.&lt;br&gt;&lt;br&gt;Такой лес по закону учитывается так же, как из делянки. Владельцы участков узнают об этом обычно уже после того, как спилили, и упираются в то, что вывезти объём нельзя.&lt;br&gt;&lt;br&gt;Порядок работы: проводим происхождение через договор купли-продажи, вносим партию в ФГИС ЛК, ставим её вам на баланс. Дальше на каждую машину выписываем ЭСД с QR кодом, делаем это быстро, обычно за пятнадцать минут.&lt;br&gt;&lt;br&gt;Объём любой, от одной машины до постоянных отгрузок на комбинат.&lt;br&gt;&lt;br&gt;Берёза кругляк, дрова, баланс, фанкряж, Рязанская область.</t>
+          <t>Дрова тоже древесина, и учёт для них такой же, как для делового леса. Оформляем документы тем, кто продаёт дрова машинами.&lt;br&gt;&lt;br&gt;Частника с одной машиной для себя это не касается, а вот когда возишь на продажу регулярно, нужен сопроводительный документ на рейс. Особенно если покупатель юрлицо и ему нужно провести покупку по бухгалтерии.&lt;br&gt;&lt;br&gt;Делаем полный круг: происхождение объёма, внесение в ФГИС ЛК, ЭСД с QR на каждую отгрузку, отчётность за период.&lt;br&gt;&lt;br&gt;Напишите, сколько машин в месяц возите, подберём вариант по цене.&lt;br&gt;&lt;br&gt;Дрова колотые берёза и осина, баланс, горбыль, Нижегородская область.</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/01/01_01.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_15_3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_18_2.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/05/05_01.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_10_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_10_3.jpg</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -28421,7 +28421,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Рязанская обл., Касимов, ул. Советская, 14</t>
+          <t>Нижегородская обл., Ветлуга, ул. Ленина, 6</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -28430,7 +28430,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>2026-10-20T08:00:00+03:00</t>
+          <t>2026-10-19T10:00:00+03:00</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -28504,12 +28504,12 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>2026-09-20T11:00:00+03:00</t>
+          <t>2026-09-19T13:00:00+03:00</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
         <is>
-          <t>2026-10-20T08:00:00+03:00</t>
+          <t>2026-10-19T10:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -32678,7 +32678,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4740067166</t>
+          <t>6198700758</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -32707,7 +32707,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>350</v>
+        <v>490</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -32791,24 +32791,24 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16T08:00:00+03:00</t>
+          <t>2026-10-17T10:00:00+03:00</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-09-16T11:00:00+03:00</t>
+          <t>2026-09-17T13:00:00+03:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>2026-10-16T08:00:00+03:00</t>
+          <t>2026-10-17T10:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8269348027</t>
+          <t>4553072030</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -32837,7 +32837,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>350</v>
+        <v>190</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -32921,17 +32921,17 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-20T10:00:00+03:00</t>
+          <t>2026-10-19T04:00:00+03:00</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-09-20T13:00:00+03:00</t>
+          <t>2026-09-19T07:00:00+03:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>2026-10-20T10:00:00+03:00</t>
+          <t>2026-10-19T04:00:00+03:00</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -8492,7 +8492,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Новгородская обл., Любытино, ул. Советов, 29</t>
+          <t>Хабаровский край, Комсомольск-на-Амуре, пр-т Ленина, 22</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Республика Коми, Троицко-Печорск, ул. Ленина, 2</t>
+          <t>Республика Мордовия, Ковылкино, ул. Пролетарская, 20</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Смоленская обл., Рославль, ул. Советская, 66</t>
+          <t>Калининградская обл., Черняховск, ул. Ленина, 5</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -8822,17 +8822,17 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>2026-10-20T02:00:00+03:00</t>
+          <t>2026-10-20T06:00:00+03:00</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>2026-09-20T05:00:00+03:00</t>
+          <t>2026-09-20T09:00:00+03:00</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2026-10-20T02:00:00+03:00</t>
+          <t>2026-10-20T06:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -25836,7 +25836,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Оформляем документы на берёзу, которая уже заготовлена: дрова, баланс, кругляк с зарастающего поля.&lt;br&gt;&lt;br&gt;На каждую машину с древесиной нужен электронный сопроводительный документ с QR кодом. Без него рейс начинать рискованно, на посту это первый вопрос.&lt;br&gt;&lt;br&gt;Порядок простой. Вы пишете породу, объём, номер машины и маршрут. Мы проводим происхождение партии через договор купли-продажи, заносим объём в ФГИС ЛК и отдаём готовый документ на рейс. Обычно уходит пятнадцать минут.&lt;br&gt;&lt;br&gt;Работаем удалённо, свой кабинет в системе и электронную подпись заводить не придётся. Кто возит постоянно, берём на сопровождение помесячно.&lt;br&gt;&lt;br&gt;Берёза кругляк, дрова, баланс на комбинат, Кировская область.</t>
+          <t>Оформляем документы на берёзу, которая уже заготовлена: дрова, баланс, кругляк с зарастающего поля.&lt;br&gt;&lt;br&gt;На каждую машину с древесиной нужен электронный сопроводительный документ с QR кодом. Без него рейс начинать рискованно, на посту это первый вопрос.&lt;br&gt;&lt;br&gt;Порядок простой. Вы пишете породу, объём, номер машины и маршрут. Мы проводим происхождение партии через договор купли-продажи, заносим объём в ФГИС ЛК и отдаём готовый документ на рейс. Обычно уходит пятнадцать минут.&lt;br&gt;&lt;br&gt;Работаем удалённо, свой кабинет в системе и электронную подпись заводить не придётся. Кто возит постоянно, берём на сопровождение помесячно.&lt;br&gt;&lt;br&gt;Берёза кругляк, дрова, баланс на комбинат, Псковская область.</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -25856,7 +25856,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Кировская обл., Котельнич, ул. Ленина, 26</t>
+          <t>Псковская обл., Великие Луки, пр-т Ленина, 14</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -25971,7 +25971,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Оформляем документы на берёзовый баланс и кругляк, который уже лежит на площадке.&lt;br&gt;&lt;br&gt;Без электронного сопроводительного документа машину с лесом дальше поста не пустят, а если объёма нет в системе учёта, то и сам документ выписать не из чего. Мы закрываем обе части сразу.&lt;br&gt;&lt;br&gt;Сначала проводим происхождение партии через договор купли-продажи и ставим объём вам на баланс в ФГИС ЛК. Дальше на каждый рейс выдаём ЭСД с QR кодом, обычно в течение пятнадцати минут после ваших данных.&lt;br&gt;&lt;br&gt;Подойдёт и хозяйству, которое расчищает поля, и тем, кто скупает лес у населения.&lt;br&gt;&lt;br&gt;Берёза баланс, дрова, кругляк, осина, Псковская область.</t>
+          <t>Оформляем документы на берёзовый баланс и кругляк, который уже лежит на площадке.&lt;br&gt;&lt;br&gt;Без электронного сопроводительного документа машину с лесом дальше поста не пустят, а если объёма нет в системе учёта, то и сам документ выписать не из чего. Мы закрываем обе части сразу.&lt;br&gt;&lt;br&gt;Сначала проводим происхождение партии через договор купли-продажи и ставим объём вам на баланс в ФГИС ЛК. Дальше на каждый рейс выдаём ЭСД с QR кодом, обычно в течение пятнадцати минут после ваших данных.&lt;br&gt;&lt;br&gt;Подойдёт и хозяйству, которое расчищает поля, и тем, кто скупает лес у населения.&lt;br&gt;&lt;br&gt;Берёза баланс, дрова, кругляк, осина, Смоленская область.</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -25991,7 +25991,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Псковская обл., Великие Луки, пр-т Ленина, 14</t>
+          <t>Смоленская обл., Вязьма, ул. Ленина, 14</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -26106,7 +26106,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Машина готова, водитель ждёт, а документа на рейс нет. Делаем его за пятнадцать минут.&lt;br&gt;&lt;br&gt;Электронный сопроводительный документ с QR кодом оформляем на любую породу и любой объём, хоть на одну машину дров, хоть на регулярные отгрузки пиловочника. Документ настоящий, виден в системе, на весовой и на посту вопросов не вызывает.&lt;br&gt;&lt;br&gt;Если объёма в системе нет, заводим его: договор купли-продажи как основание, партия на балансе, дальше рейсы.&lt;br&gt;&lt;br&gt;Нужны только данные машины, порода, объём и маршрут. Пишите в любое время, отвечаем быстро.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, ель, берёза, Республика Карелия.</t>
+          <t>Машина готова, водитель ждёт, а документа на рейс нет. Делаем его за пятнадцать минут.&lt;br&gt;&lt;br&gt;Электронный сопроводительный документ с QR кодом оформляем на любую породу и любой объём, хоть на одну машину дров, хоть на регулярные отгрузки пиловочника. Документ настоящий, виден в системе, на весовой и на посту вопросов не вызывает.&lt;br&gt;&lt;br&gt;Если объёма в системе нет, заводим его: договор купли-продажи как основание, партия на балансе, дальше рейсы.&lt;br&gt;&lt;br&gt;Нужны только данные машины, порода, объём и маршрут. Пишите в любое время, отвечаем быстро.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, ель, берёза, Брянская область.</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -26126,7 +26126,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Республика Карелия, Пудож, ул. Ленина, 90</t>
+          <t>Брянская обл., Трубчевск, ул. Ленина, 60</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Документы на осину и дровяную древесину для тех, кто возит её на продажу.&lt;br&gt;&lt;br&gt;Многие считают, что дрова учитывать не надо. На деле это такая же древесина, и на рейс нужен электронный сопроводительный документ. Особенно если покупатель юрлицо и проводит покупку по бухгалтерии.&lt;br&gt;&lt;br&gt;Делаем полный круг: происхождение объёма через договор, внесение в ФГИС ЛК, ЭСД с QR кодом на каждую машину. Для постоянных перевозок считаем помесячно.&lt;br&gt;&lt;br&gt;От вас порода, объём, номер машины и маршрут. Остальное на нас.&lt;br&gt;&lt;br&gt;Осина дрова, баланс, берёза, горбыль, Брянская область.</t>
+          <t>Документы на осину и дровяную древесину для тех, кто возит её на продажу.&lt;br&gt;&lt;br&gt;Многие считают, что дрова учитывать не надо. На деле это такая же древесина, и на рейс нужен электронный сопроводительный документ. Особенно если покупатель юрлицо и проводит покупку по бухгалтерии.&lt;br&gt;&lt;br&gt;Делаем полный круг: происхождение объёма через договор, внесение в ФГИС ЛК, ЭСД с QR кодом на каждую машину. Для постоянных перевозок считаем помесячно.&lt;br&gt;&lt;br&gt;От вас порода, объём, номер машины и маршрут. Остальное на нас.&lt;br&gt;&lt;br&gt;Осина дрова, баланс, берёза, горбыль, Калужская область.</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -26261,7 +26261,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Брянская обл., Трубчевск, ул. Ленина, 60</t>
+          <t>Калужская обл., Людиново, ул. Ленина, 20</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -26376,7 +26376,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ситуация обычная: пиловочник лежит на площадке, а в системе его нет. Мы делаем так, чтобы он там появился законно.&lt;br&gt;&lt;br&gt;Оформляем происхождение объёма договором купли-продажи, заводим партию в ФГИС ЛК, ставим её вам на баланс. После этого лес можно спокойно продавать и везти, а на каждую машину выписывать сопроводительный документ с QR кодом.&lt;br&gt;&lt;br&gt;Делаем и то, что обычно откладывают: лесную декларацию, отчёт 1-ИЛ, закрытие расхождений по остаткам.&lt;br&gt;&lt;br&gt;Всё удалённо, по всей стране. От вас порода, объём и что уже есть на руках.&lt;br&gt;&lt;br&gt;Сосна пиловочник, кругляк, баланс, ель и лиственница, Иркутская область.</t>
+          <t>Ситуация обычная: пиловочник лежит на площадке, а в системе его нет. Мы делаем так, чтобы он там появился законно.&lt;br&gt;&lt;br&gt;Оформляем происхождение объёма договором купли-продажи, заводим партию в ФГИС ЛК, ставим её вам на баланс. После этого лес можно спокойно продавать и везти, а на каждую машину выписывать сопроводительный документ с QR кодом.&lt;br&gt;&lt;br&gt;Делаем и то, что обычно откладывают: лесную декларацию, отчёт 1-ИЛ, закрытие расхождений по остаткам.&lt;br&gt;&lt;br&gt;Всё удалённо, по всей стране. От вас порода, объём и что уже есть на руках.&lt;br&gt;&lt;br&gt;Сосна пиловочник, кругляк, баланс, ель и лиственница, Приморский край.</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -26396,7 +26396,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Иркутская обл., Усть-Илимск, ул. Героев Труда, 38</t>
+          <t>Приморский край, Дальнереченск, ул. Героев Даманского, 28</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -26646,7 +26646,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Возите еловый баланс на комбинат, а документы каждый раз собираются в последний момент. Забираем эту часть себе.&lt;br&gt;&lt;br&gt;Оформляем электронный сопроводительный документ на рейс, тот самый с QR кодом. Заводим объём в систему учёта древесины, если его там ещё нет, и приводим в порядок остатки, чтобы приёмка не спорила с цифрами.&lt;br&gt;&lt;br&gt;Работаем и разово, и на потоке. Для постоянных отгрузок удобнее сопровождение: вы пишете машину и объём, документ приходит в ответ, без переписки на полдня.&lt;br&gt;&lt;br&gt;Ель баланс, сосна, берёза, кругляк и дрова, Вологодская область.</t>
+          <t>Возите еловый баланс на комбинат, а документы каждый раз собираются в последний момент. Забираем эту часть себе.&lt;br&gt;&lt;br&gt;Оформляем электронный сопроводительный документ на рейс, тот самый с QR кодом. Заводим объём в систему учёта древесины, если его там ещё нет, и приводим в порядок остатки, чтобы приёмка не спорила с цифрами.&lt;br&gt;&lt;br&gt;Работаем и разово, и на потоке. Для постоянных отгрузок удобнее сопровождение: вы пишете машину и объём, документ приходит в ответ, без переписки на полдня.&lt;br&gt;&lt;br&gt;Ель баланс, сосна, берёза, кругляк и дрова, Мурманская область.</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -26666,7 +26666,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Вологодская обл., Великий Устюг, Советский пр-т, 100</t>
+          <t>Мурманская обл., Кандалакша, ул. Первомайская, 34</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -26781,7 +26781,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Оформляем сопроводительные документы на машины с пиломатериалом. Доска, брусок, обапол, тарная дощечка.&lt;br&gt;&lt;br&gt;Вопрос от пилорам звучит одинаково: нужен ли документ, если лес уже распилен. Нужен. Учёт никуда не исчезает после переработки, и на дороге это проверяют.&lt;br&gt;&lt;br&gt;Мы вносим объёмы в ФГИС ЛК, оформляем происхождение договором, готовим ЭСД с QR кодом на каждую отгрузку и собираем пакет, который спокойно принимает бухгалтерия покупателя.&lt;br&gt;&lt;br&gt;Если отгружаете регулярно, берём на сопровождение, так дешевле и быстрее.&lt;br&gt;&lt;br&gt;Доска обрезная, брусок, брус, пиломатериал хвоя, Брянская область.</t>
+          <t>Оформляем сопроводительные документы на машины с пиломатериалом. Доска, брусок, обапол, тарная дощечка.&lt;br&gt;&lt;br&gt;Вопрос от пилорам звучит одинаково: нужен ли документ, если лес уже распилен. Нужен. Учёт никуда не исчезает после переработки, и на дороге это проверяют.&lt;br&gt;&lt;br&gt;Мы вносим объёмы в ФГИС ЛК, оформляем происхождение договором, готовим ЭСД с QR кодом на каждую отгрузку и собираем пакет, который спокойно принимает бухгалтерия покупателя.&lt;br&gt;&lt;br&gt;Если отгружаете регулярно, берём на сопровождение, так дешевле и быстрее.&lt;br&gt;&lt;br&gt;Доска обрезная, брусок, брус, пиломатериал хвоя, Тамбовская область.</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -26801,7 +26801,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Брянская обл., Жуковка, ул. Октябрьская, 3</t>
+          <t>Тамбовская обл., Моршанск, ул. Октябрьская, 22</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -26916,7 +26916,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Фанкряж и берёзовый баланс отгружают быстро, а документы тормозят всю работу. Закрываем этот кусок.&lt;br&gt;&lt;br&gt;Ставим объём на учёт в ФГИС ЛК, оформляем основание через договор купли-продажи, готовим ЭСД с QR кодом на каждую машину. Если остатки в системе разошлись с фактом, приводим их в соответствие, чтобы отгрузки не блокировались.&lt;br&gt;&lt;br&gt;Подходит и тем, у кого своя делянка, и тем, кто берёт лес у населения и не понимает, как провести такую покупку.&lt;br&gt;&lt;br&gt;От вас порода, объём, маршрут. Ответим по срокам и цене сразу.&lt;br&gt;&lt;br&gt;Берёза фанкряж, баланс, кругляк, осина, Республика Коми.</t>
+          <t>Фанкряж и берёзовый баланс отгружают быстро, а документы тормозят всю работу. Закрываем этот кусок.&lt;br&gt;&lt;br&gt;Ставим объём на учёт в ФГИС ЛК, оформляем основание через договор купли-продажи, готовим ЭСД с QR кодом на каждую машину. Если остатки в системе разошлись с фактом, приводим их в соответствие, чтобы отгрузки не блокировались.&lt;br&gt;&lt;br&gt;Подходит и тем, у кого своя делянка, и тем, кто берёт лес у населения и не понимает, как провести такую покупку.&lt;br&gt;&lt;br&gt;От вас порода, объём, маршрут. Ответим по срокам и цене сразу.&lt;br&gt;&lt;br&gt;Берёза фанкряж, баланс, кругляк, осина, Еврейская автономная область.</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -26936,7 +26936,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Республика Коми, Усть-Кулом, ул. Советская, 37</t>
+          <t>Еврейская АО, Биробиджан, ул. Ленина, 29</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Документы на пиломатериал. Доска обрезная, необрезная, брусок, горбыль.&lt;br&gt;&lt;br&gt;Многие думают, что учёт касается только круглого леса. На доску сопроводительный документ нужен ровно так же, и вопросы на дороге к машине с пиломатериалом возникают не реже.&lt;br&gt;&lt;br&gt;Что делаем: заводим объём в ФГИС ЛК, оформляем происхождение через договор, готовим ЭСД с QR кодом на каждую отгрузку. Если у покупателя бухгалтерия требует полный пакет, собираем и его.&lt;br&gt;&lt;br&gt;От вас нужны порода, объём в кубах, откуда и куда едет машина. Остальное на нас, приезжать никуда не надо.&lt;br&gt;&lt;br&gt;Доска обрезная сосна и ель, пиломатериал, кругляк, Кировская область.</t>
+          <t>Документы на пиломатериал. Доска обрезная, необрезная, брусок, горбыль.&lt;br&gt;&lt;br&gt;Многие думают, что учёт касается только круглого леса. На доску сопроводительный документ нужен ровно так же, и вопросы на дороге к машине с пиломатериалом возникают не реже.&lt;br&gt;&lt;br&gt;Что делаем: заводим объём в ФГИС ЛК, оформляем происхождение через договор, готовим ЭСД с QR кодом на каждую отгрузку. Если у покупателя бухгалтерия требует полный пакет, собираем и его.&lt;br&gt;&lt;br&gt;От вас нужны порода, объём в кубах, откуда и куда едет машина. Остальное на нас, приезжать никуда не надо.&lt;br&gt;&lt;br&gt;Доска обрезная сосна и ель, пиломатериал, кругляк, Республика Саха.</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -27071,7 +27071,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Кировская обл., Омутнинск, ул. Комсомольская, 9</t>
+          <t>Республика Саха (Якутия), Ленск, ул. Ленина, 65</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -27186,7 +27186,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ставим еловый пиловочник на учёт и готовим документы под продажу.&lt;br&gt;&lt;br&gt;Покупатели с производством почти всегда просят подтверждение происхождения. Если объём не проведён в государственной системе, сделка либо срывается, либо идёт в серую, а это уже риск для обеих сторон.&lt;br&gt;&lt;br&gt;Берём весь оформительский круг на себя: договор купли-продажи, внесение партии в ФГИС ЛК, сопроводительные документы с QR кодом на каждую машину, отчётность за период.&lt;br&gt;&lt;br&gt;Пишите породу, объём и откуда лес, скажем по срокам и цене сразу.&lt;br&gt;&lt;br&gt;Ель пиловочник, сосна, кругляк, баланс, Смоленская область.</t>
+          <t>Ставим еловый пиловочник на учёт и готовим документы под продажу.&lt;br&gt;&lt;br&gt;Покупатели с производством почти всегда просят подтверждение происхождения. Если объём не проведён в государственной системе, сделка либо срывается, либо идёт в серую, а это уже риск для обеих сторон.&lt;br&gt;&lt;br&gt;Берём весь оформительский круг на себя: договор купли-продажи, внесение партии в ФГИС ЛК, сопроводительные документы с QR кодом на каждую машину, отчётность за период.&lt;br&gt;&lt;br&gt;Пишите породу, объём и откуда лес, скажем по срокам и цене сразу.&lt;br&gt;&lt;br&gt;Ель пиловочник, сосна, кругляк, баланс, Московская область.</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Смоленская обл., Вязьма, ул. Ленина, 14</t>
+          <t>Московская обл., Шатура, пр-т Ильича, 55</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -27321,7 +27321,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Собираем документы на брус и доску для тех, кто продаёт пиломатериал юрлицам.&lt;br&gt;&lt;br&gt;Когда покупатель крупный, у него свои требования: происхождение древесины, сопроводительные документы, чтобы всё сходилось в системе. Без этого сделку часто просто не проводят, даже если товар устраивает.&lt;br&gt;&lt;br&gt;Что делаем: заводим объём в ФГИС ЛК, оформляем основание договором купли-продажи, готовим ЭСД с QR кодом на отгрузки и полный комплект, который спокойно уходит в бухгалтерию покупателя.&lt;br&gt;&lt;br&gt;Работаем с пилорамами и перекупщиками по всей стране, удалённо.&lt;br&gt;&lt;br&gt;Брус, доска обрезная, пиломатериал хвоя, кругляк, Архангельская область.</t>
+          <t>Собираем документы на брус и доску для тех, кто продаёт пиломатериал юрлицам.&lt;br&gt;&lt;br&gt;Когда покупатель крупный, у него свои требования: происхождение древесины, сопроводительные документы, чтобы всё сходилось в системе. Без этого сделку часто просто не проводят, даже если товар устраивает.&lt;br&gt;&lt;br&gt;Что делаем: заводим объём в ФГИС ЛК, оформляем основание договором купли-продажи, готовим ЭСД с QR кодом на отгрузки и полный комплект, который спокойно уходит в бухгалтерию покупателя.&lt;br&gt;&lt;br&gt;Работаем с пилорамами и перекупщиками по всей стране, удалённо.&lt;br&gt;&lt;br&gt;Брус, доска обрезная, пиломатериал хвоя, кругляк, Орловская область.</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -27341,7 +27341,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Архангельская обл., Вельск, ул. Дзержинского, 48</t>
+          <t>Орловская обл., Мценск, ул. Ленина, 25</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -27456,7 +27456,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Разбираемся с учётом ели и готовим документы на вывоз.&lt;br&gt;&lt;br&gt;Чаще всего приходят с двумя вещами. Первая: лес заготовлен, а в системе его нет, продать официально нельзя. Вторая: объёмы когда-то внесли неверно, остатки не сходятся, и отгрузка встала.&lt;br&gt;&lt;br&gt;Закрываем и то и другое. Оформляем происхождение через договор, вносим партию в ФГИС ЛК, правим расхождения по остаткам, дальше выписываем сопроводительные документы на каждую машину.&lt;br&gt;&lt;br&gt;Работаем по всей стране удалённо, нужен только ваш объём и понимание, откуда он взялся.&lt;br&gt;&lt;br&gt;Ель пиловочник, баланс, сосна, кругляк, Костромская область.</t>
+          <t>Разбираемся с учётом ели и готовим документы на вывоз.&lt;br&gt;&lt;br&gt;Чаще всего приходят с двумя вещами. Первая: лес заготовлен, а в системе его нет, продать официально нельзя. Вторая: объёмы когда-то внесли неверно, остатки не сходятся, и отгрузка встала.&lt;br&gt;&lt;br&gt;Закрываем и то и другое. Оформляем происхождение через договор, вносим партию в ФГИС ЛК, правим расхождения по остаткам, дальше выписываем сопроводительные документы на каждую машину.&lt;br&gt;&lt;br&gt;Работаем по всей стране удалённо, нужен только ваш объём и понимание, откуда он взялся.&lt;br&gt;&lt;br&gt;Ель пиловочник, баланс, сосна, кругляк, Республика Бурятия.</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -27476,7 +27476,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Костромская обл., Мантурово, ул. Советская, 25</t>
+          <t>Республика Бурятия, Заиграево, ул. Октябрьская, 4</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -27591,7 +27591,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Делаем QR код на вывоз соснового кругляка. Это тот самый электронный документ, который сейчас спрашивают на каждую машину с древесиной.&lt;br&gt;&lt;br&gt;Чаще всего к нам приходят, когда лес уже свален, покупатель найден, а бумаг на происхождение нет вообще. Оформляем их с нуля: договор купли-продажи как основание, внесение объёма в ФГИС ЛК, сопроводительный документ на рейс.&lt;br&gt;&lt;br&gt;Если остатки в системе не сходятся с фактом, приводим в порядок и это, иначе отгрузки начнут блокировать.&lt;br&gt;&lt;br&gt;Работаем удалённо, свой кабинет и электронную подпись заводить не нужно.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, ель, баланс, Псковская область.</t>
+          <t>Делаем QR код на вывоз соснового кругляка. Это тот самый электронный документ, который сейчас спрашивают на каждую машину с древесиной.&lt;br&gt;&lt;br&gt;Чаще всего к нам приходят, когда лес уже свален, покупатель найден, а бумаг на происхождение нет вообще. Оформляем их с нуля: договор купли-продажи как основание, внесение объёма в ФГИС ЛК, сопроводительный документ на рейс.&lt;br&gt;&lt;br&gt;Если остатки в системе не сходятся с фактом, приводим в порядок и это, иначе отгрузки начнут блокировать.&lt;br&gt;&lt;br&gt;Работаем удалённо, свой кабинет и электронную подпись заводить не нужно.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, ель, баланс, Забайкальский край.</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -27611,7 +27611,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Псковская обл., Себеж, ул. 7 Ноября, 2</t>
+          <t>Забайкальский край, Хилок, ул. Ленина, 9</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -27726,7 +27726,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Документы на лиственницу под отгрузку: машинами, вагонами, партиями на экспортёра.&lt;br&gt;&lt;br&gt;Когда объём идёт на станцию, покупатель смотрит не только на качество, но и на то, сходятся ли данные в системе. Если партия не проведена, отгрузка встаёт, и это дороже любых документов.&lt;br&gt;&lt;br&gt;Берём на себя всю цепочку: происхождение объёма через договор, внесение в ФГИС ЛК, ЭСД с QR на каждый рейс, сверка остатков перед отгрузкой. Работаем с ИП, ООО и с частниками.&lt;br&gt;&lt;br&gt;Напишите объём и куда идёт лес, разберём вашу ситуацию и скажем, что нужно.&lt;br&gt;&lt;br&gt;Лиственница кругляк, пиловочник, сосна, ель, Иркутская область.</t>
+          <t>Документы на лиственницу под отгрузку: машинами, вагонами, партиями на экспортёра.&lt;br&gt;&lt;br&gt;Когда объём идёт на станцию, покупатель смотрит не только на качество, но и на то, сходятся ли данные в системе. Если партия не проведена, отгрузка встаёт, и это дороже любых документов.&lt;br&gt;&lt;br&gt;Берём на себя всю цепочку: происхождение объёма через договор, внесение в ФГИС ЛК, ЭСД с QR на каждый рейс, сверка остатков перед отгрузкой. Работаем с ИП, ООО и с частниками.&lt;br&gt;&lt;br&gt;Напишите объём и куда идёт лес, разберём вашу ситуацию и скажем, что нужно.&lt;br&gt;&lt;br&gt;Лиственница кругляк, пиловочник, сосна, ель, Амурская область.</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -27746,7 +27746,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Иркутская обл., Усть-Кут, ул. Кирова, 18</t>
+          <t>Амурская обл., Тында, ул. Красная Пресня, 29</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -27861,7 +27861,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ведём документы на хвойный пиломатериал: доска, брус, оцилиндрованное бревно, погонаж.&lt;br&gt;&lt;br&gt;Покупатель из другого региона почти всегда просит показать происхождение древесины. Без этого товар смотрят, но сделку не проводят, и хороший объём зависает на площадке.&lt;br&gt;&lt;br&gt;Закрываем это полностью. Оформляем договор купли-продажи как основание, заводим объёмы в систему учёта, выдаём сопроводительный документ с QR кодом на каждую отгрузку, готовим отчётность.&lt;br&gt;&lt;br&gt;Работаем с пилорамами и перекупщиками, удалённо, по всей стране.&lt;br&gt;&lt;br&gt;Пиломатериал хвоя, доска обрезная, брус, кругляк, Калужская область.</t>
+          <t>Ведём документы на хвойный пиломатериал: доска, брус, оцилиндрованное бревно, погонаж.&lt;br&gt;&lt;br&gt;Покупатель из другого региона почти всегда просит показать происхождение древесины. Без этого товар смотрят, но сделку не проводят, и хороший объём зависает на площадке.&lt;br&gt;&lt;br&gt;Закрываем это полностью. Оформляем договор купли-продажи как основание, заводим объёмы в систему учёта, выдаём сопроводительный документ с QR кодом на каждую отгрузку, готовим отчётность.&lt;br&gt;&lt;br&gt;Работаем с пилорамами и перекупщиками, удалённо, по всей стране.&lt;br&gt;&lt;br&gt;Пиломатериал хвоя, доска обрезная, брус, кругляк, Ульяновская область.</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -27881,7 +27881,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Калужская обл., Людиново, ул. Ленина, 20</t>
+          <t>Ульяновская обл., Инза, ул. Заводская, 1</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -27996,7 +27996,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Лес, выросший на пашне или в лесополосе, по документам такой же, как из делянки. Оформляем его с нуля.&lt;br&gt;&lt;br&gt;Собственники земли часто узнают об этом уже после того, как спилили: покупатель просит бумаги, а бумаг нет, и продать несколько сотен кубов не получается.&lt;br&gt;&lt;br&gt;Мы проводим объём через договор купли-продажи, заносим в ФГИС ЛК, ставим на баланс и дальше выдаём сопроводительные документы на вывоз. В сложных случаях помогаем разобраться с назначением участка и с тем, как это правильно показать.&lt;br&gt;&lt;br&gt;Работаем удалённо, приезжать не нужно. Напишите породу и примерный объём.&lt;br&gt;&lt;br&gt;Сосна кругляк, берёза, ель, лес с сельхозземель, Новгородская область.</t>
+          <t>Лес, выросший на пашне или в лесополосе, по документам такой же, как из делянки. Оформляем его с нуля.&lt;br&gt;&lt;br&gt;Собственники земли часто узнают об этом уже после того, как спилили: покупатель просит бумаги, а бумаг нет, и продать несколько сотен кубов не получается.&lt;br&gt;&lt;br&gt;Мы проводим объём через договор купли-продажи, заносим в ФГИС ЛК, ставим на баланс и дальше выдаём сопроводительные документы на вывоз. В сложных случаях помогаем разобраться с назначением участка и с тем, как это правильно показать.&lt;br&gt;&lt;br&gt;Работаем удалённо, приезжать не нужно. Напишите породу и примерный объём.&lt;br&gt;&lt;br&gt;Сосна кругляк, берёза, ель, лес с сельхозземель, Пензенская область.</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -28016,7 +28016,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Новгородская обл., Чудово, ул. Некрасова, 24</t>
+          <t>Пензенская обл., Кузнецк, ул. Ленина, 245</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -28131,7 +28131,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ставим на учёт осиновый баланс и делаем документы на вывозку.&lt;br&gt;&lt;br&gt;Осину берут плитные комбинаты, но без бумаг на происхождение партию на приёмке развернут. Отдельная история, когда лес пилили на своей земле или на расчистке, в системе такого объёма нет вообще.&lt;br&gt;&lt;br&gt;Мы это закрываем: заводим объём, оформляем договор купли-продажи как основание, дальше на каждый рейс выдаём ЭСД с QR кодом. Отчёт за период тоже готовим, если он с вас спросят.&lt;br&gt;&lt;br&gt;Объём любой, от одной машины до постоянного потока. Пишите, что и куда везёте, посчитаем сроки.&lt;br&gt;&lt;br&gt;Осина баланс, дрова, кругляк, ольха и берёза, Кировская область.</t>
+          <t>Ставим на учёт осиновый баланс и делаем документы на вывозку.&lt;br&gt;&lt;br&gt;Осину берут плитные комбинаты, но без бумаг на происхождение партию на приёмке развернут. Отдельная история, когда лес пилили на своей земле или на расчистке, в системе такого объёма нет вообще.&lt;br&gt;&lt;br&gt;Мы это закрываем: заводим объём, оформляем договор купли-продажи как основание, дальше на каждый рейс выдаём ЭСД с QR кодом. Отчёт за период тоже готовим, если он с вас спросят.&lt;br&gt;&lt;br&gt;Объём любой, от одной машины до постоянного потока. Пишите, что и куда везёте, посчитаем сроки.&lt;br&gt;&lt;br&gt;Осина баланс, дрова, кругляк, ольха и берёза, Республика Хакасия.</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -28151,7 +28151,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Кировская обл., Яранск, ул. Кирова, 10</t>
+          <t>Республика Хакасия, Саяногорск, Советский мкр, 1</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -28266,7 +28266,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Делаем QR код на машину с пиломатериалом. Доска, брус, брусок, тарная дощечка.&lt;br&gt;&lt;br&gt;Вопрос, который задают чаще всего: нужен ли документ на доску, если это уже не круглый лес. Нужен. Переработка не снимает учёт, и на посту это проверяют так же.&lt;br&gt;&lt;br&gt;Оформляем быстро. Вы даёте объём, породу и маршрут, мы вносим данные и отдаём готовый ЭСД. Если объём не заведён в системе, сначала проводим происхождение через договор, это тоже наша работа.&lt;br&gt;&lt;br&gt;Пилорамам, которые отгружают регулярно, считаем помесячно, так выходит дешевле.&lt;br&gt;&lt;br&gt;Пиломатериал хвоя, доска обрезная, брус, кругляк, Вологодская область.</t>
+          <t>Делаем QR код на машину с пиломатериалом. Доска, брус, брусок, тарная дощечка.&lt;br&gt;&lt;br&gt;Вопрос, который задают чаще всего: нужен ли документ на доску, если это уже не круглый лес. Нужен. Переработка не снимает учёт, и на посту это проверяют так же.&lt;br&gt;&lt;br&gt;Оформляем быстро. Вы даёте объём, породу и маршрут, мы вносим данные и отдаём готовый ЭСД. Если объём не заведён в системе, сначала проводим происхождение через договор, это тоже наша работа.&lt;br&gt;&lt;br&gt;Пилорамам, которые отгружают регулярно, считаем помесячно, так выходит дешевле.&lt;br&gt;&lt;br&gt;Пиломатериал хвоя, доска обрезная, брус, кругляк, Республика Тыва.</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -28286,7 +28286,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Вологодская обл., Тотьма, ул. Ленина, 44</t>
+          <t>Республика Тыва, Кызыл, ул. Ленина, 32</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -28401,7 +28401,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Дрова тоже древесина, и учёт для них такой же, как для делового леса. Оформляем документы тем, кто продаёт дрова машинами.&lt;br&gt;&lt;br&gt;Частника с одной машиной для себя это не касается, а вот когда возишь на продажу регулярно, нужен сопроводительный документ на рейс. Особенно если покупатель юрлицо и ему нужно провести покупку по бухгалтерии.&lt;br&gt;&lt;br&gt;Делаем полный круг: происхождение объёма, внесение в ФГИС ЛК, ЭСД с QR на каждую отгрузку, отчётность за период.&lt;br&gt;&lt;br&gt;Напишите, сколько машин в месяц возите, подберём вариант по цене.&lt;br&gt;&lt;br&gt;Дрова колотые берёза и осина, баланс, горбыль, Нижегородская область.</t>
+          <t>Дрова тоже древесина, и учёт для них такой же, как для делового леса. Оформляем документы тем, кто продаёт дрова машинами.&lt;br&gt;&lt;br&gt;Частника с одной машиной для себя это не касается, а вот когда возишь на продажу регулярно, нужен сопроводительный документ на рейс. Особенно если покупатель юрлицо и ему нужно провести покупку по бухгалтерии.&lt;br&gt;&lt;br&gt;Делаем полный круг: происхождение объёма, внесение в ФГИС ЛК, ЭСД с QR на каждую отгрузку, отчётность за период.&lt;br&gt;&lt;br&gt;Напишите, сколько машин в месяц возите, подберём вариант по цене.&lt;br&gt;&lt;br&gt;Дрова колотые берёза и осина, баланс, горбыль, Курская область.</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -28421,7 +28421,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Нижегородская обл., Ветлуга, ул. Ленина, 6</t>
+          <t>Курская обл., Льгов, Красная площадь, 13</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -32721,7 +32721,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Республика Карелия, Медвежьегорск, ул. Кирова, 7</t>
+          <t>Липецкая обл., Елец, ул. Коммунаров, 14</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -32851,7 +32851,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Рязанская обл., Спас-Клепики, ул. Просвещения, 64</t>
+          <t>Республика Алтай, Горно-Алтайск, пр-т Коммунистический, 18</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -4648,7 +4648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE32"/>
+  <dimension ref="A1:AE35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="26"/>
@@ -8833,6 +8833,396 @@
       <c r="AE32" t="inlineStr">
         <is>
           <t>2026-10-20T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>5135248935</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_04_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_10_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_10_3.jpg</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>240</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Документы на лес с полей и лесополос</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Оформляем документы на древесину, которую спилили не в делянке, а на своём поле, на пастбище или в лесополосе вдоль дороги.&lt;br&gt;&lt;br&gt;Собственники земли обычно узнают об учёте уже после того, как расчистили участок. Лес лежит, покупатель есть, а провести сделку нельзя: в государственной системе этого объёма не существует.&lt;br&gt;&lt;br&gt;Мы делаем так, чтобы он там появился законно. Оформляем происхождение партии через договор купли-продажи со своей стороны, заносим объём в ФГИС ЛК, ставим его вам на баланс. Дальше на каждую машину идёт сопроводительный документ с QR кодом, а за период сдаётся отчётность.&lt;br&gt;&lt;br&gt;Работаем удалённо по всей стране, свой кабинет в системе и электронную подпись заводить не нужно.&lt;br&gt;&lt;br&gt;Напишите породу, примерный объём и откуда лес, разберём ситуацию бесплатно.</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Белгородская обл., Белгород, Гражданский пр-т, 38</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>2026-10-22T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>2026-09-22T09:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>2026-10-22T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>6664047944</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_08_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_14_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_14_3.jpg</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>1100</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Оформим происхождение древесины</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Главный вопрос к любой партии леса звучит одинаково: откуда она взялась. Если ответа по документам нет, дальше не двигается ничего.&lt;br&gt;&lt;br&gt;Закрываем именно это. Оформляем происхождение объёма договором купли-продажи через своё предприятие, заносим партию в ФГИС ЛК и ставим её на ваш баланс. После этого древесину можно официально продавать, возить и показывать покупателю.&lt;br&gt;&lt;br&gt;В работу входит и то, что обычно откладывают: сопроводительные документы с QR кодом на каждый рейс, лесная декларация, отчёт за период, разбор расхождений по остаткам.&lt;br&gt;&lt;br&gt;Подходит хозяйствам после расчистки участков, ИП с пилорамой, перекупщикам и тем, кто берёт лес у населения.&lt;br&gt;&lt;br&gt;Всё удалённо, приезжать никуда не надо. Напишите, что есть на руках.</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Ставропольский край, Ставрополь, ул. Ленина, 293</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>2026-09-22T13:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3288260852</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/03/03_01.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_17_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_17_3.jpg</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>2200</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Лес без документов, оформим учёт</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Древесина в наличии, а по бумагам её нет. Приводим такой объём в порядок, чтобы его можно было законно продать и вывезти.&lt;br&gt;&lt;br&gt;Типичные истории: спилили при расчистке участка, купили у населения без оформления, взяли партию у знакомых и остались без документов. В государственной системе учёта такой древесины не существует, и любая проверка это видит сразу.&lt;br&gt;&lt;br&gt;Порядок работы у нас такой. Разбираем, что есть на руках. Оформляем происхождение объёма через договор купли-продажи. Заносим партию в ФГИС ЛК и ставим на баланс. Дальше выдаём сопроводительные документы с QR кодом на рейсы и закрываем отчётность за период.&lt;br&gt;&lt;br&gt;Всё делается удалённо, свой кабинет и электронная подпись не нужны.&lt;br&gt;&lt;br&gt;Напишите объём и породу, посмотрим и ответим по срокам.</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Республика Крым, Симферополь, ул. Севастопольская, 22</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>2026-10-22T14:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>2026-09-22T17:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>2026-10-22T14:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -29906,7 +30296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD24"/>
+  <dimension ref="A1:AD26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="21"/>
@@ -32932,6 +33322,266 @@
       <c r="AD24" t="inlineStr">
         <is>
           <t>2026-10-19T04:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>7486650874</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/1481923475/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_15_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_15_3.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>740</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ЭСД и QR код на вывоз древесины</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Делаем электронный сопроводительный документ на рейс с древесиной. Тот самый, с QR кодом, который проверяют на дороге.&lt;br&gt;&lt;br&gt;Нужен на любую машину с лесом, хоть с деловым пиловочником, хоть с дровами на продажу. Оформляем за пятнадцать минут после того, как вы пришлёте породу, объём, номер машины и маршрут.&lt;br&gt;&lt;br&gt;Если объёма нет в системе учёта, сначала проводим происхождение через договор купли-продажи, ставим партию на баланс, и только потом выписываем документ. Без этого шага ЭСД делать не из чего.&lt;br&gt;&lt;br&gt;Кто возит регулярно, работает на сопровождении: пишете машину, в ответ получаете готовый документ, без переписки на полдня.&lt;br&gt;&lt;br&gt;Берёза, осина, сосна, ель, порода любая. Пишите объёмы.</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Саратовская обл., Балашов, ул. Советская, 178</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>У себя</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>2026-10-22T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2026-09-22T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>2026-10-22T08:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>6348846298</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_20_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_16_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_16_3.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>1700</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Документы ФГИС ЛК на древесину</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Ведём документацию по древесине в ФГИС ЛК за тех, кому некогда в этом разбираться.&lt;br&gt;&lt;br&gt;Что берём на себя: внесение объёмов и сделок, оформление происхождения через договор купли-продажи, сопроводительные документы с QR кодом на отгрузки, декларация, отчёт 1-ИЛ, сверка и правка остатков.&lt;br&gt;&lt;br&gt;Чаще всего приходят в двух случаях. Либо древесина есть, а в системе её нет, и продать законно не получается. Либо в кабинете накопились ошибки, объёмы не сходятся, и из-за этого встают отгрузки.&lt;br&gt;&lt;br&gt;Работаем с бук, дуб, граб, хвоя, порода не принципиальна. Удалённо, по всей стране, с физлицами, ИП и организациями.&lt;br&gt;&lt;br&gt;Опишите свою ситуацию, скажем сразу, что нужно и сколько это займёт.</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Республика Адыгея, Майкоп, ул. Краснооктябрьская, 20</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>У себя</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>2026-10-22T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>2026-10-22T12:00:00+03:00</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -9142,7 +9142,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Республика Крым, Симферополь, ул. Севастопольская, 22</t>
+          <t>Карачаево-Черкесская Республика, Черкесск, ул. Ленина, 56</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -4648,7 +4648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE35"/>
+  <dimension ref="A1:AE37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="26"/>
@@ -9223,6 +9223,266 @@
       <c r="AE35" t="inlineStr">
         <is>
           <t>2026-10-22T14:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>9007848965</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_10_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_s05.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_s10.jpg</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>320</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Лесная декларация и отчёт 1-ИЛ</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Берём на себя отчётность по древесине: лесную декларацию, годовой отчёт об использовании лесов, складской учёт и движение остатков.&lt;br&gt;&lt;br&gt;Это та часть работы, которую откладывают до последнего, а потом ловят штрафы и заблокированные отгрузки. Сроки жёсткие, форма неудобная, и ошибиться в ней проще, чем заполнить правильно.&lt;br&gt;&lt;br&gt;Мы собираем отчётность по вашим сделкам за период, сверяем то, что лежит по факту, с тем, что показано в системе, и подаём в срок. Если по остаткам есть расхождения, сначала приводим их в порядок, иначе отчёт уйдёт с ошибкой.&lt;br&gt;&lt;br&gt;Работаем удалённо по всей стране, с ИП, организациями и частниками. Свой кабинет и электронную подпись заводить не нужно.&lt;br&gt;&lt;br&gt;Напишите, за какой период нужна отчётность и что уже подано.</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Республика Дагестан, Махачкала, пр-т Расула Гамзатова, 39</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1923554209</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_13_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_p01.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_p06.jpg</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>QR код на перевозку леса за 15 минут</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Машина загружена, водитель на телефоне, а сопроводительного документа нет. Делаем его быстро, обычно за пятнадцать минут.&lt;br&gt;&lt;br&gt;Нужен на любую перевозку древесины: кругляк, дрова, доска, брус. Документ настоящий, с QR кодом, виден в государственной системе, на посту и на весовой вопросов не вызывает.&lt;br&gt;&lt;br&gt;Если объёма в системе нет, сначала заводим его туда: оформляем происхождение через договор купли-продажи и ставим партию на баланс. Работает и со старой заготовкой, которая лежит с прошлого сезона.&lt;br&gt;&lt;br&gt;От вас нужны порода, объём, номер машины и маршрут. Пишите, отвечаем быстро, оформляем удалённо.&lt;br&gt;&lt;br&gt;Для тех, кто возит регулярно, есть помесячное сопровождение.</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Республика Северная Осетия, Владикавказ, пр-т Мира, 25</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>2026-09-23T15:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -30296,7 +30556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD26"/>
+  <dimension ref="A1:AD28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="21"/>
@@ -33582,6 +33842,266 @@
       <c r="AD26" t="inlineStr">
         <is>
           <t>2026-10-22T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>4465212740</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_15_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_d06.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_p04.jpg</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>850</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Ведение ФГИС ЛК под ключ</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Ведём кабинет в системе учёта древесины целиком, помесячно. Вы занимаетесь лесом, мы бумагами.&lt;br&gt;&lt;br&gt;Что входит: внесение сделок и объёмов, оформление происхождения через договор купли-продажи, сопроводительные документы на каждую машину, сверка остатков, декларация и отчётность в срок.&lt;br&gt;&lt;br&gt;Отдельно разбираем ситуации, когда учёт уже запутан. Объёмы задвоены, списано меньше, чем вывезено, приняты партии без основания. Пересобираем данные и приводим их к тому, что есть на самом деле.&lt;br&gt;&lt;br&gt;Формат подходит тем, у кого отгрузки идут постоянно и каждый раз всё делается в последний момент. По деньгам выходит дешевле, чем разовое оформление на каждый рейс.&lt;br&gt;&lt;br&gt;Напишите, сколько машин в месяц отгружаете, посчитаем.</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Кабардино-Балкарская Республика, Нальчик, пр-т Ленина, 27</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>У себя</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>2026-10-23T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2026-09-23T13:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>2026-10-23T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>5375341404</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_14_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_12_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_12_3.jpg</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>2700</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Документы на дрова и деловой лес</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Оформляем документы и на дровяную древесину, и на деловой лес. Разницы в учёте между ними нет, спрашивают одинаково.&lt;br&gt;&lt;br&gt;Чаще всего приходят те, кто продаёт дрова машинами населению и организациям. Пока возишь по знакомым, вопросов нет, а как только покупателю нужно провести покупку по бухгалтерии, сразу требуется происхождение и сопроводительный документ.&lt;br&gt;&lt;br&gt;Делаем всё с нуля: договор купли-продажи как основание на объём, внесение партии в систему учёта, документ с QR кодом на каждый рейс, отчётность за период.&lt;br&gt;&lt;br&gt;Порода значения не имеет, работаем с бук, дуб, граб, ольха, хвоя. Удалённо, по всей стране.&lt;br&gt;&lt;br&gt;Напишите объём и куда возите, скажем по срокам и цене.</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Чеченская Республика, Грозный, пр-т Владимира Путина, 12</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>У себя</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>2026-10-23T14:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>2026-09-23T17:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>2026-10-23T14:00:00+03:00</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -4648,7 +4648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE37"/>
+  <dimension ref="A1:AE39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="26"/>
@@ -9483,6 +9483,266 @@
       <c r="AE37" t="inlineStr">
         <is>
           <t>2026-10-23T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>5968561661</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_03_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_p07.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/field_windbreak.jpg</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>390</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Документы на древесину под отгрузку</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Готовим документы на древесину, которая идёт под отгрузку: покупателю, на переработку, на склад в порту.&lt;br&gt;&lt;br&gt;У крупного получателя разговор короткий. Нет подтверждённого происхождения и данных в системе учёта, значит партию не принимают, и неважно, какого она качества. Отдельная беда, когда объём внесён неточно и цифры не сходятся с фактом на площадке.&lt;br&gt;&lt;br&gt;Что делаем. Оформляем происхождение через договор купли-продажи, заводим партию в ФГИС ЛК, ставим на баланс, сводим остатки. На каждый рейс или вагон готовим сопроводительный документ с QR кодом. Отчётность за период тоже наша.&lt;br&gt;&lt;br&gt;Работаем удалённо по всей стране, с ИП, организациями и частниками. Кабинет и подпись заводить не нужно.&lt;br&gt;&lt;br&gt;Напишите породу, объём и куда идёт древесина, ответим по срокам.</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Сахалинская обл., Южно-Сахалинск, пр-т Мира, 107</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>2026-10-24T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>2026-09-24T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>2026-10-24T02:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>6105817105</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/bg08.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_05_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/n05_1.jpg</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>3200</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Оформление древесины в ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Занимаемся оформлением древесины в государственной системе учёта за тех, у кого на это нет ни времени, ни желания разбираться.&lt;br&gt;&lt;br&gt;Обычные ситуации: лес заготовлен и лежит, а по бумагам его нет. Купили партию у частника и не понимаете, как её провести. Нужен документ на перевозку, а объёма в системе не числится. Накопились ошибки в кабинете, и отгрузки из-за этого встали.&lt;br&gt;&lt;br&gt;Разбираем каждую по порядку. Оформляем происхождение через договор купли-продажи, заносим объёмы, правим остатки, готовим сопроводительные документы с QR кодом, сдаём отчётность за период.&lt;br&gt;&lt;br&gt;Всё удалённо, приезжать никуда не надо, свой кабинет и электронная подпись не требуются.&lt;br&gt;&lt;br&gt;Опишите ситуацию своими словами, посмотрим и скажем, что реально сделать.</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Магаданская обл., Магадан, пр-т Ленина, 14</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2026-10-24T04:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>2026-09-24T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>2026-10-24T04:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -30556,7 +30816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD28"/>
+  <dimension ref="A1:AD29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="21"/>
@@ -34102,6 +34362,136 @@
       <c r="AD28" t="inlineStr">
         <is>
           <t>2026-10-23T14:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1068329421</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_14_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/ig_d07.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/nb_tractor_field.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>1600</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Учёт древесины и ЭСД на рейс</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Ставим древесину на учёт и выписываем сопроводительные документы на перевозку.&lt;br&gt;&lt;br&gt;Две вещи, которые приходится делать всем, кто работает с лесом. Первая: объём должен быть в государственной системе, иначе его юридически не существует. Вторая: на каждую машину нужен электронный документ с QR кодом, без него рейс лучше не начинать.&lt;br&gt;&lt;br&gt;Берём обе на себя. Происхождение оформляем договором купли-продажи со своей стороны, партию заводим в ФГИС ЛК, дальше выдаём документы на рейсы по мере отгрузок. Обычно документ готов за пятнадцать минут после ваших данных.&lt;br&gt;&lt;br&gt;Работает и с той заготовкой, что лежит с прошлого сезона. Срок давности тут роли не играет.&lt;br&gt;&lt;br&gt;Напишите, что и куда возите, посчитаем по вашему объёму.</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Камчатский край, Петропавловск-Камчатский, пр-т Карла Маркса, 29</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>У себя</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>2026-10-24T03:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>2026-10-24T03:00:00+03:00</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -4648,7 +4648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE39"/>
+  <dimension ref="A1:AE41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="26"/>
@@ -9743,6 +9743,266 @@
       <c r="AE39" t="inlineStr">
         <is>
           <t>2026-10-24T04:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>6144959812</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/3819625066/1.png|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260924/ig24_uchastok.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/05/05_02.jpg</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>450</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Документы на лес с вашего участка</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Спилили лес на своей земле, а продать не выходит: у покупателя первый вопрос про документы. Делаем эти документы.&lt;br&gt;&lt;br&gt;По закону неважно, где выросла древесина, в делянке или у вас на поле. Учёт один и тот же. Пока объёма нет в государственной системе, его как бы не существует, и любая сделка повисает.&lt;br&gt;&lt;br&gt;Как работаем. Смотрим, что у вас срублено и сколько. Оформляем происхождение партии договором купли-продажи со своей стороны. Заводим объём в ФГИС ЛК и ставим вам на баланс. Дальше на каждую машину выдаём сопроводительный документ с QR кодом.&lt;br&gt;&lt;br&gt;После этого лес можно спокойно продавать и вывозить, а вопросы на посту закрываются одним документом.&lt;br&gt;&lt;br&gt;Свой кабинет в системе и электронную подпись заводить не нужно, всё делаем со своей стороны. Работаем удалённо, приезжать никуда не надо.&lt;br&gt;&lt;br&gt;Напишите породу и примерный объём, посмотрим вашу ситуацию бесплатно.</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Псковская обл., Порхов, пр-т Ленина, 14</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>2026-09-24T11:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2934002809</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/14/14_01.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260924/ig24_kabinet.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/03/03_02.jpg</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>1950</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Проверим кабинет ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Цифры в кабинете не сходятся с тем, что реально лежит на складе. Разбираем и приводим в порядок.&lt;br&gt;&lt;br&gt;Типичная картина: объёмы задвоены, списано меньше, чем вывезено, приняты партии без основания, часть сделок висит незакрытой. Пока так, отгрузки блокируются, а отчётность уходит с ошибками.&lt;br&gt;&lt;br&gt;Что делаем. Считаем факт по вашим данным, поднимаем историю операций в системе, находим, где именно разошлось, и правим. Там, где на объём нужно основание, оформляем договор купли-продажи со своей стороны.&lt;br&gt;&lt;br&gt;После сверки кабинет чистый: остатки соответствуют складу, отгрузки проходят, отчёт за период сдаётся без вопросов.&lt;br&gt;&lt;br&gt;Работаем удалённо, с ИП, организациями и частниками, по всей стране. Доступ к вашему кабинету не требуем, работаем по выгрузкам и документам.&lt;br&gt;&lt;br&gt;Опишите, что происходит, скажем, сколько времени займёт разбор.</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Брянская обл., Жуковка, ул. Октябрьская, 3</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>2026-09-24T15:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -30816,7 +31076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD29"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="21"/>
@@ -34492,6 +34752,266 @@
       <c r="AD29" t="inlineStr">
         <is>
           <t>2026-10-24T03:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>8255013334</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_11_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260924/ig24_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/08/08_02.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1250</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ЭСД на перевозку леса за час</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Машина загружена, водитель ждёт, а документа на рейс нет. Выдаём его в течение часа, обычно быстрее.&lt;br&gt;&lt;br&gt;Речь про электронный сопроводительный документ с QR кодом. Он нужен на каждую перевозку древесины, и на кругляк, и на дрова, и на доску. Документ настоящий, виден в системе, на посту и на весовой проверяется за минуту.&lt;br&gt;&lt;br&gt;От вас нужно немного: порода, объём, номер машины, откуда и куда едет. Всё остальное на нашей стороне.&lt;br&gt;&lt;br&gt;Если объёма в системе ещё нет, сначала заводим его через договор купли-продажи и ставим на баланс, иначе документ выписывать не из чего. Это делается в тот же день.&lt;br&gt;&lt;br&gt;Кто возит регулярно, работает на сопровождении: пишете машину, получаете готовый документ в ответ, без переписки на полдня.&lt;br&gt;&lt;br&gt;Пишите в любое время, отвечаем быстро.</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Смоленская обл., Рославль, ул. Советская, 66</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>У себя</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>2026-10-24T10:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2026-09-24T13:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>2026-10-24T10:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>8295382711</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_16_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260924/ig24_tender.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/01/01_02.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>4200</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Документы на лес для тендера</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Заказчик требует подтвердить происхождение древесины, иначе контракт не подпишут. Собираем полный пакет.&lt;br&gt;&lt;br&gt;С юрлицами и по госзаказу проверка жёстче, чем на обычной продаже. Смотрят договор на партию, наличие объёма в государственной системе, сопроводительные документы и то, чтобы данные сходились между собой. Одна нестыковка, и поставку разворачивают.&lt;br&gt;&lt;br&gt;Мы закрываем это целиком. Оцениваем объём, оформляем договор купли-продажи как основание, заводим партию в ФГИС ЛК, готовим сопроводительные документы на отгрузки и собираем комплект, который спокойно проходит у юристов и бухгалтерии заказчика.&lt;br&gt;&lt;br&gt;Работаем и тогда, когда лес уже заготовлен, и тогда, когда контракт только на подходе и надо понять, что потребуется.&lt;br&gt;&lt;br&gt;Напишите, что за поставка и какой объём, разберём требования заказчика и скажем по срокам.</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Калужская обл., Козельск, ул. Большая Советская, 55</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>У себя</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>2026-10-24T14:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2026-09-24T17:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>2026-10-24T14:30:00+03:00</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -9787,7 +9787,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Спилили лес на своей земле, а продать не выходит: у покупателя первый вопрос про документы. Делаем эти документы.&lt;br&gt;&lt;br&gt;По закону неважно, где выросла древесина, в делянке или у вас на поле. Учёт один и тот же. Пока объёма нет в государственной системе, его как бы не существует, и любая сделка повисает.&lt;br&gt;&lt;br&gt;Как работаем. Смотрим, что у вас срублено и сколько. Оформляем происхождение партии договором купли-продажи со своей стороны. Заводим объём в ФГИС ЛК и ставим вам на баланс. Дальше на каждую машину выдаём сопроводительный документ с QR кодом.&lt;br&gt;&lt;br&gt;После этого лес можно спокойно продавать и вывозить, а вопросы на посту закрываются одним документом.&lt;br&gt;&lt;br&gt;Свой кабинет в системе и электронную подпись заводить не нужно, всё делаем со своей стороны. Работаем удалённо, приезжать никуда не надо.&lt;br&gt;&lt;br&gt;Напишите породу и примерный объём, посмотрим вашу ситуацию бесплатно.</t>
+          <t>Спилили лес у себя на участке, а продать не получается: покупатель просит документы. Делаю эти документы.&lt;br&gt;&lt;br&gt;По закону неважно, где вырос лес, в делянке или у вас на поле. Учёт одинаковый. Пока объёма нет в государственной системе, его как бы не существует, и сделка стоит.&lt;br&gt;&lt;br&gt;Порядок такой. Смотрим, что срублено и сколько кубов. Оформляю договор купли-продажи на партию. Завожу объём в ФГИС ЛК и ставлю вам на баланс. Дальше выдаю документ с QR кодом на каждую машину.&lt;br&gt;&lt;br&gt;После этого лес можно спокойно продавать и вывозить.&lt;br&gt;&lt;br&gt;Свой кабинет и электронная подпись вам не нужны, всё делаю со своей стороны, удалённо.&lt;br&gt;&lt;br&gt;Напишите породу и примерный объём, посмотрю вашу ситуацию бесплатно.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -9917,7 +9917,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Цифры в кабинете не сходятся с тем, что реально лежит на складе. Разбираем и приводим в порядок.&lt;br&gt;&lt;br&gt;Типичная картина: объёмы задвоены, списано меньше, чем вывезено, приняты партии без основания, часть сделок висит незакрытой. Пока так, отгрузки блокируются, а отчётность уходит с ошибками.&lt;br&gt;&lt;br&gt;Что делаем. Считаем факт по вашим данным, поднимаем историю операций в системе, находим, где именно разошлось, и правим. Там, где на объём нужно основание, оформляем договор купли-продажи со своей стороны.&lt;br&gt;&lt;br&gt;После сверки кабинет чистый: остатки соответствуют складу, отгрузки проходят, отчёт за период сдаётся без вопросов.&lt;br&gt;&lt;br&gt;Работаем удалённо, с ИП, организациями и частниками, по всей стране. Доступ к вашему кабинету не требуем, работаем по выгрузкам и документам.&lt;br&gt;&lt;br&gt;Опишите, что происходит, скажем, сколько времени займёт разбор.</t>
+          <t>Цифры в кабинете ФГИС не сходятся с тем, что реально лежит на складе. Разбираю и привожу в порядок.&lt;br&gt;&lt;br&gt;Обычно причина простая: объём задвоили, списали меньше, чем увезли, приняли партию без основания, часть сделок осталась незакрытой. Пока так, отгрузки блокируются, а отчёт уходит с ошибкой.&lt;br&gt;&lt;br&gt;Что делаю. Считаю факт по вашим данным, поднимаю историю операций, нахожу, где именно разошлось, и правлю. Где на объём нужно основание, оформляю договор купли-продажи со своей стороны.&lt;br&gt;&lt;br&gt;После сверки остатки совпадают со складом, отгрузки идут, отчёт за период сдаётся без вопросов.&lt;br&gt;&lt;br&gt;Доступ в ваш кабинет не прошу, работаю по выгрузкам и документам. Удалённо, по всей стране.&lt;br&gt;&lt;br&gt;Напишите, что происходит, скажу, сколько займёт разбор.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -10655,7 +10655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK139"/>
+  <dimension ref="A1:AK141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -29680,6 +29680,276 @@
       <c r="AK139" t="inlineStr">
         <is>
           <t>2026-10-19T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>8255013334</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Берёза дрова и баланс(эсд на рейс)</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Смоленская область, берёза дровяная и баланс с расчистки полей.&lt;br&gt;&lt;br&gt;Документы на такой лес делаю я. Сам лес не вожу, занимаюсь бумагами.&lt;br&gt;&lt;br&gt;На каждую машину нужен ЭСД, это электронная накладная из ФГИС ЛК с QR кодом. Без неё на первом же посту будут вопросы, откуда древесина и чья она.&lt;br&gt;&lt;br&gt;Работает так. Вы пишете породу, сколько кубов, номер машины и куда едет. Я оформляю происхождение через договор купли-продажи, завожу объём в систему и отдаю готовый документ. Обычно за час, часто быстрее.&lt;br&gt;&lt;br&gt;Кабинет в ФГИС и электронную подпись заводить не надо, всё с моей стороны. Кто возит постоянно, беру на сопровождение помесячно, так дешевле.&lt;br&gt;&lt;br&gt;Берёза дрова, баланс, кругляк, осина, ольха, Смоленская область.</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n07/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260924/ig24_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/08/08_02.jpg</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Смоленская обл., Рославль, ул. Советская, 66</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>1250</v>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>2026-10-24T10:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>2026-09-24T13:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>2026-10-24T10:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>8295382711</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Кругляк сосна пиловочник(документы фгис)</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Калужская область, сосновый пиловочник и кругляк. Помогаю с документами на уже заготовленный лес.&lt;br&gt;&lt;br&gt;Ситуация обычная: древесина лежит, покупатель есть, а в системе её нет. Продать в таком виде нельзя, у любого нормального покупателя первый вопрос про происхождение.&lt;br&gt;&lt;br&gt;Что делаю. Оформляю договор купли-продажи как основание на объём, завожу партию в ФГИС ЛК и ставлю вам на баланс. Дальше на каждый рейс выписываю сопроводительный документ с QR кодом. Отчётность за период тоже закрываю.&lt;br&gt;&lt;br&gt;Подходит и тем, кто расчищал поле или лесополосу, и тем, кто купил лес у населения и не знает, как его провести.&lt;br&gt;&lt;br&gt;Всё удалённо, ехать никуда не надо. Напишите объём и породу, разберём бесплатно.&lt;br&gt;&lt;br&gt;Сосна пиловочник, кругляк, баланс, ель, берёза, Калужская область.</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_16_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260924/ig24_tender.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/01/01_02.jpg</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Калужская обл., Козельск, ул. Большая Советская, 55</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>4200</v>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>2026-10-24T14:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>2026-09-24T17:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>2026-10-24T14:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -31076,7 +31346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD31"/>
+  <dimension ref="A1:AD29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="21"/>
@@ -34752,266 +35022,6 @@
       <c r="AD29" t="inlineStr">
         <is>
           <t>2026-10-24T03:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>8255013334</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>79824510018</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_11_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260924/ig24_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/08/08_02.jpg</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Предложение услуг</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>1250</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>ЭСД на перевозку леса за час</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Машина загружена, водитель ждёт, а документа на рейс нет. Выдаём его в течение часа, обычно быстрее.&lt;br&gt;&lt;br&gt;Речь про электронный сопроводительный документ с QR кодом. Он нужен на каждую перевозку древесины, и на кругляк, и на дрова, и на доску. Документ настоящий, виден в системе, на посту и на весовой проверяется за минуту.&lt;br&gt;&lt;br&gt;От вас нужно немного: порода, объём, номер машины, откуда и куда едет. Всё остальное на нашей стороне.&lt;br&gt;&lt;br&gt;Если объёма в системе ещё нет, сначала заводим его через договор купли-продажи и ставим на баланс, иначе документ выписывать не из чего. Это делается в тот же день.&lt;br&gt;&lt;br&gt;Кто возит регулярно, работает на сопровождении: пишете машину, получаете готовый документ в ответ, без переписки на полдня.&lt;br&gt;&lt;br&gt;Пишите в любое время, отвечаем быстро.</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Смоленская обл., Рославль, ул. Советская, 66</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Услуги посредников</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Консультации</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Другое</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>4–7 лет</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>У себя</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>belpool.1@gmail.com</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>ФГИС ЛК объемы</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>2026-10-24T10:30:00+03:00</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>2026-09-24T13:30:00+03:00</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>2026-10-24T10:30:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>8295382711</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>79824510018</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_16_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260924/ig24_tender.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/01/01_02.jpg</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Предложение услуг</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>4200</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Документы на лес для тендера</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Заказчик требует подтвердить происхождение древесины, иначе контракт не подпишут. Собираем полный пакет.&lt;br&gt;&lt;br&gt;С юрлицами и по госзаказу проверка жёстче, чем на обычной продаже. Смотрят договор на партию, наличие объёма в государственной системе, сопроводительные документы и то, чтобы данные сходились между собой. Одна нестыковка, и поставку разворачивают.&lt;br&gt;&lt;br&gt;Мы закрываем это целиком. Оцениваем объём, оформляем договор купли-продажи как основание, заводим партию в ФГИС ЛК, готовим сопроводительные документы на отгрузки и собираем комплект, который спокойно проходит у юристов и бухгалтерии заказчика.&lt;br&gt;&lt;br&gt;Работаем и тогда, когда лес уже заготовлен, и тогда, когда контракт только на подходе и надо понять, что потребуется.&lt;br&gt;&lt;br&gt;Напишите, что за поставка и какой объём, разберём требования заказчика и скажем по срокам.</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Калужская обл., Козельск, ул. Большая Советская, 55</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Услуги посредников</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Консультации</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Другое</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>4–7 лет</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>У себя</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>belpool.1@gmail.com</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>ФГИС ЛК объемы</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>2026-10-24T14:30:00+03:00</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>2026-09-24T17:30:00+03:00</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>2026-10-24T14:30:00+03:00</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -4648,7 +4648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE41"/>
+  <dimension ref="A1:AE46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="26"/>
@@ -10003,6 +10003,656 @@
       <c r="AE41" t="inlineStr">
         <is>
           <t>2026-10-24T12:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>5534681826</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_02_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_02_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_02_3.jpg</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>280</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ЭСД и QR код на лес, ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Делаю ЭСД на перевозку леса. Это электронный сопроводительный документ с QR кодом, тот самый, который просят на дороге.&lt;br&gt;&lt;br&gt;Нужен на любую машину с древесиной: кругляк, дрова, доска, брус. Без него рейс начинать не стоит, первый же пост обернётся разговором про происхождение.&lt;br&gt;&lt;br&gt;Как это выглядит у вас. Пишете породу, сколько кубов, номер машины и маршрут. В ответ получаете готовый документ, обычно в течение часа.&lt;br&gt;&lt;br&gt;Если объёма в системе нет, сначала завожу его туда: оформляю договор купли-продажи как основание и ставлю партию на баланс. Это тоже моя работа, отдельно бегать никуда не надо.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС ЛК и электронную подпись заводить не нужно. Работаю удалённо, по всей стране.&lt;br&gt;&lt;br&gt;ЭСД, QR код на лес, ФГИС ЛК, сопроводительный документ на древесину, Псковская область.</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Псковская обл., Невель, ул. Ленина, 25</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>2026-11-01T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>2026-10-02T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>2026-11-01T08:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>4200300253</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_09_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_09_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_09_3.jpg</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>680</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Учёт древесины в ФГИС ЛК под ключ</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Веду учёт древесины в ФГИС ЛК за вас. Вы занимаетесь лесом, я бумагами.&lt;br&gt;&lt;br&gt;Что входит: вношу сделки и объёмы, оформляю происхождение договором купли-продажи, выписываю сопроводительные документы на отгрузки, свожу остатки, сдаю отчётность за период.&lt;br&gt;&lt;br&gt;Формат удобен тем, у кого машины идут регулярно и каждый раз всё делается в последний момент. Вы пишете, что отгружаете, остальное закрываю я.&lt;br&gt;&lt;br&gt;Отдельно разбираю запущенные кабинеты. Бывает, объёмы задвоены, часть сделок не закрыта, остатки не сходятся со складом. Пересобираю данные так, чтобы отгрузки перестали блокироваться.&lt;br&gt;&lt;br&gt;Доступ в ваш кабинет не прошу, работаю по выгрузкам и документам. Удалённо, по всей стране, с ИП, ООО и частниками.&lt;br&gt;&lt;br&gt;Учёт древесины, ФГИС ЛК, сопровождение, ЭСД, отчётность, Брянская область.</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Брянская обл., Унеча, ул. Октябрьская, 1</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2026-11-01T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>2026-10-02T15:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>2026-11-01T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2726578016</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_19_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_19_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_19_3.jpg</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>1150</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Документы на вывоз леса с участка</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Расчистили участок, лес лежит, а вывезти его нельзя. Делаю документы, после которых можно.&lt;br&gt;&lt;br&gt;Многие узнают об этом уже после того, как спилили. Кажется, что земля своя и вопросов быть не должно, но учёт древесины одинаковый и для делянки, и для поля, и для лесополосы вдоль дороги.&lt;br&gt;&lt;br&gt;Порядок работы такой. Смотрим объём и породу. Оформляю договор купли-продажи на партию. Завожу древесину в ФГИС ЛК и ставлю вам на баланс. Дальше выдаю сопроводительный документ с QR кодом на каждую машину.&lt;br&gt;&lt;br&gt;Подходит фермерам, собственникам участков, подрядчикам на расчистке и тем, кто берёт лес у населения.&lt;br&gt;&lt;br&gt;Всё делается удалённо, свой кабинет и электронная подпись не нужны.&lt;br&gt;&lt;br&gt;Документы на вывоз леса, расчистка участка, ФГИС ЛК, ЭСД, QR код, Рязанская область.</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Рязанская обл., Шилово, ул. Советская, 9</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>2026-11-02T04:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>2026-10-03T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>2026-11-02T04:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>3384561572</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_23_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_23_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_23_3.jpg</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>1850</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Документы на дрова и пиломатериал</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Делаю документы и на дрова, и на пиломатериал. Для учёта разницы нет, спрашивают одинаково.&lt;br&gt;&lt;br&gt;Чаще всего приходят двое. Первый возит дрова машинами на продажу, и покупателю нужно провести покупку по бухгалтерии. Второй держит пилораму, отгружает доску и брус, а у заказчика требование показать происхождение.&lt;br&gt;&lt;br&gt;Закрываю это целиком. Оформляю договор купли-продажи на объём, завожу партию в ФГИС ЛК, выписываю сопроводительные документы с QR кодом на отгрузки, сдаю отчётность за период.&lt;br&gt;&lt;br&gt;Порода значения не имеет: берёза, осина, ольха, сосна, ель. Переработка тоже не мешает, на доску документ делается так же, как на кругляк.&lt;br&gt;&lt;br&gt;Работаю удалённо, по всей стране. Напишите, что отгружаете и какой объём в месяц, посчитаю.&lt;br&gt;&lt;br&gt;Документы на дрова, пиломатериал, доска, брус, ЭСД, ФГИС ЛК, Орловская область.</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Орловская обл., Болхов, ул. Ленина, 24</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>2026-11-02T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>2026-10-03T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>2026-11-02T08:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>3310128368</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261002/green_dok_fgis.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_01_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_03_1.jpg</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>3100</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Лесная декларация и отчёт 1-ИЛ</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Беру на себя отчётность по лесу: лесную декларацию, отчёт 1-ИЛ, складской учёт и движение остатков.&lt;br&gt;&lt;br&gt;Это та часть, которую откладывают до последнего. Сроки жёсткие, форма неудобная, и ошибиться в ней проще, чем заполнить верно. А дальше идут штрафы и заблокированные отгрузки.&lt;br&gt;&lt;br&gt;Что делаю. Собираю отчётность по вашим сделкам за период, сверяю то, что лежит по факту, с тем, что показано в системе, и подаю в срок. Если остатки разошлись, сначала привожу их в порядок, иначе отчёт уйдёт с ошибкой.&lt;br&gt;&lt;br&gt;Работаю с арендаторами участков, ИП, организациями и частниками. Удалённо, по всей стране, кабинет и подпись заводить не нужно.&lt;br&gt;&lt;br&gt;Напишите, за какой период нужна отчётность и что уже подано, скажу сроки и цену.&lt;br&gt;&lt;br&gt;Лесная декларация, отчёт 1-ИЛ, отчётность ФГИС ЛК, учёт древесины, Курская область.</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Курская обл., Рыльск, ул. Ленина, 59</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>2026-11-02T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>2026-10-03T15:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>2026-11-02T12:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -31346,7 +31996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD29"/>
+  <dimension ref="A1:AD33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="21"/>
@@ -35022,6 +35672,526 @@
       <c r="AD29" t="inlineStr">
         <is>
           <t>2026-10-24T03:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>8271970671</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_06_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_06_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_06_3.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>520</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Документы на древесину, ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Древесина есть, а бумаг на неё нет. Делаю документы, чтобы лес можно было спокойно продать и вывезти.&lt;br&gt;&lt;br&gt;Самая частая история: лес заготовлен, покупатель найден, и тут выясняется, что в государственной системе этого объёма не существует. Для закона его просто нет, поэтому сделка встаёт.&lt;br&gt;&lt;br&gt;Что делаю по порядку. Смотрю, что у вас на руках. Оформляю договор купли-продажи на партию, он и становится основанием на объём. Завожу древесину в ФГИС ЛК и ставлю вам на баланс. Дальше на каждую машину выписываю сопроводительный документ с QR кодом.&lt;br&gt;&lt;br&gt;Работаю и со свежей заготовкой, и с той, что лежит с прошлого сезона. Срок тут роли не играет.&lt;br&gt;&lt;br&gt;Всё удалённо, приезжать никуда не надо. Напишите породу и объём, разберу вашу ситуацию бесплатно.&lt;br&gt;&lt;br&gt;Документы на лес, ФГИС ЛК, учёт древесины, ЭСД, Смоленская область.</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Смоленская обл., Ярцево, ул. Советская, 17</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>У себя</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>2026-11-01T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2026-10-02T13:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>2026-11-01T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1844878614</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_11_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_11_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_11_3.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>820</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Закрытие расхождений в ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>По системе один объём, по факту на площадке другой. Разбираю такие расхождения и привожу данные в порядок.&lt;br&gt;&lt;br&gt;Причины почти всегда простые. Внесли не ту породу или сортимент, задвоили партию, списали меньше, чем увезли, приняли объём без основания. Дальше ошибка тянется, а у покупателя она видна сразу, и отгрузка встаёт.&lt;br&gt;&lt;br&gt;Что делаю. Считаю факт по вашим данным, поднимаю историю операций, нахожу, где именно разошлось, и правлю. Там, где на объём нужно основание, оформляю договор купли-продажи со своей стороны.&lt;br&gt;&lt;br&gt;После разбора остатки совпадают со складом, машины едут, отчёт за период сдаётся без вопросов.&lt;br&gt;&lt;br&gt;Работаю удалённо, доступ в кабинет не требуется, достаточно выгрузок и документов.&lt;br&gt;&lt;br&gt;Расхождения ФГИС ЛК, остатки древесины, сверка объёмов, учёт леса, Калужская область.</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Калужская обл., Жиздра, ул. Володарского, 29</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>У себя</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>2026-11-02T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2026-10-03T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>2026-11-02T02:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4427075166</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_22_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_22_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_22_3.jpg</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>1450</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Сопроводительные документы на лес</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Оформляю сопроводительные документы на древесину. Один рейс, десять рейсов или поток отгрузок, работаю и так, и так.&lt;br&gt;&lt;br&gt;По каждой машине нужен электронный документ с QR кодом. Он подтверждает, что объём стоит на учёте и везёт его тот, кто имеет на это право. На весовой и на посту проверяется за минуту.&lt;br&gt;&lt;br&gt;От вас: порода, кубатура, номер машины, откуда и куда едет. От меня готовый документ, обычно в течение часа.&lt;br&gt;&lt;br&gt;Если объёма в системе нет, завожу его через договор купли-продажи, это делается в тот же день.&lt;br&gt;&lt;br&gt;Тем, кто возит постоянно, считаю помесячно. Выходит дешевле, чем оформлять каждый рейс отдельно, и не надо каждый раз писать заново.&lt;br&gt;&lt;br&gt;Сопроводительные документы, ЭСД, QR код на перевозку, ФГИС ЛК, Тамбовская область.</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Тамбовская обл., Рассказово, ул. Советская, 6</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>У себя</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>2026-11-02T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2026-10-03T09:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>2026-11-02T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>3656837736</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_17_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_01_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_01_3.jpg</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>2350</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Договор и учёт на партию леса</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Купили лес у частника или у хозяйства и не понимаете, как провести эту покупку. Оформляю такую сделку по правилам.&lt;br&gt;&lt;br&gt;Проблема в том, что продавец часто сам не стоит на учёте, а значит передать объём официально он не может. Покупатель остаётся с древесиной на руках и без основания на неё.&lt;br&gt;&lt;br&gt;Как решаю. Оформляю договор купли-продажи через своё предприятие, он становится законным основанием на партию. Завожу объём в ФГИС ЛК и ставлю его вам на баланс. Дальше вы спокойно продаёте дальше или везёте, а на каждый рейс получаете сопроводительный документ.&lt;br&gt;&lt;br&gt;Подходит перекупщикам, пилорамам и тем, кто собирает объём по несколько машин у разных людей.&lt;br&gt;&lt;br&gt;Разбор ситуации бесплатный, работаю удалённо.&lt;br&gt;&lt;br&gt;Договор на лес, происхождение древесины, учёт в ФГИС ЛК, партия леса, Липецкая область.</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Липецкая обл., Усмань, ул. Ленина, 36</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>У себя</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>2026-11-02T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>2026-10-03T13:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>2026-11-02T10:00:00+03:00</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -4648,7 +4648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE46"/>
+  <dimension ref="A1:AE43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="26"/>
@@ -10009,7 +10009,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5534681826</t>
+          <t>3384561572</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_02_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_02_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_02_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_23_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_23_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_23_3.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -10038,21 +10038,21 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>280</v>
+        <v>1850</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>ЭСД и QR код на лес, ФГИС ЛК</t>
+          <t>Документы на доску и брус, QR код</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Делаю ЭСД на перевозку леса. Это электронный сопроводительный документ с QR кодом, тот самый, который просят на дороге.&lt;br&gt;&lt;br&gt;Нужен на любую машину с древесиной: кругляк, дрова, доска, брус. Без него рейс начинать не стоит, первый же пост обернётся разговором про происхождение.&lt;br&gt;&lt;br&gt;Как это выглядит у вас. Пишете породу, сколько кубов, номер машины и маршрут. В ответ получаете готовый документ, обычно в течение часа.&lt;br&gt;&lt;br&gt;Если объёма в системе нет, сначала завожу его туда: оформляю договор купли-продажи как основание и ставлю партию на баланс. Это тоже моя работа, отдельно бегать никуда не надо.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС ЛК и электронную подпись заводить не нужно. Работаю удалённо, по всей стране.&lt;br&gt;&lt;br&gt;ЭСД, QR код на лес, ФГИС ЛК, сопроводительный документ на древесину, Псковская область.</t>
+          <t>Делаю документы и QR коды на пиломатериал: доска, брус, брусок, горбыль, тарная дощечка.&lt;br&gt;&lt;br&gt;Вопрос, который задают почти все: нужен ли документ, если лес уже распилен. Нужен. Переработка учёт не отменяет, и на машину с доской сопроводительный документ спрашивают так же, как на кругляк.&lt;br&gt;&lt;br&gt;Что делаю. Завожу объёмы в ФГИС ЛК, оформляю происхождение через договор купли-продажи, выписываю ЭСД с QR кодом на каждую отгрузку, собираю пакет, который спокойно принимает бухгалтерия покупателя.&lt;br&gt;&lt;br&gt;От вас порода, кубатура и маршрут. Документ присылаю в течение часа.&lt;br&gt;&lt;br&gt;Пилорамам, которые отгружают постоянно, считаю помесячно.&lt;br&gt;&lt;br&gt;Документы на доску, брус, пиломатериал, QR код на перевозку, ЭСД, ФГИС ЛК, Орловская область.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Псковская обл., Невель, ул. Ленина, 25</t>
+          <t>Орловская обл., Болхов, ул. Ленина, 24</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -10122,24 +10122,24 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>2026-11-01T08:00:00+03:00</t>
+          <t>2026-11-02T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>2026-10-02T11:00:00+03:00</t>
+          <t>2026-10-03T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>2026-11-01T08:00:00+03:00</t>
+          <t>2026-11-02T08:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4200300253</t>
+          <t>3310128368</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -10154,7 +10154,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_09_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_09_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_09_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_19_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_04_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_04_3.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -10168,21 +10168,21 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>680</v>
+        <v>820</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Учёт древесины в ФГИС ЛК под ключ</t>
+          <t>Документы ФГИС ЛК, декларация, 1-ИЛ</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Веду учёт древесины в ФГИС ЛК за вас. Вы занимаетесь лесом, я бумагами.&lt;br&gt;&lt;br&gt;Что входит: вношу сделки и объёмы, оформляю происхождение договором купли-продажи, выписываю сопроводительные документы на отгрузки, свожу остатки, сдаю отчётность за период.&lt;br&gt;&lt;br&gt;Формат удобен тем, у кого машины идут регулярно и каждый раз всё делается в последний момент. Вы пишете, что отгружаете, остальное закрываю я.&lt;br&gt;&lt;br&gt;Отдельно разбираю запущенные кабинеты. Бывает, объёмы задвоены, часть сделок не закрыта, остатки не сходятся со складом. Пересобираю данные так, чтобы отгрузки перестали блокироваться.&lt;br&gt;&lt;br&gt;Доступ в ваш кабинет не прошу, работаю по выгрузкам и документам. Удалённо, по всей стране, с ИП, ООО и частниками.&lt;br&gt;&lt;br&gt;Учёт древесины, ФГИС ЛК, сопровождение, ЭСД, отчётность, Брянская область.</t>
+          <t>Веду документы по лесу: QR коды на перевозку, лесную декларацию, отчёт 1-ИЛ, учёт объёмов.&lt;br&gt;&lt;br&gt;Если коротко, закрываю всю бумажную часть. На рейс делаю ЭСД с QR кодом, обычно в течение часа после ваших данных. За период собираю и сдаю отчётность, чтобы не словить штраф и блокировку отгрузок.&lt;br&gt;&lt;br&gt;Если объёма нет в системе, оформляю договор купли-продажи и завожу партию в ФГИС ЛК на ваш баланс. Если остатки разошлись с фактом, сначала привожу их в порядок, иначе отчёт уйдёт с ошибкой.&lt;br&gt;&lt;br&gt;Работаю с арендаторами участков, ИП, организациями и частниками. Удалённо, по всей стране, свой кабинет и электронную подпись заводить не нужно.&lt;br&gt;&lt;br&gt;Напишите, что нужно и за какой период, скажу сроки и цену.&lt;br&gt;&lt;br&gt;Лесная декларация, отчёт 1-ИЛ, QR код на лес, ЭСД, документы ФГИС ЛК, Курская область.</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Брянская обл., Унеча, ул. Октябрьская, 1</t>
+          <t>Курская обл., Рыльск, ул. Ленина, 59</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -10252,405 +10252,15 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>2026-11-01T12:00:00+03:00</t>
+          <t>2026-11-02T12:00:00+03:00</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>2026-10-02T15:00:00+03:00</t>
+          <t>2026-10-03T15:00:00+03:00</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr">
-        <is>
-          <t>2026-11-01T12:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2726578016</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>79824510018</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_19_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_19_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_19_3.jpg</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Предложение услуг</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>1150</v>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Документы на вывоз леса с участка</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Расчистили участок, лес лежит, а вывезти его нельзя. Делаю документы, после которых можно.&lt;br&gt;&lt;br&gt;Многие узнают об этом уже после того, как спилили. Кажется, что земля своя и вопросов быть не должно, но учёт древесины одинаковый и для делянки, и для поля, и для лесополосы вдоль дороги.&lt;br&gt;&lt;br&gt;Порядок работы такой. Смотрим объём и породу. Оформляю договор купли-продажи на партию. Завожу древесину в ФГИС ЛК и ставлю вам на баланс. Дальше выдаю сопроводительный документ с QR кодом на каждую машину.&lt;br&gt;&lt;br&gt;Подходит фермерам, собственникам участков, подрядчикам на расчистке и тем, кто берёт лес у населения.&lt;br&gt;&lt;br&gt;Всё делается удалённо, свой кабинет и электронная подпись не нужны.&lt;br&gt;&lt;br&gt;Документы на вывоз леса, расчистка участка, ФГИС ЛК, ЭСД, QR код, Рязанская область.</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Рязанская обл., Шилово, ул. Советская, 9</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Деловые услуги</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Консультирование</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Другое</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>4–7 лет</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>Удалённо</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Есть</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>belpool.1@gmail.com</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>ФГИС ЛК объемы</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>2026-11-02T04:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>2026-10-03T07:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>2026-11-02T04:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>3384561572</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>79824510018</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_23_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_23_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_23_3.jpg</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Предложение услуг</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>1850</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Документы на дрова и пиломатериал</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Делаю документы и на дрова, и на пиломатериал. Для учёта разницы нет, спрашивают одинаково.&lt;br&gt;&lt;br&gt;Чаще всего приходят двое. Первый возит дрова машинами на продажу, и покупателю нужно провести покупку по бухгалтерии. Второй держит пилораму, отгружает доску и брус, а у заказчика требование показать происхождение.&lt;br&gt;&lt;br&gt;Закрываю это целиком. Оформляю договор купли-продажи на объём, завожу партию в ФГИС ЛК, выписываю сопроводительные документы с QR кодом на отгрузки, сдаю отчётность за период.&lt;br&gt;&lt;br&gt;Порода значения не имеет: берёза, осина, ольха, сосна, ель. Переработка тоже не мешает, на доску документ делается так же, как на кругляк.&lt;br&gt;&lt;br&gt;Работаю удалённо, по всей стране. Напишите, что отгружаете и какой объём в месяц, посчитаю.&lt;br&gt;&lt;br&gt;Документы на дрова, пиломатериал, доска, брус, ЭСД, ФГИС ЛК, Орловская область.</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Орловская обл., Болхов, ул. Ленина, 24</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Деловые услуги</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Консультирование</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Другое</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>4–7 лет</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>Удалённо</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Есть</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>belpool.1@gmail.com</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>ФГИС ЛК объемы</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>2026-11-02T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>2026-10-03T11:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>2026-11-02T08:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>3310128368</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>79824510018</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261002/green_dok_fgis.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_01_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_03_1.jpg</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Предложение услуг</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>3100</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Лесная декларация и отчёт 1-ИЛ</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Беру на себя отчётность по лесу: лесную декларацию, отчёт 1-ИЛ, складской учёт и движение остатков.&lt;br&gt;&lt;br&gt;Это та часть, которую откладывают до последнего. Сроки жёсткие, форма неудобная, и ошибиться в ней проще, чем заполнить верно. А дальше идут штрафы и заблокированные отгрузки.&lt;br&gt;&lt;br&gt;Что делаю. Собираю отчётность по вашим сделкам за период, сверяю то, что лежит по факту, с тем, что показано в системе, и подаю в срок. Если остатки разошлись, сначала привожу их в порядок, иначе отчёт уйдёт с ошибкой.&lt;br&gt;&lt;br&gt;Работаю с арендаторами участков, ИП, организациями и частниками. Удалённо, по всей стране, кабинет и подпись заводить не нужно.&lt;br&gt;&lt;br&gt;Напишите, за какой период нужна отчётность и что уже подано, скажу сроки и цену.&lt;br&gt;&lt;br&gt;Лесная декларация, отчёт 1-ИЛ, отчётность ФГИС ЛК, учёт древесины, Курская область.</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Курская обл., Рыльск, ул. Ленина, 59</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Деловые услуги</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Консультирование</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Другое</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>4–7 лет</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>Удалённо</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Есть</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>belpool.1@gmail.com</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>ФГИС ЛК объемы</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>2026-11-02T12:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>2026-10-03T15:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AE46" t="inlineStr">
         <is>
           <t>2026-11-02T12:00:00+03:00</t>
         </is>
@@ -11305,7 +10915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK141"/>
+  <dimension ref="A1:AK145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -30600,6 +30210,546 @@
       <c r="AK141" t="inlineStr">
         <is>
           <t>2026-10-24T14:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>5534681826</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Кругляк сосна (QR код на перевозку)</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Псковская область. Делаю QR коды на перевозку леса и документы на древесину. Сам лес не продаю, занимаюсь только бумагами.&lt;br&gt;&lt;br&gt;Что это за QR код. На каждую машину с лесом нужен электронный сопроводительный документ, ЭСД. В нём есть QR код, его сканируют на посту и на весовой. Нет документа, значит рейс под вопросом, а это штраф и разговоры.&lt;br&gt;&lt;br&gt;Как работаем. Вы пишете породу, сколько кубов, номер машины и куда едет. Я делаю документ и присылаю, обычно в течение часа.&lt;br&gt;&lt;br&gt;Если вашего объёма нет в системе ФГИС ЛК, сначала завожу его туда: оформляю договор купли-продажи на партию и ставлю её вам на баланс. После этого лес можно законно продавать и возить.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС и электронную подпись заводить не надо, всё делаю со своей стороны, удалённо.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, QR код на перевозку, ЭСД, документы ФГИС ЛК, Псковская область.</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_09_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_02_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_02_3.jpg</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Псковская обл., Невель, ул. Ленина, 25</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>3100</v>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>2026-11-01T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>2026-10-02T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>2026-11-01T08:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>4200300253</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Берёза дрова (QR код и документы)</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Брянская область. Помогаю с QR кодами на перевозку и с документами на дрова и баланс.&lt;br&gt;&lt;br&gt;Многие думают, что на дрова бумаги не нужны. Нужны такие же, как на деловой лес. Если возите машинами на продажу, а тем более юрлицу, у вас спросят и происхождение, и сопроводительный документ на рейс.&lt;br&gt;&lt;br&gt;Что делаю. Оформляю договор купли-продажи на ваш объём, завожу древесину в ФГИС ЛК, ставлю на баланс. Дальше на каждую машину выписываю ЭСД с QR кодом, тот самый, который проверяют на дороге.&lt;br&gt;&lt;br&gt;От вас нужны порода, кубатура, номер машины и маршрут. Документ присылаю в течение часа.&lt;br&gt;&lt;br&gt;Кто возит постоянно, берёт сопровождение помесячно, так дешевле и быстрее.&lt;br&gt;&lt;br&gt;Берёза дрова, баланс, кругляк, QR код на перевозку, ЭСД, документы ФГИС ЛК, Брянская область.</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_02_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_09_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_09_3.jpg</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Брянская обл., Унеча, ул. Октябрьская, 1</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>1150</v>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>2026-11-01T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>2026-10-02T15:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>2026-11-01T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2726578016</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Кругляк ель (документы ФГИС ЛК)</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Рязанская область. Делаю документы на еловый кругляк и QR коды на перевозку.&lt;br&gt;&lt;br&gt;Частая ситуация: лес спилили на своём участке или при расчистке, он лежит, покупатель есть, а продать нельзя. В государственной системе учёта этого объёма нет, значит для закона его как бы и не существует.&lt;br&gt;&lt;br&gt;Как это закрывается. Смотрим объём и породу. Оформляю договор купли-продажи на партию, это и есть законное основание. Завожу древесину в ФГИС ЛК и ставлю вам на баланс. Дальше на каждый рейс выдаю ЭСД с QR кодом.&lt;br&gt;&lt;br&gt;После этого машина едет спокойно, а покупатель видит нормальные документы.&lt;br&gt;&lt;br&gt;Работаю удалённо по всей стране, кабинет и подпись вам заводить не нужно. Разбор ситуации бесплатный.&lt;br&gt;&lt;br&gt;Ель кругляк, пиловочник, баланс, QR код на перевозку, ЭСД, документы ФГИС ЛК, Рязанская область.</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261002/green_dok_fgis.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_19_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_19_3.jpg</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Рязанская обл., Шилово, ул. Советская, 9</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>2350</v>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>2026-11-02T04:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>2026-10-03T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>2026-11-02T04:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>3656837736</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Осина баланс (эсд и документы)</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Липецкая область. Оформляю документы на осину и делаю QR коды на вывоз.&lt;br&gt;&lt;br&gt;Осину берут плитные комбинаты, но на приёмке сразу спрашивают, откуда объём. Без бумаг партию разворачивают, и неважно, сколько вы её везли.&lt;br&gt;&lt;br&gt;Беру это на себя. Оформляю договор купли-продажи как основание на объём, завожу партию в ФГИС ЛК, ставлю на ваш баланс. На каждую машину делаю ЭСД с QR кодом, по времени обычно час.&lt;br&gt;&lt;br&gt;Отдельно помогаю тем, кто купил лес у частника и не понимает, как провести такую покупку. Это оформляется через меня.&lt;br&gt;&lt;br&gt;Всё удалённо, ехать никуда не надо. Напишите объём и куда везёте, посчитаю.&lt;br&gt;&lt;br&gt;Осина баланс, дрова, кругляк, QR код на перевозку, ЭСД, документы ФГИС ЛК, Липецкая область.</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_17_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_01_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_01_3.jpg</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Липецкая обл., Усмань, ул. Ленина, 36</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>1450</v>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Осина</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>2026-11-02T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>2026-10-03T13:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>2026-11-02T10:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -31996,7 +32146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD33"/>
+  <dimension ref="A1:AD32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="21"/>
@@ -35707,16 +35857,16 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>520</v>
+        <v>280</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Документы на древесину, ФГИС ЛК</t>
+          <t>QR код на перевозку леса и документы</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Древесина есть, а бумаг на неё нет. Делаю документы, чтобы лес можно было спокойно продать и вывезти.&lt;br&gt;&lt;br&gt;Самая частая история: лес заготовлен, покупатель найден, и тут выясняется, что в государственной системе этого объёма не существует. Для закона его просто нет, поэтому сделка встаёт.&lt;br&gt;&lt;br&gt;Что делаю по порядку. Смотрю, что у вас на руках. Оформляю договор купли-продажи на партию, он и становится основанием на объём. Завожу древесину в ФГИС ЛК и ставлю вам на баланс. Дальше на каждую машину выписываю сопроводительный документ с QR кодом.&lt;br&gt;&lt;br&gt;Работаю и со свежей заготовкой, и с той, что лежит с прошлого сезона. Срок тут роли не играет.&lt;br&gt;&lt;br&gt;Всё удалённо, приезжать никуда не надо. Напишите породу и объём, разберу вашу ситуацию бесплатно.&lt;br&gt;&lt;br&gt;Документы на лес, ФГИС ЛК, учёт древесины, ЭСД, Смоленская область.</t>
+          <t>Делаю QR коды на перевозку леса и документы на древесину. Коротко и по делу, чем помогаю.&lt;br&gt;&lt;br&gt;Первое. ЭСД на рейс. Это электронный сопроводительный документ с QR кодом, который нужен на каждую машину с лесом. Вы пишете породу, кубы, номер машины и маршрут, я присылаю готовый документ, обычно в течение часа.&lt;br&gt;&lt;br&gt;Второе. Документы на сам объём. Если древесины нет в ФГИС ЛК, оформляю договор купли-продажи, завожу партию в систему и ставлю вам на баланс. После этого лес можно законно продать и вывезти.&lt;br&gt;&lt;br&gt;Третье. Отчётность и порядок в кабинете: декларация, отчёт за период, сверка остатков.&lt;br&gt;&lt;br&gt;Работаю с кругляком, дровами, балансом, доской и брусом. Удалённо, по всей стране. Свой кабинет и электронная подпись вам не нужны.&lt;br&gt;&lt;br&gt;QR код на лес, ЭСД на перевозку, документы ФГИС ЛК, учёт древесины, Смоленская область.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -35837,16 +35987,16 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>820</v>
+        <v>520</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Закрытие расхождений в ФГИС ЛК</t>
+          <t>QR код на лес, расхождения ФГИС</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>По системе один объём, по факту на площадке другой. Разбираю такие расхождения и привожу данные в порядок.&lt;br&gt;&lt;br&gt;Причины почти всегда простые. Внесли не ту породу или сортимент, задвоили партию, списали меньше, чем увезли, приняли объём без основания. Дальше ошибка тянется, а у покупателя она видна сразу, и отгрузка встаёт.&lt;br&gt;&lt;br&gt;Что делаю. Считаю факт по вашим данным, поднимаю историю операций, нахожу, где именно разошлось, и правлю. Там, где на объём нужно основание, оформляю договор купли-продажи со своей стороны.&lt;br&gt;&lt;br&gt;После разбора остатки совпадают со складом, машины едут, отчёт за период сдаётся без вопросов.&lt;br&gt;&lt;br&gt;Работаю удалённо, доступ в кабинет не требуется, достаточно выгрузок и документов.&lt;br&gt;&lt;br&gt;Расхождения ФГИС ЛК, остатки древесины, сверка объёмов, учёт леса, Калужская область.</t>
+          <t>Помогаю с QR кодами на перевозку леса и с порядком в ФГИС ЛК, когда цифры не сходятся.&lt;br&gt;&lt;br&gt;Две вещи, с которыми приходят чаще всего.&lt;br&gt;&lt;br&gt;Нужен документ на рейс. Делаю ЭСД с QR кодом на каждую машину, по вашим данным: порода, кубы, номер машины, маршрут. Обычно готово в течение часа.&lt;br&gt;&lt;br&gt;Не сходятся объёмы. По системе одно, на складе другое, из-за этого отгрузки встают. Считаю факт, поднимаю историю операций, нахожу, где разошлось, и правлю. Где на объём нужно основание, оформляю договор купли-продажи.&lt;br&gt;&lt;br&gt;После разбора остатки совпадают, машины едут, отчёт за период уходит без ошибок.&lt;br&gt;&lt;br&gt;Доступ в ваш кабинет не прошу, хватает выгрузок и документов. Работаю удалённо.&lt;br&gt;&lt;br&gt;QR код на лес, ЭСД, расхождения ФГИС ЛК, остатки древесины, учёт леса, Калужская область.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -35967,16 +36117,16 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>1450</v>
+        <v>680</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Сопроводительные документы на лес</t>
+          <t>ЭСД и QR код на машину с лесом</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Оформляю сопроводительные документы на древесину. Один рейс, десять рейсов или поток отгрузок, работаю и так, и так.&lt;br&gt;&lt;br&gt;По каждой машине нужен электронный документ с QR кодом. Он подтверждает, что объём стоит на учёте и везёт его тот, кто имеет на это право. На весовой и на посту проверяется за минуту.&lt;br&gt;&lt;br&gt;От вас: порода, кубатура, номер машины, откуда и куда едет. От меня готовый документ, обычно в течение часа.&lt;br&gt;&lt;br&gt;Если объёма в системе нет, завожу его через договор купли-продажи, это делается в тот же день.&lt;br&gt;&lt;br&gt;Тем, кто возит постоянно, считаю помесячно. Выходит дешевле, чем оформлять каждый рейс отдельно, и не надо каждый раз писать заново.&lt;br&gt;&lt;br&gt;Сопроводительные документы, ЭСД, QR код на перевозку, ФГИС ЛК, Тамбовская область.</t>
+          <t>Делаю сопроводительные документы на древесину. На одну машину, на десять, на постоянный поток.&lt;br&gt;&lt;br&gt;На каждый рейс с лесом нужен ЭСД, электронный документ с QR кодом. Он подтверждает, что объём стоит на учёте и везёт его тот, кто имеет на это право. На посту и на весовой проверяется за минуту.&lt;br&gt;&lt;br&gt;От вас: порода, кубатура, номер машины, откуда и куда едет. От меня готовый документ, обычно в течение часа.&lt;br&gt;&lt;br&gt;Если объёма нет в ФГИС ЛК, сначала завожу его через договор купли-продажи, это делается в тот же день.&lt;br&gt;&lt;br&gt;Кто отгружает регулярно, работает на сопровождении помесячно. Выходит дешевле, чем оформлять каждый рейс отдельно.&lt;br&gt;&lt;br&gt;Кругляк, дрова, баланс, доска, брус, порода любая.&lt;br&gt;&lt;br&gt;ЭСД на рейс, QR код на перевозку леса, сопроводительные документы, ФГИС ЛК, Тамбовская область.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -36062,136 +36212,6 @@
       <c r="AD32" t="inlineStr">
         <is>
           <t>2026-11-02T06:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>3656837736</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>79824510018</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_17_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_01_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_01_3.jpg</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Предложение услуг</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>2350</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Договор и учёт на партию леса</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Купили лес у частника или у хозяйства и не понимаете, как провести эту покупку. Оформляю такую сделку по правилам.&lt;br&gt;&lt;br&gt;Проблема в том, что продавец часто сам не стоит на учёте, а значит передать объём официально он не может. Покупатель остаётся с древесиной на руках и без основания на неё.&lt;br&gt;&lt;br&gt;Как решаю. Оформляю договор купли-продажи через своё предприятие, он становится законным основанием на партию. Завожу объём в ФГИС ЛК и ставлю его вам на баланс. Дальше вы спокойно продаёте дальше или везёте, а на каждый рейс получаете сопроводительный документ.&lt;br&gt;&lt;br&gt;Подходит перекупщикам, пилорамам и тем, кто собирает объём по несколько машин у разных людей.&lt;br&gt;&lt;br&gt;Разбор ситуации бесплатный, работаю удалённо.&lt;br&gt;&lt;br&gt;Договор на лес, происхождение древесины, учёт в ФГИС ЛК, партия леса, Липецкая область.</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Липецкая обл., Усмань, ул. Ленина, 36</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Услуги посредников</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Консультации</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Другое</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>4–7 лет</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>У себя</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>belpool.1@gmail.com</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>ФГИС ЛК объемы</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>2026-11-02T10:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>2026-10-03T13:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>2026-11-02T10:00:00+03:00</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -4648,7 +4648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE43"/>
+  <dimension ref="A1:AE44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="26"/>
@@ -10009,7 +10009,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3384561572</t>
+          <t>5534681826</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_23_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_23_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_23_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_09_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_02_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_02_3.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -10038,21 +10038,21 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>1850</v>
+        <v>280</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Документы на доску и брус, QR код</t>
+          <t>QR код на перевозку леса и документы</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Делаю документы и QR коды на пиломатериал: доска, брус, брусок, горбыль, тарная дощечка.&lt;br&gt;&lt;br&gt;Вопрос, который задают почти все: нужен ли документ, если лес уже распилен. Нужен. Переработка учёт не отменяет, и на машину с доской сопроводительный документ спрашивают так же, как на кругляк.&lt;br&gt;&lt;br&gt;Что делаю. Завожу объёмы в ФГИС ЛК, оформляю происхождение через договор купли-продажи, выписываю ЭСД с QR кодом на каждую отгрузку, собираю пакет, который спокойно принимает бухгалтерия покупателя.&lt;br&gt;&lt;br&gt;От вас порода, кубатура и маршрут. Документ присылаю в течение часа.&lt;br&gt;&lt;br&gt;Пилорамам, которые отгружают постоянно, считаю помесячно.&lt;br&gt;&lt;br&gt;Документы на доску, брус, пиломатериал, QR код на перевозку, ЭСД, ФГИС ЛК, Орловская область.</t>
+          <t>Делаю QR коды на перевозку леса и документы на древесину. Вот чем конкретно помогаю.&lt;br&gt;&lt;br&gt;Первое. Документ на рейс. Это ЭСД, электронная накладная из ФГИС ЛК с QR кодом. Её нужно иметь на каждую машину с лесом, её сканируют на посту и на весовой. Вы пишете породу, кубы, номер машины и маршрут, я присылаю готовый документ, обычно в течение часа.&lt;br&gt;&lt;br&gt;Второе. Документы на сам объём. Если древесины нет в системе, оформляю договор купли-продажи, завожу партию в ФГИС ЛК и ставлю вам на баланс. После этого лес можно законно продать и вывезти.&lt;br&gt;&lt;br&gt;Третье. Отчётность: лесная декларация, отчёт за период, сверка остатков.&lt;br&gt;&lt;br&gt;Работаю с кругляком, дровами, балансом, доской и брусом. Удалённо, по всей стране. Свой кабинет в ФГИС и электронная подпись вам не нужны.&lt;br&gt;&lt;br&gt;QR код на лес, ЭСД на перевозку, документы ФГИС ЛК, учёт древесины, Псковская область.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Орловская обл., Болхов, ул. Ленина, 24</t>
+          <t>Псковская обл., Невель, ул. Ленина, 25</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -10122,145 +10122,275 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>2026-11-02T08:00:00+03:00</t>
+          <t>2026-11-01T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>2026-10-03T11:00:00+03:00</t>
+          <t>2026-10-02T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>2026-11-02T08:00:00+03:00</t>
+          <t>2026-11-01T08:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>3384561572</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_23_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_23_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_23_3.jpg</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>1850</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Документы на доску и брус, QR код</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Делаю документы и QR коды на пиломатериал: доска, брус, брусок, горбыль, тарная дощечка.&lt;br&gt;&lt;br&gt;Вопрос, который задают почти все: нужен ли документ, если лес уже распилен. Нужен. Переработка учёт не отменяет, и на машину с доской сопроводительный документ спрашивают так же, как на кругляк.&lt;br&gt;&lt;br&gt;Что делаю. Завожу объёмы в ФГИС ЛК, оформляю происхождение через договор купли-продажи, выписываю ЭСД с QR кодом на каждую отгрузку, собираю пакет, который спокойно принимает бухгалтерия покупателя.&lt;br&gt;&lt;br&gt;От вас порода, кубатура и маршрут. Документ присылаю в течение часа.&lt;br&gt;&lt;br&gt;Пилорамам, которые отгружают постоянно, считаю помесячно.&lt;br&gt;&lt;br&gt;Документы на доску, брус, пиломатериал, QR код на перевозку, ЭСД, ФГИС ЛК, Орловская область.</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Орловская обл., Болхов, ул. Ленина, 24</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2026-11-02T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>2026-10-03T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>2026-11-02T08:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>3310128368</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>BBL</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>79824510018</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_19_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_04_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_04_3.jpg</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>Предложение услуг</t>
         </is>
       </c>
-      <c r="J43" t="n">
+      <c r="J44" t="n">
         <v>820</v>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>Документы ФГИС ЛК, декларация, 1-ИЛ</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>Веду документы по лесу: QR коды на перевозку, лесную декларацию, отчёт 1-ИЛ, учёт объёмов.&lt;br&gt;&lt;br&gt;Если коротко, закрываю всю бумажную часть. На рейс делаю ЭСД с QR кодом, обычно в течение часа после ваших данных. За период собираю и сдаю отчётность, чтобы не словить штраф и блокировку отгрузок.&lt;br&gt;&lt;br&gt;Если объёма нет в системе, оформляю договор купли-продажи и завожу партию в ФГИС ЛК на ваш баланс. Если остатки разошлись с фактом, сначала привожу их в порядок, иначе отчёт уйдёт с ошибкой.&lt;br&gt;&lt;br&gt;Работаю с арендаторами участков, ИП, организациями и частниками. Удалённо, по всей стране, свой кабинет и электронную подпись заводить не нужно.&lt;br&gt;&lt;br&gt;Напишите, что нужно и за какой период, скажу сроки и цену.&lt;br&gt;&lt;br&gt;Лесная декларация, отчёт 1-ИЛ, QR код на лес, ЭСД, документы ФГИС ЛК, Курская область.</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>Курская обл., Рыльск, ул. Ленина, 59</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>Деловые услуги</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>Консультирование</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>Другое</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>4–7 лет</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>Удалённо</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>Есть</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>belpool.1@gmail.com</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>ФГИС ЛК объемы</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
+      <c r="AC44" t="inlineStr">
         <is>
           <t>2026-11-02T12:00:00+03:00</t>
         </is>
       </c>
-      <c r="AD43" t="inlineStr">
+      <c r="AD44" t="inlineStr">
         <is>
           <t>2026-10-03T15:00:00+03:00</t>
         </is>
       </c>
-      <c r="AE43" t="inlineStr">
+      <c r="AE44" t="inlineStr">
         <is>
           <t>2026-11-02T12:00:00+03:00</t>
         </is>
@@ -30216,7 +30346,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>5534681826</t>
+          <t>8271970671</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -30236,12 +30366,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Псковская область. Делаю QR коды на перевозку леса и документы на древесину. Сам лес не продаю, занимаюсь только бумагами.&lt;br&gt;&lt;br&gt;Что это за QR код. На каждую машину с лесом нужен электронный сопроводительный документ, ЭСД. В нём есть QR код, его сканируют на посту и на весовой. Нет документа, значит рейс под вопросом, а это штраф и разговоры.&lt;br&gt;&lt;br&gt;Как работаем. Вы пишете породу, сколько кубов, номер машины и куда едет. Я делаю документ и присылаю, обычно в течение часа.&lt;br&gt;&lt;br&gt;Если вашего объёма нет в системе ФГИС ЛК, сначала завожу его туда: оформляю договор купли-продажи на партию и ставлю её вам на баланс. После этого лес можно законно продавать и возить.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС и электронную подпись заводить не надо, всё делаю со своей стороны, удалённо.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, QR код на перевозку, ЭСД, документы ФГИС ЛК, Псковская область.</t>
+          <t>Смоленская область, сосновый кругляк и пиловочник. Делаю QR коды на перевозку и документы на древесину. Сам лес не продаю, занимаюсь бумагами.&lt;br&gt;&lt;br&gt;Что за QR код. На каждую машину с лесом нужен электронный сопроводительный документ, ЭСД. В нём есть QR код, который сканируют на посту. Нет документа, значит рейс под вопросом и штраф.&lt;br&gt;&lt;br&gt;Как работаем. Вы пишете породу, сколько кубов, номер машины и куда едет. Я делаю документ и присылаю, обычно за час.&lt;br&gt;&lt;br&gt;Если вашего объёма нет в ФГИС ЛК, сначала завожу его туда: оформляю договор купли-продажи на партию и ставлю её вам на баланс. После этого лес можно законно продавать и возить.&lt;br&gt;&lt;br&gt;Кабинет и электронную подпись заводить не надо, всё с моей стороны, удалённо.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, QR код на перевозку, ЭСД, документы ФГИС ЛК, Смоленская область.</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_09_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_02_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_02_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_06_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_06_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_06_3.jpg</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -30256,7 +30386,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Псковская обл., Невель, ул. Ленина, 25</t>
+          <t>Смоленская обл., Ярцево, ул. Советская, 17</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -30319,7 +30449,7 @@
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>2026-11-01T08:00:00+03:00</t>
+          <t>2026-11-01T10:00:00+03:00</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -30339,12 +30469,12 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>2026-10-02T11:00:00+03:00</t>
+          <t>2026-10-02T13:00:00+03:00</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>2026-11-01T08:00:00+03:00</t>
+          <t>2026-11-01T10:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -32146,7 +32276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD32"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="21"/>
@@ -35828,7 +35958,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8271970671</t>
+          <t>1844878614</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -35843,7 +35973,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_06_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_06_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_06_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_11_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_11_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_11_3.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -35857,21 +35987,21 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>280</v>
+        <v>520</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>QR код на перевозку леса и документы</t>
+          <t>QR код на лес, расхождения ФГИС</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Делаю QR коды на перевозку леса и документы на древесину. Коротко и по делу, чем помогаю.&lt;br&gt;&lt;br&gt;Первое. ЭСД на рейс. Это электронный сопроводительный документ с QR кодом, который нужен на каждую машину с лесом. Вы пишете породу, кубы, номер машины и маршрут, я присылаю готовый документ, обычно в течение часа.&lt;br&gt;&lt;br&gt;Второе. Документы на сам объём. Если древесины нет в ФГИС ЛК, оформляю договор купли-продажи, завожу партию в систему и ставлю вам на баланс. После этого лес можно законно продать и вывезти.&lt;br&gt;&lt;br&gt;Третье. Отчётность и порядок в кабинете: декларация, отчёт за период, сверка остатков.&lt;br&gt;&lt;br&gt;Работаю с кругляком, дровами, балансом, доской и брусом. Удалённо, по всей стране. Свой кабинет и электронная подпись вам не нужны.&lt;br&gt;&lt;br&gt;QR код на лес, ЭСД на перевозку, документы ФГИС ЛК, учёт древесины, Смоленская область.</t>
+          <t>Помогаю с QR кодами на перевозку леса и с порядком в ФГИС ЛК, когда цифры не сходятся.&lt;br&gt;&lt;br&gt;Две вещи, с которыми приходят чаще всего.&lt;br&gt;&lt;br&gt;Нужен документ на рейс. Делаю ЭСД с QR кодом на каждую машину, по вашим данным: порода, кубы, номер машины, маршрут. Обычно готово в течение часа.&lt;br&gt;&lt;br&gt;Не сходятся объёмы. По системе одно, на складе другое, из-за этого отгрузки встают. Считаю факт, поднимаю историю операций, нахожу, где разошлось, и правлю. Где на объём нужно основание, оформляю договор купли-продажи.&lt;br&gt;&lt;br&gt;После разбора остатки совпадают, машины едут, отчёт за период уходит без ошибок.&lt;br&gt;&lt;br&gt;Доступ в ваш кабинет не прошу, хватает выгрузок и документов. Работаю удалённо.&lt;br&gt;&lt;br&gt;QR код на лес, ЭСД, расхождения ФГИС ЛК, остатки древесины, учёт леса, Калужская область.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Смоленская обл., Ярцево, ул. Советская, 17</t>
+          <t>Калужская обл., Жиздра, ул. Володарского, 29</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -35941,24 +36071,24 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-11-01T10:00:00+03:00</t>
+          <t>2026-11-02T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-10-02T13:00:00+03:00</t>
+          <t>2026-10-03T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>2026-11-01T10:00:00+03:00</t>
+          <t>2026-11-02T02:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1844878614</t>
+          <t>4427075166</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -35973,7 +36103,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_11_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_11_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_11_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_22_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_22_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_22_3.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -35987,21 +36117,21 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>520</v>
+        <v>680</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>QR код на лес, расхождения ФГИС</t>
+          <t>ЭСД и QR код на машину с лесом</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Помогаю с QR кодами на перевозку леса и с порядком в ФГИС ЛК, когда цифры не сходятся.&lt;br&gt;&lt;br&gt;Две вещи, с которыми приходят чаще всего.&lt;br&gt;&lt;br&gt;Нужен документ на рейс. Делаю ЭСД с QR кодом на каждую машину, по вашим данным: порода, кубы, номер машины, маршрут. Обычно готово в течение часа.&lt;br&gt;&lt;br&gt;Не сходятся объёмы. По системе одно, на складе другое, из-за этого отгрузки встают. Считаю факт, поднимаю историю операций, нахожу, где разошлось, и правлю. Где на объём нужно основание, оформляю договор купли-продажи.&lt;br&gt;&lt;br&gt;После разбора остатки совпадают, машины едут, отчёт за период уходит без ошибок.&lt;br&gt;&lt;br&gt;Доступ в ваш кабинет не прошу, хватает выгрузок и документов. Работаю удалённо.&lt;br&gt;&lt;br&gt;QR код на лес, ЭСД, расхождения ФГИС ЛК, остатки древесины, учёт леса, Калужская область.</t>
+          <t>Делаю сопроводительные документы на древесину. На одну машину, на десять, на постоянный поток.&lt;br&gt;&lt;br&gt;На каждый рейс с лесом нужен ЭСД, электронный документ с QR кодом. Он подтверждает, что объём стоит на учёте и везёт его тот, кто имеет на это право. На посту и на весовой проверяется за минуту.&lt;br&gt;&lt;br&gt;От вас: порода, кубатура, номер машины, откуда и куда едет. От меня готовый документ, обычно в течение часа.&lt;br&gt;&lt;br&gt;Если объёма нет в ФГИС ЛК, сначала завожу его через договор купли-продажи, это делается в тот же день.&lt;br&gt;&lt;br&gt;Кто отгружает регулярно, работает на сопровождении помесячно. Выходит дешевле, чем оформлять каждый рейс отдельно.&lt;br&gt;&lt;br&gt;Кругляк, дрова, баланс, доска, брус, порода любая.&lt;br&gt;&lt;br&gt;ЭСД на рейс, QR код на перевозку леса, сопроводительные документы, ФГИС ЛК, Тамбовская область.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Калужская обл., Жиздра, ул. Володарского, 29</t>
+          <t>Тамбовская обл., Рассказово, ул. Советская, 6</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -36071,145 +36201,15 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-11-02T02:00:00+03:00</t>
+          <t>2026-11-02T06:00:00+03:00</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-10-03T05:00:00+03:00</t>
+          <t>2026-10-03T09:00:00+03:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
-        <is>
-          <t>2026-11-02T02:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>4427075166</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>79824510018</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_22_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_22_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_22_3.jpg</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Предложение услуг</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>680</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>ЭСД и QR код на машину с лесом</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Делаю сопроводительные документы на древесину. На одну машину, на десять, на постоянный поток.&lt;br&gt;&lt;br&gt;На каждый рейс с лесом нужен ЭСД, электронный документ с QR кодом. Он подтверждает, что объём стоит на учёте и везёт его тот, кто имеет на это право. На посту и на весовой проверяется за минуту.&lt;br&gt;&lt;br&gt;От вас: порода, кубатура, номер машины, откуда и куда едет. От меня готовый документ, обычно в течение часа.&lt;br&gt;&lt;br&gt;Если объёма нет в ФГИС ЛК, сначала завожу его через договор купли-продажи, это делается в тот же день.&lt;br&gt;&lt;br&gt;Кто отгружает регулярно, работает на сопровождении помесячно. Выходит дешевле, чем оформлять каждый рейс отдельно.&lt;br&gt;&lt;br&gt;Кругляк, дрова, баланс, доска, брус, порода любая.&lt;br&gt;&lt;br&gt;ЭСД на рейс, QR код на перевозку леса, сопроводительные документы, ФГИС ЛК, Тамбовская область.</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Тамбовская обл., Рассказово, ул. Советская, 6</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Услуги посредников</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Консультации</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Другое</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>4–7 лет</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>У себя</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>belpool.1@gmail.com</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>ФГИС ЛК объемы</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>2026-11-02T06:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>2026-10-03T09:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
         <is>
           <t>2026-11-02T06:00:00+03:00</t>
         </is>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -10252,17 +10252,17 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>2026-11-02T08:00:00+03:00</t>
+          <t>2026-11-02T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>2026-10-03T11:00:00+03:00</t>
+          <t>2026-10-03T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>2026-11-02T08:00:00+03:00</t>
+          <t>2026-11-02T02:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -10382,17 +10382,17 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>2026-11-02T12:00:00+03:00</t>
+          <t>2026-11-02T06:00:00+03:00</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>2026-10-03T15:00:00+03:00</t>
+          <t>2026-10-03T09:00:00+03:00</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>2026-11-02T12:00:00+03:00</t>
+          <t>2026-11-02T06:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -30719,7 +30719,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>2026-11-02T04:00:00+03:00</t>
+          <t>2026-11-01T13:30:00+03:00</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -30739,12 +30739,12 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>2026-10-03T07:00:00+03:00</t>
+          <t>2026-10-02T16:30:00+03:00</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
         <is>
-          <t>2026-11-02T04:00:00+03:00</t>
+          <t>2026-11-01T13:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -30854,7 +30854,7 @@
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>2026-11-02T10:00:00+03:00</t>
+          <t>2026-11-02T04:00:00+03:00</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
@@ -30874,12 +30874,12 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>2026-10-03T13:00:00+03:00</t>
+          <t>2026-10-03T07:00:00+03:00</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>2026-11-02T10:00:00+03:00</t>
+          <t>2026-11-02T04:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -36071,17 +36071,17 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-11-02T02:00:00+03:00</t>
+          <t>2026-11-01T11:30:00+03:00</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-10-03T05:00:00+03:00</t>
+          <t>2026-10-02T14:30:00+03:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>2026-11-02T02:00:00+03:00</t>
+          <t>2026-11-01T11:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -36201,17 +36201,17 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-11-02T06:00:00+03:00</t>
+          <t>2026-11-01T15:00:00+03:00</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-10-03T09:00:00+03:00</t>
+          <t>2026-10-02T18:00:00+03:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>2026-11-02T06:00:00+03:00</t>
+          <t>2026-11-01T15:00:00+03:00</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -11045,7 +11045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK145"/>
+  <dimension ref="A1:AK151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -30880,6 +30880,816 @@
       <c r="AK145" t="inlineStr">
         <is>
           <t>2026-11-02T04:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>3318214608</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Пиловочник хвоя кругляк(QR на рейс)</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Псковская область, хвойный пиловочник и кругляк. Делаю QR коды на перевозку и документы на древесину. Сам лес не продаю, занимаюсь бумагами.&lt;br&gt;&lt;br&gt;На каждую машину с лесом нужен ЭСД, электронный сопроводительный документ. В нём QR код, его сканируют на посту и на весовой. Нет документа, значит рейс под вопросом и штраф.&lt;br&gt;&lt;br&gt;Как работаем. Вы пишете породу, сколько кубов, номер машины и куда едет. Я делаю документ и отправляю, обычно в течение часа.&lt;br&gt;&lt;br&gt;Если вашего объёма нет в ФГИС ЛК, сначала завожу его туда: оформляю договор купли-продажи на партию и ставлю её вам на баланс. После этого лес можно законно продавать и возить.&lt;br&gt;&lt;br&gt;Свой кабинет и электронную подпись заводить не нужно, всё с моей стороны, удалённо.&lt;br&gt;&lt;br&gt;Сосна пиловочник, хвоя, кругляк, QR код на перевозку, ЭСД на рейс, документы ФГИС ЛК, Псковская область.</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_18_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_18_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_18_3.jpg</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Псковская обл., Новоржев, ул. Германа, 20</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>2026-11-04T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>2026-10-05T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>2026-11-04T08:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2827020997</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Доска и брус хвоя(документы фгис)</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Смоленская область, пиломатериал хвоя. Помогаю с документами на доску и брус и с QR кодами на перевозку.&lt;br&gt;&lt;br&gt;Самый частый вопрос: нужен ли документ, если лес уже распилен. Нужен. Переработка учёт не отменяет, и машину с доской проверяют так же, как с кругляком.&lt;br&gt;&lt;br&gt;Что делаю. Завожу объём в ФГИС ЛК, оформляю происхождение договором купли-продажи, выписываю ЭСД с QR кодом на каждую отгрузку. Собираю пакет, который спокойно принимает бухгалтерия покупателя.&lt;br&gt;&lt;br&gt;От вас порода, кубатура и маршрут. Документ присылаю в течение часа.&lt;br&gt;&lt;br&gt;Пилорамам, которые отгружают постоянно, считаю помесячно, так дешевле.&lt;br&gt;&lt;br&gt;Доска обрезная, брус, брусок, пиломатериал хвоя, QR код на перевозку, ЭСД, документы ФГИС ЛК, Смоленская область.</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261005/g1_qr_perevozka.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_21_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_21_3.jpg</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Смоленская обл., Дорогобуж, ул. Мира, 2</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>290</v>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>2026-11-04T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>2026-10-05T12:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>2026-11-04T09:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>5794505787</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Берёза дрова баланс(эсд на рейс)</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Брянская область, берёза дровяная и баланс. Делаю ЭСД на рейс и документы на древесину.&lt;br&gt;&lt;br&gt;Многие думают, что на дрова бумаги не нужны. Нужны такие же, как на деловой лес. Особенно если возите машинами на продажу или покупатель юрлицо и проводит покупку по бухгалтерии.&lt;br&gt;&lt;br&gt;Порядок простой. Оформляю договор купли-продажи на ваш объём, завожу древесину в ФГИС ЛК, ставлю на баланс. Дальше на каждую машину выписываю сопроводительный документ с QR кодом.&lt;br&gt;&lt;br&gt;От вас порода, кубатура, номер машины и маршрут. Документ готов обычно за час.&lt;br&gt;&lt;br&gt;Кто возит постоянно, берёт сопровождение помесячно.&lt;br&gt;&lt;br&gt;Берёза дрова, баланс, кругляк, осина, ольха, ЭСД на рейс, QR код, документы ФГИС ЛК, Брянская область.</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n15/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/06/06_02.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/06/06_03.jpg</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Брянская обл., Мглин, ул. Советская, 10</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>2026-11-04T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>2026-10-05T14:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>2026-11-04T11:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>6108956389</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Лес кругляк хвоя(QR код на вывоз)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Рязанская область, хвойный кругляк, ель и сосна. Делаю QR коды на вывоз леса и документы на объём.&lt;br&gt;&lt;br&gt;Частая ситуация: лес спилили при расчистке участка или купили у хозяйства, он лежит, покупатель есть, а продать нельзя. В государственной системе учёта этого объёма нет, для закона его как бы не существует.&lt;br&gt;&lt;br&gt;Как закрывается. Смотрим объём и породу. Оформляю договор купли-продажи на партию, это законное основание. Завожу древесину в ФГИС ЛК и ставлю вам на баланс. Дальше на каждый рейс выдаю ЭСД с QR кодом.&lt;br&gt;&lt;br&gt;После этого машина едет спокойно, а покупатель видит нормальные документы.&lt;br&gt;&lt;br&gt;Работаю удалённо по всей стране, кабинет и подпись вам не нужны. Разбор ситуации бесплатный.&lt;br&gt;&lt;br&gt;Ель кругляк, сосна, хвоя, пиловочник, баланс, QR код на вывоз, ЭСД, документы ФГИС ЛК, Рязанская область.</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261005/g2_dok_fgis.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_07_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_07_3.jpg</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Рязанская обл., Сасово, ул. Ленина, 14</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>2026-11-04T12:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>2026-10-05T15:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>2026-11-04T12:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2386155403</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Осина баланс дрова(QR и документы)</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Тамбовская область, осина на баланс и дрова. Помогаю с QR кодами на перевозку и с документами на древесину.&lt;br&gt;&lt;br&gt;Осину берут плитные комбинаты, но на приёмке сразу спрашивают, откуда объём. Без бумаг партию разворачивают, и неважно, сколько вы её везли.&lt;br&gt;&lt;br&gt;Беру это на себя. Оформляю договор купли-продажи как основание на объём, завожу партию в ФГИС ЛК, ставлю вам на баланс. На каждую машину делаю ЭСД с QR кодом, обычно в течение часа.&lt;br&gt;&lt;br&gt;Отдельно помогаю тем, кто купил лес у частника и не понимает, как провести такую покупку. Это оформляется через меня.&lt;br&gt;&lt;br&gt;Всё удалённо, ехать никуда не надо. Напишите объём и куда везёте, посчитаю.&lt;br&gt;&lt;br&gt;Осина баланс, дрова, кругляк, берёза, ольха, QR код на перевозку, ЭСД, документы ФГИС ЛК, Тамбовская область.</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/n02_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_02_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_02_3.jpg</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Тамбовская обл., Уварово, ул. Советская, 4</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>240</v>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Осина</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>2026-11-04T14:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>2026-10-05T17:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>2026-11-04T14:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>8271667438</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Пиломатериал хвоя(эсд и QR на рейс)</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Липецкая область, пиломатериал хвоя. Делаю ЭСД и QR коды на рейс, оформляю документы на древесину.&lt;br&gt;&lt;br&gt;Чем конкретно помогаю. Первое: документ на машину. Это электронная накладная из ФГИС ЛК с QR кодом, нужна на каждую перевозку, хоть кругляк, хоть доска, хоть дрова. Второе: сам объём. Если его нет в системе, оформляю договор купли-продажи и завожу партию вам на баланс. Третье: отчётность за период, чтобы не прилетел штраф.&lt;br&gt;&lt;br&gt;От вас порода, кубатура, номер машины и маршрут. Документ присылаю обычно за час.&lt;br&gt;&lt;br&gt;Работаю с пилорамами, ИП и частниками, удалённо по всей стране. Свой кабинет и электронная подпись вам не нужны.&lt;br&gt;&lt;br&gt;Пиломатериал хвоя, доска, брус, кругляк, пиловочник, ЭСД на рейс, QR код, документы ФГИС ЛК, Липецкая область.</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261005/g3_esd_reis.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_06_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_06_3.jpg</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Липецкая обл., Лебедянь, ул. Советская, 23</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>280</v>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>2026-11-04T15:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>2026-10-05T18:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>2026-11-04T15:30:00+03:00</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -30929,9 +30929,19 @@
           <t>Псковская обл., Новоржев, ул. Германа, 20</t>
         </is>
       </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P146" t="n">
@@ -31064,9 +31074,19 @@
           <t>Смоленская обл., Дорогобуж, ул. Мира, 2</t>
         </is>
       </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P147" t="n">
@@ -31199,9 +31219,19 @@
           <t>Брянская обл., Мглин, ул. Советская, 10</t>
         </is>
       </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P148" t="n">
@@ -31334,9 +31364,19 @@
           <t>Рязанская обл., Сасово, ул. Ленина, 14</t>
         </is>
       </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P149" t="n">
@@ -31469,9 +31509,19 @@
           <t>Тамбовская обл., Уварово, ул. Советская, 4</t>
         </is>
       </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -31604,9 +31654,19 @@
           <t>Липецкая обл., Лебедянь, ул. Советская, 23</t>
         </is>
       </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P151" t="n">

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -11045,7 +11045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK151"/>
+  <dimension ref="A1:AK157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -31750,6 +31750,876 @@
       <c r="AK151" t="inlineStr">
         <is>
           <t>2026-11-04T15:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>7620518916</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Сосна кругляк лесовоз(эсд на рейс)</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Курская область, сосновый кругляк и пиловочник. Делаю ЭСД на рейс и документы на древесину. Сам лес не продаю, занимаюсь бумагами.&lt;br&gt;&lt;br&gt;На каждую машину с лесом нужен электронный сопроводительный документ. В нём QR код, его сканируют на посту и на весовой. Нет документа, значит рейс под вопросом и штраф.&lt;br&gt;&lt;br&gt;Как работаем. Вы пишете породу, сколько кубов, номер машины и куда едет. Я делаю документ и отправляю, обычно в течение часа.&lt;br&gt;&lt;br&gt;Если вашего объёма нет в ФГИС ЛК, сначала завожу его туда: оформляю договор купли-продажи на партию и ставлю её вам на баланс. После этого лес можно законно продавать и возить.&lt;br&gt;&lt;br&gt;Свой кабинет и электронную подпись заводить не нужно, всё с моей стороны, удалённо.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, лесовоз, ЭСД на рейс, QR код на перевозку, документы ФГИС ЛК, Курская область.</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261006/h1_qr_reis.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/07/07_02.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/07/07_03.jpg</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Курская обл., Суджа, ул. Ленина, 18</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>230</v>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>2026-11-05T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>2026-10-06T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>2026-11-05T07:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>1067002415</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Берёза фанкряж баланс(QR на вывоз)</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Липецкая область, берёза на фанкряж и баланс. Делаю QR коды на вывоз и документы на древесину.&lt;br&gt;&lt;br&gt;Фанкряж и баланс отгружают быстро, а документы тормозят всю работу. Комбинат на приёмке первым делом смотрит происхождение, и без бумаг партию разворачивают.&lt;br&gt;&lt;br&gt;Что делаю. Оформляю договор купли-продажи на ваш объём, завожу древесину в ФГИС ЛК, ставлю на баланс. Дальше на каждую машину выписываю ЭСД с QR кодом, тот самый, который проверяют на дороге.&lt;br&gt;&lt;br&gt;Если остатки в системе разошлись с фактом, привожу их в порядок, иначе отгрузки начнут блокировать.&lt;br&gt;&lt;br&gt;От вас порода, кубатура, номер машины и маршрут. Документ готов обычно за час.&lt;br&gt;&lt;br&gt;Берёза фанкряж, баланс, дрова, кругляк, осина, QR код на вывоз, ЭСД, документы ФГИС ЛК, Липецкая область.</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/11/11_01.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/11/11_02.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/11/11_03.jpg</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Липецкая обл., Данков, ул. Ленина, 14</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>210</v>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>2026-11-05T08:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>2026-10-06T11:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>2026-11-05T08:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>1152981799</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Доска обрезная хвоя(документы фгис)</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Белгородская область, пиломатериал хвоя. Помогаю с документами на доску и брус и с QR кодами на перевозку.&lt;br&gt;&lt;br&gt;Самый частый вопрос: нужен ли документ, если лес уже распилен. Нужен. Переработка учёт не отменяет, и машину с доской проверяют так же, как с кругляком.&lt;br&gt;&lt;br&gt;Что делаю. Завожу объём в ФГИС ЛК, оформляю происхождение договором купли-продажи, выписываю ЭСД с QR кодом на каждую отгрузку. Собираю пакет, который спокойно принимает бухгалтерия покупателя.&lt;br&gt;&lt;br&gt;От вас порода, кубатура и маршрут. Документ присылаю в течение часа.&lt;br&gt;&lt;br&gt;Пилорамам, которые отгружают постоянно, считаю помесячно, так выходит дешевле.&lt;br&gt;&lt;br&gt;Доска обрезная, брус, брусок, пиломатериал хвоя, QR код на перевозку, ЭСД, документы ФГИС ЛК, Белгородская область.</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261006/h2_dok.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/10/10_02.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/10/10_03.jpg</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Белгородская обл., Алексеевка, ул. Мостовая, 95</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>270</v>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>2026-11-05T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>2026-10-06T13:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>2026-11-05T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>7127110787</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Ель пиловочник кругляк(QR на рейс)</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Саратовская область, еловый пиловочник и кругляк. Делаю QR коды на рейс и документы на объём.&lt;br&gt;&lt;br&gt;Частая ситуация: лес спилили при расчистке участка или купили у хозяйства, он лежит, покупатель есть, а продать нельзя. В государственной системе учёта этого объёма нет, для закона его как бы не существует.&lt;br&gt;&lt;br&gt;Как закрывается. Смотрим объём и породу. Оформляю договор купли-продажи на партию, это законное основание. Завожу древесину в ФГИС ЛК и ставлю вам на баланс. Дальше на каждый рейс выдаю ЭСД с QR кодом.&lt;br&gt;&lt;br&gt;После этого машина едет спокойно, а покупатель видит нормальные документы.&lt;br&gt;&lt;br&gt;Работаю удалённо по всей стране, кабинет и подпись вам не нужны. Разбор ситуации бесплатный.&lt;br&gt;&lt;br&gt;Ель пиловочник, кругляк, сосна, хвоя, баланс, QR код на рейс, ЭСД, документы ФГИС ЛК, Саратовская область.</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261006/h3_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/12/12_02.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/12/12_03.jpg</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Саратовская обл., Ртищево, ул. Красная, 6</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>260</v>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>2026-11-05T11:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>2026-10-06T14:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>2026-11-05T11:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>8621917267</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Осина дрова баланс(эсд и документы)</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Пензенская область, осина на баланс и дрова. Делаю ЭСД на рейс и документы на древесину.&lt;br&gt;&lt;br&gt;Многие думают, что на дрова бумаги не нужны. Нужны такие же, как на деловой лес. Особенно если возите машинами на продажу или покупатель юрлицо и проводит покупку по бухгалтерии.&lt;br&gt;&lt;br&gt;Порядок простой. Оформляю договор купли-продажи на ваш объём, завожу древесину в ФГИС ЛК, ставлю на баланс. Дальше на каждую машину выписываю сопроводительный документ с QR кодом.&lt;br&gt;&lt;br&gt;От вас порода, кубатура, номер машины и маршрут. Документ готов обычно за час.&lt;br&gt;&lt;br&gt;Кто возит постоянно, берёт сопровождение помесячно, так дешевле и быстрее.&lt;br&gt;&lt;br&gt;Осина дрова, баланс, кругляк, берёза, ольха, ЭСД на рейс, QR код на перевозку, документы ФГИС ЛК, Пензенская область.</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/12/12_01.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_16_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_16_3.jpg</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Пензенская обл., Никольск, ул. Ленина, 15</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>190</v>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Осина</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>2026-11-05T13:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>2026-10-06T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>2026-11-05T13:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>6184052263</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Хвоя кругляк оптом(QR на вывозку)</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Калужская область, хвойный кругляк оптом. Делаю QR коды на вывозку и документы на древесину.&lt;br&gt;&lt;br&gt;Когда объём идёт потоком, документы нужны на каждую машину, и собирать их в последний момент не выходит. Беру эту часть на себя целиком.&lt;br&gt;&lt;br&gt;Что делаю. Оформляю происхождение объёма договором купли-продажи, завожу партию в ФГИС ЛК, ставлю вам на баланс, свожу остатки перед отгрузками. На каждый рейс выдаю ЭСД с QR кодом, обычно в течение часа.&lt;br&gt;&lt;br&gt;Работаю и с разовой машиной, и с постоянным потоком. Для регулярных отгрузок считаю помесячно.&lt;br&gt;&lt;br&gt;От вас порода, кубатура, номера машин и маршруты. Всё удалённо, кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Сосна кругляк, ель, хвоя оптом, пиловочник, баланс, QR код на вывозку, ЭСД, документы ФГИС ЛК, Калужская область.</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261006/h4_qr15.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_12_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_12_3.jpg</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Калужская обл., Спас-Деменск, ул. Советская, 99</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P157" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>2026-11-05T14:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>2026-10-06T17:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>2026-11-05T14:30:00+03:00</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -11045,7 +11045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK157"/>
+  <dimension ref="A1:AK163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -32620,6 +32620,876 @@
       <c r="AK157" t="inlineStr">
         <is>
           <t>2026-11-05T14:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>8476209398</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Берёза кругляк, QR код на рейс</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Брянская область, берёза кругляком, дрова и баланс. Делаю QR коды на рейс и документы на древесину. Сам лес не продаю, занимаюсь бумагами.&lt;br&gt;&lt;br&gt;На каждую машину с лесом нужен ЭСД, электронная накладная из ФГИС ЛК. В ней QR код, его сканируют на посту и на весовой. Нет документа, значит рейс под вопросом и штраф.&lt;br&gt;&lt;br&gt;Как работаем. Вы пишете породу, сколько кубов, номер машины и куда едет. Я делаю документ и отправляю, обычно в течение часа.&lt;br&gt;&lt;br&gt;Если вашего объёма нет в ФГИС ЛК, сначала завожу его туда: оформляю договор купли-продажи на партию и ставлю её вам на баланс. После этого лес можно законно продавать и возить.&lt;br&gt;&lt;br&gt;Свой кабинет и электронную подпись заводить не нужно, всё с моей стороны, удалённо по всей стране.&lt;br&gt;&lt;br&gt;Берёза кругляк, дрова, баланс, QR код на рейс, ЭСД на перевозку, документы ФГИС ЛК, Брянская область.</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261007/k1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/13/13_02.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/13/13_03.jpg</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Брянская обл., Севск, ул. Фрунзе, 4</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P158" t="n">
+        <v>2900</v>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>2026-11-06T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>2026-10-07T09:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>2026-11-06T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>3884811476</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник, ЭСД на вывоз</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Калужская область, сосновый пиловочник и кругляк. Делаю ЭСД на вывоз и документы на древесину.&lt;br&gt;&lt;br&gt;Частая ситуация: лес заготовлен, покупатель найден, а вывезти нельзя. В государственной системе учёта объёма нет, для закона он как бы не существует, и машину на дороге остановят первым же вопросом про происхождение.&lt;br&gt;&lt;br&gt;Как закрывается. Смотрим объём и породу. Оформляю договор купли-продажи на партию, это законное основание. Завожу древесину в ФГИС ЛК и ставлю вам на баланс. Дальше на каждый рейс выдаю сопроводительный документ с QR кодом.&lt;br&gt;&lt;br&gt;После этого машина едет спокойно, а покупатель видит нормальные бумаги.&lt;br&gt;&lt;br&gt;Работаю удалённо, кабинет и электронная подпись вам не нужны. Разбор ситуации бесплатный.&lt;br&gt;&lt;br&gt;Сосна пиловочник, кругляк, хвоя, баланс, ЭСД на вывоз, QR код на перевозку, документы ФГИС ЛК, Калужская область.</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261007/k2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/15/15_02.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/15/15_03.jpg</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Калужская обл., Мещовск, ул. Горького, 7</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P159" t="n">
+        <v>4900</v>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>2026-11-06T07:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>2026-10-07T10:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>2026-11-06T07:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>1112119864</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Ель баланс, QR код на перевозку</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Рязанская область, еловый баланс и кругляк. Делаю QR коды на перевозку и документы на объём.&lt;br&gt;&lt;br&gt;Баланс отгружают потоком, а бумаги каждый раз собираются в последний момент. Комбинат на приёмке первым делом смотрит происхождение, и без документов партию разворачивают.&lt;br&gt;&lt;br&gt;Что делаю. Оформляю договор купли-продажи на ваш объём, завожу древесину в ФГИС ЛК, ставлю на баланс, свожу остатки перед отгрузками. На каждую машину выписываю ЭСД с QR кодом, обычно в течение часа.&lt;br&gt;&lt;br&gt;От вас порода, кубатура, номер машины и маршрут. Остальное на мне.&lt;br&gt;&lt;br&gt;Кто возит постоянно, берёт сопровождение помесячно, так дешевле и быстрее.&lt;br&gt;&lt;br&gt;Ель баланс, кругляк, пиловочник, сосна, QR код на перевозку, ЭСД на рейс, документы ФГИС ЛК, Рязанская область.</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/06/06_01.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/09/09_02.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/09/09_03.jpg</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Рязанская обл., Пронск, ул. Первомайская, 12</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P160" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>2026-11-06T09:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>2026-10-07T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>2026-11-06T09:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>1346611059</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Осина дрова, ЭСД на машину</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Тамбовская область, осина на дрова и баланс. Делаю ЭСД на машину и документы на древесину.&lt;br&gt;&lt;br&gt;Многие думают, что на дрова бумаги не нужны. Нужны такие же, как на деловой лес. Особенно если возите машинами на продажу или покупатель юрлицо и проводит покупку по бухгалтерии.&lt;br&gt;&lt;br&gt;Порядок простой. Оформляю договор купли-продажи на ваш объём, завожу древесину в ФГИС ЛК, ставлю на баланс. Дальше на каждый рейс выписываю сопроводительный документ с QR кодом.&lt;br&gt;&lt;br&gt;От вас порода, кубатура, номер машины и маршрут. Документ готов обычно за час.&lt;br&gt;&lt;br&gt;Отдельно помогаю тем, кто купил лес у частника и не понимает, как провести такую покупку. Это оформляется через меня.&lt;br&gt;&lt;br&gt;Осина дрова, баланс, кругляк, берёза, ольха, ЭСД на машину, QR код на перевозку, документы ФГИС ЛК, Тамбовская область.</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261007/k3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/14/14_02.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/14/14_03.jpg</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Тамбовская обл., Инжавино, ул. Карла Маркса, 9</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P161" t="n">
+        <v>2600</v>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Осина</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>2026-11-06T10:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>2026-10-07T13:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>2026-11-06T10:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>9130061464</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Хвоя кругляк, QR код на отгрузку</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Липецкая область, хвойный кругляк, сосна и ель. Делаю QR коды на отгрузку и документы на древесину.&lt;br&gt;&lt;br&gt;Когда объём идёт партиями, документы нужны на каждую машину, и собирать их по ходу не выходит. Беру эту часть на себя целиком.&lt;br&gt;&lt;br&gt;Что делаю. Оформляю происхождение объёма договором купли-продажи, завожу партию в ФГИС ЛК, ставлю вам на баланс, свожу остатки перед отгрузками. На каждый рейс выдаю ЭСД с QR кодом, обычно в течение часа.&lt;br&gt;&lt;br&gt;Работаю и с разовой машиной, и с постоянным потоком. Для регулярных отгрузок считаю помесячно.&lt;br&gt;&lt;br&gt;Всё удалённо, свой кабинет в системе и электронная подпись вам не нужны.&lt;br&gt;&lt;br&gt;Сосна кругляк, ель, хвоя, пиловочник, баланс, QR код на отгрузку, ЭСД на рейс, документы ФГИС ЛК, Липецкая область.</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261007/k4.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/10/10_00.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/09/09_00.jpg</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Липецкая обл., Задонск, ул. Крупской, 21</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P162" t="n">
+        <v>4300</v>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>2026-11-06T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>2026-10-07T15:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>2026-11-06T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>4980714650</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Доска обрезная, ЭСД на рейс</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Белгородская область, пиломатериал хвоя. Делаю ЭСД на рейс и документы на доску и брус.&lt;br&gt;&lt;br&gt;Самый частый вопрос: нужен ли документ, если лес уже распилен. Нужен. Переработка учёт не отменяет, машину с доской проверяют так же, как с кругляком, и покупатель с бухгалтерией спрашивает происхождение в первую очередь.&lt;br&gt;&lt;br&gt;Что делаю. Завожу объём в ФГИС ЛК, оформляю происхождение договором купли-продажи, выписываю ЭСД с QR кодом на каждую отгрузку, собираю пакет, который спокойно принимает бухгалтерия.&lt;br&gt;&lt;br&gt;От вас порода, кубатура и маршрут. Документ присылаю в течение часа.&lt;br&gt;&lt;br&gt;Пилорамам, которые отгружают постоянно, считаю помесячно.&lt;br&gt;&lt;br&gt;Доска обрезная, брус, брусок, пиломатериал хвоя, ЭСД на рейс, QR код на перевозку, документы ФГИС ЛК, Белгородская область.</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261007/k5.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/13/13_00.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/07/07_00.jpg</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Белгородская обл., Короча, ул. Дорошенко, 15</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P163" t="n">
+        <v>3800</v>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>2026-11-06T13:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>2026-11-06T13:30:00+03:00</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -11045,7 +11045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK163"/>
+  <dimension ref="A1:AK169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -33490,6 +33490,876 @@
       <c r="AK163" t="inlineStr">
         <is>
           <t>2026-11-06T13:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>6692153290</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Сосна кругляк лесовоз(QR на рейс)</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Калужская область, сосновый кругляк и пиловочник. Делаю QR коды на рейс и документы на древесину. Сам лес не продаю, занимаюсь бумагами.&lt;br&gt;&lt;br&gt;На каждую машину с лесом нужен ЭСД, электронная накладная из ФГИС ЛК. В ней QR код, его сканируют на посту и на весовой. Нет документа, значит рейс под вопросом и штраф.&lt;br&gt;&lt;br&gt;Как работаем. Вы пишете породу, сколько кубов, номер машины и куда едет. Я делаю документ и отправляю, обычно в течение часа.&lt;br&gt;&lt;br&gt;Если вашего объёма нет в ФГИС ЛК, сначала завожу его туда: оформляю договор купли-продажи на партию и ставлю её вам на баланс. После этого лес можно законно продавать и возить.&lt;br&gt;&lt;br&gt;Свой кабинет и электронную подпись заводить не нужно, всё с моей стороны, удалённо по всей стране.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, лесовоз, QR код на рейс, ЭСД на перевозку, документы ФГИС ЛК, Калужская область.</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261008/m1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_01_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_01_3.jpg</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Калужская обл., Юхнов, ул. Кирова, 8</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P164" t="n">
+        <v>230</v>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>2026-11-07T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>2026-10-08T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>2026-11-07T07:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>7019102831</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Ель пиловочник кругляк(эсд на вывоз)</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Рязанская область, еловый пиловочник и кругляк. Делаю ЭСД на вывоз и документы на объём.&lt;br&gt;&lt;br&gt;Частая ситуация: лес заготовлен, покупатель найден, а вывезти нельзя. В государственной системе учёта объёма нет, для закона он как бы не существует, и машину остановят первым же вопросом про происхождение.&lt;br&gt;&lt;br&gt;Как закрывается. Смотрим объём и породу. Оформляю договор купли-продажи на партию, это законное основание. Завожу древесину в ФГИС ЛК и ставлю вам на баланс. Дальше на каждый рейс выдаю сопроводительный документ с QR кодом.&lt;br&gt;&lt;br&gt;После этого машина едет спокойно, а покупатель видит нормальные бумаги.&lt;br&gt;&lt;br&gt;Работаю удалённо, кабинет и электронная подпись вам не нужны. Разбор ситуации бесплатный.&lt;br&gt;&lt;br&gt;Ель пиловочник, кругляк, сосна, хвоя, баланс, ЭСД на вывоз, QR код на перевозку, документы ФГИС ЛК, Рязанская область.</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261008/m2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_03_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_03_3.jpg</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Рязанская обл., Шацк, ул. Красная площадь, 7</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P165" t="n">
+        <v>260</v>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>2026-11-07T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>2026-10-08T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>2026-11-07T08:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>5312649583</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Хвоя кругляк оптом(QR на вывозку)</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Белгородская область, хвойный кругляк оптом, сосна и ель. Делаю QR коды на вывозку и документы на древесину.&lt;br&gt;&lt;br&gt;Когда объём идёт потоком, документы нужны на каждую машину, и собирать их по ходу не выходит. Беру эту часть на себя целиком.&lt;br&gt;&lt;br&gt;Что делаю. Оформляю происхождение объёма договором купли-продажи, завожу партию в ФГИС ЛК, ставлю вам на баланс, свожу остатки перед отгрузками. На каждый рейс выдаю ЭСД с QR кодом, обычно в течение часа.&lt;br&gt;&lt;br&gt;Работаю и с разовой машиной, и с постоянным потоком. Для регулярных отгрузок считаю помесячно, так дешевле.&lt;br&gt;&lt;br&gt;Всё удалённо, свой кабинет в системе и электронная подпись вам не нужны.&lt;br&gt;&lt;br&gt;Сосна кругляк, ель, хвоя оптом, пиловочник, баланс, QR код на вывозку, ЭСД на рейс, документы ФГИС ЛК, Белгородская область.</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261008/m3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_05_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_05_3.jpg</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Белгородская обл., Грайворон, ул. Комсомольская, 21</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P166" t="n">
+        <v>290</v>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>2026-11-07T09:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>2026-10-08T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>2026-11-07T09:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2397223937</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Берёза дрова баланс, эсд на рейс</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Мордовия, берёза дровяная и баланс. Делаю ЭСД на рейс и документы на древесину.&lt;br&gt;&lt;br&gt;Многие думают, что на дрова бумаги не нужны. Нужны такие же, как на деловой лес. Особенно если возите машинами на продажу или покупатель юрлицо и проводит покупку по бухгалтерии.&lt;br&gt;&lt;br&gt;Порядок простой. Оформляю договор купли-продажи на ваш объём, завожу древесину в ФГИС ЛК, ставлю на баланс. Дальше на каждую машину выписываю сопроводительный документ с QR кодом.&lt;br&gt;&lt;br&gt;От вас порода, кубатура, номер машины и маршрут. Документ готов обычно за час.&lt;br&gt;&lt;br&gt;Кто возит постоянно, берёт сопровождение помесячно, так дешевле и быстрее.&lt;br&gt;&lt;br&gt;Берёза дрова, баланс, кругляк, осина, ольха, ЭСД на рейс, QR код на перевозку, документы ФГИС ЛК, Мордовия.</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/n07_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_08_2.png|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_08_3.png</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Республика Мордовия, Темников, ул. Коммунистическая, 16</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P167" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>2026-11-07T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>2026-10-08T13:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>2026-11-07T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>3209735867</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Осина баланс дрова, QR на вывоз</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Смоленская область, осина на баланс и дрова. Делаю QR коды на вывоз и документы на древесину.&lt;br&gt;&lt;br&gt;Осину берут плитные комбинаты, но на приёмке сразу спрашивают, откуда объём. Без бумаг партию разворачивают, и неважно, сколько вы её везли.&lt;br&gt;&lt;br&gt;Беру это на себя. Оформляю договор купли-продажи как основание на объём, завожу партию в ФГИС ЛК, ставлю вам на баланс. На каждую машину делаю ЭСД с QR кодом, обычно в течение часа.&lt;br&gt;&lt;br&gt;Отдельно помогаю тем, кто купил лес у частника и не понимает, как провести такую покупку. Это оформляется через меня.&lt;br&gt;&lt;br&gt;Всё удалённо, ехать никуда не надо. Напишите объём и куда везёте, посчитаю.&lt;br&gt;&lt;br&gt;Осина баланс, дрова, кругляк, берёза, ольха, QR код на вывоз, ЭСД на рейс, документы ФГИС ЛК, Смоленская область.</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261008/m4.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_15_2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_17_2.jpg</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Смоленская обл., Сычёвка, ул. Пушкина, 11</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P168" t="n">
+        <v>190</v>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Осина</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>2026-11-07T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF168" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>2026-10-08T14:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>2026-11-07T11:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>9674591295</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Доска и брус хвоя, документы фгис</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Курская область, пиломатериал хвоя. Делаю документы на доску и брус и QR коды на перевозку.&lt;br&gt;&lt;br&gt;Самый частый вопрос: нужен ли документ, если лес уже распилен. Нужен. Переработка учёт не отменяет, машину с доской проверяют так же, как с кругляком, и покупатель с бухгалтерией спрашивает происхождение в первую очередь.&lt;br&gt;&lt;br&gt;Что делаю. Завожу объём в ФГИС ЛК, оформляю происхождение договором купли-продажи, выписываю ЭСД с QR кодом на каждую отгрузку, собираю пакет, который спокойно принимает бухгалтерия.&lt;br&gt;&lt;br&gt;От вас порода, кубатура и маршрут. Документ присылаю в течение часа.&lt;br&gt;&lt;br&gt;Пилорамам, которые отгружают постоянно, считаю помесячно.&lt;br&gt;&lt;br&gt;Доска обрезная, брус, брусок, пиломатериал хвоя, документы ФГИС ЛК, ЭСД на рейс, QR код на перевозку, Курская область.</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/n04_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_17_3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_17_1.png</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Курская обл., Дмитриев, ул. Володарского, 44</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P169" t="n">
+        <v>280</v>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>2026-11-07T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>2026-10-08T15:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>2026-11-07T12:00:00+03:00</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -11045,7 +11045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK169"/>
+  <dimension ref="A1:AK175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -34360,6 +34360,876 @@
       <c r="AK169" t="inlineStr">
         <is>
           <t>2026-11-07T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>5442064706</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Сосна кругляк (QR код на перевозку)</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа.&lt;br&gt;&lt;br&gt;Брянская область, сосновый кругляк и пиловочник. Делаю документы на древесину. Сам лес не продаю, занимаюсь бумагами.&lt;br&gt;&lt;br&gt;На каждую машину с лесом нужен ЭСД, электронная накладная из ФГИС ЛК. В ней QR код, его сканируют на посту и на весовой. Нет документа, значит рейс под вопросом и штраф.&lt;br&gt;&lt;br&gt;Порядок работы. Вы пишете породу, сколько кубов, номер машины и куда едет. Я делаю документ и отправляю, обычно за пятнадцать минут.&lt;br&gt;&lt;br&gt;Если вашего объёма нет в ФГИС ЛК, сначала завожу его туда: оформляю договор купли-продажи на партию и ставлю её вам на баланс. После этого лес можно законно продавать и возить.&lt;br&gt;&lt;br&gt;Свой кабинет и электронную подпись заводить не нужно, всё с моей стороны, удалённо по всей стране.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, QR код на перевозку, ЭСД на рейс, документы ФГИС ЛК, Брянская область.</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261010/p1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/1481923475/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/1481923475/3.jpg</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Брянская обл., Карачев, ул. Урицкого, 12</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P170" t="n">
+        <v>3100</v>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>2026-11-09T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>2026-10-10T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>2026-11-09T05:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>1652593484</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Ель пиловочник кругляк(QR на рейс)</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа.&lt;br&gt;&lt;br&gt;Смоленская область, еловый пиловочник и кругляк. Делаю документы на вывоз и перевозку.&lt;br&gt;&lt;br&gt;Частая ситуация: лес заготовлен, покупатель найден, а вывезти нельзя. В системе учёта объёма нет, для закона он как бы не существует, и машину остановят первым же вопросом про происхождение.&lt;br&gt;&lt;br&gt;Как закрывается. Смотрим объём и породу. Оформляю договор купли-продажи на партию, это законное основание. Завожу древесину в ФГИС ЛК и ставлю вам на баланс. Дальше на каждый рейс выдаю сопроводительный документ с QR кодом.&lt;br&gt;&lt;br&gt;После этого машина едет спокойно, а покупатель видит нормальные бумаги.&lt;br&gt;&lt;br&gt;Работаю удалённо, кабинет и электронная подпись вам не нужны. Разбор ситуации бесплатный.&lt;br&gt;&lt;br&gt;Ель пиловочник, кругляк, сосна, хвоя, баланс, QR код на рейс, ЭСД на вывоз, документы ФГИС ЛК, Смоленская область.</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261010/p2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/2153018262/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/2153018262/3.jpg</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Смоленская обл., Ельня, ул. Карла Либкнехта, 9</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P171" t="n">
+        <v>260</v>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>2026-11-09T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>2026-10-10T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>2026-11-09T06:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>9220763535</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Хвоя кругляк оптом(QR на вывозку)</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа.&lt;br&gt;&lt;br&gt;Калужская область, хвойный кругляк оптом, сосна и ель. Делаю документы на вывозку.&lt;br&gt;&lt;br&gt;Когда объём идёт потоком, бумаги нужны на каждую машину, и собирать их по ходу не выходит. Беру эту часть на себя целиком.&lt;br&gt;&lt;br&gt;Что делаю. Оформляю происхождение объёма договором купли-продажи, завожу партию в ФГИС ЛК, ставлю вам на баланс, свожу остатки перед отгрузками. На каждый рейс выдаю ЭСД с QR кодом.&lt;br&gt;&lt;br&gt;Работаю и с разовой машиной, и с постоянным потоком. Для регулярных отгрузок считаю помесячно, так дешевле.&lt;br&gt;&lt;br&gt;Всё удалённо, свой кабинет в системе и электронная подпись вам не нужны.&lt;br&gt;&lt;br&gt;Сосна кругляк, ель, хвоя оптом, пиловочник, баланс, QR код на вывозку, ЭСД на рейс, документы ФГИС ЛК, Калужская область.</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261010/p3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/3819625066/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/3819625066/3.jpg</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Калужская обл., Мосальск, ул. Чапаева, 4</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P172" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>2026-11-09T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>2026-10-10T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>2026-11-09T08:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>4254993016</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Берёза дрова баланс(эсд на рейс)</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа.&lt;br&gt;&lt;br&gt;Рязанская область, берёза дровяная и баланс. Делаю ЭСД на рейс и документы на древесину.&lt;br&gt;&lt;br&gt;Многие думают, что на дрова бумаги не нужны. Нужны такие же, как на деловой лес. Особенно если возите машинами на продажу или покупатель юрлицо и проводит покупку по бухгалтерии.&lt;br&gt;&lt;br&gt;Порядок простой. Оформляю договор купли-продажи на ваш объём, завожу древесину в ФГИС ЛК, ставлю на баланс. Дальше на каждую машину выписываю сопроводительный документ с QR кодом.&lt;br&gt;&lt;br&gt;От вас порода, кубатура, номер машины и маршрут. Остальное на мне.&lt;br&gt;&lt;br&gt;Кто возит постоянно, берёт сопровождение помесячно, так дешевле и быстрее.&lt;br&gt;&lt;br&gt;Берёза дрова, баланс, кругляк, осина, ольха, ЭСД на рейс, QR код на перевозку, документы ФГИС ЛК, Рязанская область.</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261010/p4.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/4382774059/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/4382774059/3.jpg</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Рязанская обл., Сапожок, ул. Гагарина, 18</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P173" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>2026-11-09T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>2026-10-10T12:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>2026-11-09T09:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>9925868476</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Берёза кругляк, QR код на рейс</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа.&lt;br&gt;&lt;br&gt;Липецкая область, берёза кругляком, дрова и баланс. Делаю QR коды на рейс и документы на древесину.&lt;br&gt;&lt;br&gt;На каждую машину с лесом нужна электронная накладная из ФГИС ЛК с QR кодом. Её сканируют на посту и на весовой, без неё рейс начинать рискованно.&lt;br&gt;&lt;br&gt;Как работаем. Вы пишете породу, сколько кубов, номер машины и куда едет. Я делаю документ и присылаю, обычно за пятнадцать минут.&lt;br&gt;&lt;br&gt;Если объёма нет в системе, сначала завожу его: оформляю договор купли-продажи на партию и ставлю её вам на баланс. После этого лес можно законно продавать и возить.&lt;br&gt;&lt;br&gt;Работаю удалённо по всей стране, свой кабинет и подпись вам не нужны.&lt;br&gt;&lt;br&gt;Берёза кругляк, дрова, баланс, фанкряж, QR код на рейс, ЭСД на перевозку, документы ФГИС ЛК, Липецкая область.</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_01_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/5312403632/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/fgis_doc_mo/01_02.jpg</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Липецкая обл., Чаплыгин, ул. Школьная, 6</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P174" t="n">
+        <v>2500</v>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t>2026-11-09T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF174" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI174" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>2026-10-10T14:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>2026-11-09T11:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>3258597148</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Пиломатериал хвоя, документы фгис</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа.&lt;br&gt;&lt;br&gt;Белгородская область, пиломатериал хвоя. Делаю документы на доску и брус и QR коды на перевозку.&lt;br&gt;&lt;br&gt;Самый частый вопрос: нужен ли документ, если лес уже распилен. Нужен. Переработка учёт не отменяет, машину с доской проверяют так же, как с кругляком, и покупатель с бухгалтерией спрашивает происхождение в первую очередь.&lt;br&gt;&lt;br&gt;Что делаю. Завожу объём в ФГИС ЛК, оформляю происхождение договором купли-продажи, выписываю ЭСД с QR кодом на каждую отгрузку, собираю пакет, который спокойно принимает бухгалтерия.&lt;br&gt;&lt;br&gt;От вас порода, кубатура и маршрут. Документ присылаю в течение часа.&lt;br&gt;&lt;br&gt;Пилорамам, которые отгружают постоянно, считаю помесячно.&lt;br&gt;&lt;br&gt;Пиломатериал хвоя, доска обрезная, брус, брусок, документы ФГИС ЛК, ЭСД на рейс, QR код, Белгородская область.</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_02_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/fgis_doc_mo/01_03.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_07_1.png</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Белгородская обл., Валуйки, ул. Пионерская, 23</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P175" t="n">
+        <v>2900</v>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>2026-11-09T12:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>2026-11-09T12:30:00+03:00</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -11045,7 +11045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK175"/>
+  <dimension ref="A1:AK181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -35230,6 +35230,876 @@
       <c r="AK175" t="inlineStr">
         <is>
           <t>2026-11-09T12:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2861338465</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Берёза кругляк, QR код на рейс</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа.&lt;br&gt;&lt;br&gt;Брянская область, берёза кругляком, дрова и баланс. Делаю документы на древесину. Сам лес не продаю, занимаюсь бумагами.&lt;br&gt;&lt;br&gt;На каждую машину с лесом нужна электронная накладная из ФГИС ЛК с QR кодом. Её сканируют на посту и на весовой, без неё рейс начинать рискованно.&lt;br&gt;&lt;br&gt;Как работаем. Вы пишете породу, сколько кубов, номер машины и куда едет. Я делаю документ и присылаю, обычно за пятнадцать минут.&lt;br&gt;&lt;br&gt;Если объёма нет в системе, сначала завожу его: оформляю договор купли-продажи на партию и ставлю её вам на баланс. После этого лес можно законно продавать и возить.&lt;br&gt;&lt;br&gt;Работаю удалённо по всей стране, свой кабинет и электронная подпись вам не нужны.&lt;br&gt;&lt;br&gt;Берёза кругляк, дрова, баланс, фанкряж, QR код на рейс, ЭСД на перевозку, документы ФГИС ЛК, Брянская область.</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261013/q1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/6654494961/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/6654494961/3.jpg</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Брянская обл., Почеп, ул. Мичурина, 9</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P176" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>2026-11-12T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>2026-10-13T09:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>2026-11-12T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>5178315545</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Хвоя кругляк, QR код на отгрузку</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа.&lt;br&gt;&lt;br&gt;Смоленская область, хвойный кругляк, сосна и ель. Делаю QR коды на отгрузку и документы на древесину.&lt;br&gt;&lt;br&gt;Когда объём идёт партиями, бумаги нужны на каждую машину, и собирать их по ходу не выходит. Беру эту часть на себя целиком.&lt;br&gt;&lt;br&gt;Что делаю. Оформляю происхождение объёма договором купли-продажи, завожу партию в ФГИС ЛК, ставлю вам на баланс, свожу остатки перед отгрузками. На каждый рейс выдаю ЭСД с QR кодом.&lt;br&gt;&lt;br&gt;Работаю и с разовой машиной, и с постоянным потоком. Для регулярных отгрузок считаю помесячно.&lt;br&gt;&lt;br&gt;Всё удалённо, свой кабинет в системе и электронная подпись вам не нужны.&lt;br&gt;&lt;br&gt;Сосна кругляк, ель, хвоя, пиловочник, баланс, QR код на отгрузку, ЭСД на рейс, документы ФГИС ЛК, Смоленская область.</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261013/q2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/7393214976/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/7393214976/3.jpg</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Смоленская обл., Гагарин, ул. Бахтина, 14</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P177" t="n">
+        <v>4300</v>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>2026-11-12T07:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>2026-10-13T10:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>2026-11-12T07:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>3225176732</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Осина баланс дрова, QR на вывоз</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа.&lt;br&gt;&lt;br&gt;Калужская область, осина на баланс и дрова. Делаю QR коды на вывоз и документы на древесину.&lt;br&gt;&lt;br&gt;Осину берут плитные комбинаты, но на приёмке сразу спрашивают, откуда объём. Без бумаг партию разворачивают, и неважно, сколько вы её везли.&lt;br&gt;&lt;br&gt;Беру это на себя. Оформляю договор купли-продажи как основание на объём, завожу партию в ФГИС ЛК, ставлю вам на баланс. На каждую машину делаю ЭСД с QR кодом.&lt;br&gt;&lt;br&gt;Отдельно помогаю тем, кто купил лес у частника и не понимает, как провести такую покупку. Это оформляется через меня.&lt;br&gt;&lt;br&gt;Всё удалённо, ехать никуда не надо. Напишите объём и куда везёте, посчитаю.&lt;br&gt;&lt;br&gt;Осина баланс, дрова, кругляк, берёза, ольха, QR код на вывоз, ЭСД на рейс, документы ФГИС ЛК, Калужская область.</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261013/q3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/8194168577/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/8194168577/3.jpg</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Калужская обл., Медынь, ул. Варшавская, 5</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P178" t="n">
+        <v>190</v>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>Осина</t>
+        </is>
+      </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE178" t="inlineStr">
+        <is>
+          <t>2026-11-12T09:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF178" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ178" t="inlineStr">
+        <is>
+          <t>2026-10-13T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK178" t="inlineStr">
+        <is>
+          <t>2026-11-12T09:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>6745733622</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Доска обрезная, документы и эсд</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа.&lt;br&gt;&lt;br&gt;Рязанская область, пиломатериал хвоя. Делаю документы на доску и брус и QR коды на перевозку.&lt;br&gt;&lt;br&gt;Самый частый вопрос: нужен ли документ, если лес уже распилен. Нужен. Переработка учёт не отменяет, машину с доской проверяют так же, как с кругляком, и покупатель с бухгалтерией спрашивает происхождение в первую очередь.&lt;br&gt;&lt;br&gt;Что делаю. Завожу объём в ФГИС ЛК, оформляю происхождение договором купли-продажи, выписываю ЭСД с QR кодом на каждую отгрузку, собираю пакет, который спокойно принимает бухгалтерия.&lt;br&gt;&lt;br&gt;От вас порода, кубатура и маршрут. Документ присылаю быстро.&lt;br&gt;&lt;br&gt;Пилорамам, которые отгружают постоянно, считаю помесячно.&lt;br&gt;&lt;br&gt;Доска обрезная, брус, брусок, пиломатериал хвоя, ЭСД на рейс, QR код на перевозку, документы ФГИС ЛК, Рязанская область.</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261013/q4.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/01/01_03.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/02/02_00.jpg</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Рязанская обл., Кораблино, ул. Текстильщиков, 3</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P179" t="n">
+        <v>450</v>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>2026-11-12T10:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>2026-10-13T13:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>2026-11-12T10:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2809039681</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Сосна кругляк (QR код на перевозку)</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа.&lt;br&gt;&lt;br&gt;Липецкая область, сосновый кругляк и пиловочник. Делаю документы на перевозку древесины.&lt;br&gt;&lt;br&gt;На каждую машину с лесом нужен ЭСД, электронная накладная из ФГИС ЛК. В ней QR код, его сканируют на посту и на весовой. Нет документа, значит рейс под вопросом и штраф.&lt;br&gt;&lt;br&gt;Порядок работы. Вы пишете породу, сколько кубов, номер машины и куда едет. Я делаю документ и отправляю, обычно за пятнадцать минут.&lt;br&gt;&lt;br&gt;Если вашего объёма нет в ФГИС ЛК, сначала завожу его туда: оформляю договор купли-продажи на партию и ставлю её вам на баланс. После этого лес можно законно продавать и возить.&lt;br&gt;&lt;br&gt;Свой кабинет и электронную подпись заводить не нужно, всё с моей стороны.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, хвоя, баланс, QR код на перевозку, ЭСД на рейс, документы ФГИС ЛК, Липецкая область.</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261013/q5.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/03/03_03.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/5312403632/3.jpg</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Липецкая обл., Лев Толстой, ул. Стаханова, 7</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P180" t="n">
+        <v>3100</v>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>2026-11-12T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>2026-10-13T15:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>2026-11-12T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>8064940085</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Кругляк ель (документы фгис лк)</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа.&lt;br&gt;&lt;br&gt;Белгородская область, еловый кругляк и пиловочник. Делаю документы на древесину и QR коды на рейс.&lt;br&gt;&lt;br&gt;Частая ситуация: лес заготовлен, покупатель найден, а вывезти нельзя. В государственной системе учёта объёма нет, для закона он как бы не существует, и машину остановят первым же вопросом про происхождение.&lt;br&gt;&lt;br&gt;Как закрывается. Смотрим объём и породу. Оформляю договор купли-продажи на партию, это законное основание. Завожу древесину в ФГИС ЛК и ставлю вам на баланс. Дальше на каждый рейс выдаю сопроводительный документ с QR кодом.&lt;br&gt;&lt;br&gt;После этого машина едет спокойно, а покупатель видит нормальные бумаги.&lt;br&gt;&lt;br&gt;Работаю удалённо, разбор ситуации бесплатный.&lt;br&gt;&lt;br&gt;Ель кругляк, пиловочник, сосна, хвоя, баланс, документы ФГИС ЛК, ЭСД на рейс, QR код на перевозку, Белгородская область.</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261013/q6.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/9218798416/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260806/9218798416/3.jpg</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Белгородская обл., Бирюч, ул. Ольминского, 20</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P181" t="n">
+        <v>2350</v>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>2026-11-12T13:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF181" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>2026-10-13T16:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>2026-11-12T13:30:00+03:00</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -11045,7 +11045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK181"/>
+  <dimension ref="A1:AK187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -36100,6 +36100,876 @@
       <c r="AK181" t="inlineStr">
         <is>
           <t>2026-11-12T13:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>7550352105</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Осина баланс дрова, QR на вывоз</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа.&lt;br&gt;&lt;br&gt;Воронежская область, осина на баланс и дрова. Делаю QR коды на вывоз и документы на древесину. Сам лес не продаю, занимаюсь бумагами.&lt;br&gt;&lt;br&gt;Осину берут плитные комбинаты, и на приёмке первым делом спрашивают, откуда объём. Без бумаг партию разворачивают, сколько бы вы её ни везли.&lt;br&gt;&lt;br&gt;Как работаем. Вы пишете породу, кубатуру, номер машины и куда едет. Я делаю ЭСД с QR кодом и присылаю, обычно за пятнадцать минут.&lt;br&gt;&lt;br&gt;Если объёма в системе нет, его заводим по договору купли-продажи. По шагам это на втором фото: подписываем договор, вы оплачиваете по счёту на расчётный счёт, я закрепляю древесину за вами в ФГИС ЛК. За QR на рейс платите уже после того, как документ готов.&lt;br&gt;&lt;br&gt;Отдельно помогаю тем, кто купил лес у частника или с лесополосы и не понимает, как провести такую покупку.&lt;br&gt;&lt;br&gt;Осина баланс, дрова, кругляк, берёза, тополь, QR код на вывоз, ЭСД на рейс, документы ФГИС ЛК, Воронежская область.</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261014/r1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261014/ig_how.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261014/ig_offer.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/logs_close.jpg</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Воронежская обл., Бобров, ул. Кирова, 28</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P182" t="n">
+        <v>190</v>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Осина</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>2026-11-13T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>2026-10-14T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>2026-11-13T06:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>3422954378</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Хвоя кругляк оптом(QR на вывозку)</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа.&lt;br&gt;&lt;br&gt;Оренбургская область, хвойный кругляк оптом, сосна. Делаю QR коды на вывозку и документы на древесину.&lt;br&gt;&lt;br&gt;Когда объём идёт потоком, бумаги нужны на каждую машину, и собирать их по ходу не выходит. Беру эту часть на себя целиком.&lt;br&gt;&lt;br&gt;Что делаю. Оформляю происхождение объёма договором купли-продажи, завожу партию в ФГИС ЛК, ставлю вам на баланс, свожу остатки перед отгрузками. На каждый рейс выдаю ЭСД с QR кодом.&lt;br&gt;&lt;br&gt;Работаю и с разовой машиной, и с постоянным потоком. Для регулярных отгрузок считаю помесячно, так дешевле.&lt;br&gt;&lt;br&gt;Всё удалённо, свой кабинет в системе и электронная подпись вам не нужны.&lt;br&gt;&lt;br&gt;Сосна кругляк, хвоя оптом, пиловочник, баланс, QR код на вывозку, ЭСД на рейс, документы ФГИС ЛК, Оренбургская область, Бузулук.</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261014/r2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/jl15.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n12/1.jpg</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Оренбургская обл., Бузулук, ул. Галактионова, 20</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P183" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>2026-11-13T07:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>2026-10-14T10:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>2026-11-13T07:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>6182191679</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Сосна кругляк (QR код на перевозку)</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа.&lt;br&gt;&lt;br&gt;Самарская область, сосновый кругляк и пиловочник. Делаю документы на перевозку древесины.&lt;br&gt;&lt;br&gt;На каждую машину с лесом нужен ЭСД, электронная накладная из ФГИС ЛК. В ней QR код, его сканируют на посту и на весовой. Нет документа, значит рейс под вопросом и штраф.&lt;br&gt;&lt;br&gt;Порядок работы. Вы пишете породу, сколько кубов, номер машины и куда едет. Я делаю документ и отправляю, обычно за пятнадцать минут.&lt;br&gt;&lt;br&gt;Если объёма в системе нет, его заводим по договору купли-продажи. По шагам это на втором фото: подписываем договор, вы оплачиваете по счёту на расчётный счёт, я закрепляю древесину за вами в ФГИС ЛК. За QR на рейс платите уже после того, как документ готов.&lt;br&gt;&lt;br&gt;Свой кабинет и электронную подпись заводить не нужно, всё с моей стороны.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, хвоя, баланс, QR код на перевозку, ЭСД на рейс, документы ФГИС ЛК, Самарская область.</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261014/r3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261014/ig_how.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261014/ig_offer.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/batch/08/08_03.jpg</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Самарская обл., Жигулёвск, ул. Морквашинская, 15</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P184" t="n">
+        <v>3400</v>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>2026-11-13T08:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>2026-10-14T11:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>2026-11-13T08:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>5952854771</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Доска обрезная, эсд на рейс</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа.&lt;br&gt;&lt;br&gt;Волгоградская область, доска обрезная и брус. Делаю ЭСД на рейс и документы на пиломатериал.&lt;br&gt;&lt;br&gt;Самый частый вопрос: нужен ли документ, если лес уже распилен. Нужен. Переработка учёт не отменяет, машину с доской проверяют так же, как с кругляком, а покупатель с бухгалтерией спрашивает происхождение в первую очередь.&lt;br&gt;&lt;br&gt;Что делаю. Завожу объём в ФГИС ЛК, оформляю происхождение договором купли-продажи, выписываю ЭСД с QR кодом на каждую отгрузку, собираю пакет, который спокойно принимает бухгалтерия.&lt;br&gt;&lt;br&gt;От вас порода, кубатура и маршрут. Документ присылаю быстро.&lt;br&gt;&lt;br&gt;Пилорамам и базам, которые отгружают постоянно, считаю помесячно.&lt;br&gt;&lt;br&gt;Доска обрезная, брус, брусок, пиломатериал хвоя, ЭСД на рейс, QR код на перевозку, документы ФГИС ЛК, Волгоградская область.</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261014/r4.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n10/1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_05_1.jpg</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Волгоградская обл., Урюпинск, ул. Штеменко, 20</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P185" t="n">
+        <v>390</v>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>2026-11-13T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>2026-11-13T09:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>3231552261</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Берёза кругляк, QR код на рейс</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа.&lt;br&gt;&lt;br&gt;Тульская область, берёза кругляком, дрова и баланс. Делаю документы на древесину. Сам лес не продаю, занимаюсь бумагами.&lt;br&gt;&lt;br&gt;На каждую машину с лесом нужна электронная накладная из ФГИС ЛК с QR кодом. Её сканируют на посту и на весовой, без неё рейс начинать рискованно.&lt;br&gt;&lt;br&gt;Как работаем. Вы пишете породу, сколько кубов, номер машины и куда едет. Я делаю документ и присылаю, обычно за пятнадцать минут.&lt;br&gt;&lt;br&gt;Если объёма в системе нет, его заводим по договору купли-продажи. По шагам это на втором фото: подписываем договор, вы оплачиваете по счёту на расчётный счёт, я закрепляю древесину за вами в ФГИС ЛК. За QR на рейс платите уже после того, как документ готов.&lt;br&gt;&lt;br&gt;Работаю удалённо по всей стране, свой кабинет и электронная подпись вам не нужны.&lt;br&gt;&lt;br&gt;Берёза кругляк, дрова, баланс, фанкряж, QR код на рейс, ЭСД на перевозку, документы ФГИС ЛК, Тульская область.</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261014/r5.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261014/ig_how.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261014/ig_offer.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/sd_field_pile.jpg</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Тульская обл., Белёв, ул. Рабочая, 12</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P186" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>2026-11-13T10:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>2026-10-14T13:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>2026-11-13T10:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>9667640850</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Хвоя кругляк, QR код на отгрузку</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа.&lt;br&gt;&lt;br&gt;Краснодарский край, хвойный кругляк, пихта, сосна и ель. Делаю QR коды на отгрузку и документы на древесину.&lt;br&gt;&lt;br&gt;Когда объём идёт партиями, бумаги нужны на каждую машину, и собирать их по ходу не выходит. Беру эту часть на себя целиком.&lt;br&gt;&lt;br&gt;Что делаю. Оформляю происхождение объёма договором купли-продажи, завожу партию в ФГИС ЛК, ставлю вам на баланс, свожу остатки перед отгрузками. На каждый рейс выдаю ЭСД с QR кодом.&lt;br&gt;&lt;br&gt;Работаю и с разовой машиной, и с постоянным потоком. Для регулярных отгрузок считаю помесячно.&lt;br&gt;&lt;br&gt;Всё удалённо, свой кабинет в системе и электронная подпись вам не нужны.&lt;br&gt;&lt;br&gt;Пихта кругляк, сосна, ель, хвоя, пиловочник, QR код на отгрузку, ЭСД на рейс, документы ФГИС ЛК, Краснодарский край.</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261014/r6.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-21/fgis_2607_04_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_06_1.jpg</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Краснодарский край, Апшеронск, ул. Ворошилова, 40</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P187" t="n">
+        <v>2900</v>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>2026-11-13T11:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>2026-10-14T14:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>2026-11-13T11:30:00+03:00</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -4648,7 +4648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE44"/>
+  <dimension ref="A1:AE46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="26"/>
@@ -10393,6 +10393,266 @@
       <c r="AE44" t="inlineStr">
         <is>
           <t>2026-11-02T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>9973184566</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261015/s3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n16/3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n06/3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261014/ig_how.jpg</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>2200</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Лес без документов, оформим учёт</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Оформляю документы на лес, который уже лежит без бумаг. Работаю с ИП и ООО, всё удалённо.&lt;br&gt;&lt;br&gt;С чем приходят чаще всего. Купили лес у частника, заготовили на своём участке, остался объём после стройки или расчистки. Древесина есть, а в ФГИС ЛК её нет, и продать или вывезти её законно нельзя.&lt;br&gt;&lt;br&gt;Как это решается. Смотрю, откуда объём и какая порода. Оформляю договор купли-продажи как основание, завожу древесину в ФГИС ЛК и ставлю вам на баланс. Порядок шагов есть на фото. Дальше на каждую машину выписываю ЭСД с QR кодом.&lt;br&gt;&lt;br&gt;После этого лес можно спокойно продавать, возить и проводить по бухгалтерии.&lt;br&gt;&lt;br&gt;Свой кабинет в системе и электронная подпись вам не нужны. Первый разговор бесплатный: напишите объём и что за ситуация, скажу, как закрыть.&lt;br&gt;&lt;br&gt;Документы на лес, учёт древесины в ФГИС ЛК, ЭСД, QR код на перевозку, договор купли-продажи, Крым, Симферополь.</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Республика Крым, Симферополь, ул. Киевская, 41</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>2026-11-14T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>2026-10-15T13:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>2026-11-14T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>6527634879</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261015/s4.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n14/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n12/3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n13/3.jpg</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>280</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>QR код на перевозку леса и документы</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Делаю QR коды и ЭСД на перевозку леса и пиломатериала за 15 минут. Работаю с ИП и ООО, оплата после готового документа.&lt;br&gt;&lt;br&gt;Кому это нужно. Всем, кто возит древесину машиной: кругляк, доску, брус, дрова. На каждый рейс нужен электронный сопроводительный документ из ФГИС ЛК, его QR код проверяют на дороге и на приёмке. Нет документа, значит штраф и простой машины.&lt;br&gt;&lt;br&gt;Как работаем. Вы пишете породу, объём, номер машины и куда она едет. Я выписываю ЭСД и присылаю, водитель показывает QR с телефона или распечатку.&lt;br&gt;&lt;br&gt;Если объёма в системе нет или остатки не сходятся, сначала навожу порядок: завожу древесину в ФГИС ЛК и свожу баланс.&lt;br&gt;&lt;br&gt;Свой кабинет и электронная подпись вам не нужны. Для тех, кто отгружает постоянно, считаю помесячно.&lt;br&gt;&lt;br&gt;QR код на перевозку леса, ЭСД, документы ФГИС ЛК, пиломатериал, кругляк, отгрузка, Астраханская область, Астрахань.</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Астраханская обл., Астрахань, ул. Адмиралтейская, 33</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>2026-11-14T11:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>2026-10-15T14:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>2026-11-14T11:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -11045,7 +11305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK187"/>
+  <dimension ref="A1:AL189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -11256,6 +11516,11 @@
           <t>DateEnd</t>
         </is>
       </c>
+      <c r="AL2" s="7" t="inlineStr">
+        <is>
+          <t>ТН ВЭД</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -11410,6 +11675,11 @@
           <t>Необязательный</t>
         </is>
       </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Необязательный</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -11560,6 +11830,11 @@
       <c r="AD4" t="inlineStr">
         <is>
           <t>Одно значение из выпадающего списка в ячейке</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Подробнее о параметре</t>
         </is>
       </c>
     </row>
@@ -35522,6 +35797,11 @@
           <t>2026-11-12T07:30:00+03:00</t>
         </is>
       </c>
+      <c r="AL177" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -35957,6 +36237,11 @@
           <t>2026-11-12T12:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL180" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -36102,6 +36387,11 @@
           <t>2026-11-12T13:30:00+03:00</t>
         </is>
       </c>
+      <c r="AL181" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -36392,6 +36682,11 @@
           <t>2026-11-13T07:30:00+03:00</t>
         </is>
       </c>
+      <c r="AL183" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -36537,6 +36832,11 @@
           <t>2026-11-13T08:30:00+03:00</t>
         </is>
       </c>
+      <c r="AL184" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -36970,6 +37270,311 @@
       <c r="AK187" t="inlineStr">
         <is>
           <t>2026-11-13T11:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL187" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>9286435703</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Ель пиловочник, документы фгис лк</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Оформляю документы на лес, сам лес не продаю. QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа.&lt;br&gt;&lt;br&gt;Приморский край, ель пиловочник и кругляк. Цена в объявлении за оформление, не за кубометр древесины.&lt;br&gt;&lt;br&gt;Что нужно на машину с лесом. Электронный сопроводительный документ из ФГИС ЛК с QR кодом. Его сканируют на посту и на приёмке, а без него рейс останавливают и выписывают штраф.&lt;br&gt;&lt;br&gt;Что я делаю. Завожу ваш объём в ФГИС ЛК, если его там нет, свожу остатки и на каждый рейс выписываю ЭСД. Вы присылаете породу, кубатуру, номер машины и пункт назначения, документ приходит обратно в мессенджер.&lt;br&gt;&lt;br&gt;Свой кабинет в системе и электронная подпись вам не нужны, всё делаю со своей стороны удалённо. Разовую машину оформлю так же, как постоянный поток.&lt;br&gt;&lt;br&gt;Ель пиловочник, кругляк, пихта, кедр, лиственница, документы ФГИС ЛК, ЭСД на рейс, QR код на перевозку, Приморский край, Лесозаводск.</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261015/s1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n05/3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n03/3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260831/jl14.jpg</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Приморский край, Лесозаводск, ул. Будённого, 34</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P188" t="n">
+        <v>3900</v>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>2026-11-14T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF188" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ188" t="inlineStr">
+        <is>
+          <t>2026-10-15T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK188" t="inlineStr">
+        <is>
+          <t>2026-11-14T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL188" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>6187483936</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Кругляк сосна пиловочник(документы фгис)</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Оформляю документы на лес, сам лес не продаю. QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа.&lt;br&gt;&lt;br&gt;Амурская область, сосновый кругляк и пиловочник. Делаю документы на вывоз и перевозку.&lt;br&gt;&lt;br&gt;Частая история: лес заготовлен, покупатель есть, а вывезти нельзя, потому что в ФГИС ЛК объёма нет. Для закона его как будто не существует.&lt;br&gt;&lt;br&gt;Как закрываю. Объём оформляется договором купли-продажи, по шагам это на втором фото: договор, оплата по счёту, и древесина закрепляется за вами в ФГИС ЛК. После этого на каждую машину выписываю ЭСД с QR кодом, за него платите уже по готовому документу.&lt;br&gt;&lt;br&gt;От вас порода, кубатура и маршрут. Разбор ситуации бесплатный, напишите, посмотрю и скажу, что нужно именно вам.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, лиственница, документы ФГИС ЛК, ЭСД на вывоз, QR код на рейс, договор купли-продажи древесины, Амурская область.</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261015/s2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261014/ig_how.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261014/ig_offer.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_03_1.jpg</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Амурская обл., Свободный, ул. Почтамтская, 50</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P189" t="n">
+        <v>290</v>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>2026-11-14T08:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>2026-10-15T11:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>2026-11-14T08:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL189" t="inlineStr">
+        <is>
+          <t>4403211200</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -11305,7 +11305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL189"/>
+  <dimension ref="A1:AM194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -11521,6 +11521,11 @@
           <t>ТН ВЭД</t>
         </is>
       </c>
+      <c r="AM2" s="7" t="inlineStr">
+        <is>
+          <t>ОКПД 2</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -11680,6 +11685,11 @@
           <t>Необязательный</t>
         </is>
       </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Необязательный</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -11833,6 +11843,11 @@
         </is>
       </c>
       <c r="AL4" t="inlineStr">
+        <is>
+          <t>Подробнее о параметре</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
         <is>
           <t>Подробнее о параметре</t>
         </is>
@@ -28639,9 +28654,19 @@
           <t>Тамбовская обл., Моршанск, ул. Октябрьская, 22</t>
         </is>
       </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P127" t="n">
@@ -28727,6 +28752,11 @@
           <t>2026-10-16T10:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL127" t="inlineStr">
+        <is>
+          <t>4407119000</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -28774,9 +28804,19 @@
           <t>Еврейская АО, Биробиджан, ул. Ленина, 29</t>
         </is>
       </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -28862,6 +28902,16 @@
           <t>2026-10-17T02:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL128" t="inlineStr">
+        <is>
+          <t>4401120001</t>
+        </is>
+      </c>
+      <c r="AM128" t="inlineStr">
+        <is>
+          <t>02.20.14.000</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -28909,9 +28959,19 @@
           <t>Республика Саха (Якутия), Ленск, ул. Ленина, 65</t>
         </is>
       </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -28997,6 +29057,11 @@
           <t>2026-10-17T04:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL129" t="inlineStr">
+        <is>
+          <t>4407119000</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -29044,9 +29109,19 @@
           <t>Московская обл., Шатура, пр-т Ильича, 55</t>
         </is>
       </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -29132,6 +29207,11 @@
           <t>2026-10-17T06:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL130" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -29179,9 +29259,19 @@
           <t>Орловская обл., Мценск, ул. Ленина, 25</t>
         </is>
       </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P131" t="n">
@@ -29267,6 +29357,11 @@
           <t>2026-10-17T08:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL131" t="inlineStr">
+        <is>
+          <t>4407119000</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -29314,9 +29409,19 @@
           <t>Республика Бурятия, Заиграево, ул. Октябрьская, 4</t>
         </is>
       </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P132" t="n">
@@ -29402,6 +29507,11 @@
           <t>2026-10-18T02:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL132" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -29449,9 +29559,19 @@
           <t>Забайкальский край, Хилок, ул. Ленина, 9</t>
         </is>
       </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P133" t="n">
@@ -29537,6 +29657,11 @@
           <t>2026-10-18T04:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL133" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -29584,9 +29709,19 @@
           <t>Амурская обл., Тында, ул. Красная Пресня, 29</t>
         </is>
       </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P134" t="n">
@@ -29672,6 +29807,11 @@
           <t>2026-10-18T06:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL134" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -29719,9 +29859,19 @@
           <t>Ульяновская обл., Инза, ул. Заводская, 1</t>
         </is>
       </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P135" t="n">
@@ -29807,6 +29957,11 @@
           <t>2026-10-18T08:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL135" t="inlineStr">
+        <is>
+          <t>4407119000</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -29854,9 +30009,19 @@
           <t>Пензенская обл., Кузнецк, ул. Ленина, 245</t>
         </is>
       </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -29942,6 +30107,11 @@
           <t>2026-10-18T10:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL136" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -29989,9 +30159,19 @@
           <t>Республика Хакасия, Саяногорск, Советский мкр, 1</t>
         </is>
       </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P137" t="n">
@@ -30077,6 +30257,16 @@
           <t>2026-10-19T02:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL137" t="inlineStr">
+        <is>
+          <t>4401120001</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>02.20.14.000</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -30124,9 +30314,19 @@
           <t>Республика Тыва, Кызыл, ул. Ленина, 32</t>
         </is>
       </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -30212,6 +30412,11 @@
           <t>2026-10-19T06:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL138" t="inlineStr">
+        <is>
+          <t>4407119000</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -30259,9 +30464,19 @@
           <t>Курская обл., Льгов, Красная площадь, 13</t>
         </is>
       </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -30347,6 +30562,16 @@
           <t>2026-10-19T10:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL139" t="inlineStr">
+        <is>
+          <t>4401120001</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>02.20.14.000</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -30394,9 +30619,19 @@
           <t>Смоленская обл., Рославль, ул. Советская, 66</t>
         </is>
       </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P140" t="n">
@@ -30482,6 +30717,16 @@
           <t>2026-10-24T10:30:00+03:00</t>
         </is>
       </c>
+      <c r="AL140" t="inlineStr">
+        <is>
+          <t>4401120001</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>02.20.14.000</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -30529,9 +30774,19 @@
           <t>Калужская обл., Козельск, ул. Большая Советская, 55</t>
         </is>
       </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -30617,6 +30872,11 @@
           <t>2026-10-24T14:30:00+03:00</t>
         </is>
       </c>
+      <c r="AL141" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -30664,9 +30924,19 @@
           <t>Смоленская обл., Ярцево, ул. Советская, 17</t>
         </is>
       </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P142" t="n">
@@ -30752,6 +31022,11 @@
           <t>2026-11-01T10:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL142" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -30799,9 +31074,19 @@
           <t>Брянская обл., Унеча, ул. Октябрьская, 1</t>
         </is>
       </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -30887,6 +31172,16 @@
           <t>2026-11-01T12:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL143" t="inlineStr">
+        <is>
+          <t>4401120001</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>02.20.14.000</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -30934,9 +31229,19 @@
           <t>Рязанская обл., Шилово, ул. Советская, 9</t>
         </is>
       </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -31022,6 +31327,11 @@
           <t>2026-11-01T13:30:00+03:00</t>
         </is>
       </c>
+      <c r="AL144" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -31069,9 +31379,19 @@
           <t>Липецкая обл., Усмань, ул. Ленина, 36</t>
         </is>
       </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>ПВЗ</t>
+          <t>Свой курьер</t>
         </is>
       </c>
       <c r="P145" t="n">
@@ -31157,6 +31477,16 @@
           <t>2026-11-02T04:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL145" t="inlineStr">
+        <is>
+          <t>4401120001</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>02.20.14.000</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -31302,6 +31632,11 @@
           <t>2026-11-04T08:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL146" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -31447,6 +31782,11 @@
           <t>2026-11-04T09:30:00+03:00</t>
         </is>
       </c>
+      <c r="AL147" t="inlineStr">
+        <is>
+          <t>4407119000</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -31592,6 +31932,16 @@
           <t>2026-11-04T11:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL148" t="inlineStr">
+        <is>
+          <t>4401120001</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>02.20.14.000</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -31737,6 +32087,11 @@
           <t>2026-11-04T12:30:00+03:00</t>
         </is>
       </c>
+      <c r="AL149" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -31882,6 +32237,16 @@
           <t>2026-11-04T14:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL150" t="inlineStr">
+        <is>
+          <t>4401120001</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>02.20.14.000</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -32027,6 +32392,11 @@
           <t>2026-11-04T15:30:00+03:00</t>
         </is>
       </c>
+      <c r="AL151" t="inlineStr">
+        <is>
+          <t>4407119000</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -32172,6 +32542,11 @@
           <t>2026-11-05T07:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL152" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -32317,6 +32692,16 @@
           <t>2026-11-05T08:30:00+03:00</t>
         </is>
       </c>
+      <c r="AL153" t="inlineStr">
+        <is>
+          <t>4401120001</t>
+        </is>
+      </c>
+      <c r="AM153" t="inlineStr">
+        <is>
+          <t>02.20.14.000</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -32462,6 +32847,11 @@
           <t>2026-11-05T10:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL154" t="inlineStr">
+        <is>
+          <t>4407119000</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -32607,6 +32997,11 @@
           <t>2026-11-05T11:30:00+03:00</t>
         </is>
       </c>
+      <c r="AL155" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -32752,6 +33147,16 @@
           <t>2026-11-05T13:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL156" t="inlineStr">
+        <is>
+          <t>4401120001</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>02.20.14.000</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -32897,6 +33302,11 @@
           <t>2026-11-05T14:30:00+03:00</t>
         </is>
       </c>
+      <c r="AL157" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -33042,6 +33452,16 @@
           <t>2026-11-06T06:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL158" t="inlineStr">
+        <is>
+          <t>4401120001</t>
+        </is>
+      </c>
+      <c r="AM158" t="inlineStr">
+        <is>
+          <t>02.20.14.000</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -33187,6 +33607,11 @@
           <t>2026-11-06T07:30:00+03:00</t>
         </is>
       </c>
+      <c r="AL159" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -33332,6 +33757,11 @@
           <t>2026-11-06T09:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL160" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -33477,6 +33907,16 @@
           <t>2026-11-06T10:30:00+03:00</t>
         </is>
       </c>
+      <c r="AL161" t="inlineStr">
+        <is>
+          <t>4401120001</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>02.20.14.000</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -33622,6 +34062,11 @@
           <t>2026-11-06T12:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL162" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -33767,6 +34212,11 @@
           <t>2026-11-06T13:30:00+03:00</t>
         </is>
       </c>
+      <c r="AL163" t="inlineStr">
+        <is>
+          <t>4407119000</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -33912,6 +34362,11 @@
           <t>2026-11-07T07:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL164" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -34057,6 +34512,11 @@
           <t>2026-11-07T08:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL165" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -34202,6 +34662,11 @@
           <t>2026-11-07T09:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL166" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -34347,6 +34812,16 @@
           <t>2026-11-07T10:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL167" t="inlineStr">
+        <is>
+          <t>4401120001</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>02.20.14.000</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -34492,6 +34967,16 @@
           <t>2026-11-07T11:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL168" t="inlineStr">
+        <is>
+          <t>4401120001</t>
+        </is>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t>02.20.14.000</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -34637,6 +35122,11 @@
           <t>2026-11-07T12:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL169" t="inlineStr">
+        <is>
+          <t>4407119000</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -34782,6 +35272,11 @@
           <t>2026-11-09T05:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL170" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -34927,6 +35422,11 @@
           <t>2026-11-09T06:30:00+03:00</t>
         </is>
       </c>
+      <c r="AL171" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -35072,6 +35572,11 @@
           <t>2026-11-09T08:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL172" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -35217,6 +35722,16 @@
           <t>2026-11-09T09:30:00+03:00</t>
         </is>
       </c>
+      <c r="AL173" t="inlineStr">
+        <is>
+          <t>4401120001</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>02.20.14.000</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -35362,6 +35877,16 @@
           <t>2026-11-09T11:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL174" t="inlineStr">
+        <is>
+          <t>4401120001</t>
+        </is>
+      </c>
+      <c r="AM174" t="inlineStr">
+        <is>
+          <t>02.20.14.000</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -35507,6 +36032,11 @@
           <t>2026-11-09T12:30:00+03:00</t>
         </is>
       </c>
+      <c r="AL175" t="inlineStr">
+        <is>
+          <t>4407119000</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -35652,6 +36182,16 @@
           <t>2026-11-12T06:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL176" t="inlineStr">
+        <is>
+          <t>4401120001</t>
+        </is>
+      </c>
+      <c r="AM176" t="inlineStr">
+        <is>
+          <t>02.20.14.000</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -35947,6 +36487,16 @@
           <t>2026-11-12T09:00:00+03:00</t>
         </is>
       </c>
+      <c r="AL178" t="inlineStr">
+        <is>
+          <t>4401120001</t>
+        </is>
+      </c>
+      <c r="AM178" t="inlineStr">
+        <is>
+          <t>02.20.14.000</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -36092,6 +36642,11 @@
           <t>2026-11-12T10:30:00+03:00</t>
         </is>
       </c>
+      <c r="AL179" t="inlineStr">
+        <is>
+          <t>4407119000</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -36537,6 +37092,16 @@
           <t>2026-11-13T06:30:00+03:00</t>
         </is>
       </c>
+      <c r="AL182" t="inlineStr">
+        <is>
+          <t>4401120001</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>02.20.14.000</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -36982,6 +37547,11 @@
           <t>2026-11-13T09:30:00+03:00</t>
         </is>
       </c>
+      <c r="AL185" t="inlineStr">
+        <is>
+          <t>4407119000</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -37127,6 +37697,16 @@
           <t>2026-11-13T10:30:00+03:00</t>
         </is>
       </c>
+      <c r="AL186" t="inlineStr">
+        <is>
+          <t>4401120001</t>
+        </is>
+      </c>
+      <c r="AM186" t="inlineStr">
+        <is>
+          <t>02.20.14.000</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -37573,6 +38153,756 @@
         </is>
       </c>
       <c r="AL189" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>1758144505</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Хвоя кругляк, QR код на отгрузку</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа. Оформляю документы на лес, сам лес не продаю, цена указана за оформление.&lt;br&gt;&lt;br&gt;Белгородская область, хвойный кругляк, сосна и ель. Делаю QR коды на отгрузку и документы на древесину.&lt;br&gt;&lt;br&gt;Когда объём идёт партиями, бумага нужна на каждую машину, и собирать её по ходу не выходит. Беру эту часть на себя.&lt;br&gt;&lt;br&gt;Что делаю. Завожу партию в ФГИС ЛК, если её там нет, оформляю происхождение договором купли-продажи, свожу остатки перед отгрузками. На каждый рейс выписываю ЭСД с QR кодом. Как выглядит готовый документ, показал на втором фото.&lt;br&gt;&lt;br&gt;Работаю и с разовой машиной, и с постоянным потоком. Для регулярных отгрузок считаю помесячно.&lt;br&gt;&lt;br&gt;Свой кабинет в системе и электронная подпись вам не нужны, всё удалённо.&lt;br&gt;&lt;br&gt;Сосна кругляк, ель, хвоя, пиловочник, баланс, QR код на отгрузку, ЭСД на рейс, документы ФГИС ЛК, Белгородская область.</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261016/t1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261016/e1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_05_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n03/3.jpg</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Белгородская обл., Новый Оскол, ул. Гражданская, 14</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P190" t="n">
+        <v>4300</v>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>2026-11-15T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF190" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ190" t="inlineStr">
+        <is>
+          <t>2026-10-16T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t>2026-11-15T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL190" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>8843424464</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Хвоя кругляк оптом(QR на вывозку)</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа. Оформляю документы на лес, сам лес не продаю, цена указана за оформление.&lt;br&gt;&lt;br&gt;Воронежская область, хвойный кругляк оптом. Делаю QR коды на вывозку и документы на древесину.&lt;br&gt;&lt;br&gt;На каждую машину с лесом нужен электронный сопроводительный документ из ФГИС ЛК. Его QR код сканируют на посту и на приёмке, без него рейс останавливают.&lt;br&gt;&lt;br&gt;Как работаем. Вы пишете породу, кубатуру, номер машины и куда она едет. Я выписываю ЭСД и присылаю в мессенджер, водитель показывает QR с телефона.&lt;br&gt;&lt;br&gt;Если объёма в системе нет, сначала завожу его по договору купли-продажи. По шагам это на последнем фото: договор, оплата по счёту, и древесина закреплена за вами в ФГИС ЛК.&lt;br&gt;&lt;br&gt;Для тех, кто вывозит постоянно, считаю помесячно, так дешевле.&lt;br&gt;&lt;br&gt;Хвоя оптом, сосна кругляк, ель, пиловочник, баланс, QR код на вывозку, ЭСД на рейс, документы ФГИС ЛК, Воронежская область, Россошь.</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261016/t2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n05/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261016/e2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261014/ig_how.jpg</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Воронежская обл., Россошь, ул. Простеева, 12</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P191" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>2026-11-15T07:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>2026-10-16T10:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>2026-11-15T07:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL191" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>1936590964</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Ель пиловочник кругляк(QR на рейс)</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа. Оформляю документы на лес, сам лес не продаю, цена указана за оформление.&lt;br&gt;&lt;br&gt;Орловская область, еловый пиловочник и кругляк. Делаю QR коды на рейс и документы на объём.&lt;br&gt;&lt;br&gt;Частая ситуация: лес заготовлен, покупатель найден, а вывезти нельзя. В ФГИС ЛК объёма нет, и машину остановят первым же вопросом про происхождение.&lt;br&gt;&lt;br&gt;Как закрывается. Смотрим объём и породу. Оформляю договор купли-продажи на партию, завожу древесину в ФГИС ЛК и ставлю вам на баланс. Дальше на каждый рейс выписываю ЭСД с QR кодом, он приходит вам в мессенджер, образец на втором фото.&lt;br&gt;&lt;br&gt;После этого машина едет спокойно, а покупатель видит нормальные бумаги.&lt;br&gt;&lt;br&gt;Разбор ситуации бесплатный, напишите объём и маршрут.&lt;br&gt;&lt;br&gt;Ель пиловочник, кругляк, сосна, хвоя, баланс, QR код на рейс, ЭСД на вывоз, документы ФГИС ЛК, Орловская область.</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261016/t3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261016/e3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n15/3.jpg</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Орловская обл., Кромы, ул. Свободы, 5</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P192" t="n">
+        <v>260</v>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>2026-11-15T08:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>2026-10-16T11:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>2026-11-15T08:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL192" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>1355553666</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Ель пиловочник, документы фгис лк</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа. Оформляю документы на лес, сам лес не продаю, цена указана за оформление.&lt;br&gt;&lt;br&gt;Курская область, ель пиловочник. Делаю документы ФГИС ЛК под продажу и вывоз.&lt;br&gt;&lt;br&gt;С чем приходят. Лес есть, а в системе он не числится, или остатки по бумагам не сходятся с фактом. Продать такой объём законно нельзя, покупатель с бухгалтерией его не примет.&lt;br&gt;&lt;br&gt;Что делаю. Оформляю договор купли-продажи как основание, завожу древесину в ФГИС ЛК, свожу баланс. Дальше на каждую машину выписываю ЭСД с QR кодом, как он выглядит, есть на фото.&lt;br&gt;&lt;br&gt;От вас порода, кубатура и что за ситуация. Скажу, как закрыть, и сколько это займёт.&lt;br&gt;&lt;br&gt;Свой кабинет и электронная подпись вам не нужны, всё делаю со своей стороны.&lt;br&gt;&lt;br&gt;Ель пиловочник, кругляк, сосна, хвоя, документы ФГИС ЛК, учёт древесины, ЭСД на рейс, QR код на перевозку, Курская область.</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261016/t4.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n01/2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261016/e4.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261014/ig_offer.jpg</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Курская обл., Обоянь, ул. Курская, 30</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P193" t="n">
+        <v>2900</v>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>2026-11-15T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>2026-10-16T12:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>2026-11-15T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL193" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>6771074493</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Сосна кругляк (QR код на перевозку)</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа. Оформляю документы на лес, сам лес не продаю, цена указана за оформление.&lt;br&gt;&lt;br&gt;Саратовская область, сосновый кругляк и пиловочник. Делаю документы на перевозку древесины.&lt;br&gt;&lt;br&gt;На каждую машину с лесом нужен ЭСД, электронная накладная из ФГИС ЛК. В ней QR код, его сканируют на посту и на весовой. Нет документа, значит рейс под вопросом и штраф.&lt;br&gt;&lt;br&gt;Порядок работы. Вы пишете породу, сколько кубов, номер машины и куда едет. Я делаю документ и отправляю, обычно за пятнадцать минут. Образец готового ЭСД на третьем фото.&lt;br&gt;&lt;br&gt;Если вашего объёма нет в ФГИС ЛК, сначала завожу его: договор купли-продажи на партию и постановка вам на баланс.&lt;br&gt;&lt;br&gt;Свой кабинет и электронную подпись заводить не нужно, всё с моей стороны.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, хвоя, баланс, QR код на перевозку, ЭСД на рейс, документы ФГИС ЛК, Саратовская область, Аткарск.</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261016/t5.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/campaign_2026-07-29/fgis_0729_06_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261016/e5.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n02/2.jpg</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Саратовская обл., Аткарск, ул. Гагарина, 51</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P194" t="n">
+        <v>3100</v>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>2026-11-15T10:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>2026-11-15T10:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL194" t="inlineStr">
         <is>
           <t>4403211200</t>
         </is>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -28754,7 +28754,12 @@
       </c>
       <c r="AL127" t="inlineStr">
         <is>
-          <t>4407119000</t>
+          <t>4407119406</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>16.10.10.111</t>
         </is>
       </c>
     </row>
@@ -28904,12 +28909,12 @@
       </c>
       <c r="AL128" t="inlineStr">
         <is>
-          <t>4401120001</t>
+          <t>4403950000</t>
         </is>
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>02.20.14.000</t>
+          <t>Не требуется</t>
         </is>
       </c>
     </row>
@@ -29059,7 +29064,12 @@
       </c>
       <c r="AL129" t="inlineStr">
         <is>
-          <t>4407119000</t>
+          <t>4407119406</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>16.10.10.111</t>
         </is>
       </c>
     </row>
@@ -29209,7 +29219,7 @@
       </c>
       <c r="AL130" t="inlineStr">
         <is>
-          <t>4403211200</t>
+          <t>4403231200</t>
         </is>
       </c>
     </row>
@@ -29359,7 +29369,12 @@
       </c>
       <c r="AL131" t="inlineStr">
         <is>
-          <t>4407119000</t>
+          <t>4407119406</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>16.10.10.111</t>
         </is>
       </c>
     </row>
@@ -29509,7 +29524,7 @@
       </c>
       <c r="AL132" t="inlineStr">
         <is>
-          <t>4403211200</t>
+          <t>4403231200</t>
         </is>
       </c>
     </row>
@@ -29809,7 +29824,7 @@
       </c>
       <c r="AL134" t="inlineStr">
         <is>
-          <t>4403211200</t>
+          <t>4403251000</t>
         </is>
       </c>
     </row>
@@ -29959,7 +29974,12 @@
       </c>
       <c r="AL135" t="inlineStr">
         <is>
-          <t>4407119000</t>
+          <t>4407119406</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>16.10.10.111</t>
         </is>
       </c>
     </row>
@@ -30259,12 +30279,12 @@
       </c>
       <c r="AL137" t="inlineStr">
         <is>
-          <t>4401120001</t>
+          <t>4403970002</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>02.20.14.000</t>
+          <t>Не требуется</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30434,12 @@
       </c>
       <c r="AL138" t="inlineStr">
         <is>
-          <t>4407119000</t>
+          <t>4407119406</t>
+        </is>
+      </c>
+      <c r="AM138" t="inlineStr">
+        <is>
+          <t>16.10.10.111</t>
         </is>
       </c>
     </row>
@@ -30564,12 +30589,12 @@
       </c>
       <c r="AL139" t="inlineStr">
         <is>
-          <t>4401120001</t>
+          <t>4401120009</t>
         </is>
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>02.20.14.000</t>
+          <t>02.20.14.130</t>
         </is>
       </c>
     </row>
@@ -30719,12 +30744,12 @@
       </c>
       <c r="AL140" t="inlineStr">
         <is>
-          <t>4401120001</t>
+          <t>4403950000</t>
         </is>
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>02.20.14.000</t>
+          <t>Не требуется</t>
         </is>
       </c>
     </row>
@@ -31174,12 +31199,12 @@
       </c>
       <c r="AL143" t="inlineStr">
         <is>
-          <t>4401120001</t>
+          <t>4403950000</t>
         </is>
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>02.20.14.000</t>
+          <t>Не требуется</t>
         </is>
       </c>
     </row>
@@ -31329,7 +31354,7 @@
       </c>
       <c r="AL144" t="inlineStr">
         <is>
-          <t>4403211200</t>
+          <t>4403231200</t>
         </is>
       </c>
     </row>
@@ -31479,12 +31504,12 @@
       </c>
       <c r="AL145" t="inlineStr">
         <is>
-          <t>4401120001</t>
+          <t>4403970002</t>
         </is>
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>02.20.14.000</t>
+          <t>Не требуется</t>
         </is>
       </c>
     </row>
@@ -31784,7 +31809,12 @@
       </c>
       <c r="AL147" t="inlineStr">
         <is>
-          <t>4407119000</t>
+          <t>4407119406</t>
+        </is>
+      </c>
+      <c r="AM147" t="inlineStr">
+        <is>
+          <t>16.10.10.111</t>
         </is>
       </c>
     </row>
@@ -31934,12 +31964,12 @@
       </c>
       <c r="AL148" t="inlineStr">
         <is>
-          <t>4401120001</t>
+          <t>4403950000</t>
         </is>
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>02.20.14.000</t>
+          <t>Не требуется</t>
         </is>
       </c>
     </row>
@@ -32089,7 +32119,7 @@
       </c>
       <c r="AL149" t="inlineStr">
         <is>
-          <t>4403211200</t>
+          <t>4403231200</t>
         </is>
       </c>
     </row>
@@ -32239,12 +32269,12 @@
       </c>
       <c r="AL150" t="inlineStr">
         <is>
-          <t>4401120001</t>
+          <t>4403970002</t>
         </is>
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>02.20.14.000</t>
+          <t>Не требуется</t>
         </is>
       </c>
     </row>
@@ -32394,7 +32424,12 @@
       </c>
       <c r="AL151" t="inlineStr">
         <is>
-          <t>4407119000</t>
+          <t>4407119406</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>16.10.10.111</t>
         </is>
       </c>
     </row>
@@ -32694,12 +32729,12 @@
       </c>
       <c r="AL153" t="inlineStr">
         <is>
-          <t>4401120001</t>
+          <t>4403950000</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>02.20.14.000</t>
+          <t>Не требуется</t>
         </is>
       </c>
     </row>
@@ -32849,7 +32884,12 @@
       </c>
       <c r="AL154" t="inlineStr">
         <is>
-          <t>4407119000</t>
+          <t>4407119406</t>
+        </is>
+      </c>
+      <c r="AM154" t="inlineStr">
+        <is>
+          <t>16.10.10.111</t>
         </is>
       </c>
     </row>
@@ -32999,7 +33039,7 @@
       </c>
       <c r="AL155" t="inlineStr">
         <is>
-          <t>4403211200</t>
+          <t>4403231200</t>
         </is>
       </c>
     </row>
@@ -33149,12 +33189,12 @@
       </c>
       <c r="AL156" t="inlineStr">
         <is>
-          <t>4401120001</t>
+          <t>4403970002</t>
         </is>
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>02.20.14.000</t>
+          <t>Не требуется</t>
         </is>
       </c>
     </row>
@@ -33454,12 +33494,12 @@
       </c>
       <c r="AL158" t="inlineStr">
         <is>
-          <t>4401120001</t>
+          <t>4403950000</t>
         </is>
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>02.20.14.000</t>
+          <t>Не требуется</t>
         </is>
       </c>
     </row>
@@ -33759,7 +33799,7 @@
       </c>
       <c r="AL160" t="inlineStr">
         <is>
-          <t>4403211200</t>
+          <t>4403231200</t>
         </is>
       </c>
     </row>
@@ -33909,12 +33949,12 @@
       </c>
       <c r="AL161" t="inlineStr">
         <is>
-          <t>4401120001</t>
+          <t>4403970002</t>
         </is>
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>02.20.14.000</t>
+          <t>Не требуется</t>
         </is>
       </c>
     </row>
@@ -34214,7 +34254,12 @@
       </c>
       <c r="AL163" t="inlineStr">
         <is>
-          <t>4407119000</t>
+          <t>4407119406</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>16.10.10.111</t>
         </is>
       </c>
     </row>
@@ -34514,7 +34559,7 @@
       </c>
       <c r="AL165" t="inlineStr">
         <is>
-          <t>4403211200</t>
+          <t>4403231200</t>
         </is>
       </c>
     </row>
@@ -34814,12 +34859,12 @@
       </c>
       <c r="AL167" t="inlineStr">
         <is>
-          <t>4401120001</t>
+          <t>4403950000</t>
         </is>
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>02.20.14.000</t>
+          <t>Не требуется</t>
         </is>
       </c>
     </row>
@@ -34969,12 +35014,12 @@
       </c>
       <c r="AL168" t="inlineStr">
         <is>
-          <t>4401120001</t>
+          <t>4403970002</t>
         </is>
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>02.20.14.000</t>
+          <t>Не требуется</t>
         </is>
       </c>
     </row>
@@ -35124,7 +35169,12 @@
       </c>
       <c r="AL169" t="inlineStr">
         <is>
-          <t>4407119000</t>
+          <t>4407119406</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>16.10.10.111</t>
         </is>
       </c>
     </row>
@@ -35424,7 +35474,7 @@
       </c>
       <c r="AL171" t="inlineStr">
         <is>
-          <t>4403211200</t>
+          <t>4403231200</t>
         </is>
       </c>
     </row>
@@ -35724,12 +35774,12 @@
       </c>
       <c r="AL173" t="inlineStr">
         <is>
-          <t>4401120001</t>
+          <t>4403950000</t>
         </is>
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>02.20.14.000</t>
+          <t>Не требуется</t>
         </is>
       </c>
     </row>
@@ -35879,12 +35929,12 @@
       </c>
       <c r="AL174" t="inlineStr">
         <is>
-          <t>4401120001</t>
+          <t>4403950000</t>
         </is>
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>02.20.14.000</t>
+          <t>Не требуется</t>
         </is>
       </c>
     </row>
@@ -36034,7 +36084,12 @@
       </c>
       <c r="AL175" t="inlineStr">
         <is>
-          <t>4407119000</t>
+          <t>4407119406</t>
+        </is>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t>16.10.10.111</t>
         </is>
       </c>
     </row>
@@ -36184,12 +36239,12 @@
       </c>
       <c r="AL176" t="inlineStr">
         <is>
-          <t>4401120001</t>
+          <t>4403950000</t>
         </is>
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>02.20.14.000</t>
+          <t>Не требуется</t>
         </is>
       </c>
     </row>
@@ -36489,12 +36544,12 @@
       </c>
       <c r="AL178" t="inlineStr">
         <is>
-          <t>4401120001</t>
+          <t>4403970002</t>
         </is>
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>02.20.14.000</t>
+          <t>Не требуется</t>
         </is>
       </c>
     </row>
@@ -36644,7 +36699,12 @@
       </c>
       <c r="AL179" t="inlineStr">
         <is>
-          <t>4407119000</t>
+          <t>4407119406</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>16.10.10.111</t>
         </is>
       </c>
     </row>
@@ -36944,7 +37004,7 @@
       </c>
       <c r="AL181" t="inlineStr">
         <is>
-          <t>4403211200</t>
+          <t>4403231200</t>
         </is>
       </c>
     </row>
@@ -37094,12 +37154,12 @@
       </c>
       <c r="AL182" t="inlineStr">
         <is>
-          <t>4401120001</t>
+          <t>4403970002</t>
         </is>
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>02.20.14.000</t>
+          <t>Не требуется</t>
         </is>
       </c>
     </row>
@@ -37549,7 +37609,12 @@
       </c>
       <c r="AL185" t="inlineStr">
         <is>
-          <t>4407119000</t>
+          <t>4407119406</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr">
+        <is>
+          <t>16.10.10.111</t>
         </is>
       </c>
     </row>
@@ -37699,12 +37764,12 @@
       </c>
       <c r="AL186" t="inlineStr">
         <is>
-          <t>4401120001</t>
+          <t>4403950000</t>
         </is>
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>02.20.14.000</t>
+          <t>Не требуется</t>
         </is>
       </c>
     </row>
@@ -38004,7 +38069,7 @@
       </c>
       <c r="AL188" t="inlineStr">
         <is>
-          <t>4403211200</t>
+          <t>4403231200</t>
         </is>
       </c>
     </row>
@@ -38481,7 +38546,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа. Оформляю документы на лес, сам лес не продаю, цена указана за оформление.&lt;br&gt;&lt;br&gt;Орловская область, еловый пиловочник и кругляк. Делаю QR коды на рейс и документы на объём.&lt;br&gt;&lt;br&gt;Частая ситуация: лес заготовлен, покупатель найден, а вывезти нельзя. В ФГИС ЛК объёма нет, и машину остановят первым же вопросом про происхождение.&lt;br&gt;&lt;br&gt;Как закрывается. Смотрим объём и породу. Оформляю договор купли-продажи на партию, завожу древесину в ФГИС ЛК и ставлю вам на баланс. Дальше на каждый рейс выписываю ЭСД с QR кодом, он приходит вам в мессенджер, образец на втором фото.&lt;br&gt;&lt;br&gt;После этого машина едет спокойно, а покупатель видит нормальные бумаги.&lt;br&gt;&lt;br&gt;Разбор ситуации бесплатный, напишите объём и маршрут.&lt;br&gt;&lt;br&gt;Ель пиловочник, кругляк, сосна, хвоя, баланс, QR код на рейс, ЭСД на вывоз, документы ФГИС ЛК, Орловская область.</t>
+          <t>QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа. Оформляю документы на лес, сам лес не продаю, цена указана за оформление.&lt;br&gt;&lt;br&gt;Тамбовская область, еловый пиловочник и кругляк. Делаю QR коды на рейс и документы на объём.&lt;br&gt;&lt;br&gt;Частая ситуация: лес заготовлен, покупатель найден, а вывезти нельзя. В ФГИС ЛК объёма нет, и машину остановят первым же вопросом про происхождение.&lt;br&gt;&lt;br&gt;Как закрывается. Смотрим объём и породу. Оформляю договор купли-продажи на партию, завожу древесину в ФГИС ЛК и ставлю вам на баланс. Дальше на каждый рейс выписываю ЭСД с QR кодом, он приходит вам в мессенджер, образец на втором фото.&lt;br&gt;&lt;br&gt;После этого машина едет спокойно, а покупатель видит нормальные бумаги.&lt;br&gt;&lt;br&gt;Разбор ситуации бесплатный, напишите объём и маршрут.&lt;br&gt;&lt;br&gt;Ель пиловочник, кругляк, сосна, хвоя, баланс, QR код на рейс, ЭСД на вывоз, документы ФГИС ЛК, Тамбовская область.</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -38501,7 +38566,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Орловская обл., Кромы, ул. Свободы, 5</t>
+          <t>Тамбовская обл., Котовск, ул. Кирова, 14</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -38604,7 +38669,7 @@
       </c>
       <c r="AL192" t="inlineStr">
         <is>
-          <t>4403211200</t>
+          <t>4403231200</t>
         </is>
       </c>
     </row>
@@ -38754,7 +38819,7 @@
       </c>
       <c r="AL193" t="inlineStr">
         <is>
-          <t>4403211200</t>
+          <t>4403231200</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -4648,7 +4648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE46"/>
+  <dimension ref="A1:AE48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="26"/>
@@ -10653,6 +10653,260 @@
       <c r="AE46" t="inlineStr">
         <is>
           <t>2026-11-14T11:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>4330000104</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261019/c3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n04/2.png|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n02/3.jpg</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ЭСД и QR код на рейс с лесом</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Оформляю ЭСД и QR код на перевозку леса и пиломатериалов за 15 минут. Сам лес и доску не продаю, цена указана за оформление.&lt;br&gt;&lt;br&gt;Пишите в чат: порода, сколько кубов, номер машины и куда едет. Посчитаю и скажу срок сразу.&lt;br&gt;&lt;br&gt;Для кого. Для тех, кто возит кругляк, доску, брус или дрова. На каждый рейс нужен электронный сопроводительный документ из ФГИС ЛК. QR код проверяют на посту и на приёмке. Нет документа, значит штраф и простой машины.&lt;br&gt;&lt;br&gt;Как работаю. Вы пишете данные по рейсу, я выписываю ЭСД и присылаю файлом. Водитель показывает QR с телефона или распечатку. Работаю с ИП и ООО, оплата после готового документа.&lt;br&gt;&lt;br&gt;Если вашего объёма нет в системе, сначала завожу партию: договор купли-продажи и постановка на баланс. Кабинет в ФГИС ЛК и электронная подпись вам не нужны.&lt;br&gt;&lt;br&gt;ЭСД, QR код на перевозку леса, документы ФГИС ЛК, Белгородская область, Тербуны.</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Липецкая обл., Тербуны, ул. Дорожная, 5</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>2026-10-19T09:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>2026-11-18T06:40:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>4330000105</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261019/c4.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261016/e1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n01/3.jpg</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Лес не числится в ФГИС ЛК, поставлю на баланс</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Помогаю, если лес не числится в ФГИС ЛК или остатки не сходятся. Сам лес не продаю, оформляю документы. Цена указана за постановку партии на баланс.&lt;br&gt;&lt;br&gt;Пишите в чат: что за древесина, сколько кубов, откуда она у вас. Скажу, что нужно и за сколько.&lt;br&gt;&lt;br&gt;Что делаю. Оформляю договор купли-продажи на партию и ставлю её вам на баланс. После этого выписываю ЭСД с QR кодом на каждый рейс. Обычно в тот же день.&lt;br&gt;&lt;br&gt;Работаю с ИП и ООО, оплата после готового результата. Кабинет в ФГИС ЛК и электронная подпись вам не нужны, всё с моей стороны.&lt;br&gt;&lt;br&gt;Постановка на баланс ФГИС ЛК, ЭСД, QR код на перевозку, документы на древесину, Белгородская область, Чернянка.</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Белгородская обл., Чернянка, ул. Кольцова, 10</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>2026-10-19T09:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>2026-11-18T06:40:00+03:00</t>
         </is>
       </c>
     </row>
@@ -11305,7 +11559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM194"/>
+  <dimension ref="A1:AM197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -38968,6 +39222,447 @@
         </is>
       </c>
       <c r="AL194" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>4330000103</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Ель пиловочник кругляк(QR на рейс)</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Сам лес и доску не продаю, оформляю документы. Цена указана за оформление.&lt;br&gt;QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа. Пишите в чат породу и кубатуру, посчитаю сразу.&lt;br&gt;&lt;br&gt;Саратовская область, еловый пиловочник и кругляк. Делаю QR коды на рейс и документы на объём.&lt;br&gt;&lt;br&gt;Частая история: лес взяли при расчистке участка или купили у хозяйства, покупатель есть, а отправить машину нельзя. В ФГИС ЛК этого объёма нет, и для поста он как будто не существует.&lt;br&gt;&lt;br&gt;Как работаем:&lt;br&gt;1. Пишете в чат породу, кубы, номер машины и маршрут.&lt;br&gt;2. Оформляю договор купли-продажи на партию, завожу древесину в систему и ставлю вам на баланс, обычно в тот же день.&lt;br&gt;3. На каждый рейс выписываю ЭСД с QR кодом за 15 минут, водитель показывает его с телефона.&lt;br&gt;&lt;br&gt;Кабинет в ФГИС ЛК и электронная подпись вам не нужны, всё удалённо. Разбор ситуации бесплатный.&lt;br&gt;&lt;br&gt;Ель пиловочник, кругляк, сосна, хвоя, баланс, QR код на рейс, ЭСД, документы ФГИС ЛК, Саратовская область, Аркадак.</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261019/c2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261016/e3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n04/3.jpg</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Саратовская обл., Аркадак, ул. Луначарского, 12</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>2026-10-19T09:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>2026-11-18T06:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL195" t="inlineStr">
+        <is>
+          <t>4403231200</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>4330000102</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Хвоя кругляк оптом(QR на вывозку)</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Сам лес и доску не продаю, оформляю документы. Цена указана за оформление.&lt;br&gt;QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа. Пишите в чат породу и кубатуру, посчитаю сразу.&lt;br&gt;&lt;br&gt;Калужская область, хвойный кругляк оптом, сосна и ель. Делаю QR коды на вывозку и документы на древесину.&lt;br&gt;&lt;br&gt;Когда объём идёт потоком, документ нужен на каждую машину. Эту часть беру на себя.&lt;br&gt;&lt;br&gt;Как работаем:&lt;br&gt;1. Пишете в чат породу, кубы, номер машины и маршрут.&lt;br&gt;2. Проверяю партию в ФГИС ЛК. Нет её там, оформляю договор купли-продажи и ставлю вам на баланс, обычно в тот же день.&lt;br&gt;3. На каждый рейс выписываю ЭСД с QR кодом за 15 минут. Как выглядит документ, видно на втором фото.&lt;br&gt;&lt;br&gt;Разовая машина или постоянный поток, регулярные отгрузки считаю помесячно.&lt;br&gt;&lt;br&gt;Кабинет в ФГИС ЛК и электронная подпись вам не нужны, всё удалённо. Разбор ситуации бесплатный.&lt;br&gt;&lt;br&gt;Хвоя оптом, сосна кругляк, ель, пиловочник, баланс, QR код на вывозку, ЭСД на рейс, документы ФГИС ЛК, Калужская область, Думиничи.</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261019/c1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261016/e2.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n13/2.jpg</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Калужская обл., Думиничи, ул. Тургенева, 7</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>2026-10-19T09:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>2026-11-18T06:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL196" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>4330000106</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Кругляк сосна (ЭСД на машину)</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Сам лес и доску не продаю, оформляю документы. Цена указана за оформление.&lt;br&gt;QR и ЭСД за 15 минут, работаю с ИП и ООО, оплата после готового документа. Пишите в чат породу и кубатуру, посчитаю сразу.&lt;br&gt;&lt;br&gt;Калужская область, сосновый кругляк и пиловочник. Делаю QR коды на перевозку и документы на древесину.&lt;br&gt;&lt;br&gt;Что за QR код. На каждую машину с лесом нужен электронный сопроводительный документ, ЭСД. В нём QR код, который сканируют на посту и на весовой. Нет документа, значит рейс под вопросом и штраф.&lt;br&gt;&lt;br&gt;Как работаем:&lt;br&gt;1. Пишете в чат породу, сколько кубов, номер машины и куда едет.&lt;br&gt;2. Если объёма нет в ФГИС ЛК, оформляю договор купли-продажи и ставлю партию вам на баланс, обычно в тот же день.&lt;br&gt;3. Делаю ЭСД с QR кодом за 15 минут и присылаю файлом.&lt;br&gt;&lt;br&gt;Кабинет в ФГИС ЛК и электронная подпись вам не нужны, всё удалённо. Разбор ситуации бесплатный.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, QR код на перевозку, ЭСД, документы ФГИС ЛК, Калужская область, Перемышль.</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261019/c5.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261016/e5.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n08/3.jpg</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Калужская обл., Перемышль, ул. Некрасова, 4</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>2026-10-19T09:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>2026-11-18T06:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL197" t="inlineStr">
         <is>
           <t>4403211200</t>
         </is>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -4648,7 +4648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE48"/>
+  <dimension ref="A1:AE53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="26"/>
@@ -10907,6 +10907,656 @@
       <c r="AE48" t="inlineStr">
         <is>
           <t>2026-11-18T06:40:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2451409014</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/c110.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n06/3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/e110.jpg</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>2200</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Лес без документов, оформим учёт</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Оформлю лес, на который нет бумаг, чтобы его можно было законно продать и вывезти.&lt;br&gt;&lt;br&gt;Вы рассказываете, что за лес, сколько кубов и откуда он. Я проверяю, есть ли он в ФГИС ЛК. Если нет, оформляю его через договор купли-продажи и ставлю вам на баланс. После этого на каждую машину делаю ЭСД с QR кодом, около 15 минут на рейс.&lt;br&gt;&lt;br&gt;Что нужно от вас:&lt;br&gt;- ИНН вашего ИП или ООО;&lt;br&gt;- порода и примерный объём;&lt;br&gt;- откуда лес: купили, свой участок, расчистка;&lt;br&gt;- где он сейчас лежит;&lt;br&gt;- если есть, любые бумаги на этот лес: договор, акт, фото.&lt;br&gt;&lt;br&gt;Электронная подпись и кабинет в системе вам не нужны. Работаю с ИП и ООО, оплата по безналу за готовый документ.&lt;br&gt;&lt;br&gt;Лес без документов, учёт древесины в ФГИС ЛК, ЭСД, QR код, договор купли-продажи, Курская область, Щигры.&lt;br&gt;&lt;br&gt;Напишите в чат, сколько леса и как он у вас появился, скажу, как оформить.</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Курская обл., Щигры, ул. Плеханова, 8</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>2026-11-21T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>2026-11-21T06:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>7955335616</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/c114.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n06/3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/e114.jpg</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>280</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>QR код на перевозку леса и документы</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Сделаю QR код на перевозку для любой машины с лесом: кругляк, доска, брус или дрова.&lt;br&gt;&lt;br&gt;Вы пишете, что везёте, сколько кубов и куда. Я проверяю, числится ли объём за вами в ФГИС ЛК, и выписываю ЭСД, электронный документ на машину с QR кодом. Если объёма нет, сначала оформляю его по договору купли-продажи. Один рейс около 15 минут.&lt;br&gt;&lt;br&gt;Что нужно от вас:&lt;br&gt;- ИНН продавца и покупателя;&lt;br&gt;- порода, сортимент и кубы;&lt;br&gt;- госномер машины и прицепа;&lt;br&gt;- откуда и куда едет машина;&lt;br&gt;- дата и примерное время выезда.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС ЛК и подпись заводить не нужно. Работаю с ИП и ООО, безнал, платите за готовый документ.&lt;br&gt;&lt;br&gt;QR код на перевозку леса, ЭСД, ФГИС ЛК, кругляк, пиломатериал, дрова, Воронежская область, Павловск.&lt;br&gt;&lt;br&gt;Скиньте в чат груз и маршрут, пришлю QR до выезда машины.</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Воронежская обл., Павловск, пр-т Революции, 30</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>2026-11-22T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>2026-11-22T05:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>9662145474</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/c116.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n06/3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/e116.jpg</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>450</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Документы на лес с вашего участка</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Оформлю документы на лес с вашего участка, чтобы его можно было вывезти и продать.&lt;br&gt;&lt;br&gt;Сообщаете, где рубили, какая порода и сколько кубов. Я проверяю ФГИС ЛК, оформляю объём по договору купли-продажи и ставлю его вам на баланс. Дальше на каждую машину делаю ЭСД с QR кодом, это минут 15 на рейс.&lt;br&gt;&lt;br&gt;Что нужно от вас:&lt;br&gt;- ИНН вашего ИП или ООО;&lt;br&gt;- порода и примерный объём;&lt;br&gt;- откуда лес: купили, свой участок, расчистка;&lt;br&gt;- где он сейчас лежит;&lt;br&gt;- если есть, любые бумаги на этот лес: договор, акт, фото.&lt;br&gt;&lt;br&gt;Ни подписи, ни кабинета от вас не требуется. ИП и ООО, оплата безналом, когда документ готов.&lt;br&gt;&lt;br&gt;Документы на лес с участка, учёт в ФГИС ЛК, ЭСД, QR код на вывоз, Курская область, Фатеж.&lt;br&gt;&lt;br&gt;Напишите, сколько леса лежит и куда хотите вывезти, подскажу сроки.</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Курская обл., Фатеж, ул. Урицкого, 9</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>2026-11-22T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>2026-10-23T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>2026-11-22T08:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>6904989802</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/c119.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n06/3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/e119.jpg</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>490</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Эсд и QR код на перевозку леса</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Выпишу ЭСД с QR кодом на машину с лесом, чтобы рейс прошёл проверку на посту и на весах.&lt;br&gt;&lt;br&gt;Присылаете породу, объём, номер машины и пункт назначения. Проверяю, стоит ли лес за вами в ФГИС ЛК, и оформляю ЭСД, внутри него QR код. Если леса в системе нет, сначала ставлю его на баланс по договору купли-продажи. На рейс уходит около 15 минут.&lt;br&gt;&lt;br&gt;Что нужно от вас:&lt;br&gt;- ИНН продавца и покупателя;&lt;br&gt;- порода, сортимент и кубы;&lt;br&gt;- госномер машины и прицепа;&lt;br&gt;- откуда и куда едет машина;&lt;br&gt;- дата и примерное время выезда.&lt;br&gt;&lt;br&gt;Подпись и личный кабинет не понадобятся. Работаю с ИП и ООО по безналу, оплата после готового документа.&lt;br&gt;&lt;br&gt;ЭСД на перевозку леса, QR код, ФГИС ЛК, кругляк, пиломатериал, дрова, Тамбовская область, Жердевка.&lt;br&gt;&lt;br&gt;Сообщите в чат номер машины и куда едет, документ сделаю к отправке.</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Тамбовская обл., Жердевка, ул. Чапаева, 11</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>2026-11-23T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>2026-11-23T05:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>7823441126</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/c121.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n06/3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/e121.jpg</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>500</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>QR код на перевозку леса за 15 минут</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Сделаю QR код на перевозку леса минут за 15, чтобы машина ушла с погрузки без задержек.&lt;br&gt;&lt;br&gt;Вы пишете, что везёте, сколько кубов и куда. Я сверяю остаток в ФГИС ЛК и выписываю ЭСД с QR кодом, водитель показывает его с телефона. Если объём за вами не числится, сначала оформляю его договором купли-продажи.&lt;br&gt;&lt;br&gt;Что нужно от вас:&lt;br&gt;- ИНН продавца и покупателя;&lt;br&gt;- порода, сортимент и кубы;&lt;br&gt;- госномер машины и прицепа;&lt;br&gt;- откуда и куда едет машина;&lt;br&gt;- дата и примерное время выезда.&lt;br&gt;&lt;br&gt;Электронная подпись и кабинет в системе вам не нужны. Работаю с ИП и ООО, оплата по безналу за готовый документ.&lt;br&gt;&lt;br&gt;QR код на перевозку леса, ЭСД на рейс, ФГИС ЛК, кругляк, дрова, пиломатериал, Оренбургская область, Сорочинск.&lt;br&gt;&lt;br&gt;Пишите в чат прямо с погрузки, QR будет к выходу машины.</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Оренбургская обл., Сорочинск, ул. Чкалова, 14</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>2026-11-23T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>2026-11-23T08:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -11559,7 +12209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM197"/>
+  <dimension ref="A1:AM207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -39665,6 +40315,1521 @@
       <c r="AL197" t="inlineStr">
         <is>
           <t>4403211200</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2662391028</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Хвоя кругляк, QR код на отгрузку</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Сделаю QR код на отгрузку хвойного кругляка, чтобы машина прошла пост и весовую без остановок.&lt;br&gt;&lt;br&gt;Вы пишете, сколько кубов и куда везёте. Я смотрю, числится ли этот объём за вами в ФГИС ЛК. Если нет, оформляю его по договору купли-продажи и ставлю вам на баланс. Потом делаю ЭСД, электронный документ на машину, в нём и есть QR код. На один рейс уходит около 15 минут.&lt;br&gt;&lt;br&gt;Что нужно от вас:&lt;br&gt;- порода и сортимент, сколько кубов;&lt;br&gt;- госномер машины и прицепа;&lt;br&gt;- откуда грузите и куда везёте;&lt;br&gt;- ИНН вашего ИП или ООО и данные покупателя;&lt;br&gt;- дата выезда.&lt;br&gt;&lt;br&gt;Электронная подпись и кабинет в системе вам не нужны. Работаю с ИП и ООО, оплата по безналу за готовый документ.&lt;br&gt;&lt;br&gt;Сосна кругляк, ель, хвоя, пиловочник, QR код на отгрузку, ЭСД, ФГИС ЛК, Белгородская область, Шебекино.&lt;br&gt;&lt;br&gt;Напишите в чат объём и куда идёт машина, подготовлю QR код к отгрузке.</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/c107.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/e107.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n03/3.jpg</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Белгородская обл., Шебекино, ул. Харьковская, 20</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P198" t="n">
+        <v>4300</v>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>2026-11-21T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>2026-10-22T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>2026-11-21T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL198" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>3403078478</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Ель пиловочник кругляк(QR на рейс)</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Оформлю QR код на рейс с еловым пиловочником, чтобы пилорама приняла лес без вопросов про происхождение.&lt;br&gt;&lt;br&gt;Присылаете кубатуру и пункт назначения. Проверяю, стоит ли лес за вами в ФГИС ЛК. Если не стоит, сначала оформляем его через договор купли-продажи, и объём встаёт вам на баланс. Дальше выписываю ЭСД, это электронная накладная на машину с QR кодом. Один рейс оформляю минут за 15.&lt;br&gt;&lt;br&gt;Что от вас потребуется:&lt;br&gt;- ИНН вашей организации или ИП;&lt;br&gt;- порода, кубатура, сортимент;&lt;br&gt;- номер лесовоза и прицепа;&lt;br&gt;- адрес погрузки и адрес приёмки;&lt;br&gt;- кому везёте: название и ИНН покупателя.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС ЛК и подпись заводить не нужно. Работаю с ИП и ООО, безнал, платите за готовый документ.&lt;br&gt;&lt;br&gt;Ель пиловочник, кругляк, хвоя, QR код на рейс, ЭСД, ФГИС ЛК, Воронежская область, Острогожск.&lt;br&gt;&lt;br&gt;Пришлите кубатуру ели и адрес пилорамы, документ будет готов до выезда.</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/c108.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n12/3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/e108.jpg</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Воронежская обл., Острогожск, ул. Медведовского, 15</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P199" t="n">
+        <v>260</v>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>2026-11-21T03:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>2026-10-22T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>2026-11-21T03:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL199" t="inlineStr">
+        <is>
+          <t>4403231200</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2789584456</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Хвоя кругляк оптом(QR на вывозку)</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Беру на себя документы на вывоз хвои оптом: QR код на каждую машину, чтобы поток не вставал на постах.&lt;br&gt;&lt;br&gt;Вы сообщаете породу, объём и куда идёт машина. Я проверяю ваш остаток в ФГИС ЛК, а если леса там нет, оформляю его договором купли-продажи и ставлю на баланс. Затем формирую ЭСД на рейс, внутри него QR код. Обычно это 15 минут на машину.&lt;br&gt;&lt;br&gt;Для документа пришлите:&lt;br&gt;- ИНН продавца и покупателя;&lt;br&gt;- что везёте и сколько кубов;&lt;br&gt;- госномер машины, если есть прицеп, то и его;&lt;br&gt;- место погрузки и куда едет машина;&lt;br&gt;- когда выезд.&lt;br&gt;&lt;br&gt;Ни подписи, ни кабинета от вас не требуется. ИП и ООО, оплата безналом, когда документ готов.&lt;br&gt;&lt;br&gt;Хвоя кругляк оптом, сосна, ель, баланс, QR код на вывозку, ЭСД, ФГИС ЛК, Оренбургская область, Бугуруслан.&lt;br&gt;&lt;br&gt;Скиньте в чат, сколько машин в неделю и куда, посчитаю оформление на весь поток.</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/c109.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/e109.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n06/3.jpg</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Оренбургская обл., Бугуруслан, ул. Красногвардейская, 30</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P200" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>2026-11-21T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>2026-10-22T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>2026-11-21T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL200" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>7634581130</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Сосна кругляк (QR код на перевозку)</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Подготовлю QR код на перевозку сосны, чтобы лесовоз спокойно доехал до покупателя.&lt;br&gt;&lt;br&gt;Пишете, сколько кубов и куда. Смотрю, есть ли этот лес за вами в системе ФГИС ЛК. Если нет, сначала оформляю его по договору купли-продажи на ваш баланс. После этого делаю электронный документ на машину, ЭСД, с QR кодом. Рейс занимает около 15 минут.&lt;br&gt;&lt;br&gt;Что от вас потребуется:&lt;br&gt;- ИНН вашей организации или ИП;&lt;br&gt;- порода, кубатура, сортимент;&lt;br&gt;- номер лесовоза и прицепа;&lt;br&gt;- адрес погрузки и адрес приёмки;&lt;br&gt;- кому везёте: название и ИНН покупателя.&lt;br&gt;&lt;br&gt;Подпись и личный кабинет не понадобятся. Работаю с ИП и ООО по безналу, оплата после готового документа.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, хвоя, QR код на перевозку, ЭСД, ФГИС ЛК, Тамбовская область, Мичуринск.&lt;br&gt;&lt;br&gt;Напишите объём сосны и пункт выгрузки, оформлю QR код к выходу лесовоза.</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/c111.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/e111.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n12/3.jpg</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Тамбовская обл., Мичуринск, ул. Интернациональная, 40</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P201" t="n">
+        <v>3100</v>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>2026-11-21T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>2026-10-22T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>2026-11-21T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL201" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>9468426929</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Берёза кругляк, QR код на рейс</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Оформлю QR код на рейс с берёзой, чтобы приёмка не развернула машину с кругляком или дровами.&lt;br&gt;&lt;br&gt;От вас объём и пункт приёмки. Я сверяю, числится ли лес за вами в ФГИС ЛК. Если не числится, оформляю через договор купли-продажи и ставлю на баланс. Потом выписываю ЭСД, электронный документ на рейс с QR кодом. На одну машину около 15 минут.&lt;br&gt;&lt;br&gt;Для документа пришлите:&lt;br&gt;- ИНН продавца и покупателя;&lt;br&gt;- что везёте и сколько кубов;&lt;br&gt;- госномер машины, если есть прицеп, то и его;&lt;br&gt;- место погрузки и куда едет машина;&lt;br&gt;- когда выезд.&lt;br&gt;&lt;br&gt;Электронная подпись и кабинет в системе вам не нужны. Работаю с ИП и ООО, оплата по безналу за готовый документ.&lt;br&gt;&lt;br&gt;Берёза кругляк, дрова, баланс, фанкряж, QR код на рейс, ЭСД, ФГИС ЛК, Белгородская область, Губкин.&lt;br&gt;&lt;br&gt;Сообщите в чат кубы берёзы и куда везёте, сделаю документ к погрузке.</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/c112.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n06/3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/e112.jpg</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Белгородская обл., Губкин, ул. Дзержинского, 70</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P202" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>2026-11-22T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>2026-10-23T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>2026-11-22T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL202" t="inlineStr">
+        <is>
+          <t>4403950000</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t>Не требуется</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>4307851435</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Ель пиловочник, документы фгис лк</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Приведу в порядок документы на еловый пиловочник в ФГИС ЛК, чтобы лес можно было продать и вывезти.&lt;br&gt;&lt;br&gt;Вы пишете, сколько кубов и куда везёте. Я смотрю, числится ли этот объём за вами в ФГИС ЛК. Если нет, оформляю его по договору купли-продажи и ставлю вам на баланс. Потом делаю ЭСД, электронный документ на машину, в нём и есть QR код. На один рейс уходит около 15 минут.&lt;br&gt;&lt;br&gt;Что нужно от вас:&lt;br&gt;- порода и сортимент, сколько кубов;&lt;br&gt;- госномер машины и прицепа;&lt;br&gt;- откуда грузите и куда везёте;&lt;br&gt;- ИНН вашего ИП или ООО и данные покупателя;&lt;br&gt;- дата выезда.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС ЛК и подпись заводить не нужно. Работаю с ИП и ООО, безнал, платите за готовый документ.&lt;br&gt;&lt;br&gt;Ель пиловочник, кругляк, хвоя, документы ФГИС ЛК, учёт древесины, ЭСД, QR код, Калужская область, Боровск.&lt;br&gt;&lt;br&gt;Опишите в чат, сколько леса и что не сходится, скажу, как поправить.</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/c113.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/e113.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n03/3.jpg</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Калужская обл., Боровск, ул. Калужская, 5</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P203" t="n">
+        <v>2900</v>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>2026-11-22T03:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>2026-11-22T03:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL203" t="inlineStr">
+        <is>
+          <t>4403231200</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>9940673025</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Осина баланс дрова, QR на вывоз</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Сделаю QR код на вывоз осины, чтобы плитный комбинат принял баланс без лишних вопросов.&lt;br&gt;&lt;br&gt;Присылаете кубатуру и пункт назначения. Проверяю, стоит ли лес за вами в ФГИС ЛК. Если не стоит, сначала оформляем его через договор купли-продажи, и объём встаёт вам на баланс. Дальше выписываю ЭСД, это электронная накладная на машину с QR кодом. Один рейс оформляю минут за 15.&lt;br&gt;&lt;br&gt;Для документа пришлите:&lt;br&gt;- ИНН продавца и покупателя;&lt;br&gt;- что везёте и сколько кубов;&lt;br&gt;- госномер машины, если есть прицеп, то и его;&lt;br&gt;- место погрузки и куда едет машина;&lt;br&gt;- когда выезд.&lt;br&gt;&lt;br&gt;Ни подписи, ни кабинета от вас не требуется. ИП и ООО, оплата безналом, когда документ готов.&lt;br&gt;&lt;br&gt;Осина баланс, дрова, кругляк, QR код на вывоз, ЭСД, ФГИС ЛК, Липецкая область, Грязи.&lt;br&gt;&lt;br&gt;Напишите кубатуру осины и комбинат, куда везёте, QR будет к выходу машины.</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/c115.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/e115.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n06/3.jpg</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Липецкая обл., Грязи, ул. Воровского, 12</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P204" t="n">
+        <v>190</v>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>Осина</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>2026-11-22T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>2026-11-22T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL204" t="inlineStr">
+        <is>
+          <t>4403970002</t>
+        </is>
+      </c>
+      <c r="AM204" t="inlineStr">
+        <is>
+          <t>Не требуется</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>1957589076</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Хвоя кругляк, QR код на отгрузку</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Оформлю QR код на отгрузку хвои, чтобы покупатель получил машину с чистыми бумагами.&lt;br&gt;&lt;br&gt;Вы сообщаете породу, объём и куда идёт машина. Я проверяю ваш остаток в ФГИС ЛК, а если леса там нет, оформляю его договором купли-продажи и ставлю на баланс. Затем формирую ЭСД на рейс, внутри него QR код. Обычно это 15 минут на машину.&lt;br&gt;&lt;br&gt;Что от вас потребуется:&lt;br&gt;- ИНН вашей организации или ИП;&lt;br&gt;- порода, кубатура, сортимент;&lt;br&gt;- номер лесовоза и прицепа;&lt;br&gt;- адрес погрузки и адрес приёмки;&lt;br&gt;- кому везёте: название и ИНН покупателя.&lt;br&gt;&lt;br&gt;Подпись и личный кабинет не понадобятся. Работаю с ИП и ООО по безналу, оплата после готового документа.&lt;br&gt;&lt;br&gt;Хвоя кругляк, сосна, ель, пиловочник, QR код на отгрузку, ЭСД, ФГИС ЛК, Белгородская область, Ракитное.&lt;br&gt;&lt;br&gt;Пришлите объём и покупателя, подготовлю документ на каждую машину.</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/c117.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/e117.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n12/3.jpg</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Белгородская обл., Ракитное, ул. Пролетарская, 20</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P205" t="n">
+        <v>4300</v>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>2026-11-23T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>2026-10-24T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>2026-11-23T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL205" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>1766445938</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Доска обрезная, эсд на рейс</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Делаю ЭСД на рейс с доской и брусом, чтобы машину с пиломатериалом не держали на посту.&lt;br&gt;&lt;br&gt;Пишете, сколько кубов и куда. Смотрю, есть ли этот лес за вами в системе ФГИС ЛК. Если нет, сначала оформляю его по договору купли-продажи на ваш баланс. После этого делаю электронный документ на машину, ЭСД, с QR кодом. Рейс занимает около 15 минут.&lt;br&gt;&lt;br&gt;Для документа пришлите:&lt;br&gt;- ИНН продавца и покупателя;&lt;br&gt;- что везёте и сколько кубов;&lt;br&gt;- госномер машины, если есть прицеп, то и его;&lt;br&gt;- место погрузки и куда едет машина;&lt;br&gt;- когда выезд.&lt;br&gt;&lt;br&gt;Электронная подпись и кабинет в системе вам не нужны. Работаю с ИП и ООО, оплата по безналу за готовый документ.&lt;br&gt;&lt;br&gt;Доска обрезная, брус, пиломатериал хвоя, ЭСД на рейс, QR код, ФГИС ЛК, Калужская область, Малоярославец.&lt;br&gt;&lt;br&gt;Напишите, сколько кубов доски и куда везёте, оформлю к отгрузке.</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/c118.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n06/3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/e118.jpg</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Калужская обл., Малоярославец, ул. Московская, 15</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P206" t="n">
+        <v>390</v>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>2026-11-23T03:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>2026-10-24T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>2026-11-23T03:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL206" t="inlineStr">
+        <is>
+          <t>4407119406</t>
+        </is>
+      </c>
+      <c r="AM206" t="inlineStr">
+        <is>
+          <t>16.10.10.111</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>4308380189</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Ель пиловочник кругляк(QR на рейс)</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Подготовлю QR код на рейс с елью, чтобы машина ушла с делянки уже с документом.&lt;br&gt;&lt;br&gt;От вас объём и пункт приёмки. Я сверяю, числится ли лес за вами в ФГИС ЛК. Если не числится, оформляю через договор купли-продажи и ставлю на баланс. Потом выписываю ЭСД, электронный документ на рейс с QR кодом. На одну машину около 15 минут.&lt;br&gt;&lt;br&gt;Что от вас потребуется:&lt;br&gt;- ИНН вашей организации или ИП;&lt;br&gt;- порода, кубатура, сортимент;&lt;br&gt;- номер лесовоза и прицепа;&lt;br&gt;- адрес погрузки и адрес приёмки;&lt;br&gt;- кому везёте: название и ИНН покупателя.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС ЛК и подпись заводить не нужно. Работаю с ИП и ООО, безнал, платите за готовый документ.&lt;br&gt;&lt;br&gt;Ель пиловочник, кругляк, сосна, хвоя, QR код на рейс, ЭСД, ФГИС ЛК, Воронежская область, Лиски.&lt;br&gt;&lt;br&gt;Сообщите кубатуру и пункт приёмки, документ будет до того, как машина тронется.</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/c120.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20260813/n12/3.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261021/e120.jpg</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Воронежская обл., Лиски, ул. Сеченова, 25</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P207" t="n">
+        <v>260</v>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>2026-11-23T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>2026-10-24T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>2026-11-23T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL207" t="inlineStr">
+        <is>
+          <t>4403231200</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -4648,7 +4648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE53"/>
+  <dimension ref="A1:AE68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="26"/>
@@ -11557,6 +11557,1956 @@
       <c r="AE53" t="inlineStr">
         <is>
           <t>2026-11-23T08:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>6099922300</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a201_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a201_ig.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a201_esd.jpg</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>420</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>QR код на перевозку леса за 15 минут</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>QR код на перевозку леса делаю минут за 15, документ приходит прямо в мессенджер.&lt;br&gt;&lt;br&gt;Присылаете породу, объём, номер машины и пункт назначения. Проверяю, стоит ли лес за вами в ФГИС ЛК, и оформляю ЭСД, внутри него QR код. Если леса в системе нет, сначала ставлю его на баланс по договору купли-продажи.&lt;br&gt;&lt;br&gt;Для документа пришлите:&lt;br&gt;- ИНН продавца и покупателя;&lt;br&gt;- что везёте и сколько кубов;&lt;br&gt;- когда выезд;&lt;br&gt;- место погрузки и куда едет машина;&lt;br&gt;- госномер машины, если есть прицеп, то и его.&lt;br&gt;&lt;br&gt;Подпись и личный кабинет не понадобятся. Работаю с ИП и ООО по безналу, оплата после готового документа.&lt;br&gt;&lt;br&gt;QR код на перевозку леса, ЭСД на рейс, ФГИС ЛК, кругляк, дрова, Белгородская область, Борисовка.&lt;br&gt;&lt;br&gt;Напишите в чат объём и куда идёт машина, подготовлю QR код к отгрузке.</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Белгородская обл., Борисовка, ул. Куйбышева, 33</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>2026-11-26T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>2026-10-27T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>2026-11-26T02:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>8180513406</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a202_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a202_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a202_ig.jpg</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>280</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>QR код на перевозку леса и документы</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Документы на перевозку леса и QR код для водителя, на одну машину или на поток.&lt;br&gt;&lt;br&gt;Присылаете породу, объём, номер машины и пункт назначения. Проверяю, стоит ли лес за вами в ФГИС ЛК, и оформляю ЭСД, внутри него QR код. Если леса в системе нет, сначала ставлю его на баланс по договору купли-продажи.&lt;br&gt;&lt;br&gt;Для документа пришлите:&lt;br&gt;- когда выезд;&lt;br&gt;- что везёте и сколько кубов;&lt;br&gt;- ИНН продавца и покупателя;&lt;br&gt;- госномер машины, если есть прицеп, то и его;&lt;br&gt;- место погрузки и куда едет машина.&lt;br&gt;&lt;br&gt;Подпись и личный кабинет не понадобятся. Работаю с ИП и ООО по безналу, оплата после готового документа.&lt;br&gt;&lt;br&gt;QR код на перевозку леса, ЭСД, ФГИС ЛК, кругляк, пиломатериал, дрова, Курская область, Курчатов.&lt;br&gt;&lt;br&gt;Скиньте в чат, сколько машин в неделю и куда, посчитаю оформление на весь поток.</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Курская обл., Курчатов, ул. Вокзальная, 33</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>2026-11-26T03:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>2026-10-27T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>2026-11-26T03:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>9097132549</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a206_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a206_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a206_ig.jpg</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>2200</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Лес без документов, оформим учёт</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Оформлю лес, на который нет бумаг, чтобы его можно было законно продать и вывезти.&lt;br&gt;&lt;br&gt;Сообщаете, где рубили, какая порода и сколько кубов. Я проверяю ФГИС ЛК, оформляю объём по договору купли-продажи и ставлю его вам на баланс. Дальше на каждую машину делаю ЭСД с QR кодом, это минут 15 на рейс.&lt;br&gt;&lt;br&gt;Что нужно от вас:&lt;br&gt;- порода и примерный объём;&lt;br&gt;- откуда лес: купили, свой участок, расчистка;&lt;br&gt;- где он сейчас лежит;&lt;br&gt;- ИНН вашего ИП или ООО;&lt;br&gt;- если есть, любые бумаги на этот лес: договор, акт, фото.&lt;br&gt;&lt;br&gt;Подпись и личный кабинет не понадобятся. Работаю с ИП и ООО по безналу, оплата после готового документа.&lt;br&gt;&lt;br&gt;Лес без документов, учёт древесины в ФГИС ЛК, ЭСД, QR код, договор купли-продажи, Калужская область, Таруса.&lt;br&gt;&lt;br&gt;Напишите в чат, сколько леса и как он у вас появился, скажу, как оформить.</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Калужская обл., Таруса, ул. Островского, 19</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>2026-11-27T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>2026-10-28T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>2026-11-27T02:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>5047117601</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a209_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a209_ig.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a209_esd.jpg</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>2200</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Лес без документов, оформим учёт</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Лес есть, а документов нет: оформлю его в ФГИС ЛК, чтобы можно было продавать.&lt;br&gt;&lt;br&gt;Сообщаете, где рубили, какая порода и сколько кубов. Я проверяю ФГИС ЛК, оформляю объём по договору купли-продажи и ставлю его вам на баланс. Дальше на каждую машину делаю ЭСД с QR кодом, это минут 15 на рейс.&lt;br&gt;&lt;br&gt;Для начала пришлите:&lt;br&gt;- как лес у вас появился;&lt;br&gt;- фото штабеля, если есть;&lt;br&gt;- адрес или координаты, где он лежит;&lt;br&gt;- ИНН организации или ИП;&lt;br&gt;- какая порода и сколько примерно кубов.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС ЛК и подпись заводить не нужно. Работаю с ИП и ООО, безнал, платите за готовый документ.&lt;br&gt;&lt;br&gt;Лес без документов, учёт древесины в ФГИС ЛК, ЭСД, QR код, договор купли-продажи, Самарская область, Сызрань.&lt;br&gt;&lt;br&gt;Пришлите примерный объём и где лежит лес, подскажу сроки.</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Самарская обл., Сызрань, ул. Красноармейская, 52</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>2026-11-27T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>2026-10-28T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>2026-11-27T06:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>5069728316</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a212_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a212_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a212_ig.jpg</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>1900</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Лес без документов, оформим учёт</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Сделаю так, чтобы лес без документов числился за вами по всем правилам.&lt;br&gt;&lt;br&gt;Вы рассказываете, что за лес, сколько кубов и откуда он. Я проверяю, есть ли он в ФГИС ЛК. Если нет, оформляю его через договор купли-продажи и ставлю вам на баланс. После этого на каждую машину делаю ЭСД с QR кодом, около 15 минут на рейс.&lt;br&gt;&lt;br&gt;Для начала пришлите:&lt;br&gt;- адрес или координаты, где он лежит;&lt;br&gt;- как лес у вас появился;&lt;br&gt;- какая порода и сколько примерно кубов;&lt;br&gt;- ИНН организации или ИП;&lt;br&gt;- фото штабеля, если есть.&lt;br&gt;&lt;br&gt;Подпись и личный кабинет не понадобятся. Работаю с ИП и ООО по безналу, оплата после готового документа.&lt;br&gt;&lt;br&gt;Лес без документов, учёт древесины в ФГИС ЛК, ЭСД, QR код, договор купли-продажи, Орловская область, Кромы.&lt;br&gt;&lt;br&gt;Напишите в чат, сколько леса и как он у вас появился, скажу, как оформить.</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Орловская обл., Кромы, ул. Гоголя, 46</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>2026-11-28T03:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>2026-10-29T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>2026-11-28T03:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>7969543087</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a215_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a215_ig.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a215_esd.jpg</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>450</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Документы на лес с вашего участка</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Сделаю бумаги на древесину со своей земли: расчистка, стройка, лесополоса.&lt;br&gt;&lt;br&gt;Сообщаете, где рубили, какая порода и сколько кубов. Я проверяю ФГИС ЛК, оформляю объём по договору купли-продажи и ставлю его вам на баланс. Дальше на каждую машину делаю ЭСД с QR кодом, это минут 15 на рейс.&lt;br&gt;&lt;br&gt;Для начала пришлите:&lt;br&gt;- как лес у вас появился;&lt;br&gt;- адрес или координаты, где он лежит;&lt;br&gt;- фото штабеля, если есть;&lt;br&gt;- ИНН организации или ИП;&lt;br&gt;- какая порода и сколько примерно кубов.&lt;br&gt;&lt;br&gt;Электронная подпись и кабинет в системе вам не нужны. Работаю с ИП и ООО, оплата по безналу за готовый документ.&lt;br&gt;&lt;br&gt;Документы на лес с участка, учёт в ФГИС ЛК, ЭСД, QR код на вывоз, Ставропольский край, Новоалександровск.&lt;br&gt;&lt;br&gt;Опишите ситуацию в чат, первый разговор бесплатный.</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Ставропольский край, Новоалександровск, ул. Фурманова, 30</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>2026-11-28T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>2026-11-28T08:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>3766472761</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a244_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a244_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a244_ig.jpg</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>350</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>QR код на перевозку леса и документы</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Сделаю QR код на перевозку для любой машины с лесом: кругляк, доска, брус или дрова.&lt;br&gt;&lt;br&gt;Присылаете породу, объём, номер машины и пункт назначения. Проверяю, стоит ли лес за вами в ФГИС ЛК, и оформляю ЭСД, внутри него QR код. Если леса в системе нет, сначала ставлю его на баланс по договору купли-продажи.&lt;br&gt;&lt;br&gt;Чтобы оформить рейс, нужно:&lt;br&gt;- номер машины и прицепа;&lt;br&gt;- ИНН вашего ИП или ООО;&lt;br&gt;- пункт погрузки и пункт выгрузки;&lt;br&gt;- порода и объём в кубах;&lt;br&gt;- кто покупатель и когда выезд.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС ЛК и подпись заводить не нужно. Работаю с ИП и ООО, безнал, платите за готовый документ.&lt;br&gt;&lt;br&gt;QR код на перевозку леса, ЭСД, ФГИС ЛК, кругляк, пиломатериал, дрова, Воронежская область, Богучар.&lt;br&gt;&lt;br&gt;Опишите в чат, сколько леса и что нужно, скажу, как оформить и сколько займёт.</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Воронежская обл., Богучар, ул. Полевая, 50</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>2026-11-30T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>2026-10-31T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>2026-11-30T02:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>9871339737</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a235_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a235_ig.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a235_esd.jpg</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>500</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>QR код на перевозку леса за 15 минут</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Сделаю QR код на лес за 15 минут, пока машину грузят.&lt;br&gt;&lt;br&gt;Вы пишете, что везёте, сколько кубов и куда. Я проверяю, числится ли объём за вами в ФГИС ЛК, и выписываю ЭСД, электронный документ на машину с QR кодом. Если объёма нет, сначала оформляю его по договору купли-продажи. Один рейс около 15 минут.&lt;br&gt;&lt;br&gt;Что от вас потребуется:&lt;br&gt;- порода, кубатура, сортимент;&lt;br&gt;- номер лесовоза и прицепа;&lt;br&gt;- кому везёте: название и ИНН покупателя;&lt;br&gt;- адрес погрузки и адрес приёмки;&lt;br&gt;- ИНН вашей организации или ИП.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС ЛК и подпись заводить не нужно. Работаю с ИП и ООО, безнал, платите за готовый документ.&lt;br&gt;&lt;br&gt;QR код на перевозку леса, ЭСД на рейс, ФГИС ЛК, кругляк, дрова, Тульская область, Чекалин.&lt;br&gt;&lt;br&gt;Отправьте данные машины и груза, документ пришлю в мессенджер.</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Тульская обл., Чекалин, ул. Молодёжная, 56</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>2026-12-01T03:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>2026-11-01T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>2026-12-01T03:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>8309506824</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a217_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a217_ig.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a217_esd.jpg</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>490</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Эсд и QR код на перевозку леса</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>ЭСД и QR код на рейс с лесом, чтобы машину не остановили на посту.&lt;br&gt;&lt;br&gt;Вы пишете, что везёте, сколько кубов и куда. Я проверяю, числится ли объём за вами в ФГИС ЛК, и выписываю ЭСД, электронный документ на машину с QR кодом. Если объёма нет, сначала оформляю его по договору купли-продажи. Один рейс около 15 минут.&lt;br&gt;&lt;br&gt;Что нужно от вас:&lt;br&gt;- порода и сортимент, сколько кубов;&lt;br&gt;- ИНН вашего ИП или ООО и данные покупателя;&lt;br&gt;- откуда грузите и куда везёте;&lt;br&gt;- госномер машины и прицепа;&lt;br&gt;- дата выезда.&lt;br&gt;&lt;br&gt;Ни подписи, ни кабинета от вас не требуется. ИП и ООО, оплата безналом, когда документ готов.&lt;br&gt;&lt;br&gt;ЭСД на перевозку леса, QR код, ФГИС ЛК, кругляк, пиломатериал, Краснодарский край, Белореченск.&lt;br&gt;&lt;br&gt;Отправьте данные машины и груза, документ пришлю в мессенджер.</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Краснодарский край, Белореченск, ул. Ломоносова, 32</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>2026-12-01T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>2026-11-01T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>2026-12-01T08:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>6166905852</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a221_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a221_ig.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a221_esd.jpg</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>650</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Документы на лес с вашего участка</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Лес со своего участка оформлю в ФГИС ЛК, чтобы его можно было вывезти законно.&lt;br&gt;&lt;br&gt;Вы рассказываете, что за лес, сколько кубов и откуда он. Я проверяю, есть ли он в ФГИС ЛК. Если нет, оформляю его через договор купли-продажи и ставлю вам на баланс. После этого на каждую машину делаю ЭСД с QR кодом, около 15 минут на рейс.&lt;br&gt;&lt;br&gt;Для начала пришлите:&lt;br&gt;- фото штабеля, если есть;&lt;br&gt;- адрес или координаты, где он лежит;&lt;br&gt;- как лес у вас появился;&lt;br&gt;- ИНН организации или ИП;&lt;br&gt;- какая порода и сколько примерно кубов.&lt;br&gt;&lt;br&gt;Электронная подпись и кабинет в системе вам не нужны. Работаю с ИП и ООО, оплата по безналу за готовый документ.&lt;br&gt;&lt;br&gt;Документы на лес с участка, учёт в ФГИС ЛК, ЭСД, QR код на вывоз, Ставропольский край, Изобильный.&lt;br&gt;&lt;br&gt;Пришлите примерный объём и где лежит лес, подскажу сроки.</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Ставропольский край, Изобильный, ул. Орджоникидзе, 40</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>2026-12-02T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>2026-11-02T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>2026-12-02T02:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>5836043132</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a222_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a222_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a222_ig.jpg</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>280</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>QR код на перевозку леса и документы</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Оформлю документы и QR код на перевозку древесины для разового рейса или потока.&lt;br&gt;&lt;br&gt;Присылаете породу, объём, номер машины и пункт назначения. Проверяю, стоит ли лес за вами в ФГИС ЛК, и оформляю ЭСД, внутри него QR код. Если леса в системе нет, сначала ставлю его на баланс по договору купли-продажи.&lt;br&gt;&lt;br&gt;Что от вас потребуется:&lt;br&gt;- ИНН вашей организации или ИП;&lt;br&gt;- номер лесовоза и прицепа;&lt;br&gt;- кому везёте: название и ИНН покупателя;&lt;br&gt;- адрес погрузки и адрес приёмки;&lt;br&gt;- порода, кубатура, сортимент.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС ЛК и подпись заводить не нужно. Работаю с ИП и ООО, безнал, платите за готовый документ.&lt;br&gt;&lt;br&gt;QR код на перевозку леса, ЭСД, ФГИС ЛК, кругляк, пиломатериал, дрова, Пензенская область, Белинский.&lt;br&gt;&lt;br&gt;Пришлите кубатуру и адрес приёмки, документ будет готов до выезда.</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Пензенская обл., Белинский, ул. Энгельса, 54</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>2026-12-02T03:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>2026-11-02T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>2026-12-02T03:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1840736098</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a227_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a227_ig.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a227_esd.jpg</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>1900</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Лес без документов, оформим учёт</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Помогу оформить древесину, которая лежит без бумаг, и вывезти её законно.&lt;br&gt;&lt;br&gt;Сообщаете, где рубили, какая порода и сколько кубов. Я проверяю ФГИС ЛК, оформляю объём по договору купли-продажи и ставлю его вам на баланс. Дальше на каждую машину делаю ЭСД с QR кодом, это минут 15 на рейс.&lt;br&gt;&lt;br&gt;Для начала пришлите:&lt;br&gt;- какая порода и сколько примерно кубов;&lt;br&gt;- ИНН организации или ИП;&lt;br&gt;- как лес у вас появился;&lt;br&gt;- фото штабеля, если есть;&lt;br&gt;- адрес или координаты, где он лежит.&lt;br&gt;&lt;br&gt;Электронная подпись и кабинет в системе вам не нужны. Работаю с ИП и ООО, оплата по безналу за готовый документ.&lt;br&gt;&lt;br&gt;Лес без документов, учёт древесины в ФГИС ЛК, ЭСД, QR код, договор купли-продажи, Курская область, Солнцево.&lt;br&gt;&lt;br&gt;Пришлите примерный объём и где лежит лес, подскажу сроки.</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Курская обл., Солнцево, ул. Герцена, 12</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>2026-12-02T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>2026-11-02T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>2026-12-02T06:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>7857094568</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a224_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a224_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a224_ig.jpg</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>650</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Документы на лес с вашего участка</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Оформлю документы на лес с вашего участка, чтобы его можно было вывезти и продать.&lt;br&gt;&lt;br&gt;Сообщаете, где рубили, какая порода и сколько кубов. Я проверяю ФГИС ЛК, оформляю объём по договору купли-продажи и ставлю его вам на баланс. Дальше на каждую машину делаю ЭСД с QR кодом, это минут 15 на рейс.&lt;br&gt;&lt;br&gt;Что нужно от вас:&lt;br&gt;- порода и примерный объём;&lt;br&gt;- ИНН вашего ИП или ООО;&lt;br&gt;- если есть, любые бумаги на этот лес: договор, акт, фото;&lt;br&gt;- где он сейчас лежит;&lt;br&gt;- откуда лес: купили, свой участок, расчистка.&lt;br&gt;&lt;br&gt;Подпись и личный кабинет не понадобятся. Работаю с ИП и ООО по безналу, оплата после готового документа.&lt;br&gt;&lt;br&gt;Документы на лес с участка, учёт в ФГИС ЛК, ЭСД, QR код на вывоз, Оренбургская область, Кувандык.&lt;br&gt;&lt;br&gt;Напишите в чат, сколько леса и как он у вас появился, скажу, как оформить.</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Оренбургская обл., Кувандык, ул. Розы Люксембург, 50</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>2026-12-03T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>2026-11-03T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>2026-12-03T06:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>9357319406</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a243_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a243_ig.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a243_esd.jpg</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>490</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Эсд и QR код на перевозку леса</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Выпишу ЭСД с QR кодом на машину с лесом, чтобы рейс прошёл проверку на посту и на весах.&lt;br&gt;&lt;br&gt;Присылаете породу, объём, номер машины и пункт назначения. Проверяю, стоит ли лес за вами в ФГИС ЛК, и оформляю ЭСД, внутри него QR код. Если леса в системе нет, сначала ставлю его на баланс по договору купли-продажи.&lt;br&gt;&lt;br&gt;Что нужно от вас:&lt;br&gt;- дата выезда;&lt;br&gt;- откуда грузите и куда везёте;&lt;br&gt;- ИНН вашего ИП или ООО и данные покупателя;&lt;br&gt;- госномер машины и прицепа;&lt;br&gt;- порода и сортимент, сколько кубов.&lt;br&gt;&lt;br&gt;Ни подписи, ни кабинета от вас не требуется. ИП и ООО, оплата безналом, когда документ готов.&lt;br&gt;&lt;br&gt;ЭСД на перевозку леса, QR код, ФГИС ЛК, кругляк, пиломатериал, Тульская область, Плавск.&lt;br&gt;&lt;br&gt;Отправьте данные машины и груза, документ пришлю в мессенджер.</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Тульская обл., Плавск, ул. Матросова, 55</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>2026-12-04T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>2026-11-04T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>2026-12-04T05:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>5227911477</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a231_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a231_ig.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a231_esd.jpg</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>2500</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Лес без документов, оформим учёт</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Наведу порядок с лесом без бумаг, чтобы его спокойно приняли покупатель и бухгалтерия.&lt;br&gt;&lt;br&gt;Сообщаете, где рубили, какая порода и сколько кубов. Я проверяю ФГИС ЛК, оформляю объём по договору купли-продажи и ставлю его вам на баланс. Дальше на каждую машину делаю ЭСД с QR кодом, это минут 15 на рейс.&lt;br&gt;&lt;br&gt;Для начала пришлите:&lt;br&gt;- как лес у вас появился;&lt;br&gt;- какая порода и сколько примерно кубов;&lt;br&gt;- фото штабеля, если есть;&lt;br&gt;- адрес или координаты, где он лежит;&lt;br&gt;- ИНН организации или ИП.&lt;br&gt;&lt;br&gt;Ни подписи, ни кабинета от вас не требуется. ИП и ООО, оплата безналом, когда документ готов.&lt;br&gt;&lt;br&gt;Лес без документов, учёт древесины в ФГИС ЛК, ЭСД, QR код, договор купли-продажи, Орловская область, Новосиль.&lt;br&gt;&lt;br&gt;Пришлите примерный объём и где лежит лес, подскажу сроки.</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Орловская обл., Новосиль, ул. Чернышевского, 56</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>2026-12-04T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>2026-11-04T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>2026-12-04T06:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -12209,7 +14159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM207"/>
+  <dimension ref="A1:AM236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -41830,6 +43780,4411 @@
       <c r="AL207" t="inlineStr">
         <is>
           <t>4403231200</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2261167909</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Хвоя кругляк, QR код на отгрузку</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Оформлю перевозку с хвойным кругляком: документ с QR кодом на каждую машину, без простоя.&lt;br&gt;&lt;br&gt;Присылаете кубатуру и пункт назначения. Проверяю, стоит ли лес за вами в ФГИС ЛК. Если не стоит, сначала оформляем его через договор купли-продажи, и объём встаёт вам на баланс. Дальше выписываю ЭСД, это электронная накладная на машину с QR кодом. Один рейс оформляю минут за 15.&lt;br&gt;&lt;br&gt;Для документа пришлите:&lt;br&gt;- госномер машины, если есть прицеп, то и его;&lt;br&gt;- что везёте и сколько кубов;&lt;br&gt;- когда выезд;&lt;br&gt;- ИНН продавца и покупателя;&lt;br&gt;- место погрузки и куда едет машина.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС ЛК и подпись заводить не нужно. Работаю с ИП и ООО, безнал, платите за готовый документ.&lt;br&gt;&lt;br&gt;Хвоя кругляк, сосна, ель, пиловочник, баланс, QR код на рейс, ЭСД, ФГИС ЛК, Липецкая область, Хлевное.&lt;br&gt;&lt;br&gt;Скиньте в чат, сколько машин в неделю и куда, посчитаю оформление на весь поток.</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a203_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a203_ig.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a203_esd.jpg</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Липецкая обл., Хлевное, ул. Затонная, 15</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P208" t="n">
+        <v>290</v>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>2026-11-26T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>2026-10-27T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>2026-11-26T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL208" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>7949000555</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Ель пиловочник кругляк(QR на рейс)</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Сделаю QR код на машину с еловым пиловочником минут за 15, водитель покажет его с телефона.&lt;br&gt;&lt;br&gt;Вы сообщаете породу, объём и куда идёт машина. Я проверяю ваш остаток в ФГИС ЛК, а если леса там нет, оформляю его договором купли-продажи и ставлю на баланс. Затем формирую ЭСД на рейс, внутри него QR код. Обычно это 15 минут на машину.&lt;br&gt;&lt;br&gt;Чтобы оформить рейс, нужно:&lt;br&gt;- ИНН вашего ИП или ООО;&lt;br&gt;- порода и объём в кубах;&lt;br&gt;- кто покупатель и когда выезд;&lt;br&gt;- номер машины и прицепа;&lt;br&gt;- пункт погрузки и пункт выгрузки.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС ЛК и подпись заводить не нужно. Работаю с ИП и ООО, безнал, платите за готовый документ.&lt;br&gt;&lt;br&gt;Ель пиловочник, кругляк, хвоя, QR код на рейс, ЭСД, ФГИС ЛК, Тамбовская область, Мордово.&lt;br&gt;&lt;br&gt;Напишите объём и пункт выгрузки, оформлю QR код к выходу машины.</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a204_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a204_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a204_ig.jpg</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Тамбовская обл., Мордово, ул. Кутузова, 15</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P209" t="n">
+        <v>3400</v>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>2026-11-26T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>2026-10-27T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>2026-11-26T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL209" t="inlineStr">
+        <is>
+          <t>4403231200</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>5872457798</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Сосна кругляк (QR код на перевозку)</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Оформлю QR код на рейс с сосновым кругляком, чтобы весовая принял машину без вопросов.&lt;br&gt;&lt;br&gt;Пишете, сколько кубов и куда. Смотрю, есть ли этот лес за вами в системе ФГИС ЛК. Если нет, сначала оформляю его по договору купли-продажи на ваш баланс. После этого делаю электронный документ на машину, ЭСД, с QR кодом. Рейс занимает около 15 минут.&lt;br&gt;&lt;br&gt;Что нужно от вас:&lt;br&gt;- ИНН вашего ИП или ООО и данные покупателя;&lt;br&gt;- дата выезда;&lt;br&gt;- госномер машины и прицепа;&lt;br&gt;- порода и сортимент, сколько кубов;&lt;br&gt;- откуда грузите и куда везёте.&lt;br&gt;&lt;br&gt;Ни подписи, ни кабинета от вас не требуется. ИП и ООО, оплата безналом, когда документ готов.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, хвоя, QR код на рейс, ЭСД, ФГИС ЛК, Воронежская область, Калач.&lt;br&gt;&lt;br&gt;Сообщите в чат кубы и куда везёте, сделаю документ к погрузке.</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a205_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a205_ig.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a205_esd.jpg</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Воронежская обл., Калач, ул. Жукова, 11</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P210" t="n">
+        <v>390</v>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>2026-11-26T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>2026-10-27T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>2026-11-26T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL210" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>5567302159</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Хвоя кругляк оптом(QR на вывозку)</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Закрою документы на вывоз с хвойным кругляком, чтобы рейс прошёл пост и весовую спокойно.&lt;br&gt;&lt;br&gt;Вы пишете, сколько кубов и куда везёте. Я смотрю, стоит ли этот объём за вами в ФГИС ЛК. Если нет, оформляю его по договору купли-продажи и ставлю вам на баланс. Потом делаю ЭСД, электронный документ на машину, в нём и есть QR код. На один рейс уходит около 15 минут.&lt;br&gt;&lt;br&gt;Для документа пришлите:&lt;br&gt;- госномер машины, если есть прицеп, то и его;&lt;br&gt;- ИНН продавца и покупателя;&lt;br&gt;- место погрузки и куда едет машина;&lt;br&gt;- что везёте и сколько кубов;&lt;br&gt;- когда выезд.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС ЛК и подпись заводить не нужно. Работаю с ИП и ООО, безнал, платите за готовый документ.&lt;br&gt;&lt;br&gt;Хвоя кругляк, сосна, ель, пиловочник, баланс, QR код на рейс, ЭСД, ФГИС ЛК, Оренбургская область, Абдулино.&lt;br&gt;&lt;br&gt;Опишите в чат, сколько леса и что нужно, скажу, как оформить и сколько займёт.</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a207_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a207_ig.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a207_esd.jpg</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Оренбургская обл., Абдулино, ул. Новая, 50</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P211" t="n">
+        <v>230</v>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>2026-11-27T03:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>2026-10-28T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>2026-11-27T03:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL211" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2297424872</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Берёза кругляк, QR код на рейс</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Подготовлю ЭСД с QR кодом на перевозку, чтобы машина с берёзой ушла без задержек.&lt;br&gt;&lt;br&gt;Присылаете кубатуру и пункт назначения. Проверяю, стоит ли лес за вами в ФГИС ЛК. Если не стоит, сначала оформляем его через договор купли-продажи, и объём встаёт вам на баланс. Дальше выписываю ЭСД, это электронная накладная на машину с QR кодом. Один рейс оформляю минут за 15.&lt;br&gt;&lt;br&gt;Чтобы оформить рейс, нужно:&lt;br&gt;- порода и объём в кубах;&lt;br&gt;- номер машины и прицепа;&lt;br&gt;- кто покупатель и когда выезд;&lt;br&gt;- ИНН вашего ИП или ООО;&lt;br&gt;- пункт погрузки и пункт выгрузки.&lt;br&gt;&lt;br&gt;Ни подписи, ни кабинета от вас не требуется. ИП и ООО, оплата безналом, когда документ готов.&lt;br&gt;&lt;br&gt;Берёза кругляк, дрова, баланс, фанкряж, QR код на рейс, ЭСД, ФГИС ЛК, Саратовская область, Пугачёв.&lt;br&gt;&lt;br&gt;Отправьте данные машины и груза, документ пришлю в мессенджер.</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a208_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a208_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a208_ig.jpg</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Саратовская обл., Пугачёв, ул. Набережная, 18</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P212" t="n">
+        <v>3400</v>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>2026-11-27T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>2026-10-28T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>2026-11-27T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL212" t="inlineStr">
+        <is>
+          <t>4403950000</t>
+        </is>
+      </c>
+      <c r="AM212" t="inlineStr">
+        <is>
+          <t>Не требуется</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>6429525190</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Ель пиловочник, документы фгис лк</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Закрою документы на вывоз с еловым пиловочником, чтобы рейс прошёл пост и весовую спокойно.&lt;br&gt;&lt;br&gt;Пишете, сколько кубов и куда. Смотрю, есть ли этот лес за вами в системе ФГИС ЛК. Если нет, сначала оформляю его по договору купли-продажи на ваш баланс. После этого делаю электронный документ на машину, ЭСД, с QR кодом. Рейс занимает около 15 минут.&lt;br&gt;&lt;br&gt;Что от вас потребуется:&lt;br&gt;- кому везёте: название и ИНН покупателя;&lt;br&gt;- ИНН вашей организации или ИП;&lt;br&gt;- адрес погрузки и адрес приёмки;&lt;br&gt;- номер лесовоза и прицепа;&lt;br&gt;- порода, кубатура, сортимент.&lt;br&gt;&lt;br&gt;Электронная подпись и кабинет в системе вам не нужны. Работаю с ИП и ООО, оплата по безналу за готовый документ.&lt;br&gt;&lt;br&gt;Ель пиловочник, кругляк, хвоя, QR код на рейс, ЭСД, ФГИС ЛК, Волгоградская область, Михайловка.&lt;br&gt;&lt;br&gt;Пришлите кубатуру и адрес приёмки, документ будет готов до выезда.</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a210_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a210_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a210_ig.jpg</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Волгоградская обл., Михайловка, ул. Маяковского, 6</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P213" t="n">
+        <v>2900</v>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>2026-11-27T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>2026-10-28T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>2026-11-27T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL213" t="inlineStr">
+        <is>
+          <t>4403231200</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>9464209589</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Осина баланс дрова, QR на вывоз</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Беру на себя документы на вывоз: QR код на каждую машину с осиной на баланс.&lt;br&gt;&lt;br&gt;От вас объём и пункт приёмки. Я сверяю, числится ли лес за вами в ФГИС ЛК. Если не числится, оформляю через договор купли-продажи и ставлю на баланс. Потом выписываю ЭСД, электронный документ на рейс с QR кодом. На одну машину около 15 минут.&lt;br&gt;&lt;br&gt;Для документа пришлите:&lt;br&gt;- когда выезд;&lt;br&gt;- ИНН продавца и покупателя;&lt;br&gt;- госномер машины, если есть прицеп, то и его;&lt;br&gt;- место погрузки и куда едет машина;&lt;br&gt;- что везёте и сколько кубов.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС ЛК и подпись заводить не нужно. Работаю с ИП и ООО, безнал, платите за готовый документ.&lt;br&gt;&lt;br&gt;Осина баланс, дрова, кругляк, QR код на рейс, ЭСД, ФГИС ЛК, Тульская область, Суворов.&lt;br&gt;&lt;br&gt;Скиньте в чат, сколько машин в неделю и куда, посчитаю оформление на весь поток.</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a211_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a211_ig.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a211_esd.jpg</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Тульская обл., Суворов, ул. Колхозная, 5</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P214" t="n">
+        <v>290</v>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>Осина</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>2026-11-28T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ214" t="inlineStr">
+        <is>
+          <t>2026-10-29T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>2026-11-28T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL214" t="inlineStr">
+        <is>
+          <t>4403970002</t>
+        </is>
+      </c>
+      <c r="AM214" t="inlineStr">
+        <is>
+          <t>Не требуется</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>9126313657</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Кругляк сосна пиловочник(документы фгис)</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Закрою документы на вывоз с сосновым кругляком, чтобы рейс прошёл пост и весовую спокойно.&lt;br&gt;&lt;br&gt;Присылаете кубатуру и пункт назначения. Проверяю, стоит ли лес за вами в ФГИС ЛК. Если не стоит, сначала оформляем его через договор купли-продажи, и объём встаёт вам на баланс. Дальше выписываю ЭСД, это электронная накладная на машину с QR кодом. Один рейс оформляю минут за 15.&lt;br&gt;&lt;br&gt;Что нужно от вас:&lt;br&gt;- дата выезда;&lt;br&gt;- откуда грузите и куда везёте;&lt;br&gt;- порода и сортимент, сколько кубов;&lt;br&gt;- ИНН вашего ИП или ООО и данные покупателя;&lt;br&gt;- госномер машины и прицепа.&lt;br&gt;&lt;br&gt;Ни подписи, ни кабинета от вас не требуется. ИП и ООО, оплата безналом, когда документ готов.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, хвоя, QR код на рейс, ЭСД, ФГИС ЛК, Рязанская область, Скопин.&lt;br&gt;&lt;br&gt;Сообщите в чат кубы и куда везёте, сделаю документ к погрузке.</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a213_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a213_ig.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a213_esd.jpg</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Рязанская обл., Скопин, ул. Щорса, 55</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P215" t="n">
+        <v>230</v>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>2026-11-28T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>2026-10-29T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>2026-11-28T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL215" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2869846899</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Берёза дрова баланс(эсд на рейс)</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Оформлю QR код на рейс с берёзой, чтобы приёмка принял машину без вопросов.&lt;br&gt;&lt;br&gt;Вы сообщаете породу, объём и куда идёт машина. Я проверяю ваш остаток в ФГИС ЛК, а если леса там нет, оформляю его договором купли-продажи и ставлю на баланс. Затем формирую ЭСД на рейс, внутри него QR код. Обычно это 15 минут на машину.&lt;br&gt;&lt;br&gt;Что от вас потребуется:&lt;br&gt;- ИНН вашей организации или ИП;&lt;br&gt;- номер лесовоза и прицепа;&lt;br&gt;- порода, кубатура, сортимент;&lt;br&gt;- адрес погрузки и адрес приёмки;&lt;br&gt;- кому везёте: название и ИНН покупателя.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС ЛК и подпись заводить не нужно. Работаю с ИП и ООО, безнал, платите за готовый документ.&lt;br&gt;&lt;br&gt;Берёза кругляк, дрова, баланс, фанкряж, QR код на рейс, ЭСД, ФГИС ЛК, Краснодарский край, Хадыженск.&lt;br&gt;&lt;br&gt;Пишите в чат прямо с погрузки, QR будет к выходу машины.</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a214_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a214_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a214_ig.jpg</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Краснодарский край, Хадыженск, ул. Строителей, 46</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P216" t="n">
+        <v>4300</v>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>2026-11-28T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF216" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH216" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI216" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ216" t="inlineStr">
+        <is>
+          <t>2026-10-29T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK216" t="inlineStr">
+        <is>
+          <t>2026-11-28T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL216" t="inlineStr">
+        <is>
+          <t>4403950000</t>
+        </is>
+      </c>
+      <c r="AM216" t="inlineStr">
+        <is>
+          <t>Не требуется</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>4907944612</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Сосна кругляк, QR код на вывоз</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Делаю ЭСД с QR кодом на машины с сосновым кругляком, по одной или потоком.&lt;br&gt;&lt;br&gt;От вас объём и пункт приёмки. Я сверяю, числится ли лес за вами в ФГИС ЛК. Если не числится, оформляю через договор купли-продажи и ставлю на баланс. Потом выписываю ЭСД, электронный документ на рейс с QR кодом. На одну машину около 15 минут.&lt;br&gt;&lt;br&gt;Чтобы оформить рейс, нужно:&lt;br&gt;- порода и объём в кубах;&lt;br&gt;- номер машины и прицепа;&lt;br&gt;- пункт погрузки и пункт выгрузки;&lt;br&gt;- ИНН вашего ИП или ООО;&lt;br&gt;- кто покупатель и когда выезд.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС ЛК и подпись заводить не нужно. Работаю с ИП и ООО, безнал, платите за готовый документ.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, хвоя, QR код на рейс, ЭСД, ФГИС ЛК, Пензенская область, Сердобск.&lt;br&gt;&lt;br&gt;Отправьте данные машины и груза, документ пришлю в мессенджер.</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a219_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a219_ig.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a219_esd.jpg</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Пензенская обл., Сердобск, ул. Суворова, 48</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P217" t="n">
+        <v>3400</v>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>2026-11-29T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>2026-10-30T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>2026-11-29T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL217" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>5285453944</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Доска обрезная, эсд на рейс</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Оформлю QR код на рейс с доской и брусом, чтобы пост на трассе принял машину без вопросов.&lt;br&gt;&lt;br&gt;Вы пишете, сколько кубов и куда везёте. Я смотрю, стоит ли этот объём за вами в ФГИС ЛК. Если нет, оформляю его по договору купли-продажи и ставлю вам на баланс. Потом делаю ЭСД, электронный документ на машину, в нём и есть QR код. На один рейс уходит около 15 минут.&lt;br&gt;&lt;br&gt;Что нужно от вас:&lt;br&gt;- откуда грузите и куда везёте;&lt;br&gt;- порода и сортимент, сколько кубов;&lt;br&gt;- дата выезда;&lt;br&gt;- госномер машины и прицепа;&lt;br&gt;- ИНН вашего ИП или ООО и данные покупателя.&lt;br&gt;&lt;br&gt;Ни подписи, ни кабинета от вас не требуется. ИП и ООО, оплата безналом, когда документ готов.&lt;br&gt;&lt;br&gt;Доска обрезная, брус, пиломатериал хвоя, QR код на рейс, ЭСД, ФГИС ЛК, Белгородская область, Ровеньки.&lt;br&gt;&lt;br&gt;Напишите в чат объём и куда идёт машина, подготовлю QR код к отгрузке.</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a223_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a223_ig.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a223_esd.jpg</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Белгородская обл., Ровеньки, ул. Элеваторная, 5</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P218" t="n">
+        <v>290</v>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>2026-11-29T03:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ218" t="inlineStr">
+        <is>
+          <t>2026-10-30T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t>2026-11-29T03:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL218" t="inlineStr">
+        <is>
+          <t>4407119406</t>
+        </is>
+      </c>
+      <c r="AM218" t="inlineStr">
+        <is>
+          <t>16.10.10.111</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>4995986884</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Осина баланс дрова, QR на вывоз</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Сделаю документ с QR кодом на машину с осиной на баланс, чтобы плитный комбинат не развернул рейс.&lt;br&gt;&lt;br&gt;Присылаете кубатуру и пункт назначения. Проверяю, стоит ли лес за вами в ФГИС ЛК. Если не стоит, сначала оформляем его через договор купли-продажи, и объём встаёт вам на баланс. Дальше выписываю ЭСД, это электронная накладная на машину с QR кодом. Один рейс оформляю минут за 15.&lt;br&gt;&lt;br&gt;Что от вас потребуется:&lt;br&gt;- кому везёте: название и ИНН покупателя;&lt;br&gt;- адрес погрузки и адрес приёмки;&lt;br&gt;- порода, кубатура, сортимент;&lt;br&gt;- ИНН вашей организации или ИП;&lt;br&gt;- номер лесовоза и прицепа.&lt;br&gt;&lt;br&gt;Подпись и личный кабинет не понадобятся. Работаю с ИП и ООО по безналу, оплата после готового документа.&lt;br&gt;&lt;br&gt;Осина баланс, дрова, кругляк, QR код на рейс, ЭСД, ФГИС ЛК, Курская область, Тим.&lt;br&gt;&lt;br&gt;Пришлите кубатуру и адрес приёмки, документ будет готов до выезда.</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a229_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a229_ig.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a229_esd.jpg</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Курская обл., Тим, ул. Толстого, 50</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P219" t="n">
+        <v>4300</v>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>Осина</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>2026-11-29T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ219" t="inlineStr">
+        <is>
+          <t>2026-10-30T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t>2026-11-29T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL219" t="inlineStr">
+        <is>
+          <t>4403970002</t>
+        </is>
+      </c>
+      <c r="AM219" t="inlineStr">
+        <is>
+          <t>Не требуется</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>7882028608</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Кругляк ель (документы фгис лк)</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Подготовлю ЭСД с QR кодом на перевозку, чтобы машина с еловым пиловочником ушла без задержек.&lt;br&gt;&lt;br&gt;Вы сообщаете породу, объём и куда идёт машина. Я проверяю ваш остаток в ФГИС ЛК, а если леса там нет, оформляю его договором купли-продажи и ставлю на баланс. Затем формирую ЭСД на рейс, внутри него QR код. Обычно это 15 минут на машину.&lt;br&gt;&lt;br&gt;Для документа пришлите:&lt;br&gt;- место погрузки и куда едет машина;&lt;br&gt;- когда выезд;&lt;br&gt;- что везёте и сколько кубов;&lt;br&gt;- ИНН продавца и покупателя;&lt;br&gt;- госномер машины, если есть прицеп, то и его.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС ЛК и подпись заводить не нужно. Работаю с ИП и ООО, безнал, платите за готовый документ.&lt;br&gt;&lt;br&gt;Ель пиловочник, кругляк, хвоя, QR код на рейс, ЭСД, ФГИС ЛК, Липецкая область, Становое.&lt;br&gt;&lt;br&gt;Скиньте в чат, сколько машин в неделю и куда, посчитаю оформление на весь поток.</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a232_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a232_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a232_ig.jpg</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Липецкая обл., Становое, ул. Калинина, 48</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P220" t="n">
+        <v>190</v>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>2026-11-29T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF220" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH220" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI220" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ220" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK220" t="inlineStr">
+        <is>
+          <t>2026-11-29T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL220" t="inlineStr">
+        <is>
+          <t>4403231200</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>9551123854</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Пиломатериал хвоя, документы фгис</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Выпишу ЭСД на рейс с доской и брусом, чтобы пост на трассе принял груз с первого раза.&lt;br&gt;&lt;br&gt;Пишете, сколько кубов и куда. Смотрю, есть ли этот лес за вами в системе ФГИС ЛК. Если нет, сначала оформляю его по договору купли-продажи на ваш баланс. После этого делаю электронный документ на машину, ЭСД, с QR кодом. Рейс занимает около 15 минут.&lt;br&gt;&lt;br&gt;Чтобы оформить рейс, нужно:&lt;br&gt;- номер машины и прицепа;&lt;br&gt;- порода и объём в кубах;&lt;br&gt;- пункт погрузки и пункт выгрузки;&lt;br&gt;- ИНН вашего ИП или ООО;&lt;br&gt;- кто покупатель и когда выезд.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС ЛК и подпись заводить не нужно. Работаю с ИП и ООО, безнал, платите за готовый документ.&lt;br&gt;&lt;br&gt;Доска обрезная, брус, пиломатериал хвоя, QR код на рейс, ЭСД, ФГИС ЛК, Тамбовская область, Знаменка.&lt;br&gt;&lt;br&gt;Напишите объём и пункт выгрузки, оформлю QR код к выходу машины.</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a237_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a237_ig.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a237_esd.jpg</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Тамбовская обл., Знаменка, ул. Добролюбова, 47</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P221" t="n">
+        <v>4300</v>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>2026-11-29T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ221" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>2026-11-29T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL221" t="inlineStr">
+        <is>
+          <t>4407119406</t>
+        </is>
+      </c>
+      <c r="AM221" t="inlineStr">
+        <is>
+          <t>16.10.10.111</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>5428138045</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Лиственница кругляк, эсд на отгрузку</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Беру на себя документы на вывоз: QR код на каждую машину с лиственницей.&lt;br&gt;&lt;br&gt;Вы пишете, сколько кубов и куда везёте. Я смотрю, стоит ли этот объём за вами в ФГИС ЛК. Если нет, оформляю его по договору купли-продажи и ставлю вам на баланс. Потом делаю ЭСД, электронный документ на машину, в нём и есть QR код. На один рейс уходит около 15 минут.&lt;br&gt;&lt;br&gt;Что от вас потребуется:&lt;br&gt;- номер лесовоза и прицепа;&lt;br&gt;- кому везёте: название и ИНН покупателя;&lt;br&gt;- ИНН вашей организации или ИП;&lt;br&gt;- адрес погрузки и адрес приёмки;&lt;br&gt;- порода, кубатура, сортимент.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС ЛК и подпись заводить не нужно. Работаю с ИП и ООО, безнал, платите за готовый документ.&lt;br&gt;&lt;br&gt;Лиственница кругляк, хвоя, пиловочник, QR код на рейс, ЭСД, ФГИС ЛК, Калужская область, Кондрово.&lt;br&gt;&lt;br&gt;Пишите в чат прямо с погрузки, QR будет к выходу машины.</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a238_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a238_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a238_ig.jpg</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Калужская обл., Кондрово, ул. Шоссейная, 57</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P222" t="n">
+        <v>4300</v>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>Лиственница</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>2026-11-30T03:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ222" t="inlineStr">
+        <is>
+          <t>2026-10-31T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK222" t="inlineStr">
+        <is>
+          <t>2026-11-30T03:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL222" t="inlineStr">
+        <is>
+          <t>4403251000</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>9568353200</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Доска обрезная, эсд на рейс</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Оформлю перевозку с доской и брусом: документ с QR кодом на каждую машину, без простоя.&lt;br&gt;&lt;br&gt;Присылаете кубатуру и пункт назначения. Проверяю, стоит ли лес за вами в ФГИС ЛК. Если не стоит, сначала оформляем его через договор купли-продажи, и объём встаёт вам на баланс. Дальше выписываю ЭСД, это электронная накладная на машину с QR кодом. Один рейс оформляю минут за 15.&lt;br&gt;&lt;br&gt;Для документа пришлите:&lt;br&gt;- госномер машины, если есть прицеп, то и его;&lt;br&gt;- когда выезд;&lt;br&gt;- место погрузки и куда едет машина;&lt;br&gt;- ИНН продавца и покупателя;&lt;br&gt;- что везёте и сколько кубов.&lt;br&gt;&lt;br&gt;Ни подписи, ни кабинета от вас не требуется. ИП и ООО, оплата безналом, когда документ готов.&lt;br&gt;&lt;br&gt;Доска обрезная, брус, пиломатериал хвоя, QR код на рейс, ЭСД, ФГИС ЛК, Оренбургская область, Медногорск.&lt;br&gt;&lt;br&gt;Опишите в чат, сколько леса и что нужно, скажу, как оформить и сколько займёт.</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a216_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a216_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a216_ig.jpg</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Оренбургская обл., Медногорск, ул. Тимирязева, 44</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P223" t="n">
+        <v>290</v>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>2026-11-30T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI223" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ223" t="inlineStr">
+        <is>
+          <t>2026-10-31T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK223" t="inlineStr">
+        <is>
+          <t>2026-11-30T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL223" t="inlineStr">
+        <is>
+          <t>4407119406</t>
+        </is>
+      </c>
+      <c r="AM223" t="inlineStr">
+        <is>
+          <t>16.10.10.111</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2401104053</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Хвоя кругляк, QR код на отгрузку</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Сделаю QR код на машину с хвойным кругляком минут за 15, водитель покажет его с телефона.&lt;br&gt;&lt;br&gt;Вы сообщаете породу, объём и куда идёт машина. Я проверяю ваш остаток в ФГИС ЛК, а если леса там нет, оформляю его договором купли-продажи и ставлю на баланс. Затем формирую ЭСД на рейс, внутри него QR код. Обычно это 15 минут на машину.&lt;br&gt;&lt;br&gt;Чтобы оформить рейс, нужно:&lt;br&gt;- номер машины и прицепа;&lt;br&gt;- ИНН вашего ИП или ООО;&lt;br&gt;- кто покупатель и когда выезд;&lt;br&gt;- пункт погрузки и пункт выгрузки;&lt;br&gt;- порода и объём в кубах.&lt;br&gt;&lt;br&gt;Электронная подпись и кабинет в системе вам не нужны. Работаю с ИП и ООО, оплата по безналу за готовый документ.&lt;br&gt;&lt;br&gt;Хвоя кругляк, сосна, ель, пиловочник, баланс, QR код на рейс, ЭСД, ФГИС ЛК, Саратовская область, Вольск.&lt;br&gt;&lt;br&gt;Отправьте данные машины и груза, документ пришлю в мессенджер.</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a242_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a242_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a242_ig.jpg</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Саратовская обл., Вольск, ул. Садовая, 54</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P224" t="n">
+        <v>4300</v>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>2026-11-30T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ224" t="inlineStr">
+        <is>
+          <t>2026-10-31T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK224" t="inlineStr">
+        <is>
+          <t>2026-11-30T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL224" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>4231338254</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Ель пиловочник кругляк(QR на рейс)</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Сделаю документ с QR кодом на машину с еловым пиловочником, чтобы пилорама не развернул рейс.&lt;br&gt;&lt;br&gt;Пишете, сколько кубов и куда. Смотрю, есть ли этот лес за вами в системе ФГИС ЛК. Если нет, сначала оформляю его по договору купли-продажи на ваш баланс. После этого делаю электронный документ на машину, ЭСД, с QR кодом. Рейс занимает около 15 минут.&lt;br&gt;&lt;br&gt;Что нужно от вас:&lt;br&gt;- ИНН вашего ИП или ООО и данные покупателя;&lt;br&gt;- госномер машины и прицепа;&lt;br&gt;- порода и сортимент, сколько кубов;&lt;br&gt;- дата выезда;&lt;br&gt;- откуда грузите и куда везёте.&lt;br&gt;&lt;br&gt;Подпись и личный кабинет не понадобятся. Работаю с ИП и ООО по безналу, оплата после готового документа.&lt;br&gt;&lt;br&gt;Ель пиловочник, кругляк, хвоя, QR код на рейс, ЭСД, ФГИС ЛК, Самарская область, Чапаевск.&lt;br&gt;&lt;br&gt;Напишите в чат объём и куда идёт машина, подготовлю QR код к отгрузке.</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a218_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a218_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a218_ig.jpg</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Самарская обл., Чапаевск, ул. Почтовая, 24</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P225" t="n">
+        <v>230</v>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>2026-11-30T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ225" t="inlineStr">
+        <is>
+          <t>2026-10-31T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK225" t="inlineStr">
+        <is>
+          <t>2026-11-30T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL225" t="inlineStr">
+        <is>
+          <t>4403231200</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>1836932746</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Сосна кругляк (QR код на перевозку)</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Документы на рейс с сосновым кругляком: ЭСД и QR код, чтобы покупатель не задавал вопросов.&lt;br&gt;&lt;br&gt;От вас объём и пункт приёмки. Я сверяю, числится ли лес за вами в ФГИС ЛК. Если не числится, оформляю через договор купли-продажи и ставлю на баланс. Потом выписываю ЭСД, электронный документ на рейс с QR кодом. На одну машину около 15 минут.&lt;br&gt;&lt;br&gt;Что от вас потребуется:&lt;br&gt;- ИНН вашей организации или ИП;&lt;br&gt;- кому везёте: название и ИНН покупателя;&lt;br&gt;- порода, кубатура, сортимент;&lt;br&gt;- номер лесовоза и прицепа;&lt;br&gt;- адрес погрузки и адрес приёмки.&lt;br&gt;&lt;br&gt;Подпись и личный кабинет не понадобятся. Работаю с ИП и ООО по безналу, оплата после готового документа.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, хвоя, QR код на рейс, ЭСД, ФГИС ЛК, Волгоградская область, Камышин.&lt;br&gt;&lt;br&gt;Пришлите кубатуру и адрес приёмки, документ будет готов до выезда.</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a220_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a220_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a220_ig.jpg</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Волгоградская обл., Камышин, ул. Белинского, 26</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P226" t="n">
+        <v>3400</v>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>2026-12-01T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI226" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ226" t="inlineStr">
+        <is>
+          <t>2026-11-01T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK226" t="inlineStr">
+        <is>
+          <t>2026-12-01T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL226" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>6612031972</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Хвоя кругляк оптом(QR на вывозку)</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Выпишу ЭСД на рейс с хвойным кругляком, чтобы покупатель принял груз с первого раза.&lt;br&gt;&lt;br&gt;Присылаете кубатуру и пункт назначения. Проверяю, стоит ли лес за вами в ФГИС ЛК. Если не стоит, сначала оформляем его через договор купли-продажи, и объём встаёт вам на баланс. Дальше выписываю ЭСД, это электронная накладная на машину с QR кодом. Один рейс оформляю минут за 15.&lt;br&gt;&lt;br&gt;Чтобы оформить рейс, нужно:&lt;br&gt;- номер машины и прицепа;&lt;br&gt;- ИНН вашего ИП или ООО;&lt;br&gt;- кто покупатель и когда выезд;&lt;br&gt;- порода и объём в кубах;&lt;br&gt;- пункт погрузки и пункт выгрузки.&lt;br&gt;&lt;br&gt;Подпись и личный кабинет не понадобятся. Работаю с ИП и ООО по безналу, оплата после готового документа.&lt;br&gt;&lt;br&gt;Хвоя кругляк, сосна, ель, пиловочник, баланс, QR код на рейс, ЭСД, ФГИС ЛК, Орловская область, Дмитровск.&lt;br&gt;&lt;br&gt;Напишите объём и пункт выгрузки, оформлю QR код к выходу машины.</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a236_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a236_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a236_ig.jpg</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Орловская обл., Дмитровск, ул. Нагорная, 33</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P227" t="n">
+        <v>4300</v>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>2026-12-01T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF227" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH227" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI227" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ227" t="inlineStr">
+        <is>
+          <t>2026-11-01T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK227" t="inlineStr">
+        <is>
+          <t>2026-12-01T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL227" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>5480317705</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Берёза кругляк, QR код на рейс</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Сделаю документ с QR кодом на машину с берёзой, чтобы приёмка не развернул рейс.&lt;br&gt;&lt;br&gt;Вы сообщаете породу, объём и куда идёт машина. Я проверяю ваш остаток в ФГИС ЛК, а если леса там нет, оформляю его договором купли-продажи и ставлю на баланс. Затем формирую ЭСД на рейс, внутри него QR код. Обычно это 15 минут на машину.&lt;br&gt;&lt;br&gt;Что нужно от вас:&lt;br&gt;- ИНН вашего ИП или ООО и данные покупателя;&lt;br&gt;- госномер машины и прицепа;&lt;br&gt;- откуда грузите и куда везёте;&lt;br&gt;- порода и сортимент, сколько кубов;&lt;br&gt;- дата выезда.&lt;br&gt;&lt;br&gt;Ни подписи, ни кабинета от вас не требуется. ИП и ООО, оплата безналом, когда документ готов.&lt;br&gt;&lt;br&gt;Берёза кругляк, дрова, баланс, фанкряж, QR код на рейс, ЭСД, ФГИС ЛК, Рязанская область, Ряжск.&lt;br&gt;&lt;br&gt;Сообщите в чат кубы и куда везёте, сделаю документ к погрузке.</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a241_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a241_ig.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a241_esd.jpg</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Рязанская обл., Ряжск, ул. Партизанская, 43</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P228" t="n">
+        <v>450</v>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>2026-12-01T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ228" t="inlineStr">
+        <is>
+          <t>2026-11-01T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK228" t="inlineStr">
+        <is>
+          <t>2026-12-01T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL228" t="inlineStr">
+        <is>
+          <t>4403950000</t>
+        </is>
+      </c>
+      <c r="AM228" t="inlineStr">
+        <is>
+          <t>Не требуется</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>6579556571</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Ель пиловочник, документы фгис лк</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Сделаю документ с QR кодом на машину с еловым пиловочником, чтобы приёмка не развернул рейс.&lt;br&gt;&lt;br&gt;Присылаете кубатуру и пункт назначения. Проверяю, стоит ли лес за вами в ФГИС ЛК. Если не стоит, сначала оформляем его через договор купли-продажи, и объём встаёт вам на баланс. Дальше выписываю ЭСД, это электронная накладная на машину с QR кодом. Один рейс оформляю минут за 15.&lt;br&gt;&lt;br&gt;Что нужно от вас:&lt;br&gt;- откуда грузите и куда везёте;&lt;br&gt;- ИНН вашего ИП или ООО и данные покупателя;&lt;br&gt;- порода и сортимент, сколько кубов;&lt;br&gt;- дата выезда;&lt;br&gt;- госномер машины и прицепа.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС ЛК и подпись заводить не нужно. Работаю с ИП и ООО, безнал, платите за готовый документ.&lt;br&gt;&lt;br&gt;Ель пиловочник, кругляк, хвоя, QR код на рейс, ЭСД, ФГИС ЛК, Белгородская область, Вейделевка.&lt;br&gt;&lt;br&gt;Напишите в чат объём и куда идёт машина, подготовлю QR код к отгрузке.</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a226_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a226_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a226_ig.jpg</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Белгородская обл., Вейделевка, ул. Лермонтова, 37</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P229" t="n">
+        <v>260</v>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>2026-12-02T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ229" t="inlineStr">
+        <is>
+          <t>2026-11-02T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK229" t="inlineStr">
+        <is>
+          <t>2026-12-02T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL229" t="inlineStr">
+        <is>
+          <t>4403231200</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2610189927</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Ель пиловочник кругляк(QR на рейс)</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Беру на себя документы на вывоз: QR код на каждую машину с еловым пиловочником.&lt;br&gt;&lt;br&gt;Пишете, сколько кубов и куда. Смотрю, есть ли этот лес за вами в системе ФГИС ЛК. Если нет, сначала оформляю его по договору купли-продажи на ваш баланс. После этого делаю электронный документ на машину, ЭСД, с QR кодом. Рейс занимает около 15 минут.&lt;br&gt;&lt;br&gt;Для документа пришлите:&lt;br&gt;- место погрузки и куда едет машина;&lt;br&gt;- ИНН продавца и покупателя;&lt;br&gt;- что везёте и сколько кубов;&lt;br&gt;- госномер машины, если есть прицеп, то и его;&lt;br&gt;- когда выезд.&lt;br&gt;&lt;br&gt;Подпись и личный кабинет не понадобятся. Работаю с ИП и ООО по безналу, оплата после готового документа.&lt;br&gt;&lt;br&gt;Ель пиловочник, кругляк, хвоя, QR код на рейс, ЭСД, ФГИС ЛК, Липецкая область, Измалково.&lt;br&gt;&lt;br&gt;Скиньте в чат, сколько машин в неделю и куда, посчитаю оформление на весь поток.</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a228_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a228_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a228_ig.jpg</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Липецкая обл., Измалково, ул. Пирогова, 17</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P230" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>2026-12-02T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF230" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ230" t="inlineStr">
+        <is>
+          <t>2026-11-02T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK230" t="inlineStr">
+        <is>
+          <t>2026-12-02T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL230" t="inlineStr">
+        <is>
+          <t>4403231200</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>1050437988</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Берёза кругляк, QR код на рейс</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Делаю ЭСД с QR кодом на машины с берёзой, по одной или потоком.&lt;br&gt;&lt;br&gt;От вас объём и пункт приёмки. Я сверяю, числится ли лес за вами в ФГИС ЛК. Если не числится, оформляю через договор купли-продажи и ставлю на баланс. Потом выписываю ЭСД, электронный документ на рейс с QR кодом. На одну машину около 15 минут.&lt;br&gt;&lt;br&gt;Чтобы оформить рейс, нужно:&lt;br&gt;- ИНН вашего ИП или ООО;&lt;br&gt;- номер машины и прицепа;&lt;br&gt;- кто покупатель и когда выезд;&lt;br&gt;- порода и объём в кубах;&lt;br&gt;- пункт погрузки и пункт выгрузки.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС ЛК и подпись заводить не нужно. Работаю с ИП и ООО, безнал, платите за готовый документ.&lt;br&gt;&lt;br&gt;Берёза кругляк, дрова, баланс, фанкряж, QR код на рейс, ЭСД, ФГИС ЛК, Тамбовская область, Сосновка.&lt;br&gt;&lt;br&gt;Напишите объём и пункт выгрузки, оформлю QR код к выходу машины.</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a225_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a225_ig.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a225_esd.jpg</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Тамбовская обл., Сосновка, ул. Свердлова, 33</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P231" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>2026-12-03T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF231" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ231" t="inlineStr">
+        <is>
+          <t>2026-11-03T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK231" t="inlineStr">
+        <is>
+          <t>2026-12-03T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL231" t="inlineStr">
+        <is>
+          <t>4403950000</t>
+        </is>
+      </c>
+      <c r="AM231" t="inlineStr">
+        <is>
+          <t>Не требуется</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>7756790483</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Осина баланс дрова, QR на вывоз</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Документы на рейс с осиной на баланс: ЭСД и QR код, чтобы плитный комбинат не задавал вопросов.&lt;br&gt;&lt;br&gt;Вы пишете, сколько кубов и куда везёте. Я смотрю, стоит ли этот объём за вами в ФГИС ЛК. Если нет, оформляю его по договору купли-продажи и ставлю вам на баланс. Потом делаю ЭСД, электронный документ на машину, в нём и есть QR код. На один рейс уходит около 15 минут.&lt;br&gt;&lt;br&gt;Что нужно от вас:&lt;br&gt;- откуда грузите и куда везёте;&lt;br&gt;- госномер машины и прицепа;&lt;br&gt;- дата выезда;&lt;br&gt;- ИНН вашего ИП или ООО и данные покупателя;&lt;br&gt;- порода и сортимент, сколько кубов.&lt;br&gt;&lt;br&gt;Ни подписи, ни кабинета от вас не требуется. ИП и ООО, оплата безналом, когда документ готов.&lt;br&gt;&lt;br&gt;Осина баланс, дрова, кругляк, QR код на рейс, ЭСД, ФГИС ЛК, Воронежская область, Эртиль.&lt;br&gt;&lt;br&gt;Сообщите в чат кубы и куда везёте, сделаю документ к погрузке.</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a234_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a234_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a234_ig.jpg</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Воронежская обл., Эртиль, ул. Луговая, 32</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P232" t="n">
+        <v>230</v>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>Осина</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>2026-12-03T03:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF232" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI232" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ232" t="inlineStr">
+        <is>
+          <t>2026-11-03T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK232" t="inlineStr">
+        <is>
+          <t>2026-12-03T03:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL232" t="inlineStr">
+        <is>
+          <t>4403970002</t>
+        </is>
+      </c>
+      <c r="AM232" t="inlineStr">
+        <is>
+          <t>Не требуется</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>1921730025</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Кругляк сосна пиловочник(документы фгис)</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Сделаю документ с QR кодом на машину с сосновым кругляком, чтобы покупатель не развернул рейс.&lt;br&gt;&lt;br&gt;Присылаете кубатуру и пункт назначения. Проверяю, стоит ли лес за вами в ФГИС ЛК. Если не стоит, сначала оформляем его через договор купли-продажи, и объём встаёт вам на баланс. Дальше выписываю ЭСД, это электронная накладная на машину с QR кодом. Один рейс оформляю минут за 15.&lt;br&gt;&lt;br&gt;Что от вас потребуется:&lt;br&gt;- ИНН вашей организации или ИП;&lt;br&gt;- номер лесовоза и прицепа;&lt;br&gt;- адрес погрузки и адрес приёмки;&lt;br&gt;- кому везёте: название и ИНН покупателя;&lt;br&gt;- порода, кубатура, сортимент.&lt;br&gt;&lt;br&gt;Подпись и личный кабинет не понадобятся. Работаю с ИП и ООО по безналу, оплата после готового документа.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, хвоя, QR код на рейс, ЭСД, ФГИС ЛК, Калужская область, Ферзиково.&lt;br&gt;&lt;br&gt;Пишите в чат прямо с погрузки, QR будет к выходу машины.</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a239_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a239_ig.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a239_esd.jpg</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Калужская обл., Ферзиково, ул. Железнодорожная, 53</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P233" t="n">
+        <v>3100</v>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>2026-12-03T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ233" t="inlineStr">
+        <is>
+          <t>2026-11-03T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK233" t="inlineStr">
+        <is>
+          <t>2026-12-03T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL233" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>3894258513</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Берёза дрова баланс(эсд на рейс)</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Беру на себя документы на вывоз: QR код на каждую машину с берёзой.&lt;br&gt;&lt;br&gt;Пишете, сколько кубов и куда. Смотрю, есть ли этот лес за вами в системе ФГИС ЛК. Если нет, сначала оформляю его по договору купли-продажи на ваш баланс. После этого делаю электронный документ на машину, ЭСД, с QR кодом. Рейс занимает около 15 минут.&lt;br&gt;&lt;br&gt;Чтобы оформить рейс, нужно:&lt;br&gt;- пункт погрузки и пункт выгрузки;&lt;br&gt;- кто покупатель и когда выезд;&lt;br&gt;- порода и объём в кубах;&lt;br&gt;- номер машины и прицепа;&lt;br&gt;- ИНН вашего ИП или ООО.&lt;br&gt;&lt;br&gt;Подпись и личный кабинет не понадобятся. Работаю с ИП и ООО по безналу, оплата после готового документа.&lt;br&gt;&lt;br&gt;Берёза кругляк, дрова, баланс, фанкряж, QR код на рейс, ЭСД, ФГИС ЛК, Саратовская область, Калининск.&lt;br&gt;&lt;br&gt;Отправьте данные машины и груза, документ пришлю в мессенджер.</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a230_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a230_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a230_ig.jpg</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Саратовская обл., Калининск, ул. Лесная, 46</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P234" t="n">
+        <v>2900</v>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>2026-12-03T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI234" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ234" t="inlineStr">
+        <is>
+          <t>2026-11-03T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK234" t="inlineStr">
+        <is>
+          <t>2026-12-03T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL234" t="inlineStr">
+        <is>
+          <t>4403950000</t>
+        </is>
+      </c>
+      <c r="AM234" t="inlineStr">
+        <is>
+          <t>Не требуется</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2295692267</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Хвоя кругляк, QR код на отгрузку</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Оформлю QR код на рейс с хвойным кругляком, чтобы пост на трассе принял машину без вопросов.&lt;br&gt;&lt;br&gt;От вас объём и пункт приёмки. Я сверяю, числится ли лес за вами в ФГИС ЛК. Если не числится, оформляю через договор купли-продажи и ставлю на баланс. Потом выписываю ЭСД, электронный документ на рейс с QR кодом. На одну машину около 15 минут.&lt;br&gt;&lt;br&gt;Что нужно от вас:&lt;br&gt;- госномер машины и прицепа;&lt;br&gt;- дата выезда;&lt;br&gt;- откуда грузите и куда везёте;&lt;br&gt;- ИНН вашего ИП или ООО и данные покупателя;&lt;br&gt;- порода и сортимент, сколько кубов.&lt;br&gt;&lt;br&gt;Свой кабинет в ФГИС ЛК и подпись заводить не нужно. Работаю с ИП и ООО, безнал, платите за готовый документ.&lt;br&gt;&lt;br&gt;Хвоя кругляк, сосна, ель, пиловочник, баланс, QR код на рейс, ЭСД, ФГИС ЛК, Самарская область, Похвистнево.&lt;br&gt;&lt;br&gt;Напишите в чат объём и куда идёт машина, подготовлю QR код к отгрузке.</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a233_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a233_ig.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a233_esd.jpg</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Самарская обл., Похвистнево, ул. Победы, 25</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P235" t="n">
+        <v>450</v>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>2026-12-04T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF235" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH235" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI235" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ235" t="inlineStr">
+        <is>
+          <t>2026-11-04T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK235" t="inlineStr">
+        <is>
+          <t>2026-12-04T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL235" t="inlineStr">
+        <is>
+          <t>4403211200</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>6759936544</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>79824510018</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Сосна кругляк, QR код на вывоз</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Беру на себя документы на вывоз: QR код на каждую машину с сосновым кругляком.&lt;br&gt;&lt;br&gt;Вы пишете, сколько кубов и куда везёте. Я смотрю, стоит ли этот объём за вами в ФГИС ЛК. Если нет, оформляю его по договору купли-продажи и ставлю вам на баланс. Потом делаю ЭСД, электронный документ на машину, в нём и есть QR код. На один рейс уходит около 15 минут.&lt;br&gt;&lt;br&gt;Что от вас потребуется:&lt;br&gt;- кому везёте: название и ИНН покупателя;&lt;br&gt;- номер лесовоза и прицепа;&lt;br&gt;- ИНН вашей организации или ИП;&lt;br&gt;- порода, кубатура, сортимент;&lt;br&gt;- адрес погрузки и адрес приёмки.&lt;br&gt;&lt;br&gt;Электронная подпись и кабинет в системе вам не нужны. Работаю с ИП и ООО, оплата по безналу за готовый документ.&lt;br&gt;&lt;br&gt;Сосна кругляк, пиловочник, хвоя, QR код на рейс, ЭСД, ФГИС ЛК, Волгоградская область, Фролово.&lt;br&gt;&lt;br&gt;Пришлите кубатуру и адрес приёмки, документ будет готов до выезда.</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a240_1.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a240_esd.jpg|https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/433120750/wave_20261027/a240_ig.jpg</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Волгоградская обл., Фролово, ул. Чехова, 42</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>Россыпью</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>Свой курьер</t>
+        </is>
+      </c>
+      <c r="P236" t="n">
+        <v>4300</v>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>2026-12-04T03:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AF236" t="inlineStr">
+        <is>
+          <t>belpool.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>ФГИС ЛК объемы</t>
+        </is>
+      </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>не опт</t>
+        </is>
+      </c>
+      <c r="AJ236" t="inlineStr">
+        <is>
+          <t>2026-11-04T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK236" t="inlineStr">
+        <is>
+          <t>2026-12-04T03:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AL236" t="inlineStr">
+        <is>
+          <t>4403211200</t>
         </is>
       </c>
     </row>

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -2336,7 +2336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:Q8"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4311,7 +4311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O34"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>2026-11-26T02:00:00+03:00</t>
+          <t>2026-11-27T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>2026-10-27T05:00:00+03:00</t>
+          <t>2026-10-28T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>2026-11-26T02:00:00+03:00</t>
+          <t>2026-11-27T02:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -11806,17 +11806,17 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>2026-11-26T03:30:00+03:00</t>
+          <t>2026-11-27T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>2026-10-27T06:30:00+03:00</t>
+          <t>2026-10-28T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>2026-11-26T03:30:00+03:00</t>
+          <t>2026-11-27T03:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -11936,17 +11936,17 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>2026-11-27T02:00:00+03:00</t>
+          <t>2026-11-28T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>2026-10-28T05:00:00+03:00</t>
+          <t>2026-10-29T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>2026-11-27T02:00:00+03:00</t>
+          <t>2026-11-28T02:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -12066,17 +12066,17 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>2026-11-27T06:30:00+03:00</t>
+          <t>2026-11-28T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>2026-10-28T09:30:00+03:00</t>
+          <t>2026-10-29T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>2026-11-27T06:30:00+03:00</t>
+          <t>2026-11-28T06:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -12196,17 +12196,17 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>2026-11-28T03:30:00+03:00</t>
+          <t>2026-11-29T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>2026-10-29T06:30:00+03:00</t>
+          <t>2026-10-30T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>2026-11-28T03:30:00+03:00</t>
+          <t>2026-11-29T03:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -12326,17 +12326,17 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>2026-11-28T08:00:00+03:00</t>
+          <t>2026-11-29T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>2026-10-29T11:00:00+03:00</t>
+          <t>2026-10-30T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>2026-11-28T08:00:00+03:00</t>
+          <t>2026-11-29T08:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -12456,17 +12456,17 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>2026-11-30T02:00:00+03:00</t>
+          <t>2026-12-01T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>2026-10-31T05:00:00+03:00</t>
+          <t>2026-11-01T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>2026-11-30T02:00:00+03:00</t>
+          <t>2026-12-01T02:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -12586,17 +12586,17 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>2026-12-01T03:30:00+03:00</t>
+          <t>2026-12-02T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>2026-11-01T06:30:00+03:00</t>
+          <t>2026-11-02T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>2026-12-01T03:30:00+03:00</t>
+          <t>2026-12-02T03:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -12716,17 +12716,17 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>2026-12-01T08:00:00+03:00</t>
+          <t>2026-12-02T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>2026-11-01T11:00:00+03:00</t>
+          <t>2026-11-02T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>2026-12-01T08:00:00+03:00</t>
+          <t>2026-12-02T08:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -12846,17 +12846,17 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>2026-12-02T02:00:00+03:00</t>
+          <t>2026-12-03T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>2026-11-02T05:00:00+03:00</t>
+          <t>2026-11-03T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>2026-12-02T02:00:00+03:00</t>
+          <t>2026-12-03T02:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -12976,17 +12976,17 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>2026-12-02T03:30:00+03:00</t>
+          <t>2026-12-03T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>2026-11-02T06:30:00+03:00</t>
+          <t>2026-11-03T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>2026-12-02T03:30:00+03:00</t>
+          <t>2026-12-03T03:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -13106,17 +13106,17 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>2026-12-02T06:30:00+03:00</t>
+          <t>2026-12-03T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>2026-11-02T09:30:00+03:00</t>
+          <t>2026-11-03T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>2026-12-02T06:30:00+03:00</t>
+          <t>2026-12-03T06:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -13236,17 +13236,17 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>2026-12-03T06:30:00+03:00</t>
+          <t>2026-12-04T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>2026-11-03T09:30:00+03:00</t>
+          <t>2026-11-04T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>2026-12-03T06:30:00+03:00</t>
+          <t>2026-12-04T06:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -13366,17 +13366,17 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>2026-12-04T05:00:00+03:00</t>
+          <t>2026-12-05T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>2026-11-04T08:00:00+03:00</t>
+          <t>2026-11-05T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>2026-12-04T05:00:00+03:00</t>
+          <t>2026-12-05T05:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -13496,17 +13496,17 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>2026-12-04T06:30:00+03:00</t>
+          <t>2026-12-05T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>2026-11-04T09:30:00+03:00</t>
+          <t>2026-11-05T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>2026-12-04T06:30:00+03:00</t>
+          <t>2026-12-05T06:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -13582,7 +13582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:X34"/>
+  <dimension ref="A1:X34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43899,7 +43899,7 @@
       </c>
       <c r="AE208" t="inlineStr">
         <is>
-          <t>2026-11-26T05:00:00+03:00</t>
+          <t>2026-11-27T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AF208" t="inlineStr">
@@ -43919,12 +43919,12 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>2026-10-27T08:00:00+03:00</t>
+          <t>2026-10-28T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
         <is>
-          <t>2026-11-26T05:00:00+03:00</t>
+          <t>2026-11-27T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AL208" t="inlineStr">
@@ -44049,7 +44049,7 @@
       </c>
       <c r="AE209" t="inlineStr">
         <is>
-          <t>2026-11-26T06:30:00+03:00</t>
+          <t>2026-11-27T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AF209" t="inlineStr">
@@ -44069,12 +44069,12 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>2026-10-27T09:30:00+03:00</t>
+          <t>2026-10-28T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
         <is>
-          <t>2026-11-26T06:30:00+03:00</t>
+          <t>2026-11-27T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AL209" t="inlineStr">
@@ -44199,7 +44199,7 @@
       </c>
       <c r="AE210" t="inlineStr">
         <is>
-          <t>2026-11-26T08:00:00+03:00</t>
+          <t>2026-11-27T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AF210" t="inlineStr">
@@ -44219,12 +44219,12 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>2026-10-27T11:00:00+03:00</t>
+          <t>2026-10-28T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
         <is>
-          <t>2026-11-26T08:00:00+03:00</t>
+          <t>2026-11-27T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AL210" t="inlineStr">
@@ -44349,7 +44349,7 @@
       </c>
       <c r="AE211" t="inlineStr">
         <is>
-          <t>2026-11-27T03:30:00+03:00</t>
+          <t>2026-11-28T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AF211" t="inlineStr">
@@ -44369,12 +44369,12 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>2026-10-28T06:30:00+03:00</t>
+          <t>2026-10-29T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
         <is>
-          <t>2026-11-27T03:30:00+03:00</t>
+          <t>2026-11-28T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AL211" t="inlineStr">
@@ -44499,7 +44499,7 @@
       </c>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>2026-11-27T05:00:00+03:00</t>
+          <t>2026-11-28T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
@@ -44519,12 +44519,12 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>2026-10-28T08:00:00+03:00</t>
+          <t>2026-10-29T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
         <is>
-          <t>2026-11-27T05:00:00+03:00</t>
+          <t>2026-11-28T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AL212" t="inlineStr">
@@ -44654,7 +44654,7 @@
       </c>
       <c r="AE213" t="inlineStr">
         <is>
-          <t>2026-11-27T08:00:00+03:00</t>
+          <t>2026-11-28T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AF213" t="inlineStr">
@@ -44674,12 +44674,12 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>2026-10-28T11:00:00+03:00</t>
+          <t>2026-10-29T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
         <is>
-          <t>2026-11-27T08:00:00+03:00</t>
+          <t>2026-11-28T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AL213" t="inlineStr">
@@ -44804,7 +44804,7 @@
       </c>
       <c r="AE214" t="inlineStr">
         <is>
-          <t>2026-11-28T02:00:00+03:00</t>
+          <t>2026-11-29T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AF214" t="inlineStr">
@@ -44824,12 +44824,12 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>2026-10-29T05:00:00+03:00</t>
+          <t>2026-10-30T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
         <is>
-          <t>2026-11-28T02:00:00+03:00</t>
+          <t>2026-11-29T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AL214" t="inlineStr">
@@ -44959,7 +44959,7 @@
       </c>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>2026-11-28T05:00:00+03:00</t>
+          <t>2026-11-29T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
@@ -44979,12 +44979,12 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>2026-10-29T08:00:00+03:00</t>
+          <t>2026-10-30T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
         <is>
-          <t>2026-11-28T05:00:00+03:00</t>
+          <t>2026-11-29T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AL215" t="inlineStr">
@@ -45109,7 +45109,7 @@
       </c>
       <c r="AE216" t="inlineStr">
         <is>
-          <t>2026-11-28T06:30:00+03:00</t>
+          <t>2026-11-29T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
@@ -45129,12 +45129,12 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>2026-10-29T09:30:00+03:00</t>
+          <t>2026-10-30T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
         <is>
-          <t>2026-11-28T06:30:00+03:00</t>
+          <t>2026-11-29T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AL216" t="inlineStr">
@@ -45264,7 +45264,7 @@
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>2026-11-29T02:00:00+03:00</t>
+          <t>2026-11-30T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
@@ -45284,12 +45284,12 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>2026-10-30T05:00:00+03:00</t>
+          <t>2026-10-31T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
         <is>
-          <t>2026-11-29T02:00:00+03:00</t>
+          <t>2026-11-30T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AL217" t="inlineStr">
@@ -45414,7 +45414,7 @@
       </c>
       <c r="AE218" t="inlineStr">
         <is>
-          <t>2026-11-29T03:30:00+03:00</t>
+          <t>2026-11-30T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
@@ -45434,12 +45434,12 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>2026-10-30T06:30:00+03:00</t>
+          <t>2026-10-31T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
         <is>
-          <t>2026-11-29T03:30:00+03:00</t>
+          <t>2026-11-30T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AL218" t="inlineStr">
@@ -45569,7 +45569,7 @@
       </c>
       <c r="AE219" t="inlineStr">
         <is>
-          <t>2026-11-29T05:00:00+03:00</t>
+          <t>2026-11-30T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
@@ -45589,12 +45589,12 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>2026-10-30T08:00:00+03:00</t>
+          <t>2026-10-31T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
         <is>
-          <t>2026-11-29T05:00:00+03:00</t>
+          <t>2026-11-30T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AL219" t="inlineStr">
@@ -45724,7 +45724,7 @@
       </c>
       <c r="AE220" t="inlineStr">
         <is>
-          <t>2026-11-29T06:30:00+03:00</t>
+          <t>2026-11-30T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
@@ -45744,12 +45744,12 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>2026-10-30T09:30:00+03:00</t>
+          <t>2026-10-31T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
         <is>
-          <t>2026-11-29T06:30:00+03:00</t>
+          <t>2026-11-30T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AL220" t="inlineStr">
@@ -45874,7 +45874,7 @@
       </c>
       <c r="AE221" t="inlineStr">
         <is>
-          <t>2026-11-29T08:00:00+03:00</t>
+          <t>2026-11-30T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AF221" t="inlineStr">
@@ -45894,12 +45894,12 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>2026-10-30T11:00:00+03:00</t>
+          <t>2026-10-31T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
         <is>
-          <t>2026-11-29T08:00:00+03:00</t>
+          <t>2026-11-30T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AL221" t="inlineStr">
@@ -46029,7 +46029,7 @@
       </c>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>2026-11-30T03:30:00+03:00</t>
+          <t>2026-12-01T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
@@ -46049,12 +46049,12 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>2026-10-31T06:30:00+03:00</t>
+          <t>2026-11-01T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>2026-11-30T03:30:00+03:00</t>
+          <t>2026-12-01T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AL222" t="inlineStr">
@@ -46179,7 +46179,7 @@
       </c>
       <c r="AE223" t="inlineStr">
         <is>
-          <t>2026-11-30T05:00:00+03:00</t>
+          <t>2026-12-01T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AF223" t="inlineStr">
@@ -46199,12 +46199,12 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>2026-10-31T08:00:00+03:00</t>
+          <t>2026-11-01T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
         <is>
-          <t>2026-11-30T05:00:00+03:00</t>
+          <t>2026-12-01T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AL223" t="inlineStr">
@@ -46334,7 +46334,7 @@
       </c>
       <c r="AE224" t="inlineStr">
         <is>
-          <t>2026-11-30T06:30:00+03:00</t>
+          <t>2026-12-01T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
@@ -46354,12 +46354,12 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>2026-10-31T09:30:00+03:00</t>
+          <t>2026-11-01T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
         <is>
-          <t>2026-11-30T06:30:00+03:00</t>
+          <t>2026-12-01T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AL224" t="inlineStr">
@@ -46484,7 +46484,7 @@
       </c>
       <c r="AE225" t="inlineStr">
         <is>
-          <t>2026-11-30T08:00:00+03:00</t>
+          <t>2026-12-01T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
@@ -46504,12 +46504,12 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>2026-10-31T11:00:00+03:00</t>
+          <t>2026-11-01T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
         <is>
-          <t>2026-11-30T08:00:00+03:00</t>
+          <t>2026-12-01T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AL225" t="inlineStr">
@@ -46634,7 +46634,7 @@
       </c>
       <c r="AE226" t="inlineStr">
         <is>
-          <t>2026-12-01T02:00:00+03:00</t>
+          <t>2026-12-02T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AF226" t="inlineStr">
@@ -46654,12 +46654,12 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>2026-11-01T05:00:00+03:00</t>
+          <t>2026-11-02T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>2026-12-01T02:00:00+03:00</t>
+          <t>2026-12-02T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AL226" t="inlineStr">
@@ -46784,7 +46784,7 @@
       </c>
       <c r="AE227" t="inlineStr">
         <is>
-          <t>2026-12-01T05:00:00+03:00</t>
+          <t>2026-12-02T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AF227" t="inlineStr">
@@ -46804,12 +46804,12 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>2026-11-01T08:00:00+03:00</t>
+          <t>2026-11-02T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>2026-12-01T05:00:00+03:00</t>
+          <t>2026-12-02T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AL227" t="inlineStr">
@@ -46934,7 +46934,7 @@
       </c>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>2026-12-01T06:30:00+03:00</t>
+          <t>2026-12-02T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
@@ -46954,12 +46954,12 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>2026-11-01T09:30:00+03:00</t>
+          <t>2026-11-02T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
         <is>
-          <t>2026-12-01T06:30:00+03:00</t>
+          <t>2026-12-02T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AL228" t="inlineStr">
@@ -47089,7 +47089,7 @@
       </c>
       <c r="AE229" t="inlineStr">
         <is>
-          <t>2026-12-02T05:00:00+03:00</t>
+          <t>2026-12-03T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
@@ -47109,12 +47109,12 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>2026-11-02T08:00:00+03:00</t>
+          <t>2026-11-03T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
         <is>
-          <t>2026-12-02T05:00:00+03:00</t>
+          <t>2026-12-03T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AL229" t="inlineStr">
@@ -47239,7 +47239,7 @@
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>2026-12-02T08:00:00+03:00</t>
+          <t>2026-12-03T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
@@ -47259,12 +47259,12 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>2026-11-02T11:00:00+03:00</t>
+          <t>2026-11-03T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
         <is>
-          <t>2026-12-02T08:00:00+03:00</t>
+          <t>2026-12-03T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AL230" t="inlineStr">
@@ -47389,7 +47389,7 @@
       </c>
       <c r="AE231" t="inlineStr">
         <is>
-          <t>2026-12-03T02:00:00+03:00</t>
+          <t>2026-12-04T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AF231" t="inlineStr">
@@ -47409,12 +47409,12 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>2026-11-03T05:00:00+03:00</t>
+          <t>2026-11-04T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>2026-12-03T02:00:00+03:00</t>
+          <t>2026-12-04T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AL231" t="inlineStr">
@@ -47544,7 +47544,7 @@
       </c>
       <c r="AE232" t="inlineStr">
         <is>
-          <t>2026-12-03T03:30:00+03:00</t>
+          <t>2026-12-04T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AF232" t="inlineStr">
@@ -47564,12 +47564,12 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>2026-11-03T06:30:00+03:00</t>
+          <t>2026-11-04T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
         <is>
-          <t>2026-12-03T03:30:00+03:00</t>
+          <t>2026-12-04T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AL232" t="inlineStr">
@@ -47699,7 +47699,7 @@
       </c>
       <c r="AE233" t="inlineStr">
         <is>
-          <t>2026-12-03T05:00:00+03:00</t>
+          <t>2026-12-04T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
@@ -47719,12 +47719,12 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>2026-11-03T08:00:00+03:00</t>
+          <t>2026-11-04T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
         <is>
-          <t>2026-12-03T05:00:00+03:00</t>
+          <t>2026-12-04T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AL233" t="inlineStr">
@@ -47849,7 +47849,7 @@
       </c>
       <c r="AE234" t="inlineStr">
         <is>
-          <t>2026-12-03T08:00:00+03:00</t>
+          <t>2026-12-04T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
@@ -47869,12 +47869,12 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>2026-11-03T11:00:00+03:00</t>
+          <t>2026-11-04T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
         <is>
-          <t>2026-12-03T08:00:00+03:00</t>
+          <t>2026-12-04T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AL234" t="inlineStr">
@@ -48004,7 +48004,7 @@
       </c>
       <c r="AE235" t="inlineStr">
         <is>
-          <t>2026-12-04T02:00:00+03:00</t>
+          <t>2026-12-05T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AF235" t="inlineStr">
@@ -48024,12 +48024,12 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>2026-11-04T05:00:00+03:00</t>
+          <t>2026-11-05T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
         <is>
-          <t>2026-12-04T02:00:00+03:00</t>
+          <t>2026-12-05T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AL235" t="inlineStr">
@@ -48154,7 +48154,7 @@
       </c>
       <c r="AE236" t="inlineStr">
         <is>
-          <t>2026-12-04T03:30:00+03:00</t>
+          <t>2026-12-05T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AF236" t="inlineStr">
@@ -48174,12 +48174,12 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>2026-11-04T06:30:00+03:00</t>
+          <t>2026-11-05T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
         <is>
-          <t>2026-12-04T03:30:00+03:00</t>
+          <t>2026-12-05T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AL236" t="inlineStr">
@@ -48277,7 +48277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:AD45"/>
+  <dimension ref="A1:AD45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53591,7 +53591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:X34"/>
+  <dimension ref="A1:X34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -12326,17 +12326,17 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>2026-11-29T08:00:00+03:00</t>
+          <t>2026-11-30T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>2026-10-30T11:00:00+03:00</t>
+          <t>2026-10-31T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>2026-11-29T08:00:00+03:00</t>
+          <t>2026-11-30T08:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -12456,17 +12456,17 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>2026-12-01T02:00:00+03:00</t>
+          <t>2026-12-02T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>2026-11-01T05:00:00+03:00</t>
+          <t>2026-11-02T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>2026-12-01T02:00:00+03:00</t>
+          <t>2026-12-02T02:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -12586,17 +12586,17 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>2026-12-02T03:30:00+03:00</t>
+          <t>2026-12-03T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>2026-11-02T06:30:00+03:00</t>
+          <t>2026-11-03T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>2026-12-02T03:30:00+03:00</t>
+          <t>2026-12-03T03:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -12716,17 +12716,17 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>2026-12-02T08:00:00+03:00</t>
+          <t>2026-12-03T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>2026-11-02T11:00:00+03:00</t>
+          <t>2026-11-03T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>2026-12-02T08:00:00+03:00</t>
+          <t>2026-12-03T08:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -12846,17 +12846,17 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>2026-12-03T02:00:00+03:00</t>
+          <t>2026-12-04T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>2026-11-03T05:00:00+03:00</t>
+          <t>2026-11-04T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>2026-12-03T02:00:00+03:00</t>
+          <t>2026-12-04T02:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -12976,17 +12976,17 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>2026-12-03T03:30:00+03:00</t>
+          <t>2026-12-04T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>2026-11-03T06:30:00+03:00</t>
+          <t>2026-11-04T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>2026-12-03T03:30:00+03:00</t>
+          <t>2026-12-04T03:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -13106,17 +13106,17 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>2026-12-03T06:30:00+03:00</t>
+          <t>2026-12-04T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>2026-11-03T09:30:00+03:00</t>
+          <t>2026-11-04T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>2026-12-03T06:30:00+03:00</t>
+          <t>2026-12-04T06:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -13236,17 +13236,17 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>2026-12-04T06:30:00+03:00</t>
+          <t>2026-12-05T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>2026-11-04T09:30:00+03:00</t>
+          <t>2026-11-05T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>2026-12-04T06:30:00+03:00</t>
+          <t>2026-12-05T06:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -13366,17 +13366,17 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>2026-12-05T05:00:00+03:00</t>
+          <t>2026-12-06T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>2026-11-05T08:00:00+03:00</t>
+          <t>2026-11-06T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>2026-12-05T05:00:00+03:00</t>
+          <t>2026-12-06T05:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -13496,17 +13496,17 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>2026-12-05T06:30:00+03:00</t>
+          <t>2026-12-06T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>2026-11-05T09:30:00+03:00</t>
+          <t>2026-11-06T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>2026-12-05T06:30:00+03:00</t>
+          <t>2026-12-06T06:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -44959,7 +44959,7 @@
       </c>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>2026-11-29T05:00:00+03:00</t>
+          <t>2026-11-30T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
@@ -44979,12 +44979,12 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>2026-10-30T08:00:00+03:00</t>
+          <t>2026-10-31T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
         <is>
-          <t>2026-11-29T05:00:00+03:00</t>
+          <t>2026-11-30T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AL215" t="inlineStr">
@@ -45109,7 +45109,7 @@
       </c>
       <c r="AE216" t="inlineStr">
         <is>
-          <t>2026-11-29T06:30:00+03:00</t>
+          <t>2026-11-30T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
@@ -45129,12 +45129,12 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>2026-10-30T09:30:00+03:00</t>
+          <t>2026-10-31T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
         <is>
-          <t>2026-11-29T06:30:00+03:00</t>
+          <t>2026-11-30T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AL216" t="inlineStr">
@@ -45264,7 +45264,7 @@
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>2026-11-30T02:00:00+03:00</t>
+          <t>2026-12-01T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
@@ -45284,12 +45284,12 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>2026-10-31T05:00:00+03:00</t>
+          <t>2026-11-01T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
         <is>
-          <t>2026-11-30T02:00:00+03:00</t>
+          <t>2026-12-01T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AL217" t="inlineStr">
@@ -45414,7 +45414,7 @@
       </c>
       <c r="AE218" t="inlineStr">
         <is>
-          <t>2026-11-30T03:30:00+03:00</t>
+          <t>2026-12-01T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
@@ -45434,12 +45434,12 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>2026-10-31T06:30:00+03:00</t>
+          <t>2026-11-01T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
         <is>
-          <t>2026-11-30T03:30:00+03:00</t>
+          <t>2026-12-01T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AL218" t="inlineStr">
@@ -45569,7 +45569,7 @@
       </c>
       <c r="AE219" t="inlineStr">
         <is>
-          <t>2026-11-30T05:00:00+03:00</t>
+          <t>2026-12-01T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
@@ -45589,12 +45589,12 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>2026-10-31T08:00:00+03:00</t>
+          <t>2026-11-01T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
         <is>
-          <t>2026-11-30T05:00:00+03:00</t>
+          <t>2026-12-01T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AL219" t="inlineStr">
@@ -45724,7 +45724,7 @@
       </c>
       <c r="AE220" t="inlineStr">
         <is>
-          <t>2026-11-30T06:30:00+03:00</t>
+          <t>2026-12-01T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
@@ -45744,12 +45744,12 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>2026-10-31T09:30:00+03:00</t>
+          <t>2026-11-01T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
         <is>
-          <t>2026-11-30T06:30:00+03:00</t>
+          <t>2026-12-01T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AL220" t="inlineStr">
@@ -45874,7 +45874,7 @@
       </c>
       <c r="AE221" t="inlineStr">
         <is>
-          <t>2026-11-30T08:00:00+03:00</t>
+          <t>2026-12-01T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AF221" t="inlineStr">
@@ -45894,12 +45894,12 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>2026-10-31T11:00:00+03:00</t>
+          <t>2026-11-01T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
         <is>
-          <t>2026-11-30T08:00:00+03:00</t>
+          <t>2026-12-01T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AL221" t="inlineStr">
@@ -46029,7 +46029,7 @@
       </c>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>2026-12-01T03:30:00+03:00</t>
+          <t>2026-12-02T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
@@ -46049,12 +46049,12 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>2026-11-01T06:30:00+03:00</t>
+          <t>2026-11-02T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>2026-12-01T03:30:00+03:00</t>
+          <t>2026-12-02T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AL222" t="inlineStr">
@@ -46179,7 +46179,7 @@
       </c>
       <c r="AE223" t="inlineStr">
         <is>
-          <t>2026-12-01T05:00:00+03:00</t>
+          <t>2026-12-02T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AF223" t="inlineStr">
@@ -46199,12 +46199,12 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>2026-11-01T08:00:00+03:00</t>
+          <t>2026-11-02T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
         <is>
-          <t>2026-12-01T05:00:00+03:00</t>
+          <t>2026-12-02T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AL223" t="inlineStr">
@@ -46334,7 +46334,7 @@
       </c>
       <c r="AE224" t="inlineStr">
         <is>
-          <t>2026-12-01T06:30:00+03:00</t>
+          <t>2026-12-02T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
@@ -46354,12 +46354,12 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>2026-11-01T09:30:00+03:00</t>
+          <t>2026-11-02T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
         <is>
-          <t>2026-12-01T06:30:00+03:00</t>
+          <t>2026-12-02T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AL224" t="inlineStr">
@@ -46484,7 +46484,7 @@
       </c>
       <c r="AE225" t="inlineStr">
         <is>
-          <t>2026-12-01T08:00:00+03:00</t>
+          <t>2026-12-02T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
@@ -46504,12 +46504,12 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>2026-11-01T11:00:00+03:00</t>
+          <t>2026-11-02T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
         <is>
-          <t>2026-12-01T08:00:00+03:00</t>
+          <t>2026-12-02T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AL225" t="inlineStr">
@@ -46634,7 +46634,7 @@
       </c>
       <c r="AE226" t="inlineStr">
         <is>
-          <t>2026-12-02T02:00:00+03:00</t>
+          <t>2026-12-03T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AF226" t="inlineStr">
@@ -46654,12 +46654,12 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>2026-11-02T05:00:00+03:00</t>
+          <t>2026-11-03T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>2026-12-02T02:00:00+03:00</t>
+          <t>2026-12-03T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AL226" t="inlineStr">
@@ -46784,7 +46784,7 @@
       </c>
       <c r="AE227" t="inlineStr">
         <is>
-          <t>2026-12-02T05:00:00+03:00</t>
+          <t>2026-12-03T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AF227" t="inlineStr">
@@ -46804,12 +46804,12 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>2026-11-02T08:00:00+03:00</t>
+          <t>2026-11-03T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>2026-12-02T05:00:00+03:00</t>
+          <t>2026-12-03T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AL227" t="inlineStr">
@@ -46934,7 +46934,7 @@
       </c>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>2026-12-02T06:30:00+03:00</t>
+          <t>2026-12-03T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
@@ -46954,12 +46954,12 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>2026-11-02T09:30:00+03:00</t>
+          <t>2026-11-03T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
         <is>
-          <t>2026-12-02T06:30:00+03:00</t>
+          <t>2026-12-03T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AL228" t="inlineStr">
@@ -47089,7 +47089,7 @@
       </c>
       <c r="AE229" t="inlineStr">
         <is>
-          <t>2026-12-03T05:00:00+03:00</t>
+          <t>2026-12-04T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
@@ -47109,12 +47109,12 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>2026-11-03T08:00:00+03:00</t>
+          <t>2026-11-04T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
         <is>
-          <t>2026-12-03T05:00:00+03:00</t>
+          <t>2026-12-04T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AL229" t="inlineStr">
@@ -47239,7 +47239,7 @@
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>2026-12-03T08:00:00+03:00</t>
+          <t>2026-12-04T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
@@ -47259,12 +47259,12 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>2026-11-03T11:00:00+03:00</t>
+          <t>2026-11-04T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
         <is>
-          <t>2026-12-03T08:00:00+03:00</t>
+          <t>2026-12-04T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AL230" t="inlineStr">
@@ -47389,7 +47389,7 @@
       </c>
       <c r="AE231" t="inlineStr">
         <is>
-          <t>2026-12-04T02:00:00+03:00</t>
+          <t>2026-12-05T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AF231" t="inlineStr">
@@ -47409,12 +47409,12 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>2026-11-04T05:00:00+03:00</t>
+          <t>2026-11-05T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>2026-12-04T02:00:00+03:00</t>
+          <t>2026-12-05T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AL231" t="inlineStr">
@@ -47544,7 +47544,7 @@
       </c>
       <c r="AE232" t="inlineStr">
         <is>
-          <t>2026-12-04T03:30:00+03:00</t>
+          <t>2026-12-05T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AF232" t="inlineStr">
@@ -47564,12 +47564,12 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>2026-11-04T06:30:00+03:00</t>
+          <t>2026-11-05T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
         <is>
-          <t>2026-12-04T03:30:00+03:00</t>
+          <t>2026-12-05T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AL232" t="inlineStr">
@@ -47699,7 +47699,7 @@
       </c>
       <c r="AE233" t="inlineStr">
         <is>
-          <t>2026-12-04T05:00:00+03:00</t>
+          <t>2026-12-05T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
@@ -47719,12 +47719,12 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>2026-11-04T08:00:00+03:00</t>
+          <t>2026-11-05T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
         <is>
-          <t>2026-12-04T05:00:00+03:00</t>
+          <t>2026-12-05T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AL233" t="inlineStr">
@@ -47849,7 +47849,7 @@
       </c>
       <c r="AE234" t="inlineStr">
         <is>
-          <t>2026-12-04T08:00:00+03:00</t>
+          <t>2026-12-05T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
@@ -47869,12 +47869,12 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>2026-11-04T11:00:00+03:00</t>
+          <t>2026-11-05T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
         <is>
-          <t>2026-12-04T08:00:00+03:00</t>
+          <t>2026-12-05T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AL234" t="inlineStr">
@@ -48004,7 +48004,7 @@
       </c>
       <c r="AE235" t="inlineStr">
         <is>
-          <t>2026-12-05T02:00:00+03:00</t>
+          <t>2026-12-06T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AF235" t="inlineStr">
@@ -48024,12 +48024,12 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>2026-11-05T05:00:00+03:00</t>
+          <t>2026-11-06T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
         <is>
-          <t>2026-12-05T02:00:00+03:00</t>
+          <t>2026-12-06T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AL235" t="inlineStr">
@@ -48154,7 +48154,7 @@
       </c>
       <c r="AE236" t="inlineStr">
         <is>
-          <t>2026-12-05T03:30:00+03:00</t>
+          <t>2026-12-06T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AF236" t="inlineStr">
@@ -48174,12 +48174,12 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>2026-11-05T06:30:00+03:00</t>
+          <t>2026-11-06T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
         <is>
-          <t>2026-12-05T03:30:00+03:00</t>
+          <t>2026-12-06T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AL236" t="inlineStr">

--- a/fgislk.xlsx
+++ b/fgislk.xlsx
@@ -12326,17 +12326,17 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>2026-11-30T08:00:00+03:00</t>
+          <t>2026-11-30T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>2026-10-31T11:00:00+03:00</t>
+          <t>2026-10-31T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>2026-11-30T08:00:00+03:00</t>
+          <t>2026-11-30T05:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -12456,17 +12456,17 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>2026-12-02T02:00:00+03:00</t>
+          <t>2026-12-01T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>2026-11-02T05:00:00+03:00</t>
+          <t>2026-11-01T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>2026-12-02T02:00:00+03:00</t>
+          <t>2026-12-01T06:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -12586,17 +12586,17 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>2026-12-03T03:30:00+03:00</t>
+          <t>2026-12-02T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>2026-11-03T06:30:00+03:00</t>
+          <t>2026-11-02T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>2026-12-03T03:30:00+03:00</t>
+          <t>2026-12-02T08:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -12716,17 +12716,17 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>2026-12-03T08:00:00+03:00</t>
+          <t>2026-12-03T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>2026-11-03T11:00:00+03:00</t>
+          <t>2026-11-03T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>2026-12-03T08:00:00+03:00</t>
+          <t>2026-12-03T05:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -12846,17 +12846,17 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>2026-12-04T02:00:00+03:00</t>
+          <t>2026-12-03T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>2026-11-04T05:00:00+03:00</t>
+          <t>2026-11-03T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>2026-12-04T02:00:00+03:00</t>
+          <t>2026-12-03T06:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -12976,17 +12976,17 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>2026-12-04T03:30:00+03:00</t>
+          <t>2026-12-03T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>2026-11-04T06:30:00+03:00</t>
+          <t>2026-11-03T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>2026-12-04T03:30:00+03:00</t>
+          <t>2026-12-03T08:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -13106,17 +13106,17 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>2026-12-04T06:30:00+03:00</t>
+          <t>2026-12-04T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>2026-11-04T09:30:00+03:00</t>
+          <t>2026-11-04T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>2026-12-04T06:30:00+03:00</t>
+          <t>2026-12-04T03:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -13236,17 +13236,17 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>2026-12-05T06:30:00+03:00</t>
+          <t>2026-12-05T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>2026-11-05T09:30:00+03:00</t>
+          <t>2026-11-05T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>2026-12-05T06:30:00+03:00</t>
+          <t>2026-12-05T03:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -13366,17 +13366,17 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>2026-12-06T05:00:00+03:00</t>
+          <t>2026-12-06T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>2026-11-06T08:00:00+03:00</t>
+          <t>2026-11-06T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>2026-12-06T05:00:00+03:00</t>
+          <t>2026-12-06T02:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -13496,17 +13496,17 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>2026-12-06T06:30:00+03:00</t>
+          <t>2026-12-06T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>2026-11-06T09:30:00+03:00</t>
+          <t>2026-11-06T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>2026-12-06T06:30:00+03:00</t>
+          <t>2026-12-06T03:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -44959,7 +44959,7 @@
       </c>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>2026-11-30T05:00:00+03:00</t>
+          <t>2026-11-30T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
@@ -44979,12 +44979,12 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>2026-10-31T08:00:00+03:00</t>
+          <t>2026-10-31T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
         <is>
-          <t>2026-11-30T05:00:00+03:00</t>
+          <t>2026-11-30T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AL215" t="inlineStr">
@@ -45109,7 +45109,7 @@
       </c>
       <c r="AE216" t="inlineStr">
         <is>
-          <t>2026-11-30T06:30:00+03:00</t>
+          <t>2026-11-30T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
@@ -45129,12 +45129,12 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>2026-10-31T09:30:00+03:00</t>
+          <t>2026-10-31T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
         <is>
-          <t>2026-11-30T06:30:00+03:00</t>
+          <t>2026-11-30T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AL216" t="inlineStr">
@@ -45264,7 +45264,7 @@
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>2026-12-01T02:00:00+03:00</t>
+          <t>2026-11-30T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
@@ -45284,12 +45284,12 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>2026-11-01T05:00:00+03:00</t>
+          <t>2026-10-31T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
         <is>
-          <t>2026-12-01T02:00:00+03:00</t>
+          <t>2026-11-30T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AL217" t="inlineStr">
@@ -45414,7 +45414,7 @@
       </c>
       <c r="AE218" t="inlineStr">
         <is>
-          <t>2026-12-01T03:30:00+03:00</t>
+          <t>2026-11-30T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
@@ -45434,12 +45434,12 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>2026-11-01T06:30:00+03:00</t>
+          <t>2026-10-31T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
         <is>
-          <t>2026-12-01T03:30:00+03:00</t>
+          <t>2026-11-30T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AL218" t="inlineStr">
@@ -45569,7 +45569,7 @@
       </c>
       <c r="AE219" t="inlineStr">
         <is>
-          <t>2026-12-01T05:00:00+03:00</t>
+          <t>2026-12-01T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
@@ -45589,12 +45589,12 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>2026-11-01T08:00:00+03:00</t>
+          <t>2026-11-01T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
         <is>
-          <t>2026-12-01T05:00:00+03:00</t>
+          <t>2026-12-01T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AL219" t="inlineStr">
@@ -45724,7 +45724,7 @@
       </c>
       <c r="AE220" t="inlineStr">
         <is>
-          <t>2026-12-01T06:30:00+03:00</t>
+          <t>2026-12-01T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
@@ -45744,12 +45744,12 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>2026-11-01T09:30:00+03:00</t>
+          <t>2026-11-01T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
         <is>
-          <t>2026-12-01T06:30:00+03:00</t>
+          <t>2026-12-01T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AL220" t="inlineStr">
@@ -45874,7 +45874,7 @@
       </c>
       <c r="AE221" t="inlineStr">
         <is>
-          <t>2026-12-01T08:00:00+03:00</t>
+          <t>2026-12-01T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AF221" t="inlineStr">
@@ -45894,12 +45894,12 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>2026-11-01T11:00:00+03:00</t>
+          <t>2026-11-01T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
         <is>
-          <t>2026-12-01T08:00:00+03:00</t>
+          <t>2026-12-01T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AL221" t="inlineStr">
@@ -46029,7 +46029,7 @@
       </c>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>2026-12-02T03:30:00+03:00</t>
+          <t>2026-12-01T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
@@ -46049,12 +46049,12 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>2026-11-02T06:30:00+03:00</t>
+          <t>2026-11-01T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>2026-12-02T03:30:00+03:00</t>
+          <t>2026-12-01T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AL222" t="inlineStr">
@@ -46179,7 +46179,7 @@
       </c>
       <c r="AE223" t="inlineStr">
         <is>
-          <t>2026-12-02T05:00:00+03:00</t>
+          <t>2026-12-02T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AF223" t="inlineStr">
@@ -46199,12 +46199,12 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>2026-11-02T08:00:00+03:00</t>
+          <t>2026-11-02T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
         <is>
-          <t>2026-12-02T05:00:00+03:00</t>
+          <t>2026-12-02T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AL223" t="inlineStr">
@@ -46334,7 +46334,7 @@
       </c>
       <c r="AE224" t="inlineStr">
         <is>
-          <t>2026-12-02T06:30:00+03:00</t>
+          <t>2026-12-02T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
@@ -46354,12 +46354,12 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>2026-11-02T09:30:00+03:00</t>
+          <t>2026-11-02T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
         <is>
-          <t>2026-12-02T06:30:00+03:00</t>
+          <t>2026-12-02T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AL224" t="inlineStr">
@@ -46484,7 +46484,7 @@
       </c>
       <c r="AE225" t="inlineStr">
         <is>
-          <t>2026-12-02T08:00:00+03:00</t>
+          <t>2026-12-02T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
@@ -46504,12 +46504,12 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>2026-11-02T11:00:00+03:00</t>
+          <t>2026-11-02T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
         <is>
-          <t>2026-12-02T08:00:00+03:00</t>
+          <t>2026-12-02T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AL225" t="inlineStr">
@@ -46634,7 +46634,7 @@
       </c>
       <c r="AE226" t="inlineStr">
         <is>
-          <t>2026-12-03T02:00:00+03:00</t>
+          <t>2026-12-02T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AF226" t="inlineStr">
@@ -46654,12 +46654,12 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>2026-11-03T05:00:00+03:00</t>
+          <t>2026-11-02T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>2026-12-03T02:00:00+03:00</t>
+          <t>2026-12-02T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AL226" t="inlineStr">
@@ -46784,7 +46784,7 @@
       </c>
       <c r="AE227" t="inlineStr">
         <is>
-          <t>2026-12-03T05:00:00+03:00</t>
+          <t>2026-12-03T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AF227" t="inlineStr">
@@ -46804,12 +46804,12 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>2026-11-03T08:00:00+03:00</t>
+          <t>2026-11-03T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>2026-12-03T05:00:00+03:00</t>
+          <t>2026-12-03T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AL227" t="inlineStr">
@@ -46934,7 +46934,7 @@
       </c>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>2026-12-03T06:30:00+03:00</t>
+          <t>2026-12-03T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
@@ -46954,12 +46954,12 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>2026-11-03T09:30:00+03:00</t>
+          <t>2026-11-03T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
         <is>
-          <t>2026-12-03T06:30:00+03:00</t>
+          <t>2026-12-03T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AL228" t="inlineStr">
@@ -47089,7 +47089,7 @@
       </c>
       <c r="AE229" t="inlineStr">
         <is>
-          <t>2026-12-04T05:00:00+03:00</t>
+          <t>2026-12-04T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
@@ -47109,12 +47109,12 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>2026-11-04T08:00:00+03:00</t>
+          <t>2026-11-04T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
         <is>
-          <t>2026-12-04T05:00:00+03:00</t>
+          <t>2026-12-04T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AL229" t="inlineStr">
@@ -47239,7 +47239,7 @@
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>2026-12-04T08:00:00+03:00</t>
+          <t>2026-12-04T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
@@ -47259,12 +47259,12 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>2026-11-04T11:00:00+03:00</t>
+          <t>2026-11-04T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
         <is>
-          <t>2026-12-04T08:00:00+03:00</t>
+          <t>2026-12-04T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AL230" t="inlineStr">
@@ -47389,7 +47389,7 @@
       </c>
       <c r="AE231" t="inlineStr">
         <is>
-          <t>2026-12-05T02:00:00+03:00</t>
+          <t>2026-12-04T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AF231" t="inlineStr">
@@ -47409,12 +47409,12 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>2026-11-05T05:00:00+03:00</t>
+          <t>2026-11-04T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>2026-12-05T02:00:00+03:00</t>
+          <t>2026-12-04T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AL231" t="inlineStr">
@@ -47544,7 +47544,7 @@
       </c>
       <c r="AE232" t="inlineStr">
         <is>
-          <t>2026-12-05T03:30:00+03:00</t>
+          <t>2026-12-04T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AF232" t="inlineStr">
@@ -47564,12 +47564,12 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>2026-11-05T06:30:00+03:00</t>
+          <t>2026-11-04T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
         <is>
-          <t>2026-12-05T03:30:00+03:00</t>
+          <t>2026-12-04T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AL232" t="inlineStr">
@@ -47699,7 +47699,7 @@
       </c>
       <c r="AE233" t="inlineStr">
         <is>
-          <t>2026-12-05T05:00:00+03:00</t>
+          <t>2026-12-05T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
@@ -47719,12 +47719,12 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>2026-11-05T08:00:00+03:00</t>
+          <t>2026-11-05T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
         <is>
-          <t>2026-12-05T05:00:00+03:00</t>
+          <t>2026-12-05T02:00:00+03:00</t>
         </is>
       </c>
       <c r="AL233" t="inlineStr">
@@ -47849,7 +47849,7 @@
       </c>
       <c r="AE234" t="inlineStr">
         <is>
-          <t>2026-12-05T08:00:00+03:00</t>
+          <t>2026-12-05T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
@@ -47869,12 +47869,12 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>2026-11-05T11:00:00+03:00</t>
+          <t>2026-11-05T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
         <is>
-          <t>2026-12-05T08:00:00+03:00</t>
+          <t>2026-12-05T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AL234" t="inlineStr">
@@ -48004,7 +48004,7 @@
       </c>
       <c r="AE235" t="inlineStr">
         <is>
-          <t>2026-12-06T02:00:00+03:00</t>
+          <t>2026-12-05T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AF235" t="inlineStr">
@@ -48024,12 +48024,12 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>2026-11-06T05:00:00+03:00</t>
+          <t>2026-11-05T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
         <is>
-          <t>2026-12-06T02:00:00+03:00</t>
+          <t>2026-12-05T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AL235" t="inlineStr">
@@ -48154,7 +48154,7 @@
       </c>
       <c r="AE236" t="inlineStr">
         <is>
-          <t>2026-12-06T03:30:00+03:00</t>
+          <t>2026-12-05T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AF236" t="inlineStr">
@@ -48174,12 +48174,12 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>2026-11-06T06:30:00+03:00</t>
+          <t>2026-11-05T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
         <is>
-          <t>2026-12-06T03:30:00+03:00</t>
+          <t>2026-12-05T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AL236" t="inlineStr">
